--- a/Översikt EMMABODA.xlsx
+++ b/Översikt EMMABODA.xlsx
@@ -601,7 +601,7 @@
         <v>45534</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>45440</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -830,7 +830,7 @@
         <v>45387</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>45202</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
         <v>45030</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>44480</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1276,7 +1276,7 @@
         <v>45616</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>44706</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>44811</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>45330</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1713,7 +1713,7 @@
         <v>45359</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         <v>46136</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1931,7 +1931,7 @@
         <v>45369</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
         <v>45086</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>44937</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2257,7 +2257,7 @@
         <v>44462</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2367,7 +2367,7 @@
         <v>46062</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2477,7 +2477,7 @@
         <v>46069</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2583,7 +2583,7 @@
         <v>46214</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2689,7 +2689,7 @@
         <v>44762</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2794,7 +2794,7 @@
         <v>45166</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2899,7 +2899,7 @@
         <v>44966</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3004,7 +3004,7 @@
         <v>44570</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3109,7 +3109,7 @@
         <v>44984</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3214,7 +3214,7 @@
         <v>45196</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3319,7 +3319,7 @@
         <v>45763</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3428,7 +3428,7 @@
         <v>45104</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3533,7 +3533,7 @@
         <v>45335</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
         <v>45797</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3747,7 +3747,7 @@
         <v>45953</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3856,7 +3856,7 @@
         <v>45161</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3966,7 +3966,7 @@
         <v>45068</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4076,7 +4076,7 @@
         <v>44771</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4185,7 +4185,7 @@
         <v>46055</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4290,7 +4290,7 @@
         <v>45229</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4399,7 +4399,7 @@
         <v>45107</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4508,7 +4508,7 @@
         <v>46135</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4618,7 +4618,7 @@
         <v>45967</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4723,7 +4723,7 @@
         <v>44495</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4832,7 +4832,7 @@
         <v>46253</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4937,7 +4937,7 @@
         <v>45092</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
         <v>46213</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5147,7 +5147,7 @@
         <v>46213</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5252,7 +5252,7 @@
         <v>46218</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5357,7 +5357,7 @@
         <v>44488</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5467,7 +5467,7 @@
         <v>44895</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5572,7 +5572,7 @@
         <v>46282</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5677,7 +5677,7 @@
         <v>45509</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5782,7 +5782,7 @@
         <v>45387</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5891,7 +5891,7 @@
         <v>44588</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5996,7 +5996,7 @@
         <v>45611</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6105,7 +6105,7 @@
         <v>45330</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6214,7 +6214,7 @@
         <v>44852</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6323,7 +6323,7 @@
         <v>45442</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6428,7 +6428,7 @@
         <v>45153</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6533,7 +6533,7 @@
         <v>45386</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6638,7 +6638,7 @@
         <v>45685</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6747,7 +6747,7 @@
         <v>45813</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6856,7 +6856,7 @@
         <v>44459</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6929,7 +6929,7 @@
         <v>44530</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7002,7 +7002,7 @@
         <v>44496</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7075,7 +7075,7 @@
         <v>44764</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7148,7 +7148,7 @@
         <v>44496</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7221,7 +7221,7 @@
         <v>44530</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7294,7 +7294,7 @@
         <v>44488</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7367,7 +7367,7 @@
         <v>44529</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7440,7 +7440,7 @@
         <v>44490</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7513,7 +7513,7 @@
         <v>44601</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7586,7 +7586,7 @@
         <v>44600</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7659,7 +7659,7 @@
         <v>44507</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7732,7 +7732,7 @@
         <v>44507</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7805,7 +7805,7 @@
         <v>44507</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7878,7 +7878,7 @@
         <v>44728</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7951,7 +7951,7 @@
         <v>44599</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8024,7 +8024,7 @@
         <v>44691</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8097,7 +8097,7 @@
         <v>44628</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8170,7 +8170,7 @@
         <v>44504</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8243,7 +8243,7 @@
         <v>44515</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8316,7 +8316,7 @@
         <v>44851</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8389,7 +8389,7 @@
         <v>44860</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8462,7 +8462,7 @@
         <v>44648</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8535,7 +8535,7 @@
         <v>44462</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8608,7 +8608,7 @@
         <v>44523</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8681,7 +8681,7 @@
         <v>44628</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8754,7 +8754,7 @@
         <v>44788</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8827,7 +8827,7 @@
         <v>44627</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8900,7 +8900,7 @@
         <v>44462</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8973,7 +8973,7 @@
         <v>44498</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9046,7 +9046,7 @@
         <v>44768</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9119,7 +9119,7 @@
         <v>44851</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9192,7 +9192,7 @@
         <v>44529</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9265,7 +9265,7 @@
         <v>44813</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9338,7 +9338,7 @@
         <v>44809</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9411,7 +9411,7 @@
         <v>44771</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9484,7 +9484,7 @@
         <v>44587</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9557,7 +9557,7 @@
         <v>44496</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9630,7 +9630,7 @@
         <v>44466</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9703,7 +9703,7 @@
         <v>44507</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9776,7 +9776,7 @@
         <v>44487</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9854,7 +9854,7 @@
         <v>44507</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9927,7 +9927,7 @@
         <v>44628</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10000,7 +10000,7 @@
         <v>44652</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10073,7 +10073,7 @@
         <v>44600</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10146,7 +10146,7 @@
         <v>44501</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10219,7 +10219,7 @@
         <v>44600</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10292,7 +10292,7 @@
         <v>44852</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10365,7 +10365,7 @@
         <v>44839</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10438,7 +10438,7 @@
         <v>44615</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10516,7 +10516,7 @@
         <v>44622</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10589,7 +10589,7 @@
         <v>44524</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10662,7 +10662,7 @@
         <v>44712</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10735,7 +10735,7 @@
         <v>44743</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10808,7 +10808,7 @@
         <v>44532</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10886,7 +10886,7 @@
         <v>44722</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10959,7 +10959,7 @@
         <v>44470</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11032,7 +11032,7 @@
         <v>44593</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11105,7 +11105,7 @@
         <v>44652</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11178,7 +11178,7 @@
         <v>44699</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11251,7 +11251,7 @@
         <v>44820</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11329,7 +11329,7 @@
         <v>44847</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11402,7 +11402,7 @@
         <v>44743</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11475,7 +11475,7 @@
         <v>44488</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11553,7 +11553,7 @@
         <v>44589</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11626,7 +11626,7 @@
         <v>44551</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11704,7 +11704,7 @@
         <v>44600</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11777,7 +11777,7 @@
         <v>44725</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11850,7 +11850,7 @@
         <v>44600</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11923,7 +11923,7 @@
         <v>44655</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11996,7 +11996,7 @@
         <v>44530</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12069,7 +12069,7 @@
         <v>44980</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12142,7 +12142,7 @@
         <v>44788</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12215,7 +12215,7 @@
         <v>45397</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12288,7 +12288,7 @@
         <v>44953</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12361,7 +12361,7 @@
         <v>44487</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12434,7 +12434,7 @@
         <v>45590</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12507,7 +12507,7 @@
         <v>45089</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12580,7 +12580,7 @@
         <v>45251</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12653,7 +12653,7 @@
         <v>45040</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12726,7 +12726,7 @@
         <v>45411</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12799,7 +12799,7 @@
         <v>45099</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12872,7 +12872,7 @@
         <v>45191</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12945,7 +12945,7 @@
         <v>45126</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13018,7 +13018,7 @@
         <v>45606</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13091,7 +13091,7 @@
         <v>45022</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13164,7 +13164,7 @@
         <v>45022</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13237,7 +13237,7 @@
         <v>45392</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13310,7 +13310,7 @@
         <v>45187</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13383,7 +13383,7 @@
         <v>44652</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13456,7 +13456,7 @@
         <v>45637</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13529,7 +13529,7 @@
         <v>45237</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13602,7 +13602,7 @@
         <v>45159</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13675,7 +13675,7 @@
         <v>45219</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13748,7 +13748,7 @@
         <v>45049</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13821,7 +13821,7 @@
         <v>45445</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13894,7 +13894,7 @@
         <v>45230</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13967,7 +13967,7 @@
         <v>44572</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14040,7 +14040,7 @@
         <v>45392</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14113,7 +14113,7 @@
         <v>44690</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14186,7 +14186,7 @@
         <v>45079</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14259,7 +14259,7 @@
         <v>45019</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14332,7 +14332,7 @@
         <v>45211</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14405,7 +14405,7 @@
         <v>44519</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14478,7 +14478,7 @@
         <v>44973</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14556,7 +14556,7 @@
         <v>45474</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14629,7 +14629,7 @@
         <v>45341</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14702,7 +14702,7 @@
         <v>45559</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14775,7 +14775,7 @@
         <v>45309</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14848,7 +14848,7 @@
         <v>44683</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14921,7 +14921,7 @@
         <v>45211</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14994,7 +14994,7 @@
         <v>45211</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15067,7 +15067,7 @@
         <v>45665</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15140,7 +15140,7 @@
         <v>45148</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15213,7 +15213,7 @@
         <v>44978</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15286,7 +15286,7 @@
         <v>44978</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15359,7 +15359,7 @@
         <v>45164</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15432,7 +15432,7 @@
         <v>45475</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15505,7 +15505,7 @@
         <v>45166</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15578,7 +15578,7 @@
         <v>44739</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15651,7 +15651,7 @@
         <v>45394</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15724,7 +15724,7 @@
         <v>45606</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15797,7 +15797,7 @@
         <v>44896</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15870,7 +15870,7 @@
         <v>45355</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15943,7 +15943,7 @@
         <v>44949</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16016,7 +16016,7 @@
         <v>45188</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16094,7 +16094,7 @@
         <v>45422</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16167,7 +16167,7 @@
         <v>44834</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16240,7 +16240,7 @@
         <v>44791</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16313,7 +16313,7 @@
         <v>45369</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16386,7 +16386,7 @@
         <v>44982</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16459,7 +16459,7 @@
         <v>44783</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16532,7 +16532,7 @@
         <v>45349</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16605,7 +16605,7 @@
         <v>44487</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16683,7 +16683,7 @@
         <v>45021</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16756,7 +16756,7 @@
         <v>44600</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16829,7 +16829,7 @@
         <v>45415</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16902,7 +16902,7 @@
         <v>44593</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16975,7 +16975,7 @@
         <v>45740</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17048,7 +17048,7 @@
         <v>45475</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17121,7 +17121,7 @@
         <v>45323</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17194,7 +17194,7 @@
         <v>45475</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17267,7 +17267,7 @@
         <v>45735</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17340,7 +17340,7 @@
         <v>45037</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17413,7 +17413,7 @@
         <v>44690</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17486,7 +17486,7 @@
         <v>45155</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17559,7 +17559,7 @@
         <v>45641</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17632,7 +17632,7 @@
         <v>44593</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17705,7 +17705,7 @@
         <v>44504</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17778,7 +17778,7 @@
         <v>45126</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17851,7 +17851,7 @@
         <v>45126</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17924,7 +17924,7 @@
         <v>44799</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17997,7 +17997,7 @@
         <v>45155</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18070,7 +18070,7 @@
         <v>45225</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18143,7 +18143,7 @@
         <v>44852</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18216,7 +18216,7 @@
         <v>45190</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18289,7 +18289,7 @@
         <v>45433</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18362,7 +18362,7 @@
         <v>45067</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18435,7 +18435,7 @@
         <v>44953</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18508,7 +18508,7 @@
         <v>45107</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18581,7 +18581,7 @@
         <v>44729</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18654,7 +18654,7 @@
         <v>44984</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18727,7 +18727,7 @@
         <v>44507</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18800,7 +18800,7 @@
         <v>44473</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18873,7 +18873,7 @@
         <v>45434</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18946,7 +18946,7 @@
         <v>45189</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19019,7 +19019,7 @@
         <v>45048</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19092,7 +19092,7 @@
         <v>45191</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19165,7 +19165,7 @@
         <v>44619</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19238,7 +19238,7 @@
         <v>45036</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19311,7 +19311,7 @@
         <v>45273</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19389,7 +19389,7 @@
         <v>45229</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19462,7 +19462,7 @@
         <v>45132</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19535,7 +19535,7 @@
         <v>44907</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19608,7 +19608,7 @@
         <v>45211</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19681,7 +19681,7 @@
         <v>45084</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19754,7 +19754,7 @@
         <v>44519</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19827,7 +19827,7 @@
         <v>44839</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19900,7 +19900,7 @@
         <v>45317</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19973,7 +19973,7 @@
         <v>45102</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20046,7 +20046,7 @@
         <v>45102</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20119,7 +20119,7 @@
         <v>45749</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20192,7 +20192,7 @@
         <v>44979</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20265,7 +20265,7 @@
         <v>45716</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20338,7 +20338,7 @@
         <v>45551</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20416,7 +20416,7 @@
         <v>45091</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20489,7 +20489,7 @@
         <v>45401</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20562,7 +20562,7 @@
         <v>45926</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20635,7 +20635,7 @@
         <v>45716</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20708,7 +20708,7 @@
         <v>45632</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20781,7 +20781,7 @@
         <v>45574</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20854,7 +20854,7 @@
         <v>45121</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20927,7 +20927,7 @@
         <v>45191</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21000,7 +21000,7 @@
         <v>45615</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21073,7 +21073,7 @@
         <v>44979</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21146,7 +21146,7 @@
         <v>45113</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21219,7 +21219,7 @@
         <v>45113</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21292,7 +21292,7 @@
         <v>45167</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21365,7 +21365,7 @@
         <v>45818</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21438,7 +21438,7 @@
         <v>45887</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21511,7 +21511,7 @@
         <v>45915</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21589,7 +21589,7 @@
         <v>45887</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21662,7 +21662,7 @@
         <v>45069</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21735,7 +21735,7 @@
         <v>45069</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21808,7 +21808,7 @@
         <v>45401</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21881,7 +21881,7 @@
         <v>45348</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21954,7 +21954,7 @@
         <v>45408</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22027,7 +22027,7 @@
         <v>45700</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22100,7 +22100,7 @@
         <v>45819</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22173,7 +22173,7 @@
         <v>45645</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22246,7 +22246,7 @@
         <v>45376</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22319,7 +22319,7 @@
         <v>44683</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22392,7 +22392,7 @@
         <v>45629</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22465,7 +22465,7 @@
         <v>45524</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22538,7 +22538,7 @@
         <v>45818</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22611,7 +22611,7 @@
         <v>45461</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22684,7 +22684,7 @@
         <v>45349</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22757,7 +22757,7 @@
         <v>46006</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22830,7 +22830,7 @@
         <v>45972</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22903,7 +22903,7 @@
         <v>45615</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22976,7 +22976,7 @@
         <v>44524</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23049,7 +23049,7 @@
         <v>45741</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23122,7 +23122,7 @@
         <v>45091</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23195,7 +23195,7 @@
         <v>45681</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23268,7 +23268,7 @@
         <v>44897</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23341,7 +23341,7 @@
         <v>45966</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23414,7 +23414,7 @@
         <v>45909</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23487,7 +23487,7 @@
         <v>45908</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23560,7 +23560,7 @@
         <v>45113</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23633,7 +23633,7 @@
         <v>46055</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23706,7 +23706,7 @@
         <v>45938</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23779,7 +23779,7 @@
         <v>45915</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23852,7 +23852,7 @@
         <v>45976</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23925,7 +23925,7 @@
         <v>46140</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23998,7 +23998,7 @@
         <v>45915</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24071,7 +24071,7 @@
         <v>45915</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24144,7 +24144,7 @@
         <v>46043</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24217,7 +24217,7 @@
         <v>45335</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24290,7 +24290,7 @@
         <v>45335</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24363,7 +24363,7 @@
         <v>45200</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24436,7 +24436,7 @@
         <v>45976</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24509,7 +24509,7 @@
         <v>45755</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24582,7 +24582,7 @@
         <v>45070</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24655,7 +24655,7 @@
         <v>45222</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24728,7 +24728,7 @@
         <v>44944</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24801,7 +24801,7 @@
         <v>45921</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24874,7 +24874,7 @@
         <v>45370</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24947,7 +24947,7 @@
         <v>45400</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25020,7 +25020,7 @@
         <v>45021</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25093,7 +25093,7 @@
         <v>44900</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25166,7 +25166,7 @@
         <v>44922</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25239,7 +25239,7 @@
         <v>46142</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25312,7 +25312,7 @@
         <v>45931</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25385,7 +25385,7 @@
         <v>44781</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25458,7 +25458,7 @@
         <v>45466</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25531,7 +25531,7 @@
         <v>45716</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25604,7 +25604,7 @@
         <v>45327</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25677,7 +25677,7 @@
         <v>45938</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25750,7 +25750,7 @@
         <v>45938</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25823,7 +25823,7 @@
         <v>45938</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25896,7 +25896,7 @@
         <v>45938</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25969,7 +25969,7 @@
         <v>45217</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26042,7 +26042,7 @@
         <v>45425</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26115,7 +26115,7 @@
         <v>44951</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26188,7 +26188,7 @@
         <v>45099</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26261,7 +26261,7 @@
         <v>45204</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26339,7 +26339,7 @@
         <v>45561</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26417,7 +26417,7 @@
         <v>45901</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26490,7 +26490,7 @@
         <v>45258</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26563,7 +26563,7 @@
         <v>45953</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26636,7 +26636,7 @@
         <v>45727</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26709,7 +26709,7 @@
         <v>45349</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26782,7 +26782,7 @@
         <v>45789</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26855,7 +26855,7 @@
         <v>45310</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26928,7 +26928,7 @@
         <v>45740</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27001,7 +27001,7 @@
         <v>45573</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27074,7 +27074,7 @@
         <v>45960</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27147,7 +27147,7 @@
         <v>44728</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27220,7 +27220,7 @@
         <v>45964</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27293,7 +27293,7 @@
         <v>45258</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27366,7 +27366,7 @@
         <v>45258</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27439,7 +27439,7 @@
         <v>45600</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27512,7 +27512,7 @@
         <v>44930</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27585,7 +27585,7 @@
         <v>45400</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27658,7 +27658,7 @@
         <v>44698</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27731,7 +27731,7 @@
         <v>45964</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27804,7 +27804,7 @@
         <v>45028</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27877,7 +27877,7 @@
         <v>45392</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27950,7 +27950,7 @@
         <v>45967</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28023,7 +28023,7 @@
         <v>45967</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28096,7 +28096,7 @@
         <v>46083</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28169,7 +28169,7 @@
         <v>45531</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28242,7 +28242,7 @@
         <v>44900</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28315,7 +28315,7 @@
         <v>45196</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28388,7 +28388,7 @@
         <v>44586</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28461,7 +28461,7 @@
         <v>45971</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28534,7 +28534,7 @@
         <v>46155</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28607,7 +28607,7 @@
         <v>45161</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28685,7 +28685,7 @@
         <v>45180</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28758,7 +28758,7 @@
         <v>45707</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28831,7 +28831,7 @@
         <v>46069</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28909,7 +28909,7 @@
         <v>45716</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28982,7 +28982,7 @@
         <v>45048</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29055,7 +29055,7 @@
         <v>45979</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29128,7 +29128,7 @@
         <v>45727</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29201,7 +29201,7 @@
         <v>45981</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29274,7 +29274,7 @@
         <v>44897</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29347,7 +29347,7 @@
         <v>45614</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29420,7 +29420,7 @@
         <v>46161</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29493,7 +29493,7 @@
         <v>46160</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29566,7 +29566,7 @@
         <v>45230</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29639,7 +29639,7 @@
         <v>45989</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29712,7 +29712,7 @@
         <v>44977</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29785,7 +29785,7 @@
         <v>46160</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29858,7 +29858,7 @@
         <v>45587</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29931,7 +29931,7 @@
         <v>45301</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30004,7 +30004,7 @@
         <v>46160</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30077,7 +30077,7 @@
         <v>45902</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30150,7 +30150,7 @@
         <v>46162</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30223,7 +30223,7 @@
         <v>45622</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30296,7 +30296,7 @@
         <v>46162</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30369,7 +30369,7 @@
         <v>45986</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30442,7 +30442,7 @@
         <v>45994</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30515,7 +30515,7 @@
         <v>45093</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30588,7 +30588,7 @@
         <v>44965</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30661,7 +30661,7 @@
         <v>44743</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30734,7 +30734,7 @@
         <v>44749</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30807,7 +30807,7 @@
         <v>45327</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30880,7 +30880,7 @@
         <v>45327</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30953,7 +30953,7 @@
         <v>45559</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31031,7 +31031,7 @@
         <v>45182</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31104,7 +31104,7 @@
         <v>45433</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31177,7 +31177,7 @@
         <v>45107</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31250,7 +31250,7 @@
         <v>45007</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31323,7 +31323,7 @@
         <v>45007</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31396,7 +31396,7 @@
         <v>45706</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31469,7 +31469,7 @@
         <v>46169</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31542,7 +31542,7 @@
         <v>45148</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31615,7 +31615,7 @@
         <v>45084</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31688,7 +31688,7 @@
         <v>45537</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31761,7 +31761,7 @@
         <v>45281</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31834,7 +31834,7 @@
         <v>45211</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31907,7 +31907,7 @@
         <v>45021</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31980,7 +31980,7 @@
         <v>44530</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32053,7 +32053,7 @@
         <v>45189</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32126,7 +32126,7 @@
         <v>44938</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32199,7 +32199,7 @@
         <v>46024</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32272,7 +32272,7 @@
         <v>44851</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32345,7 +32345,7 @@
         <v>44960</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32418,7 +32418,7 @@
         <v>44494</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32491,7 +32491,7 @@
         <v>46036</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32564,7 +32564,7 @@
         <v>44893</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32637,7 +32637,7 @@
         <v>44518</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32710,7 +32710,7 @@
         <v>44728</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32783,7 +32783,7 @@
         <v>45009</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32856,7 +32856,7 @@
         <v>45009</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32929,7 +32929,7 @@
         <v>45009</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33002,7 +33002,7 @@
         <v>45009</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33075,7 +33075,7 @@
         <v>45923</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33148,7 +33148,7 @@
         <v>46044</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33221,7 +33221,7 @@
         <v>44911</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33294,7 +33294,7 @@
         <v>45159</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33367,7 +33367,7 @@
         <v>45514</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33440,7 +33440,7 @@
         <v>45514</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33513,7 +33513,7 @@
         <v>46049</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33586,7 +33586,7 @@
         <v>45202</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33659,7 +33659,7 @@
         <v>44879</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33732,7 +33732,7 @@
         <v>46055</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33805,7 +33805,7 @@
         <v>46055</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33878,7 +33878,7 @@
         <v>45126</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33951,7 +33951,7 @@
         <v>45126</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34024,7 +34024,7 @@
         <v>45126</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34097,7 +34097,7 @@
         <v>45155</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34170,7 +34170,7 @@
         <v>46058</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34243,7 +34243,7 @@
         <v>46062</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34316,7 +34316,7 @@
         <v>44953</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34389,7 +34389,7 @@
         <v>45362</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34462,7 +34462,7 @@
         <v>46069</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34540,7 +34540,7 @@
         <v>46182</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34613,7 +34613,7 @@
         <v>46071</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34691,7 +34691,7 @@
         <v>46182</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34764,7 +34764,7 @@
         <v>46071</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34842,7 +34842,7 @@
         <v>44700</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34915,7 +34915,7 @@
         <v>46072</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34988,7 +34988,7 @@
         <v>46072</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -35061,7 +35061,7 @@
         <v>46071</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -35139,7 +35139,7 @@
         <v>46078</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35212,7 +35212,7 @@
         <v>46183</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35285,7 +35285,7 @@
         <v>46079</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35358,7 +35358,7 @@
         <v>45743</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35431,7 +35431,7 @@
         <v>45296</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35504,7 +35504,7 @@
         <v>44530</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35577,7 +35577,7 @@
         <v>46079</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35650,7 +35650,7 @@
         <v>44777</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35723,7 +35723,7 @@
         <v>45644</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35796,7 +35796,7 @@
         <v>45181</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35869,7 +35869,7 @@
         <v>46185</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35942,7 +35942,7 @@
         <v>46085</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36015,7 +36015,7 @@
         <v>45211</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -36088,7 +36088,7 @@
         <v>46085</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36161,7 +36161,7 @@
         <v>46189</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36234,7 +36234,7 @@
         <v>46085</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36307,7 +36307,7 @@
         <v>46188</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36380,7 +36380,7 @@
         <v>46188</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36453,7 +36453,7 @@
         <v>46185</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36526,7 +36526,7 @@
         <v>45164</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36599,7 +36599,7 @@
         <v>46188</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36672,7 +36672,7 @@
         <v>45190</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36745,7 +36745,7 @@
         <v>46090</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36818,7 +36818,7 @@
         <v>44993</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36891,7 +36891,7 @@
         <v>45719</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36964,7 +36964,7 @@
         <v>45719</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37037,7 +37037,7 @@
         <v>45349</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -37110,7 +37110,7 @@
         <v>46188</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37183,7 +37183,7 @@
         <v>46185</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37256,7 +37256,7 @@
         <v>45531</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37329,7 +37329,7 @@
         <v>45126</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37402,7 +37402,7 @@
         <v>44861</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37475,7 +37475,7 @@
         <v>45772</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37548,7 +37548,7 @@
         <v>45205</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37621,7 +37621,7 @@
         <v>45474</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37694,7 +37694,7 @@
         <v>45084</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37767,7 +37767,7 @@
         <v>46190</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37845,7 +37845,7 @@
         <v>45126</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37918,7 +37918,7 @@
         <v>46120</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37991,7 +37991,7 @@
         <v>46196</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -38064,7 +38064,7 @@
         <v>45574</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -38137,7 +38137,7 @@
         <v>46196</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38215,7 +38215,7 @@
         <v>46196</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38293,7 +38293,7 @@
         <v>45204</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38371,7 +38371,7 @@
         <v>46196</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38449,7 +38449,7 @@
         <v>45232</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38522,7 +38522,7 @@
         <v>46106</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38595,7 +38595,7 @@
         <v>46106</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38668,7 +38668,7 @@
         <v>46010</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38741,7 +38741,7 @@
         <v>45098</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38814,7 +38814,7 @@
         <v>46198</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38887,7 +38887,7 @@
         <v>45392</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38960,7 +38960,7 @@
         <v>46197</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -39038,7 +39038,7 @@
         <v>46107</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -39111,7 +39111,7 @@
         <v>46197</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -39189,7 +39189,7 @@
         <v>46197</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39267,7 +39267,7 @@
         <v>45740</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39340,7 +39340,7 @@
         <v>45341</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39413,7 +39413,7 @@
         <v>44995</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39486,7 +39486,7 @@
         <v>45003</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39559,7 +39559,7 @@
         <v>45477</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39632,7 +39632,7 @@
         <v>44995</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39705,7 +39705,7 @@
         <v>46244</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39778,7 +39778,7 @@
         <v>46120</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39851,7 +39851,7 @@
         <v>46120</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39924,7 +39924,7 @@
         <v>45126</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39997,7 +39997,7 @@
         <v>45514</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -40070,7 +40070,7 @@
         <v>45146</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -40143,7 +40143,7 @@
         <v>44959</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40216,7 +40216,7 @@
         <v>45068</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40294,7 +40294,7 @@
         <v>45707</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40367,7 +40367,7 @@
         <v>44851</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40440,7 +40440,7 @@
         <v>44608</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40513,7 +40513,7 @@
         <v>45095</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40586,7 +40586,7 @@
         <v>44580</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40659,7 +40659,7 @@
         <v>46202</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40732,7 +40732,7 @@
         <v>46127</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40805,7 +40805,7 @@
         <v>46127</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40878,7 +40878,7 @@
         <v>46127</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40951,7 +40951,7 @@
         <v>45373</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -41024,7 +41024,7 @@
         <v>45161</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -41102,7 +41102,7 @@
         <v>44984</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -41175,7 +41175,7 @@
         <v>45252</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41248,7 +41248,7 @@
         <v>46133</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41321,7 +41321,7 @@
         <v>44761</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41394,7 +41394,7 @@
         <v>44802</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41467,7 +41467,7 @@
         <v>45422</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41540,7 +41540,7 @@
         <v>44808</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41613,7 +41613,7 @@
         <v>46134</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41686,7 +41686,7 @@
         <v>44993</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41759,7 +41759,7 @@
         <v>45189</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41832,7 +41832,7 @@
         <v>45772</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41905,7 +41905,7 @@
         <v>46139</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41978,7 +41978,7 @@
         <v>45049</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -42051,7 +42051,7 @@
         <v>45392</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -42124,7 +42124,7 @@
         <v>45966</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -42197,7 +42197,7 @@
         <v>45905</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42270,7 +42270,7 @@
         <v>44531</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42343,7 +42343,7 @@
         <v>45051</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42416,7 +42416,7 @@
         <v>45051</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42489,7 +42489,7 @@
         <v>45901</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42562,7 +42562,7 @@
         <v>45126</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42635,7 +42635,7 @@
         <v>45126</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42708,7 +42708,7 @@
         <v>45909</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42781,7 +42781,7 @@
         <v>45323</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42854,7 +42854,7 @@
         <v>44673</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42927,7 +42927,7 @@
         <v>45596</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -43000,7 +43000,7 @@
         <v>44893</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -43073,7 +43073,7 @@
         <v>45668</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -43146,7 +43146,7 @@
         <v>44759</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43219,7 +43219,7 @@
         <v>46205</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43297,7 +43297,7 @@
         <v>44594</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43370,7 +43370,7 @@
         <v>46251</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43443,7 +43443,7 @@
         <v>45323</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43516,7 +43516,7 @@
         <v>44852</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43589,7 +43589,7 @@
         <v>45149</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43662,7 +43662,7 @@
         <v>45111</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43735,7 +43735,7 @@
         <v>45310</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43808,7 +43808,7 @@
         <v>46253</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43881,7 +43881,7 @@
         <v>45204</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43959,7 +43959,7 @@
         <v>46127</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -44037,7 +44037,7 @@
         <v>45062</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -44110,7 +44110,7 @@
         <v>46253</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -44183,7 +44183,7 @@
         <v>45562</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44256,7 +44256,7 @@
         <v>45103</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44329,7 +44329,7 @@
         <v>45688</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44402,7 +44402,7 @@
         <v>46212</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44475,7 +44475,7 @@
         <v>44589</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44548,7 +44548,7 @@
         <v>46211</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44621,7 +44621,7 @@
         <v>46212</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44694,7 +44694,7 @@
         <v>44726</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44767,7 +44767,7 @@
         <v>45742</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44840,7 +44840,7 @@
         <v>44524</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44913,7 +44913,7 @@
         <v>44728</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44986,7 +44986,7 @@
         <v>45182</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -45059,7 +45059,7 @@
         <v>44816</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -45132,7 +45132,7 @@
         <v>44840</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -45210,7 +45210,7 @@
         <v>45595</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45283,7 +45283,7 @@
         <v>46255</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45361,7 +45361,7 @@
         <v>46230</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45434,7 +45434,7 @@
         <v>46213</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45507,7 +45507,7 @@
         <v>46255</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45585,7 +45585,7 @@
         <v>44897</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45658,7 +45658,7 @@
         <v>46255</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45736,7 +45736,7 @@
         <v>46259</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45809,7 +45809,7 @@
         <v>46255</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45887,7 +45887,7 @@
         <v>45273</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45965,7 +45965,7 @@
         <v>45349</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -46038,7 +46038,7 @@
         <v>44827</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -46111,7 +46111,7 @@
         <v>45092</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -46184,7 +46184,7 @@
         <v>46255</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -46257,7 +46257,7 @@
         <v>46255</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -46335,7 +46335,7 @@
         <v>46255</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -46413,7 +46413,7 @@
         <v>44550</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46486,7 +46486,7 @@
         <v>45076</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46559,7 +46559,7 @@
         <v>45385</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -46632,7 +46632,7 @@
         <v>45515</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -46705,7 +46705,7 @@
         <v>45307</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46778,7 +46778,7 @@
         <v>45317</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46851,7 +46851,7 @@
         <v>45187</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46924,7 +46924,7 @@
         <v>44748</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46997,7 +46997,7 @@
         <v>46255</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -47075,7 +47075,7 @@
         <v>44699</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -47148,7 +47148,7 @@
         <v>45400</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -47221,7 +47221,7 @@
         <v>45229</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -47294,7 +47294,7 @@
         <v>45188</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -47372,7 +47372,7 @@
         <v>45769</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -47445,7 +47445,7 @@
         <v>44769</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -47518,7 +47518,7 @@
         <v>44488</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -47596,7 +47596,7 @@
         <v>45769</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -47669,7 +47669,7 @@
         <v>45394</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -47742,7 +47742,7 @@
         <v>44955</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47815,7 +47815,7 @@
         <v>45048</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47888,7 +47888,7 @@
         <v>46268</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47961,7 +47961,7 @@
         <v>45351</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -48034,7 +48034,7 @@
         <v>45534</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -48107,7 +48107,7 @@
         <v>45215</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -48180,7 +48180,7 @@
         <v>45551</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -48253,7 +48253,7 @@
         <v>45523</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -48326,7 +48326,7 @@
         <v>44949</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -48399,7 +48399,7 @@
         <v>45684</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -48472,7 +48472,7 @@
         <v>45624</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -48545,7 +48545,7 @@
         <v>45484</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -48618,7 +48618,7 @@
         <v>46271</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -48691,7 +48691,7 @@
         <v>46273</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -48764,7 +48764,7 @@
         <v>46272</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -48837,7 +48837,7 @@
         <v>46188</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -48910,7 +48910,7 @@
         <v>46275</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -48983,7 +48983,7 @@
         <v>45107</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -49056,7 +49056,7 @@
         <v>45445</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -49129,7 +49129,7 @@
         <v>46279</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -49207,7 +49207,7 @@
         <v>46279</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -49285,7 +49285,7 @@
         <v>45317</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -49358,7 +49358,7 @@
         <v>46279</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -49436,7 +49436,7 @@
         <v>46279</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -49509,7 +49509,7 @@
         <v>45548</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -49582,7 +49582,7 @@
         <v>46279</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -49660,7 +49660,7 @@
         <v>45415</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -49733,7 +49733,7 @@
         <v>46279</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -49811,7 +49811,7 @@
         <v>45638</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -49884,7 +49884,7 @@
         <v>46279</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -49962,7 +49962,7 @@
         <v>46279</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -50040,7 +50040,7 @@
         <v>45565</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -50113,7 +50113,7 @@
         <v>45386</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -50186,7 +50186,7 @@
         <v>45775</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -50259,7 +50259,7 @@
         <v>46134</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -50332,7 +50332,7 @@
         <v>45481</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -50405,7 +50405,7 @@
         <v>46279</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -50483,7 +50483,7 @@
         <v>46279</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -50561,7 +50561,7 @@
         <v>46279</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -50639,7 +50639,7 @@
         <v>45566</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -50712,7 +50712,7 @@
         <v>45582</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -50785,7 +50785,7 @@
         <v>45609</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -50858,7 +50858,7 @@
         <v>45484</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -50931,7 +50931,7 @@
         <v>45688</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -51004,7 +51004,7 @@
         <v>45610</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -51077,7 +51077,7 @@
         <v>46245</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -51150,7 +51150,7 @@
         <v>45400</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -51223,7 +51223,7 @@
         <v>45455</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -51296,7 +51296,7 @@
         <v>46282</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -51369,7 +51369,7 @@
         <v>45665</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -51442,7 +51442,7 @@
         <v>44977</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -51515,7 +51515,7 @@
         <v>45537</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -51588,7 +51588,7 @@
         <v>44958</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -51661,7 +51661,7 @@
         <v>45800</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -51734,7 +51734,7 @@
         <v>45804</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -51807,7 +51807,7 @@
         <v>45813</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -51880,7 +51880,7 @@
         <v>45825</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -51953,7 +51953,7 @@
         <v>45826</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -52026,7 +52026,7 @@
         <v>45826</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -52099,7 +52099,7 @@
         <v>45826</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -52172,7 +52172,7 @@
         <v>45826</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -52245,7 +52245,7 @@
         <v>45826</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -52318,7 +52318,7 @@
         <v>45826</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -52391,7 +52391,7 @@
         <v>45832</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -52464,7 +52464,7 @@
         <v>45835</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -52537,7 +52537,7 @@
         <v>45805</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -52610,7 +52610,7 @@
         <v>45845</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -52683,7 +52683,7 @@
         <v>45621</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -52756,7 +52756,7 @@
         <v>45727</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -52829,7 +52829,7 @@
         <v>45849</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -52902,7 +52902,7 @@
         <v>45775</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -52975,7 +52975,7 @@
         <v>45716</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -53048,7 +53048,7 @@
         <v>45851</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -53121,7 +53121,7 @@
         <v>45851</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -53194,7 +53194,7 @@
         <v>45772</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -53267,7 +53267,7 @@
         <v>45857</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -53340,7 +53340,7 @@
         <v>45863</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -53413,7 +53413,7 @@
         <v>45750</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -53486,7 +53486,7 @@
         <v>45790</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -53559,7 +53559,7 @@
         <v>45881</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -53632,7 +53632,7 @@
         <v>44476</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -53705,7 +53705,7 @@
         <v>45191</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -53778,7 +53778,7 @@
         <v>44462</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -53851,7 +53851,7 @@
         <v>44959</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -53924,7 +53924,7 @@
         <v>45194</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -53997,7 +53997,7 @@
         <v>45377</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -54070,7 +54070,7 @@
         <v>45387</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -54143,7 +54143,7 @@
         <v>44903</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -54216,7 +54216,7 @@
         <v>44900</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -54289,7 +54289,7 @@
         <v>44852</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -54362,7 +54362,7 @@
         <v>45200</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -54435,7 +54435,7 @@
         <v>45534</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -54508,7 +54508,7 @@
         <v>45191</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -54581,7 +54581,7 @@
         <v>45386</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -54654,7 +54654,7 @@
         <v>45287</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -54727,7 +54727,7 @@
         <v>45386</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -54800,7 +54800,7 @@
         <v>45386</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -54873,7 +54873,7 @@
         <v>45386</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -54946,7 +54946,7 @@
         <v>44460</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -55019,7 +55019,7 @@
         <v>45387</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -55092,7 +55092,7 @@
         <v>44519</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -55165,7 +55165,7 @@
         <v>45534</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -55238,7 +55238,7 @@
         <v>45377</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -55311,7 +55311,7 @@
         <v>44928</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -55384,7 +55384,7 @@
         <v>45377</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -55457,7 +55457,7 @@
         <v>44519</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -55530,7 +55530,7 @@
         <v>45200</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -55603,7 +55603,7 @@
         <v>44900</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -55676,7 +55676,7 @@
         <v>45330</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -55749,7 +55749,7 @@
         <v>44959</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -55822,7 +55822,7 @@
         <v>45348</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -55895,7 +55895,7 @@
         <v>45813</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -55968,7 +55968,7 @@
         <v>45813</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -56041,7 +56041,7 @@
         <v>45849</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -56114,7 +56114,7 @@
         <v>45898</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -56187,7 +56187,7 @@
         <v>45935</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -56260,7 +56260,7 @@
         <v>45978</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -56333,7 +56333,7 @@
         <v>46034</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -56406,7 +56406,7 @@
         <v>46049</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -56479,7 +56479,7 @@
         <v>46049</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -56552,7 +56552,7 @@
         <v>46065</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -56625,7 +56625,7 @@
         <v>46092</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -56698,7 +56698,7 @@
         <v>46062</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -56771,7 +56771,7 @@
         <v>46119</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -56844,7 +56844,7 @@
         <v>46119</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -56917,7 +56917,7 @@
         <v>46127</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -56990,7 +56990,7 @@
         <v>46167</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -57063,7 +57063,7 @@
         <v>46156</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -57136,7 +57136,7 @@
         <v>46183</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -57209,7 +57209,7 @@
         <v>46191</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -57282,7 +57282,7 @@
         <v>46276</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>

--- a/Översikt EMMABODA.xlsx
+++ b/Översikt EMMABODA.xlsx
@@ -601,7 +601,7 @@
         <v>45534</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>45440</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -830,7 +830,7 @@
         <v>45387</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>45202</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
         <v>45030</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>44480</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1276,7 +1276,7 @@
         <v>45616</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>44706</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>44811</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>45330</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1713,7 +1713,7 @@
         <v>45359</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         <v>46136</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1931,7 +1931,7 @@
         <v>45369</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
         <v>45086</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>44937</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2257,7 +2257,7 @@
         <v>46062</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2367,7 +2367,7 @@
         <v>46069</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         <v>46214</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2579,7 +2579,7 @@
         <v>44771</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2688,7 +2688,7 @@
         <v>45161</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2798,7 +2798,7 @@
         <v>45797</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2907,7 +2907,7 @@
         <v>45166</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3012,7 +3012,7 @@
         <v>44762</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3117,7 +3117,7 @@
         <v>45953</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3226,7 +3226,7 @@
         <v>45092</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3331,7 +3331,7 @@
         <v>44495</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3440,7 +3440,7 @@
         <v>45967</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3545,7 +3545,7 @@
         <v>46135</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3655,7 +3655,7 @@
         <v>45763</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         <v>45196</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3869,7 +3869,7 @@
         <v>45107</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3978,7 +3978,7 @@
         <v>45104</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4083,7 +4083,7 @@
         <v>46253</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4188,7 +4188,7 @@
         <v>44570</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4293,7 +4293,7 @@
         <v>46213</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4398,7 +4398,7 @@
         <v>46213</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4503,7 +4503,7 @@
         <v>46218</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4608,7 +4608,7 @@
         <v>46282</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4713,7 +4713,7 @@
         <v>46055</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4818,7 +4818,7 @@
         <v>44984</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4923,7 +4923,7 @@
         <v>45229</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5032,7 +5032,7 @@
         <v>44966</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5137,7 +5137,7 @@
         <v>44488</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5247,7 +5247,7 @@
         <v>45335</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5352,7 +5352,7 @@
         <v>45068</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
         <v>44895</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5567,7 +5567,7 @@
         <v>44588</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5672,7 +5672,7 @@
         <v>45509</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5777,7 +5777,7 @@
         <v>45387</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5886,7 +5886,7 @@
         <v>45611</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5995,7 +5995,7 @@
         <v>45330</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6104,7 +6104,7 @@
         <v>44852</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6213,7 +6213,7 @@
         <v>45442</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6318,7 +6318,7 @@
         <v>45153</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6423,7 +6423,7 @@
         <v>45386</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6528,7 +6528,7 @@
         <v>45685</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6637,7 +6637,7 @@
         <v>45813</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6746,7 +6746,7 @@
         <v>46275</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6855,7 +6855,7 @@
         <v>44530</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6928,7 +6928,7 @@
         <v>44488</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7001,7 +7001,7 @@
         <v>44764</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7074,7 +7074,7 @@
         <v>44530</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         <v>44496</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7220,7 +7220,7 @@
         <v>44496</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7293,7 +7293,7 @@
         <v>44529</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7366,7 +7366,7 @@
         <v>44490</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7439,7 +7439,7 @@
         <v>44601</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7512,7 +7512,7 @@
         <v>44507</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7585,7 +7585,7 @@
         <v>44507</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7658,7 +7658,7 @@
         <v>44507</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7731,7 +7731,7 @@
         <v>44600</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7804,7 +7804,7 @@
         <v>44728</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7877,7 +7877,7 @@
         <v>44691</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7950,7 +7950,7 @@
         <v>44628</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8023,7 +8023,7 @@
         <v>44504</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8096,7 +8096,7 @@
         <v>44515</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8169,7 +8169,7 @@
         <v>44851</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8242,7 +8242,7 @@
         <v>44599</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8315,7 +8315,7 @@
         <v>44860</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8388,7 +8388,7 @@
         <v>44523</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8461,7 +8461,7 @@
         <v>44648</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8534,7 +8534,7 @@
         <v>44628</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8607,7 +8607,7 @@
         <v>44788</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8680,7 +8680,7 @@
         <v>44627</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8753,7 +8753,7 @@
         <v>44498</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8826,7 +8826,7 @@
         <v>44768</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8899,7 +8899,7 @@
         <v>44851</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8972,7 +8972,7 @@
         <v>44529</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9045,7 +9045,7 @@
         <v>44813</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9118,7 +9118,7 @@
         <v>44771</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         <v>44809</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9264,7 +9264,7 @@
         <v>44587</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9337,7 +9337,7 @@
         <v>44496</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9410,7 +9410,7 @@
         <v>44466</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9483,7 +9483,7 @@
         <v>44487</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9561,7 +9561,7 @@
         <v>44507</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9634,7 +9634,7 @@
         <v>44507</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9707,7 +9707,7 @@
         <v>44600</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9780,7 +9780,7 @@
         <v>44628</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9853,7 +9853,7 @@
         <v>44652</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9926,7 +9926,7 @@
         <v>44501</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9999,7 +9999,7 @@
         <v>44600</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10072,7 +10072,7 @@
         <v>44852</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10145,7 +10145,7 @@
         <v>44839</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10218,7 +10218,7 @@
         <v>44615</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10296,7 +10296,7 @@
         <v>44622</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10369,7 +10369,7 @@
         <v>44524</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10442,7 +10442,7 @@
         <v>44712</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10515,7 +10515,7 @@
         <v>44743</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10588,7 +10588,7 @@
         <v>44722</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10661,7 +10661,7 @@
         <v>44532</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10739,7 +10739,7 @@
         <v>44470</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10812,7 +10812,7 @@
         <v>44593</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10885,7 +10885,7 @@
         <v>44652</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10958,7 +10958,7 @@
         <v>44699</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11031,7 +11031,7 @@
         <v>44820</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11109,7 +11109,7 @@
         <v>44847</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11182,7 +11182,7 @@
         <v>44743</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11255,7 +11255,7 @@
         <v>44488</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11333,7 +11333,7 @@
         <v>44589</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11406,7 +11406,7 @@
         <v>44551</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11484,7 +11484,7 @@
         <v>44600</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11557,7 +11557,7 @@
         <v>44725</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11630,7 +11630,7 @@
         <v>44600</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11703,7 +11703,7 @@
         <v>44655</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11776,7 +11776,7 @@
         <v>44530</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11849,7 +11849,7 @@
         <v>44788</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11922,7 +11922,7 @@
         <v>45335</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11995,7 +11995,7 @@
         <v>45190</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12068,7 +12068,7 @@
         <v>45204</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12146,7 +12146,7 @@
         <v>45048</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12219,7 +12219,7 @@
         <v>44739</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12292,7 +12292,7 @@
         <v>45211</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12365,7 +12365,7 @@
         <v>45719</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12438,7 +12438,7 @@
         <v>45187</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12511,7 +12511,7 @@
         <v>45719</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12584,7 +12584,7 @@
         <v>45348</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12657,7 +12657,7 @@
         <v>45069</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12730,7 +12730,7 @@
         <v>45069</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12803,7 +12803,7 @@
         <v>45397</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12876,7 +12876,7 @@
         <v>45219</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12949,7 +12949,7 @@
         <v>45411</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13022,7 +13022,7 @@
         <v>45422</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13095,7 +13095,7 @@
         <v>45229</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13168,7 +13168,7 @@
         <v>45385</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13241,7 +13241,7 @@
         <v>45126</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13314,7 +13314,7 @@
         <v>45376</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13387,7 +13387,7 @@
         <v>45461</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13460,7 +13460,7 @@
         <v>44861</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13533,7 +13533,7 @@
         <v>45400</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13606,7 +13606,7 @@
         <v>45615</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13679,7 +13679,7 @@
         <v>44907</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13752,7 +13752,7 @@
         <v>45474</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13825,7 +13825,7 @@
         <v>46024</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13898,7 +13898,7 @@
         <v>45161</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13976,7 +13976,7 @@
         <v>45273</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14054,7 +14054,7 @@
         <v>45477</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14127,7 +14127,7 @@
         <v>45514</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14200,7 +14200,7 @@
         <v>44951</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14273,7 +14273,7 @@
         <v>45161</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14351,7 +14351,7 @@
         <v>44519</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14424,7 +14424,7 @@
         <v>45887</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14497,7 +14497,7 @@
         <v>45887</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14570,7 +14570,7 @@
         <v>44530</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14643,7 +14643,7 @@
         <v>45749</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14716,7 +14716,7 @@
         <v>45800</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14789,7 +14789,7 @@
         <v>46036</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14862,7 +14862,7 @@
         <v>45537</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14935,7 +14935,7 @@
         <v>45189</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15008,7 +15008,7 @@
         <v>45189</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15081,7 +15081,7 @@
         <v>44977</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15154,7 +15154,7 @@
         <v>44550</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15227,7 +15227,7 @@
         <v>45099</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15300,7 +15300,7 @@
         <v>45070</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15373,7 +15373,7 @@
         <v>45700</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15446,7 +15446,7 @@
         <v>44896</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15519,7 +15519,7 @@
         <v>44900</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15592,7 +15592,7 @@
         <v>45537</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15665,7 +15665,7 @@
         <v>45562</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15738,7 +15738,7 @@
         <v>46044</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15811,7 +15811,7 @@
         <v>45741</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15884,7 +15884,7 @@
         <v>45475</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15957,7 +15957,7 @@
         <v>46049</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16030,7 +16030,7 @@
         <v>44893</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16103,7 +16103,7 @@
         <v>45681</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16176,7 +16176,7 @@
         <v>45665</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16249,7 +16249,7 @@
         <v>45587</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16322,7 +16322,7 @@
         <v>44683</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16395,7 +16395,7 @@
         <v>45908</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16468,7 +16468,7 @@
         <v>45909</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16541,7 +16541,7 @@
         <v>46055</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16614,7 +16614,7 @@
         <v>46055</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16687,7 +16687,7 @@
         <v>45349</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16760,7 +16760,7 @@
         <v>44995</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16833,7 +16833,7 @@
         <v>45155</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16906,7 +16906,7 @@
         <v>44897</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16979,7 +16979,7 @@
         <v>46058</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17052,7 +17052,7 @@
         <v>45915</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17125,7 +17125,7 @@
         <v>45915</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17198,7 +17198,7 @@
         <v>45915</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17271,7 +17271,7 @@
         <v>44949</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17344,7 +17344,7 @@
         <v>46062</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17417,7 +17417,7 @@
         <v>45349</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17490,7 +17490,7 @@
         <v>45007</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17563,7 +17563,7 @@
         <v>45921</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17636,7 +17636,7 @@
         <v>45400</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17709,7 +17709,7 @@
         <v>44580</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17782,7 +17782,7 @@
         <v>45804</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17855,7 +17855,7 @@
         <v>44958</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17928,7 +17928,7 @@
         <v>46069</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18006,7 +18006,7 @@
         <v>45022</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18079,7 +18079,7 @@
         <v>45022</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18152,7 +18152,7 @@
         <v>46071</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18230,7 +18230,7 @@
         <v>44839</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18303,7 +18303,7 @@
         <v>44955</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18376,7 +18376,7 @@
         <v>46071</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18454,7 +18454,7 @@
         <v>46072</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18527,7 +18527,7 @@
         <v>46072</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18600,7 +18600,7 @@
         <v>46071</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18678,7 +18678,7 @@
         <v>45098</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18751,7 +18751,7 @@
         <v>45211</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18824,7 +18824,7 @@
         <v>46078</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18897,7 +18897,7 @@
         <v>46079</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18970,7 +18970,7 @@
         <v>46079</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19043,7 +19043,7 @@
         <v>45040</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19116,7 +19116,7 @@
         <v>45931</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19189,7 +19189,7 @@
         <v>46085</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19262,7 +19262,7 @@
         <v>46085</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19335,7 +19335,7 @@
         <v>45166</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19408,7 +19408,7 @@
         <v>45252</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19481,7 +19481,7 @@
         <v>45392</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19554,7 +19554,7 @@
         <v>44995</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19627,7 +19627,7 @@
         <v>46085</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19700,7 +19700,7 @@
         <v>44973</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19778,7 +19778,7 @@
         <v>44594</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19851,7 +19851,7 @@
         <v>44524</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19924,7 +19924,7 @@
         <v>44978</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19997,7 +19997,7 @@
         <v>46090</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20070,7 +20070,7 @@
         <v>45707</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20143,7 +20143,7 @@
         <v>45938</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20216,7 +20216,7 @@
         <v>44953</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20289,7 +20289,7 @@
         <v>44690</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20362,7 +20362,7 @@
         <v>45021</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20435,7 +20435,7 @@
         <v>45021</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20508,7 +20508,7 @@
         <v>45938</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20581,7 +20581,7 @@
         <v>45938</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20654,7 +20654,7 @@
         <v>45938</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20727,7 +20727,7 @@
         <v>45048</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20800,7 +20800,7 @@
         <v>44978</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20873,7 +20873,7 @@
         <v>45769</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20946,7 +20946,7 @@
         <v>45182</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21019,7 +21019,7 @@
         <v>44748</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21092,7 +21092,7 @@
         <v>45062</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21165,7 +21165,7 @@
         <v>45191</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21238,7 +21238,7 @@
         <v>45095</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21311,7 +21311,7 @@
         <v>44777</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21384,7 +21384,7 @@
         <v>44960</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21457,7 +21457,7 @@
         <v>46106</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21530,7 +21530,7 @@
         <v>46107</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21603,7 +21603,7 @@
         <v>45362</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21676,7 +21676,7 @@
         <v>45009</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21749,7 +21749,7 @@
         <v>45009</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21822,7 +21822,7 @@
         <v>46106</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21895,7 +21895,7 @@
         <v>45953</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21968,7 +21968,7 @@
         <v>45422</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22041,7 +22041,7 @@
         <v>45559</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22114,7 +22114,7 @@
         <v>45901</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22187,7 +22187,7 @@
         <v>45084</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22260,7 +22260,7 @@
         <v>45355</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22333,7 +22333,7 @@
         <v>44700</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22406,7 +22406,7 @@
         <v>45230</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22479,7 +22479,7 @@
         <v>45960</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22552,7 +22552,7 @@
         <v>44965</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22625,7 +22625,7 @@
         <v>45629</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22698,7 +22698,7 @@
         <v>45964</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22771,7 +22771,7 @@
         <v>44852</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22844,7 +22844,7 @@
         <v>45258</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22917,7 +22917,7 @@
         <v>45964</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22990,7 +22990,7 @@
         <v>46120</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23063,7 +23063,7 @@
         <v>46120</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23136,7 +23136,7 @@
         <v>45574</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23209,7 +23209,7 @@
         <v>45009</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23282,7 +23282,7 @@
         <v>45009</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23355,7 +23355,7 @@
         <v>45107</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23428,7 +23428,7 @@
         <v>44922</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23501,7 +23501,7 @@
         <v>44743</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23574,7 +23574,7 @@
         <v>45967</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23647,7 +23647,7 @@
         <v>45967</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23720,7 +23720,7 @@
         <v>45971</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23793,7 +23793,7 @@
         <v>45092</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23866,7 +23866,7 @@
         <v>45813</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23939,7 +23939,7 @@
         <v>45229</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24012,7 +24012,7 @@
         <v>46127</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24085,7 +24085,7 @@
         <v>46127</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24158,7 +24158,7 @@
         <v>46127</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24231,7 +24231,7 @@
         <v>45515</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24304,7 +24304,7 @@
         <v>44473</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24377,7 +24377,7 @@
         <v>45079</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24450,7 +24450,7 @@
         <v>45979</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24523,7 +24523,7 @@
         <v>46134</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24596,7 +24596,7 @@
         <v>46133</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24669,7 +24669,7 @@
         <v>45981</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24742,7 +24742,7 @@
         <v>45645</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24815,7 +24815,7 @@
         <v>45632</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24888,7 +24888,7 @@
         <v>45401</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24961,7 +24961,7 @@
         <v>45614</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25034,7 +25034,7 @@
         <v>45551</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25112,7 +25112,7 @@
         <v>45819</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25185,7 +25185,7 @@
         <v>45113</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25258,7 +25258,7 @@
         <v>45818</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25331,7 +25331,7 @@
         <v>45972</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25404,7 +25404,7 @@
         <v>45596</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25477,7 +25477,7 @@
         <v>45102</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25550,7 +25550,7 @@
         <v>45966</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25623,7 +25623,7 @@
         <v>45102</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25696,7 +25696,7 @@
         <v>45901</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25769,7 +25769,7 @@
         <v>44729</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25842,7 +25842,7 @@
         <v>45392</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25915,7 +25915,7 @@
         <v>46006</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25988,7 +25988,7 @@
         <v>45818</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26061,7 +26061,7 @@
         <v>44993</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26134,7 +26134,7 @@
         <v>45989</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26207,7 +26207,7 @@
         <v>45994</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26280,7 +26280,7 @@
         <v>45905</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26353,7 +26353,7 @@
         <v>44781</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26426,7 +26426,7 @@
         <v>45148</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26499,7 +26499,7 @@
         <v>45986</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26572,7 +26572,7 @@
         <v>46043</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26645,7 +26645,7 @@
         <v>44984</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26718,7 +26718,7 @@
         <v>44761</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26791,7 +26791,7 @@
         <v>45113</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26864,7 +26864,7 @@
         <v>45742</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26937,7 +26937,7 @@
         <v>44683</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27010,7 +27010,7 @@
         <v>45524</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27083,7 +27083,7 @@
         <v>45445</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27156,7 +27156,7 @@
         <v>45021</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27229,7 +27229,7 @@
         <v>45067</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27302,7 +27302,7 @@
         <v>45966</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27375,7 +27375,7 @@
         <v>46140</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27448,7 +27448,7 @@
         <v>45976</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27521,7 +27521,7 @@
         <v>46139</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27594,7 +27594,7 @@
         <v>45716</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27667,7 +27667,7 @@
         <v>45028</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27740,7 +27740,7 @@
         <v>45772</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27813,7 +27813,7 @@
         <v>45200</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27886,7 +27886,7 @@
         <v>45740</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27959,7 +27959,7 @@
         <v>45915</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28037,7 +28037,7 @@
         <v>44518</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28110,7 +28110,7 @@
         <v>45222</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28183,7 +28183,7 @@
         <v>45211</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28256,7 +28256,7 @@
         <v>45825</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28329,7 +28329,7 @@
         <v>45826</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28402,7 +28402,7 @@
         <v>45826</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28475,7 +28475,7 @@
         <v>45826</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28548,7 +28548,7 @@
         <v>45826</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28621,7 +28621,7 @@
         <v>45826</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28694,7 +28694,7 @@
         <v>44879</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28767,7 +28767,7 @@
         <v>46055</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28840,7 +28840,7 @@
         <v>45049</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28913,7 +28913,7 @@
         <v>45909</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28986,7 +28986,7 @@
         <v>45574</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29059,7 +29059,7 @@
         <v>45826</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29132,7 +29132,7 @@
         <v>45938</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29205,7 +29205,7 @@
         <v>44690</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29278,7 +29278,7 @@
         <v>44524</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29351,7 +29351,7 @@
         <v>45415</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29424,7 +29424,7 @@
         <v>45068</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29502,7 +29502,7 @@
         <v>46142</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29575,7 +29575,7 @@
         <v>45755</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29648,7 +29648,7 @@
         <v>45976</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29721,7 +29721,7 @@
         <v>45111</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29794,7 +29794,7 @@
         <v>45772</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29867,7 +29867,7 @@
         <v>45049</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29940,7 +29940,7 @@
         <v>45832</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30013,7 +30013,7 @@
         <v>45084</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30086,7 +30086,7 @@
         <v>45099</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30159,7 +30159,7 @@
         <v>44593</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30232,7 +30232,7 @@
         <v>44816</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30305,7 +30305,7 @@
         <v>45789</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30378,7 +30378,7 @@
         <v>44608</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30451,7 +30451,7 @@
         <v>46069</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30529,7 +30529,7 @@
         <v>45349</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30602,7 +30602,7 @@
         <v>45707</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30675,7 +30675,7 @@
         <v>46155</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30748,7 +30748,7 @@
         <v>46160</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30821,7 +30821,7 @@
         <v>46160</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30894,7 +30894,7 @@
         <v>46160</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30967,7 +30967,7 @@
         <v>45740</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31040,7 +31040,7 @@
         <v>44759</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31113,7 +31113,7 @@
         <v>45835</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31186,7 +31186,7 @@
         <v>45317</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31259,7 +31259,7 @@
         <v>46162</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31332,7 +31332,7 @@
         <v>45211</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31405,7 +31405,7 @@
         <v>45211</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31478,7 +31478,7 @@
         <v>45902</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31551,7 +31551,7 @@
         <v>46162</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31624,7 +31624,7 @@
         <v>45126</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31697,7 +31697,7 @@
         <v>44959</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31770,7 +31770,7 @@
         <v>45805</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31843,7 +31843,7 @@
         <v>45621</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31916,7 +31916,7 @@
         <v>44977</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31989,7 +31989,7 @@
         <v>45327</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32062,7 +32062,7 @@
         <v>45845</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32135,7 +32135,7 @@
         <v>45727</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32208,7 +32208,7 @@
         <v>45126</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32281,7 +32281,7 @@
         <v>45772</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32354,7 +32354,7 @@
         <v>45775</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32427,7 +32427,7 @@
         <v>45849</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32500,7 +32500,7 @@
         <v>45716</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32573,7 +32573,7 @@
         <v>44728</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32646,7 +32646,7 @@
         <v>45093</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32719,7 +32719,7 @@
         <v>45851</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32792,7 +32792,7 @@
         <v>45851</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32865,7 +32865,7 @@
         <v>46169</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32938,7 +32938,7 @@
         <v>44852</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33011,7 +33011,7 @@
         <v>45121</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33084,7 +33084,7 @@
         <v>45341</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33157,7 +33157,7 @@
         <v>44953</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33230,7 +33230,7 @@
         <v>45323</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33303,7 +33303,7 @@
         <v>45857</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33376,7 +33376,7 @@
         <v>44953</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33449,7 +33449,7 @@
         <v>44572</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33522,7 +33522,7 @@
         <v>45531</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33595,7 +33595,7 @@
         <v>45600</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33668,7 +33668,7 @@
         <v>45923</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33741,7 +33741,7 @@
         <v>44593</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33814,7 +33814,7 @@
         <v>45750</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33887,7 +33887,7 @@
         <v>45769</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33960,7 +33960,7 @@
         <v>45126</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34033,7 +34033,7 @@
         <v>45863</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34106,7 +34106,7 @@
         <v>45790</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34179,7 +34179,7 @@
         <v>45003</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34252,7 +34252,7 @@
         <v>44984</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34325,7 +34325,7 @@
         <v>45019</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34398,7 +34398,7 @@
         <v>44980</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34471,7 +34471,7 @@
         <v>44840</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34549,7 +34549,7 @@
         <v>45475</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34622,7 +34622,7 @@
         <v>45132</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34695,7 +34695,7 @@
         <v>44600</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34768,7 +34768,7 @@
         <v>45037</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34841,7 +34841,7 @@
         <v>44982</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34914,7 +34914,7 @@
         <v>46183</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34987,7 +34987,7 @@
         <v>46182</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -35060,7 +35060,7 @@
         <v>46182</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -35133,7 +35133,7 @@
         <v>44993</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35206,7 +35206,7 @@
         <v>45433</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35279,7 +35279,7 @@
         <v>46185</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35352,7 +35352,7 @@
         <v>46185</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35425,7 +35425,7 @@
         <v>46185</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35498,7 +35498,7 @@
         <v>45146</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35571,7 +35571,7 @@
         <v>46188</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35644,7 +35644,7 @@
         <v>46188</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35717,7 +35717,7 @@
         <v>46188</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35790,7 +35790,7 @@
         <v>46189</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35863,7 +35863,7 @@
         <v>46188</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35936,7 +35936,7 @@
         <v>44494</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36009,7 +36009,7 @@
         <v>46190</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -36087,7 +36087,7 @@
         <v>45559</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36165,7 +36165,7 @@
         <v>45743</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36238,7 +36238,7 @@
         <v>46120</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36311,7 +36311,7 @@
         <v>46196</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36389,7 +36389,7 @@
         <v>46196</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36467,7 +36467,7 @@
         <v>46196</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36545,7 +36545,7 @@
         <v>45126</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36618,7 +36618,7 @@
         <v>45126</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36691,7 +36691,7 @@
         <v>45191</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36764,7 +36764,7 @@
         <v>45126</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36837,7 +36837,7 @@
         <v>46197</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36915,7 +36915,7 @@
         <v>46197</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36993,7 +36993,7 @@
         <v>45205</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37066,7 +37066,7 @@
         <v>46010</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -37139,7 +37139,7 @@
         <v>45167</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37212,7 +37212,7 @@
         <v>46196</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37285,7 +37285,7 @@
         <v>46197</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37363,7 +37363,7 @@
         <v>46198</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37436,7 +37436,7 @@
         <v>45644</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37509,7 +37509,7 @@
         <v>45881</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37582,7 +37582,7 @@
         <v>46202</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37655,7 +37655,7 @@
         <v>45084</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37728,7 +37728,7 @@
         <v>45622</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37801,7 +37801,7 @@
         <v>45159</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37874,7 +37874,7 @@
         <v>45573</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37947,7 +37947,7 @@
         <v>45615</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -38020,7 +38020,7 @@
         <v>46205</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -38098,7 +38098,7 @@
         <v>45225</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -38171,7 +38171,7 @@
         <v>45327</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38244,7 +38244,7 @@
         <v>44783</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38317,7 +38317,7 @@
         <v>45091</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38390,7 +38390,7 @@
         <v>44652</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38463,7 +38463,7 @@
         <v>46127</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38541,7 +38541,7 @@
         <v>45230</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38614,7 +38614,7 @@
         <v>46251</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38687,7 +38687,7 @@
         <v>45232</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38760,7 +38760,7 @@
         <v>45182</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38833,7 +38833,7 @@
         <v>46211</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38906,7 +38906,7 @@
         <v>46253</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38979,7 +38979,7 @@
         <v>46253</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -39052,7 +39052,7 @@
         <v>45392</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -39125,7 +39125,7 @@
         <v>44699</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -39198,7 +39198,7 @@
         <v>45148</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39271,7 +39271,7 @@
         <v>45531</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39344,7 +39344,7 @@
         <v>45126</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39417,7 +39417,7 @@
         <v>45434</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39490,7 +39490,7 @@
         <v>46212</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39563,7 +39563,7 @@
         <v>46212</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39636,7 +39636,7 @@
         <v>44619</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39709,7 +39709,7 @@
         <v>46213</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39782,7 +39782,7 @@
         <v>46230</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39855,7 +39855,7 @@
         <v>46255</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39933,7 +39933,7 @@
         <v>45408</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -40006,7 +40006,7 @@
         <v>46255</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -40084,7 +40084,7 @@
         <v>45394</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -40157,7 +40157,7 @@
         <v>46259</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40230,7 +40230,7 @@
         <v>46255</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40308,7 +40308,7 @@
         <v>46255</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40386,7 +40386,7 @@
         <v>46255</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40464,7 +40464,7 @@
         <v>46255</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40542,7 +40542,7 @@
         <v>46255</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40620,7 +40620,7 @@
         <v>44728</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40693,7 +40693,7 @@
         <v>46255</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40766,7 +40766,7 @@
         <v>45188</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40844,7 +40844,7 @@
         <v>45188</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40922,7 +40922,7 @@
         <v>45400</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40995,7 +40995,7 @@
         <v>45107</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -41068,7 +41068,7 @@
         <v>44673</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -41141,7 +41141,7 @@
         <v>45164</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -41214,7 +41214,7 @@
         <v>44749</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41287,7 +41287,7 @@
         <v>44726</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41360,7 +41360,7 @@
         <v>44802</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41433,7 +41433,7 @@
         <v>45258</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41506,7 +41506,7 @@
         <v>45258</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41579,7 +41579,7 @@
         <v>45735</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41652,7 +41652,7 @@
         <v>45475</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41725,7 +41725,7 @@
         <v>45716</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41798,7 +41798,7 @@
         <v>46268</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41871,7 +41871,7 @@
         <v>44799</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41944,7 +41944,7 @@
         <v>44827</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -42017,7 +42017,7 @@
         <v>45301</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -42090,7 +42090,7 @@
         <v>46272</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -42163,7 +42163,7 @@
         <v>45309</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -42236,7 +42236,7 @@
         <v>46271</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42309,7 +42309,7 @@
         <v>45126</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42382,7 +42382,7 @@
         <v>45307</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42455,7 +42455,7 @@
         <v>45716</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42528,7 +42528,7 @@
         <v>45190</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42601,7 +42601,7 @@
         <v>45310</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42674,7 +42674,7 @@
         <v>44851</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42747,7 +42747,7 @@
         <v>46188</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42820,7 +42820,7 @@
         <v>46273</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42893,7 +42893,7 @@
         <v>45089</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42966,7 +42966,7 @@
         <v>44893</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -43039,7 +43039,7 @@
         <v>46134</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -43112,7 +43112,7 @@
         <v>45159</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -43185,7 +43185,7 @@
         <v>44769</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43258,7 +43258,7 @@
         <v>46275</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43331,7 +43331,7 @@
         <v>46279</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43409,7 +43409,7 @@
         <v>45187</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43482,7 +43482,7 @@
         <v>46279</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43560,7 +43560,7 @@
         <v>46279</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43638,7 +43638,7 @@
         <v>46279</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43716,7 +43716,7 @@
         <v>45401</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43789,7 +43789,7 @@
         <v>44851</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43862,7 +43862,7 @@
         <v>46279</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43940,7 +43940,7 @@
         <v>46279</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -44013,7 +44013,7 @@
         <v>45196</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -44086,7 +44086,7 @@
         <v>46279</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -44164,7 +44164,7 @@
         <v>45392</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -44237,7 +44237,7 @@
         <v>46279</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44315,7 +44315,7 @@
         <v>46279</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44393,7 +44393,7 @@
         <v>44897</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44466,7 +44466,7 @@
         <v>46279</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44544,7 +44544,7 @@
         <v>46279</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44622,7 +44622,7 @@
         <v>45323</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44695,7 +44695,7 @@
         <v>46282</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44768,7 +44768,7 @@
         <v>44487</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44841,7 +44841,7 @@
         <v>45323</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44914,7 +44914,7 @@
         <v>45637</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44987,7 +44987,7 @@
         <v>45466</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -45060,7 +45060,7 @@
         <v>45727</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -45133,7 +45133,7 @@
         <v>45327</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -45206,7 +45206,7 @@
         <v>44488</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -45284,7 +45284,7 @@
         <v>45296</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45357,7 +45357,7 @@
         <v>46286</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45430,7 +45430,7 @@
         <v>45706</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45503,7 +45503,7 @@
         <v>45727</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45576,7 +45576,7 @@
         <v>44530</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45649,7 +45649,7 @@
         <v>45926</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45722,7 +45722,7 @@
         <v>44586</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45795,7 +45795,7 @@
         <v>46288</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45868,7 +45868,7 @@
         <v>44589</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45941,7 +45941,7 @@
         <v>46244</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -46014,7 +46014,7 @@
         <v>46288</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -46087,7 +46087,7 @@
         <v>46245</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -46160,7 +46160,7 @@
         <v>44507</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -46233,7 +46233,7 @@
         <v>44938</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -46306,7 +46306,7 @@
         <v>44979</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -46379,7 +46379,7 @@
         <v>45606</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -46452,7 +46452,7 @@
         <v>45370</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46525,7 +46525,7 @@
         <v>45091</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46598,7 +46598,7 @@
         <v>45149</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -46671,7 +46671,7 @@
         <v>45191</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -46744,7 +46744,7 @@
         <v>45155</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46817,7 +46817,7 @@
         <v>45251</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46890,7 +46890,7 @@
         <v>44930</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46963,7 +46963,7 @@
         <v>46290</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -47036,7 +47036,7 @@
         <v>45181</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -47109,7 +47109,7 @@
         <v>44728</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -47182,7 +47182,7 @@
         <v>46290</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -47255,7 +47255,7 @@
         <v>45425</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -47328,7 +47328,7 @@
         <v>45036</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -47401,7 +47401,7 @@
         <v>44834</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -47474,7 +47474,7 @@
         <v>46290</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -47547,7 +47547,7 @@
         <v>45051</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -47620,7 +47620,7 @@
         <v>45051</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -47693,7 +47693,7 @@
         <v>45590</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -47766,7 +47766,7 @@
         <v>44808</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47839,7 +47839,7 @@
         <v>44944</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47912,7 +47912,7 @@
         <v>45048</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47985,7 +47985,7 @@
         <v>44487</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -48063,7 +48063,7 @@
         <v>45514</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -48136,7 +48136,7 @@
         <v>45514</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -48209,7 +48209,7 @@
         <v>45076</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -48282,7 +48282,7 @@
         <v>45392</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -48355,7 +48355,7 @@
         <v>45217</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -48428,7 +48428,7 @@
         <v>45688</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -48501,7 +48501,7 @@
         <v>45740</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -48574,7 +48574,7 @@
         <v>45180</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -48647,7 +48647,7 @@
         <v>45668</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -48720,7 +48720,7 @@
         <v>45349</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -48793,7 +48793,7 @@
         <v>45349</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -48866,7 +48866,7 @@
         <v>45641</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -48939,7 +48939,7 @@
         <v>44791</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -49012,7 +49012,7 @@
         <v>45310</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -49085,7 +49085,7 @@
         <v>44911</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -49158,7 +49158,7 @@
         <v>45394</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -49231,7 +49231,7 @@
         <v>44900</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -49304,7 +49304,7 @@
         <v>45189</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -49377,7 +49377,7 @@
         <v>45113</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -49450,7 +49450,7 @@
         <v>45606</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -49523,7 +49523,7 @@
         <v>45007</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -49596,7 +49596,7 @@
         <v>45164</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -49669,7 +49669,7 @@
         <v>45211</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -49742,7 +49742,7 @@
         <v>45126</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -49815,7 +49815,7 @@
         <v>44698</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -49888,7 +49888,7 @@
         <v>45317</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -49961,7 +49961,7 @@
         <v>45373</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -50034,7 +50034,7 @@
         <v>45204</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -50112,7 +50112,7 @@
         <v>45335</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -50185,7 +50185,7 @@
         <v>45369</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -50258,7 +50258,7 @@
         <v>45273</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -50336,7 +50336,7 @@
         <v>45204</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -50414,7 +50414,7 @@
         <v>45595</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -50487,7 +50487,7 @@
         <v>45433</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -50560,7 +50560,7 @@
         <v>45237</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -50633,7 +50633,7 @@
         <v>44531</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -50706,7 +50706,7 @@
         <v>44504</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -50779,7 +50779,7 @@
         <v>45103</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -50852,7 +50852,7 @@
         <v>45474</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -50925,7 +50925,7 @@
         <v>45341</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -50998,7 +50998,7 @@
         <v>45665</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -51071,7 +51071,7 @@
         <v>45126</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -51144,7 +51144,7 @@
         <v>45202</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -51217,7 +51217,7 @@
         <v>45281</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -51290,7 +51290,7 @@
         <v>45155</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -51363,7 +51363,7 @@
         <v>44897</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -51436,7 +51436,7 @@
         <v>45716</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -51509,7 +51509,7 @@
         <v>44519</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -51582,7 +51582,7 @@
         <v>45561</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -51660,7 +51660,7 @@
         <v>44979</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -51733,7 +51733,7 @@
         <v>45551</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -51806,7 +51806,7 @@
         <v>45523</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -51879,7 +51879,7 @@
         <v>45215</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -51952,7 +51952,7 @@
         <v>44949</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -52025,7 +52025,7 @@
         <v>45684</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -52098,7 +52098,7 @@
         <v>45624</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -52171,7 +52171,7 @@
         <v>45534</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -52244,7 +52244,7 @@
         <v>45484</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -52317,7 +52317,7 @@
         <v>45351</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -52390,7 +52390,7 @@
         <v>45107</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -52463,7 +52463,7 @@
         <v>45317</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -52536,7 +52536,7 @@
         <v>45415</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -52609,7 +52609,7 @@
         <v>45638</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -52682,7 +52682,7 @@
         <v>45610</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -52755,7 +52755,7 @@
         <v>45582</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -52828,7 +52828,7 @@
         <v>45565</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -52901,7 +52901,7 @@
         <v>45445</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -52974,7 +52974,7 @@
         <v>45548</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -53047,7 +53047,7 @@
         <v>45609</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -53120,7 +53120,7 @@
         <v>45688</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -53193,7 +53193,7 @@
         <v>45484</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -53266,7 +53266,7 @@
         <v>45386</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -53339,7 +53339,7 @@
         <v>45775</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -53412,7 +53412,7 @@
         <v>45566</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -53485,7 +53485,7 @@
         <v>45481</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -53558,7 +53558,7 @@
         <v>45400</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -53631,7 +53631,7 @@
         <v>45455</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -53704,7 +53704,7 @@
         <v>44476</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -53777,7 +53777,7 @@
         <v>45191</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -53850,7 +53850,7 @@
         <v>44959</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -53923,7 +53923,7 @@
         <v>45194</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -53996,7 +53996,7 @@
         <v>45377</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -54069,7 +54069,7 @@
         <v>45387</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -54142,7 +54142,7 @@
         <v>44903</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -54215,7 +54215,7 @@
         <v>44900</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -54288,7 +54288,7 @@
         <v>44852</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -54361,7 +54361,7 @@
         <v>45200</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -54434,7 +54434,7 @@
         <v>45534</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -54507,7 +54507,7 @@
         <v>45191</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -54580,7 +54580,7 @@
         <v>45386</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -54653,7 +54653,7 @@
         <v>45287</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -54726,7 +54726,7 @@
         <v>45386</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -54799,7 +54799,7 @@
         <v>45386</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -54872,7 +54872,7 @@
         <v>45386</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -54945,7 +54945,7 @@
         <v>45387</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -55018,7 +55018,7 @@
         <v>44519</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -55091,7 +55091,7 @@
         <v>45534</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -55164,7 +55164,7 @@
         <v>45377</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -55237,7 +55237,7 @@
         <v>44928</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -55310,7 +55310,7 @@
         <v>45377</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -55383,7 +55383,7 @@
         <v>44519</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -55456,7 +55456,7 @@
         <v>45200</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -55529,7 +55529,7 @@
         <v>44900</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -55602,7 +55602,7 @@
         <v>45330</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -55675,7 +55675,7 @@
         <v>44959</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -55748,7 +55748,7 @@
         <v>45348</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -55821,7 +55821,7 @@
         <v>45813</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -55894,7 +55894,7 @@
         <v>45813</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -55967,7 +55967,7 @@
         <v>45849</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -56040,7 +56040,7 @@
         <v>45898</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -56113,7 +56113,7 @@
         <v>45935</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -56186,7 +56186,7 @@
         <v>45978</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -56259,7 +56259,7 @@
         <v>46034</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -56332,7 +56332,7 @@
         <v>46049</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -56405,7 +56405,7 @@
         <v>46049</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -56478,7 +56478,7 @@
         <v>46065</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -56551,7 +56551,7 @@
         <v>46092</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -56624,7 +56624,7 @@
         <v>46062</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -56697,7 +56697,7 @@
         <v>46119</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -56770,7 +56770,7 @@
         <v>46119</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -56843,7 +56843,7 @@
         <v>46127</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -56916,7 +56916,7 @@
         <v>46167</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -56989,7 +56989,7 @@
         <v>46156</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -57062,7 +57062,7 @@
         <v>46183</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -57135,7 +57135,7 @@
         <v>46191</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -57208,7 +57208,7 @@
         <v>46276</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -57286,7 +57286,7 @@
         <v>46286</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -57359,7 +57359,7 @@
         <v>46283</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>

--- a/Översikt EMMABODA.xlsx
+++ b/Översikt EMMABODA.xlsx
@@ -601,7 +601,7 @@
         <v>45534</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>45440</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -830,7 +830,7 @@
         <v>45387</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>45202</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
         <v>45030</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>44480</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1276,7 +1276,7 @@
         <v>45616</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>44706</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>44811</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>45330</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1713,7 +1713,7 @@
         <v>45359</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         <v>46136</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1931,7 +1931,7 @@
         <v>45369</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
         <v>45086</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>44937</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2257,7 +2257,7 @@
         <v>46062</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2367,7 +2367,7 @@
         <v>46069</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         <v>46214</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2579,7 +2579,7 @@
         <v>44771</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2688,7 +2688,7 @@
         <v>45161</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2798,7 +2798,7 @@
         <v>45797</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2907,7 +2907,7 @@
         <v>45166</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3012,7 +3012,7 @@
         <v>44762</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3117,7 +3117,7 @@
         <v>45953</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3226,7 +3226,7 @@
         <v>45092</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3331,7 +3331,7 @@
         <v>44495</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3440,7 +3440,7 @@
         <v>45967</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3545,7 +3545,7 @@
         <v>46135</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3655,7 +3655,7 @@
         <v>45763</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         <v>45196</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3869,7 +3869,7 @@
         <v>45107</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3978,7 +3978,7 @@
         <v>45104</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4083,7 +4083,7 @@
         <v>46253</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4188,7 +4188,7 @@
         <v>44570</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4293,7 +4293,7 @@
         <v>46213</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4398,7 +4398,7 @@
         <v>46213</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4503,7 +4503,7 @@
         <v>46218</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4608,7 +4608,7 @@
         <v>46282</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4713,7 +4713,7 @@
         <v>46055</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4818,7 +4818,7 @@
         <v>44984</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4923,7 +4923,7 @@
         <v>45229</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5032,7 +5032,7 @@
         <v>44966</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5137,7 +5137,7 @@
         <v>44488</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5247,7 +5247,7 @@
         <v>45335</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5352,7 +5352,7 @@
         <v>45068</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
         <v>44895</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5567,7 +5567,7 @@
         <v>44588</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5672,7 +5672,7 @@
         <v>45509</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5777,7 +5777,7 @@
         <v>45387</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5886,7 +5886,7 @@
         <v>45611</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5995,7 +5995,7 @@
         <v>45330</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6104,7 +6104,7 @@
         <v>44852</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6213,7 +6213,7 @@
         <v>45442</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6318,7 +6318,7 @@
         <v>45153</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6423,7 +6423,7 @@
         <v>45386</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6528,7 +6528,7 @@
         <v>45685</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6637,7 +6637,7 @@
         <v>45813</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6746,7 +6746,7 @@
         <v>46275</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6855,7 +6855,7 @@
         <v>44530</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6928,7 +6928,7 @@
         <v>44488</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7001,7 +7001,7 @@
         <v>44764</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7074,7 +7074,7 @@
         <v>44530</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         <v>44496</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7220,7 +7220,7 @@
         <v>44496</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7293,7 +7293,7 @@
         <v>44529</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7366,7 +7366,7 @@
         <v>44490</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7439,7 +7439,7 @@
         <v>44601</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7512,7 +7512,7 @@
         <v>44507</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7585,7 +7585,7 @@
         <v>44507</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7658,7 +7658,7 @@
         <v>44507</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7731,7 +7731,7 @@
         <v>44600</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7804,7 +7804,7 @@
         <v>44728</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7877,7 +7877,7 @@
         <v>44691</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7950,7 +7950,7 @@
         <v>44628</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8023,7 +8023,7 @@
         <v>44504</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8096,7 +8096,7 @@
         <v>44515</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8169,7 +8169,7 @@
         <v>44851</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8242,7 +8242,7 @@
         <v>44599</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8315,7 +8315,7 @@
         <v>44860</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8388,7 +8388,7 @@
         <v>44523</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8461,7 +8461,7 @@
         <v>44648</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8534,7 +8534,7 @@
         <v>44628</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8607,7 +8607,7 @@
         <v>44788</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8680,7 +8680,7 @@
         <v>44627</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8753,7 +8753,7 @@
         <v>44498</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8826,7 +8826,7 @@
         <v>44768</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8899,7 +8899,7 @@
         <v>44851</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8972,7 +8972,7 @@
         <v>44529</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9045,7 +9045,7 @@
         <v>44813</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9118,7 +9118,7 @@
         <v>44771</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         <v>44809</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9264,7 +9264,7 @@
         <v>44587</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9337,7 +9337,7 @@
         <v>44496</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9410,7 +9410,7 @@
         <v>44466</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9483,7 +9483,7 @@
         <v>44487</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9561,7 +9561,7 @@
         <v>44507</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9634,7 +9634,7 @@
         <v>44507</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9707,7 +9707,7 @@
         <v>44600</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9780,7 +9780,7 @@
         <v>44628</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9853,7 +9853,7 @@
         <v>44652</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9926,7 +9926,7 @@
         <v>44501</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9999,7 +9999,7 @@
         <v>44600</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10072,7 +10072,7 @@
         <v>44852</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10145,7 +10145,7 @@
         <v>44839</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10218,7 +10218,7 @@
         <v>44615</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10296,7 +10296,7 @@
         <v>44622</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10369,7 +10369,7 @@
         <v>44524</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10442,7 +10442,7 @@
         <v>44712</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10515,7 +10515,7 @@
         <v>44743</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10588,7 +10588,7 @@
         <v>44722</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10661,7 +10661,7 @@
         <v>44532</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10739,7 +10739,7 @@
         <v>44470</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10812,7 +10812,7 @@
         <v>44593</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10885,7 +10885,7 @@
         <v>44652</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10958,7 +10958,7 @@
         <v>44699</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11031,7 +11031,7 @@
         <v>44820</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11109,7 +11109,7 @@
         <v>44847</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11182,7 +11182,7 @@
         <v>44743</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11255,7 +11255,7 @@
         <v>44488</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11333,7 +11333,7 @@
         <v>44589</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11406,7 +11406,7 @@
         <v>44551</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11484,7 +11484,7 @@
         <v>44600</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11557,7 +11557,7 @@
         <v>44725</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11630,7 +11630,7 @@
         <v>44600</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11703,7 +11703,7 @@
         <v>44655</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11776,7 +11776,7 @@
         <v>44530</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11849,7 +11849,7 @@
         <v>44788</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11922,7 +11922,7 @@
         <v>45335</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11995,7 +11995,7 @@
         <v>45190</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12068,7 +12068,7 @@
         <v>45204</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12146,7 +12146,7 @@
         <v>45048</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12219,7 +12219,7 @@
         <v>44739</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12292,7 +12292,7 @@
         <v>45211</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12365,7 +12365,7 @@
         <v>45719</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12438,7 +12438,7 @@
         <v>45187</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12511,7 +12511,7 @@
         <v>45719</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12584,7 +12584,7 @@
         <v>45348</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12657,7 +12657,7 @@
         <v>45069</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12730,7 +12730,7 @@
         <v>45069</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12803,7 +12803,7 @@
         <v>45397</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12876,7 +12876,7 @@
         <v>45219</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12949,7 +12949,7 @@
         <v>45411</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13022,7 +13022,7 @@
         <v>45422</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13095,7 +13095,7 @@
         <v>45229</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13168,7 +13168,7 @@
         <v>45385</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13241,7 +13241,7 @@
         <v>45126</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13314,7 +13314,7 @@
         <v>45376</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13387,7 +13387,7 @@
         <v>45461</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13460,7 +13460,7 @@
         <v>44861</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13533,7 +13533,7 @@
         <v>45400</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13606,7 +13606,7 @@
         <v>45615</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13679,7 +13679,7 @@
         <v>44907</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13752,7 +13752,7 @@
         <v>45474</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13825,7 +13825,7 @@
         <v>46024</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13898,7 +13898,7 @@
         <v>45161</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13976,7 +13976,7 @@
         <v>45273</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14054,7 +14054,7 @@
         <v>45477</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14127,7 +14127,7 @@
         <v>45514</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14200,7 +14200,7 @@
         <v>44951</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14273,7 +14273,7 @@
         <v>45161</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14351,7 +14351,7 @@
         <v>44519</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14424,7 +14424,7 @@
         <v>45887</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14497,7 +14497,7 @@
         <v>45887</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14570,7 +14570,7 @@
         <v>44530</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14643,7 +14643,7 @@
         <v>45749</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14716,7 +14716,7 @@
         <v>45800</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14789,7 +14789,7 @@
         <v>46036</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14862,7 +14862,7 @@
         <v>45537</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14935,7 +14935,7 @@
         <v>45189</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15008,7 +15008,7 @@
         <v>45189</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15081,7 +15081,7 @@
         <v>44977</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15154,7 +15154,7 @@
         <v>44550</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15227,7 +15227,7 @@
         <v>45099</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15300,7 +15300,7 @@
         <v>45070</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15373,7 +15373,7 @@
         <v>45700</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15446,7 +15446,7 @@
         <v>44896</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15519,7 +15519,7 @@
         <v>44900</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15592,7 +15592,7 @@
         <v>45537</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15665,7 +15665,7 @@
         <v>45562</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15738,7 +15738,7 @@
         <v>46044</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15811,7 +15811,7 @@
         <v>45741</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15884,7 +15884,7 @@
         <v>45475</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15957,7 +15957,7 @@
         <v>46049</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16030,7 +16030,7 @@
         <v>44893</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16103,7 +16103,7 @@
         <v>45681</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16176,7 +16176,7 @@
         <v>45665</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16249,7 +16249,7 @@
         <v>45587</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16322,7 +16322,7 @@
         <v>44683</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16395,7 +16395,7 @@
         <v>45908</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16468,7 +16468,7 @@
         <v>45909</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16541,7 +16541,7 @@
         <v>46055</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16614,7 +16614,7 @@
         <v>46055</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16687,7 +16687,7 @@
         <v>45349</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16760,7 +16760,7 @@
         <v>44995</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16833,7 +16833,7 @@
         <v>45155</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16906,7 +16906,7 @@
         <v>44897</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16979,7 +16979,7 @@
         <v>46058</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17052,7 +17052,7 @@
         <v>45915</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17125,7 +17125,7 @@
         <v>45915</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17198,7 +17198,7 @@
         <v>45915</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17271,7 +17271,7 @@
         <v>44949</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17344,7 +17344,7 @@
         <v>46062</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17417,7 +17417,7 @@
         <v>45349</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17490,7 +17490,7 @@
         <v>45007</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17563,7 +17563,7 @@
         <v>45921</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17636,7 +17636,7 @@
         <v>45400</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17709,7 +17709,7 @@
         <v>44580</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17782,7 +17782,7 @@
         <v>45804</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17855,7 +17855,7 @@
         <v>44958</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17928,7 +17928,7 @@
         <v>46069</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18006,7 +18006,7 @@
         <v>45022</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18079,7 +18079,7 @@
         <v>45022</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18152,7 +18152,7 @@
         <v>46071</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18230,7 +18230,7 @@
         <v>44839</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18303,7 +18303,7 @@
         <v>44955</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18376,7 +18376,7 @@
         <v>46071</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18454,7 +18454,7 @@
         <v>46072</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18527,7 +18527,7 @@
         <v>46072</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18600,7 +18600,7 @@
         <v>46071</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18678,7 +18678,7 @@
         <v>45098</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18751,7 +18751,7 @@
         <v>45211</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18824,7 +18824,7 @@
         <v>46078</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18897,7 +18897,7 @@
         <v>46079</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18970,7 +18970,7 @@
         <v>46079</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19043,7 +19043,7 @@
         <v>45040</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19116,7 +19116,7 @@
         <v>45931</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19189,7 +19189,7 @@
         <v>46085</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19262,7 +19262,7 @@
         <v>46085</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19335,7 +19335,7 @@
         <v>45166</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19408,7 +19408,7 @@
         <v>45252</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19481,7 +19481,7 @@
         <v>45392</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19554,7 +19554,7 @@
         <v>44995</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19627,7 +19627,7 @@
         <v>46085</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19700,7 +19700,7 @@
         <v>44973</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19778,7 +19778,7 @@
         <v>44594</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19851,7 +19851,7 @@
         <v>44524</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19924,7 +19924,7 @@
         <v>44978</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19997,7 +19997,7 @@
         <v>46090</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20070,7 +20070,7 @@
         <v>45707</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20143,7 +20143,7 @@
         <v>45938</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20216,7 +20216,7 @@
         <v>44953</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20289,7 +20289,7 @@
         <v>44690</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20362,7 +20362,7 @@
         <v>45021</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20435,7 +20435,7 @@
         <v>45021</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20508,7 +20508,7 @@
         <v>45938</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20581,7 +20581,7 @@
         <v>45938</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20654,7 +20654,7 @@
         <v>45938</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20727,7 +20727,7 @@
         <v>45048</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20800,7 +20800,7 @@
         <v>44978</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20873,7 +20873,7 @@
         <v>45769</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20946,7 +20946,7 @@
         <v>45182</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21019,7 +21019,7 @@
         <v>44748</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21092,7 +21092,7 @@
         <v>45062</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21165,7 +21165,7 @@
         <v>45191</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21238,7 +21238,7 @@
         <v>45095</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21311,7 +21311,7 @@
         <v>44777</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21384,7 +21384,7 @@
         <v>44960</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21457,7 +21457,7 @@
         <v>46106</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21530,7 +21530,7 @@
         <v>46107</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21603,7 +21603,7 @@
         <v>45362</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21676,7 +21676,7 @@
         <v>45009</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21749,7 +21749,7 @@
         <v>45009</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21822,7 +21822,7 @@
         <v>46106</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21895,7 +21895,7 @@
         <v>45953</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21968,7 +21968,7 @@
         <v>45422</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22041,7 +22041,7 @@
         <v>45559</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22114,7 +22114,7 @@
         <v>45901</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22187,7 +22187,7 @@
         <v>45084</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22260,7 +22260,7 @@
         <v>45355</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22333,7 +22333,7 @@
         <v>44700</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22406,7 +22406,7 @@
         <v>45230</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22479,7 +22479,7 @@
         <v>45960</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22552,7 +22552,7 @@
         <v>44965</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22625,7 +22625,7 @@
         <v>45629</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22698,7 +22698,7 @@
         <v>45964</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22771,7 +22771,7 @@
         <v>44852</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22844,7 +22844,7 @@
         <v>45258</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22917,7 +22917,7 @@
         <v>45964</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22990,7 +22990,7 @@
         <v>46120</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23063,7 +23063,7 @@
         <v>46120</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23136,7 +23136,7 @@
         <v>45574</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23209,7 +23209,7 @@
         <v>45009</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23282,7 +23282,7 @@
         <v>45009</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23355,7 +23355,7 @@
         <v>45107</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23428,7 +23428,7 @@
         <v>44922</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23501,7 +23501,7 @@
         <v>44743</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23574,7 +23574,7 @@
         <v>45967</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23647,7 +23647,7 @@
         <v>45967</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23720,7 +23720,7 @@
         <v>45971</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23793,7 +23793,7 @@
         <v>45092</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23866,7 +23866,7 @@
         <v>45813</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23939,7 +23939,7 @@
         <v>45229</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24012,7 +24012,7 @@
         <v>46127</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24085,7 +24085,7 @@
         <v>46127</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24158,7 +24158,7 @@
         <v>46127</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24231,7 +24231,7 @@
         <v>45515</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24304,7 +24304,7 @@
         <v>44473</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24377,7 +24377,7 @@
         <v>45079</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24450,7 +24450,7 @@
         <v>45979</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24523,7 +24523,7 @@
         <v>46134</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24596,7 +24596,7 @@
         <v>46133</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24669,7 +24669,7 @@
         <v>45981</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24742,7 +24742,7 @@
         <v>45645</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24815,7 +24815,7 @@
         <v>45632</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24888,7 +24888,7 @@
         <v>45401</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24961,7 +24961,7 @@
         <v>45614</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25034,7 +25034,7 @@
         <v>45551</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25112,7 +25112,7 @@
         <v>45819</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25185,7 +25185,7 @@
         <v>45113</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25258,7 +25258,7 @@
         <v>45818</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25331,7 +25331,7 @@
         <v>45972</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25404,7 +25404,7 @@
         <v>45596</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25477,7 +25477,7 @@
         <v>45102</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25550,7 +25550,7 @@
         <v>45966</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25623,7 +25623,7 @@
         <v>45102</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25696,7 +25696,7 @@
         <v>45901</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25769,7 +25769,7 @@
         <v>44729</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25842,7 +25842,7 @@
         <v>45392</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25915,7 +25915,7 @@
         <v>46006</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25988,7 +25988,7 @@
         <v>45818</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26061,7 +26061,7 @@
         <v>44993</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26134,7 +26134,7 @@
         <v>45989</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26207,7 +26207,7 @@
         <v>45994</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26280,7 +26280,7 @@
         <v>45905</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26353,7 +26353,7 @@
         <v>44781</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26426,7 +26426,7 @@
         <v>45148</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26499,7 +26499,7 @@
         <v>45986</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26572,7 +26572,7 @@
         <v>46043</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26645,7 +26645,7 @@
         <v>44984</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26718,7 +26718,7 @@
         <v>44761</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26791,7 +26791,7 @@
         <v>45113</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26864,7 +26864,7 @@
         <v>45742</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26937,7 +26937,7 @@
         <v>44683</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27010,7 +27010,7 @@
         <v>45524</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27083,7 +27083,7 @@
         <v>45445</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27156,7 +27156,7 @@
         <v>45021</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27229,7 +27229,7 @@
         <v>45067</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27302,7 +27302,7 @@
         <v>45966</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27375,7 +27375,7 @@
         <v>46140</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27448,7 +27448,7 @@
         <v>45976</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27521,7 +27521,7 @@
         <v>46139</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27594,7 +27594,7 @@
         <v>45716</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27667,7 +27667,7 @@
         <v>45028</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27740,7 +27740,7 @@
         <v>45772</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27813,7 +27813,7 @@
         <v>45200</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27886,7 +27886,7 @@
         <v>45740</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27959,7 +27959,7 @@
         <v>45915</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28037,7 +28037,7 @@
         <v>44518</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28110,7 +28110,7 @@
         <v>45222</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28183,7 +28183,7 @@
         <v>45211</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28256,7 +28256,7 @@
         <v>45825</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28329,7 +28329,7 @@
         <v>45826</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28402,7 +28402,7 @@
         <v>45826</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28475,7 +28475,7 @@
         <v>45826</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28548,7 +28548,7 @@
         <v>45826</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28621,7 +28621,7 @@
         <v>45826</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28694,7 +28694,7 @@
         <v>44879</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28767,7 +28767,7 @@
         <v>46055</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28840,7 +28840,7 @@
         <v>45049</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28913,7 +28913,7 @@
         <v>45909</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28986,7 +28986,7 @@
         <v>45574</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29059,7 +29059,7 @@
         <v>45826</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29132,7 +29132,7 @@
         <v>45938</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29205,7 +29205,7 @@
         <v>44690</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29278,7 +29278,7 @@
         <v>44524</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29351,7 +29351,7 @@
         <v>45415</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29424,7 +29424,7 @@
         <v>45068</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29502,7 +29502,7 @@
         <v>46142</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29575,7 +29575,7 @@
         <v>45755</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29648,7 +29648,7 @@
         <v>45976</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29721,7 +29721,7 @@
         <v>45111</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29794,7 +29794,7 @@
         <v>45772</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29867,7 +29867,7 @@
         <v>45049</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29940,7 +29940,7 @@
         <v>45832</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30013,7 +30013,7 @@
         <v>45084</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30086,7 +30086,7 @@
         <v>45099</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30159,7 +30159,7 @@
         <v>44593</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30232,7 +30232,7 @@
         <v>44816</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30305,7 +30305,7 @@
         <v>45789</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30378,7 +30378,7 @@
         <v>44608</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30451,7 +30451,7 @@
         <v>46069</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30529,7 +30529,7 @@
         <v>45349</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30602,7 +30602,7 @@
         <v>45707</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30675,7 +30675,7 @@
         <v>46155</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30748,7 +30748,7 @@
         <v>46160</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30821,7 +30821,7 @@
         <v>46160</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30894,7 +30894,7 @@
         <v>46160</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30967,7 +30967,7 @@
         <v>45740</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31040,7 +31040,7 @@
         <v>44759</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31113,7 +31113,7 @@
         <v>45835</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31186,7 +31186,7 @@
         <v>45317</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31259,7 +31259,7 @@
         <v>46162</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31332,7 +31332,7 @@
         <v>45211</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31405,7 +31405,7 @@
         <v>45211</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31478,7 +31478,7 @@
         <v>45902</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31551,7 +31551,7 @@
         <v>46162</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31624,7 +31624,7 @@
         <v>45126</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31697,7 +31697,7 @@
         <v>44959</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31770,7 +31770,7 @@
         <v>45805</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31843,7 +31843,7 @@
         <v>45621</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31916,7 +31916,7 @@
         <v>44977</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31989,7 +31989,7 @@
         <v>45327</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32062,7 +32062,7 @@
         <v>45845</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32135,7 +32135,7 @@
         <v>45727</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32208,7 +32208,7 @@
         <v>45126</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32281,7 +32281,7 @@
         <v>45772</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32354,7 +32354,7 @@
         <v>45775</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32427,7 +32427,7 @@
         <v>45849</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32500,7 +32500,7 @@
         <v>45716</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32573,7 +32573,7 @@
         <v>44728</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32646,7 +32646,7 @@
         <v>45093</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32719,7 +32719,7 @@
         <v>45851</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32792,7 +32792,7 @@
         <v>45851</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32865,7 +32865,7 @@
         <v>46169</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32938,7 +32938,7 @@
         <v>44852</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33011,7 +33011,7 @@
         <v>45121</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33084,7 +33084,7 @@
         <v>45341</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33157,7 +33157,7 @@
         <v>44953</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33230,7 +33230,7 @@
         <v>45323</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33303,7 +33303,7 @@
         <v>45857</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33376,7 +33376,7 @@
         <v>44953</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33449,7 +33449,7 @@
         <v>44572</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33522,7 +33522,7 @@
         <v>45531</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33595,7 +33595,7 @@
         <v>45600</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33668,7 +33668,7 @@
         <v>45923</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33741,7 +33741,7 @@
         <v>44593</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33814,7 +33814,7 @@
         <v>45750</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33887,7 +33887,7 @@
         <v>45769</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33960,7 +33960,7 @@
         <v>45126</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34033,7 +34033,7 @@
         <v>45863</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34106,7 +34106,7 @@
         <v>45790</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34179,7 +34179,7 @@
         <v>45003</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34252,7 +34252,7 @@
         <v>44984</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34325,7 +34325,7 @@
         <v>45019</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34398,7 +34398,7 @@
         <v>44980</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34471,7 +34471,7 @@
         <v>44840</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34549,7 +34549,7 @@
         <v>45475</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34622,7 +34622,7 @@
         <v>45132</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34695,7 +34695,7 @@
         <v>44600</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34768,7 +34768,7 @@
         <v>45037</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34841,7 +34841,7 @@
         <v>44982</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34914,7 +34914,7 @@
         <v>46183</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34987,7 +34987,7 @@
         <v>46182</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -35060,7 +35060,7 @@
         <v>46182</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -35133,7 +35133,7 @@
         <v>44993</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35206,7 +35206,7 @@
         <v>45433</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35279,7 +35279,7 @@
         <v>46185</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35352,7 +35352,7 @@
         <v>46185</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35425,7 +35425,7 @@
         <v>46185</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35498,7 +35498,7 @@
         <v>45146</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35571,7 +35571,7 @@
         <v>46188</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35644,7 +35644,7 @@
         <v>46188</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35717,7 +35717,7 @@
         <v>46188</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35790,7 +35790,7 @@
         <v>46189</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35863,7 +35863,7 @@
         <v>46188</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35936,7 +35936,7 @@
         <v>44494</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36009,7 +36009,7 @@
         <v>46190</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -36087,7 +36087,7 @@
         <v>45559</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36165,7 +36165,7 @@
         <v>45743</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36238,7 +36238,7 @@
         <v>46120</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36311,7 +36311,7 @@
         <v>46196</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36389,7 +36389,7 @@
         <v>46196</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36467,7 +36467,7 @@
         <v>46196</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36545,7 +36545,7 @@
         <v>45126</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36618,7 +36618,7 @@
         <v>45126</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36691,7 +36691,7 @@
         <v>45191</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36764,7 +36764,7 @@
         <v>45126</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36837,7 +36837,7 @@
         <v>46197</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36915,7 +36915,7 @@
         <v>46197</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36993,7 +36993,7 @@
         <v>45205</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37066,7 +37066,7 @@
         <v>46010</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -37139,7 +37139,7 @@
         <v>45167</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37212,7 +37212,7 @@
         <v>46196</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37285,7 +37285,7 @@
         <v>46197</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37363,7 +37363,7 @@
         <v>46198</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37436,7 +37436,7 @@
         <v>45644</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37509,7 +37509,7 @@
         <v>45881</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37582,7 +37582,7 @@
         <v>46202</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37655,7 +37655,7 @@
         <v>45084</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37728,7 +37728,7 @@
         <v>45622</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37801,7 +37801,7 @@
         <v>45159</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37874,7 +37874,7 @@
         <v>45573</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37947,7 +37947,7 @@
         <v>45615</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -38020,7 +38020,7 @@
         <v>46205</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -38098,7 +38098,7 @@
         <v>45225</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -38171,7 +38171,7 @@
         <v>45327</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38244,7 +38244,7 @@
         <v>44783</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38317,7 +38317,7 @@
         <v>45091</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38390,7 +38390,7 @@
         <v>44652</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38463,7 +38463,7 @@
         <v>46127</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38541,7 +38541,7 @@
         <v>45230</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38614,7 +38614,7 @@
         <v>46251</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38687,7 +38687,7 @@
         <v>45232</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38760,7 +38760,7 @@
         <v>45182</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38833,7 +38833,7 @@
         <v>46211</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38906,7 +38906,7 @@
         <v>46253</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38979,7 +38979,7 @@
         <v>46253</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -39052,7 +39052,7 @@
         <v>45392</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -39125,7 +39125,7 @@
         <v>44699</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -39198,7 +39198,7 @@
         <v>45148</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39271,7 +39271,7 @@
         <v>45531</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39344,7 +39344,7 @@
         <v>45126</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39417,7 +39417,7 @@
         <v>45434</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39490,7 +39490,7 @@
         <v>46212</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39563,7 +39563,7 @@
         <v>46212</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39636,7 +39636,7 @@
         <v>44619</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39709,7 +39709,7 @@
         <v>46213</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39782,7 +39782,7 @@
         <v>46230</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39855,7 +39855,7 @@
         <v>46255</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39933,7 +39933,7 @@
         <v>45408</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -40006,7 +40006,7 @@
         <v>46255</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -40084,7 +40084,7 @@
         <v>45394</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -40157,7 +40157,7 @@
         <v>46259</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40230,7 +40230,7 @@
         <v>46255</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40308,7 +40308,7 @@
         <v>46255</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40386,7 +40386,7 @@
         <v>46255</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40464,7 +40464,7 @@
         <v>46255</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40542,7 +40542,7 @@
         <v>46255</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40620,7 +40620,7 @@
         <v>44728</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40693,7 +40693,7 @@
         <v>46255</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40766,7 +40766,7 @@
         <v>45188</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40844,7 +40844,7 @@
         <v>45188</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40922,7 +40922,7 @@
         <v>45400</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40995,7 +40995,7 @@
         <v>45107</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -41068,7 +41068,7 @@
         <v>44673</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -41141,7 +41141,7 @@
         <v>45164</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -41214,7 +41214,7 @@
         <v>44749</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41287,7 +41287,7 @@
         <v>44726</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41360,7 +41360,7 @@
         <v>44802</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41433,7 +41433,7 @@
         <v>45258</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41506,7 +41506,7 @@
         <v>45258</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41579,7 +41579,7 @@
         <v>45735</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41652,7 +41652,7 @@
         <v>45475</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41725,7 +41725,7 @@
         <v>45716</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41798,7 +41798,7 @@
         <v>46268</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41871,7 +41871,7 @@
         <v>44799</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41944,7 +41944,7 @@
         <v>44827</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -42017,7 +42017,7 @@
         <v>45301</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -42090,7 +42090,7 @@
         <v>46272</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -42163,7 +42163,7 @@
         <v>45309</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -42236,7 +42236,7 @@
         <v>46271</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42309,7 +42309,7 @@
         <v>45126</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42382,7 +42382,7 @@
         <v>45307</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42455,7 +42455,7 @@
         <v>45716</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42528,7 +42528,7 @@
         <v>45190</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42601,7 +42601,7 @@
         <v>45310</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42674,7 +42674,7 @@
         <v>44851</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42747,7 +42747,7 @@
         <v>46188</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42820,7 +42820,7 @@
         <v>46273</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42893,7 +42893,7 @@
         <v>45089</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42966,7 +42966,7 @@
         <v>44893</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -43039,7 +43039,7 @@
         <v>46134</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -43112,7 +43112,7 @@
         <v>45159</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -43185,7 +43185,7 @@
         <v>44769</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43258,7 +43258,7 @@
         <v>46275</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43331,7 +43331,7 @@
         <v>46279</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43409,7 +43409,7 @@
         <v>45187</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43482,7 +43482,7 @@
         <v>46279</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43560,7 +43560,7 @@
         <v>46279</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43638,7 +43638,7 @@
         <v>46279</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43716,7 +43716,7 @@
         <v>45401</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43789,7 +43789,7 @@
         <v>44851</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43862,7 +43862,7 @@
         <v>46279</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43940,7 +43940,7 @@
         <v>46279</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -44013,7 +44013,7 @@
         <v>45196</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -44086,7 +44086,7 @@
         <v>46279</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -44164,7 +44164,7 @@
         <v>45392</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -44237,7 +44237,7 @@
         <v>46279</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44315,7 +44315,7 @@
         <v>46279</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44393,7 +44393,7 @@
         <v>44897</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44466,7 +44466,7 @@
         <v>46279</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44544,7 +44544,7 @@
         <v>46279</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44622,7 +44622,7 @@
         <v>45323</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44695,7 +44695,7 @@
         <v>46282</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44768,7 +44768,7 @@
         <v>44487</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44841,7 +44841,7 @@
         <v>45323</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44914,7 +44914,7 @@
         <v>45637</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44987,7 +44987,7 @@
         <v>45466</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -45060,7 +45060,7 @@
         <v>45727</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -45133,7 +45133,7 @@
         <v>45327</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -45206,7 +45206,7 @@
         <v>44488</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -45284,7 +45284,7 @@
         <v>45296</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45357,7 +45357,7 @@
         <v>46286</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45430,7 +45430,7 @@
         <v>45706</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45503,7 +45503,7 @@
         <v>45727</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45576,7 +45576,7 @@
         <v>44530</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45649,7 +45649,7 @@
         <v>45926</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45722,7 +45722,7 @@
         <v>44586</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45795,7 +45795,7 @@
         <v>46288</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45868,7 +45868,7 @@
         <v>44589</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45941,7 +45941,7 @@
         <v>46244</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -46014,7 +46014,7 @@
         <v>46288</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -46087,7 +46087,7 @@
         <v>46245</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -46160,7 +46160,7 @@
         <v>44507</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -46233,7 +46233,7 @@
         <v>44938</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -46306,7 +46306,7 @@
         <v>44979</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -46379,7 +46379,7 @@
         <v>45606</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -46452,7 +46452,7 @@
         <v>45370</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46525,7 +46525,7 @@
         <v>45091</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46598,7 +46598,7 @@
         <v>45149</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -46671,7 +46671,7 @@
         <v>45191</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -46744,7 +46744,7 @@
         <v>45155</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46817,7 +46817,7 @@
         <v>45251</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46890,7 +46890,7 @@
         <v>44930</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46963,7 +46963,7 @@
         <v>46290</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -47036,7 +47036,7 @@
         <v>45181</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -47109,7 +47109,7 @@
         <v>44728</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -47182,7 +47182,7 @@
         <v>46290</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -47255,7 +47255,7 @@
         <v>45425</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -47328,7 +47328,7 @@
         <v>45036</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -47401,7 +47401,7 @@
         <v>44834</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -47474,7 +47474,7 @@
         <v>46290</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -47547,7 +47547,7 @@
         <v>45051</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -47620,7 +47620,7 @@
         <v>45051</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -47693,7 +47693,7 @@
         <v>45590</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -47766,7 +47766,7 @@
         <v>44808</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47839,7 +47839,7 @@
         <v>44944</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47912,7 +47912,7 @@
         <v>45048</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47985,7 +47985,7 @@
         <v>44487</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -48063,7 +48063,7 @@
         <v>45514</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -48136,7 +48136,7 @@
         <v>45514</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -48209,7 +48209,7 @@
         <v>45076</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -48282,7 +48282,7 @@
         <v>45392</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -48355,7 +48355,7 @@
         <v>45217</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -48428,7 +48428,7 @@
         <v>45688</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -48501,7 +48501,7 @@
         <v>45740</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -48574,7 +48574,7 @@
         <v>45180</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -48647,7 +48647,7 @@
         <v>45668</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -48720,7 +48720,7 @@
         <v>45349</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -48793,7 +48793,7 @@
         <v>45349</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -48866,7 +48866,7 @@
         <v>45641</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -48939,7 +48939,7 @@
         <v>44791</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -49012,7 +49012,7 @@
         <v>45310</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -49085,7 +49085,7 @@
         <v>44911</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -49158,7 +49158,7 @@
         <v>45394</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -49231,7 +49231,7 @@
         <v>44900</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -49304,7 +49304,7 @@
         <v>45189</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -49377,7 +49377,7 @@
         <v>45113</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -49450,7 +49450,7 @@
         <v>45606</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -49523,7 +49523,7 @@
         <v>45007</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -49596,7 +49596,7 @@
         <v>45164</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -49669,7 +49669,7 @@
         <v>45211</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -49742,7 +49742,7 @@
         <v>45126</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -49815,7 +49815,7 @@
         <v>44698</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -49888,7 +49888,7 @@
         <v>45317</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -49961,7 +49961,7 @@
         <v>45373</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -50034,7 +50034,7 @@
         <v>45204</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -50112,7 +50112,7 @@
         <v>45335</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -50185,7 +50185,7 @@
         <v>45369</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -50258,7 +50258,7 @@
         <v>45273</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -50336,7 +50336,7 @@
         <v>45204</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -50414,7 +50414,7 @@
         <v>45595</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -50487,7 +50487,7 @@
         <v>45433</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -50560,7 +50560,7 @@
         <v>45237</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -50633,7 +50633,7 @@
         <v>44531</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -50706,7 +50706,7 @@
         <v>44504</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -50779,7 +50779,7 @@
         <v>45103</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -50852,7 +50852,7 @@
         <v>45474</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -50925,7 +50925,7 @@
         <v>45341</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -50998,7 +50998,7 @@
         <v>45665</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -51071,7 +51071,7 @@
         <v>45126</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -51144,7 +51144,7 @@
         <v>45202</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -51217,7 +51217,7 @@
         <v>45281</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -51290,7 +51290,7 @@
         <v>45155</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -51363,7 +51363,7 @@
         <v>44897</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -51436,7 +51436,7 @@
         <v>45716</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -51509,7 +51509,7 @@
         <v>44519</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -51582,7 +51582,7 @@
         <v>45561</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -51660,7 +51660,7 @@
         <v>44979</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -51733,7 +51733,7 @@
         <v>45551</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -51806,7 +51806,7 @@
         <v>45523</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -51879,7 +51879,7 @@
         <v>45215</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -51952,7 +51952,7 @@
         <v>44949</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -52025,7 +52025,7 @@
         <v>45684</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -52098,7 +52098,7 @@
         <v>45624</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -52171,7 +52171,7 @@
         <v>45534</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -52244,7 +52244,7 @@
         <v>45484</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -52317,7 +52317,7 @@
         <v>45351</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -52390,7 +52390,7 @@
         <v>45107</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -52463,7 +52463,7 @@
         <v>45317</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -52536,7 +52536,7 @@
         <v>45415</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -52609,7 +52609,7 @@
         <v>45638</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -52682,7 +52682,7 @@
         <v>45610</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -52755,7 +52755,7 @@
         <v>45582</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -52828,7 +52828,7 @@
         <v>45565</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -52901,7 +52901,7 @@
         <v>45445</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -52974,7 +52974,7 @@
         <v>45548</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -53047,7 +53047,7 @@
         <v>45609</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -53120,7 +53120,7 @@
         <v>45688</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -53193,7 +53193,7 @@
         <v>45484</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -53266,7 +53266,7 @@
         <v>45386</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -53339,7 +53339,7 @@
         <v>45775</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -53412,7 +53412,7 @@
         <v>45566</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -53485,7 +53485,7 @@
         <v>45481</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -53558,7 +53558,7 @@
         <v>45400</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -53631,7 +53631,7 @@
         <v>45455</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -53704,7 +53704,7 @@
         <v>44476</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -53777,7 +53777,7 @@
         <v>45191</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -53850,7 +53850,7 @@
         <v>44959</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -53923,7 +53923,7 @@
         <v>45194</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -53996,7 +53996,7 @@
         <v>45377</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -54069,7 +54069,7 @@
         <v>45387</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -54142,7 +54142,7 @@
         <v>44903</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -54215,7 +54215,7 @@
         <v>44900</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -54288,7 +54288,7 @@
         <v>44852</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -54361,7 +54361,7 @@
         <v>45200</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -54434,7 +54434,7 @@
         <v>45534</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -54507,7 +54507,7 @@
         <v>45191</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -54580,7 +54580,7 @@
         <v>45386</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -54653,7 +54653,7 @@
         <v>45287</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -54726,7 +54726,7 @@
         <v>45386</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -54799,7 +54799,7 @@
         <v>45386</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -54872,7 +54872,7 @@
         <v>45386</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -54945,7 +54945,7 @@
         <v>45387</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -55018,7 +55018,7 @@
         <v>44519</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -55091,7 +55091,7 @@
         <v>45534</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -55164,7 +55164,7 @@
         <v>45377</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -55237,7 +55237,7 @@
         <v>44928</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -55310,7 +55310,7 @@
         <v>45377</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -55383,7 +55383,7 @@
         <v>44519</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -55456,7 +55456,7 @@
         <v>45200</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -55529,7 +55529,7 @@
         <v>44900</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -55602,7 +55602,7 @@
         <v>45330</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -55675,7 +55675,7 @@
         <v>44959</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -55748,7 +55748,7 @@
         <v>45348</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -55821,7 +55821,7 @@
         <v>45813</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -55894,7 +55894,7 @@
         <v>45813</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -55967,7 +55967,7 @@
         <v>45849</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -56040,7 +56040,7 @@
         <v>45898</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -56113,7 +56113,7 @@
         <v>45935</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -56186,7 +56186,7 @@
         <v>45978</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -56259,7 +56259,7 @@
         <v>46034</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -56332,7 +56332,7 @@
         <v>46049</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -56405,7 +56405,7 @@
         <v>46049</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -56478,7 +56478,7 @@
         <v>46065</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -56551,7 +56551,7 @@
         <v>46092</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -56624,7 +56624,7 @@
         <v>46062</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -56697,7 +56697,7 @@
         <v>46119</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -56770,7 +56770,7 @@
         <v>46119</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -56843,7 +56843,7 @@
         <v>46127</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -56916,7 +56916,7 @@
         <v>46167</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -56989,7 +56989,7 @@
         <v>46156</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -57062,7 +57062,7 @@
         <v>46183</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -57135,7 +57135,7 @@
         <v>46191</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -57208,7 +57208,7 @@
         <v>46276</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -57286,7 +57286,7 @@
         <v>46286</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -57359,7 +57359,7 @@
         <v>46283</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>

--- a/Översikt EMMABODA.xlsx
+++ b/Översikt EMMABODA.xlsx
@@ -601,7 +601,7 @@
         <v>45534</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>45440</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -830,7 +830,7 @@
         <v>45387</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>45202</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
         <v>45030</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>44480</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1276,7 +1276,7 @@
         <v>45616</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>44706</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>44811</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>45330</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1713,7 +1713,7 @@
         <v>45359</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         <v>46136</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1931,7 +1931,7 @@
         <v>45369</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
         <v>45086</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>44937</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2257,7 +2257,7 @@
         <v>46062</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2367,7 +2367,7 @@
         <v>46069</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         <v>46214</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2579,7 +2579,7 @@
         <v>44762</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         <v>44895</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2789,7 +2789,7 @@
         <v>45166</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2894,7 +2894,7 @@
         <v>44966</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2999,7 +2999,7 @@
         <v>45797</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
         <v>44570</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3213,7 +3213,7 @@
         <v>44984</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3318,7 +3318,7 @@
         <v>45953</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3427,7 +3427,7 @@
         <v>45196</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3532,7 +3532,7 @@
         <v>46135</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3642,7 +3642,7 @@
         <v>45967</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3747,7 +3747,7 @@
         <v>45763</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3856,7 +3856,7 @@
         <v>45104</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3961,7 +3961,7 @@
         <v>45335</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4066,7 +4066,7 @@
         <v>45161</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4176,7 +4176,7 @@
         <v>45068</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4286,7 +4286,7 @@
         <v>44771</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4395,7 +4395,7 @@
         <v>46213</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4500,7 +4500,7 @@
         <v>46213</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4605,7 +4605,7 @@
         <v>46218</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4710,7 +4710,7 @@
         <v>46282</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4815,7 +4815,7 @@
         <v>46055</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4920,7 +4920,7 @@
         <v>45229</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5029,7 +5029,7 @@
         <v>45107</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5138,7 +5138,7 @@
         <v>44495</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5247,7 +5247,7 @@
         <v>46253</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5352,7 +5352,7 @@
         <v>45092</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5457,7 +5457,7 @@
         <v>44488</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5567,7 +5567,7 @@
         <v>45509</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5672,7 +5672,7 @@
         <v>45387</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5781,7 +5781,7 @@
         <v>44588</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5886,7 +5886,7 @@
         <v>45611</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5995,7 +5995,7 @@
         <v>45330</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6104,7 +6104,7 @@
         <v>44852</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6213,7 +6213,7 @@
         <v>45442</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6318,7 +6318,7 @@
         <v>45153</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6423,7 +6423,7 @@
         <v>45386</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6528,7 +6528,7 @@
         <v>45685</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6637,7 +6637,7 @@
         <v>45813</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6746,7 +6746,7 @@
         <v>46275</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6855,7 +6855,7 @@
         <v>44530</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6928,7 +6928,7 @@
         <v>44764</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7001,7 +7001,7 @@
         <v>44530</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7074,7 +7074,7 @@
         <v>44496</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         <v>44488</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7220,7 +7220,7 @@
         <v>44529</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7293,7 +7293,7 @@
         <v>44490</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7366,7 +7366,7 @@
         <v>44601</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7439,7 +7439,7 @@
         <v>44600</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7512,7 +7512,7 @@
         <v>44496</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7585,7 +7585,7 @@
         <v>44507</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7658,7 +7658,7 @@
         <v>44507</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7731,7 +7731,7 @@
         <v>44507</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7804,7 +7804,7 @@
         <v>44728</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7877,7 +7877,7 @@
         <v>44599</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7950,7 +7950,7 @@
         <v>44691</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8023,7 +8023,7 @@
         <v>44628</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8096,7 +8096,7 @@
         <v>44504</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8169,7 +8169,7 @@
         <v>44515</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8242,7 +8242,7 @@
         <v>44851</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8315,7 +8315,7 @@
         <v>44860</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8388,7 +8388,7 @@
         <v>44648</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8461,7 +8461,7 @@
         <v>44523</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8534,7 +8534,7 @@
         <v>44628</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8607,7 +8607,7 @@
         <v>44788</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8680,7 +8680,7 @@
         <v>44627</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8753,7 +8753,7 @@
         <v>44498</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8826,7 +8826,7 @@
         <v>44768</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8899,7 +8899,7 @@
         <v>44851</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8972,7 +8972,7 @@
         <v>44529</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9045,7 +9045,7 @@
         <v>44813</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9118,7 +9118,7 @@
         <v>44809</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         <v>44771</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9264,7 +9264,7 @@
         <v>44587</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9337,7 +9337,7 @@
         <v>44496</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9410,7 +9410,7 @@
         <v>44507</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9483,7 +9483,7 @@
         <v>44507</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9556,7 +9556,7 @@
         <v>44487</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9634,7 +9634,7 @@
         <v>44652</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9707,7 +9707,7 @@
         <v>44600</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9780,7 +9780,7 @@
         <v>44628</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9853,7 +9853,7 @@
         <v>44600</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9926,7 +9926,7 @@
         <v>44501</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9999,7 +9999,7 @@
         <v>44852</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10072,7 +10072,7 @@
         <v>44839</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10145,7 +10145,7 @@
         <v>44615</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10223,7 +10223,7 @@
         <v>44622</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10296,7 +10296,7 @@
         <v>44524</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10369,7 +10369,7 @@
         <v>44712</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10442,7 +10442,7 @@
         <v>44743</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10515,7 +10515,7 @@
         <v>44722</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10588,7 +10588,7 @@
         <v>44532</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10666,7 +10666,7 @@
         <v>44593</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10739,7 +10739,7 @@
         <v>44652</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10812,7 +10812,7 @@
         <v>44699</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10885,7 +10885,7 @@
         <v>44820</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10963,7 +10963,7 @@
         <v>44847</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11036,7 +11036,7 @@
         <v>44743</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11109,7 +11109,7 @@
         <v>44488</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11187,7 +11187,7 @@
         <v>44589</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11260,7 +11260,7 @@
         <v>44551</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11338,7 +11338,7 @@
         <v>44600</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11411,7 +11411,7 @@
         <v>44600</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11484,7 +11484,7 @@
         <v>44725</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11557,7 +11557,7 @@
         <v>44655</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11630,7 +11630,7 @@
         <v>44530</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11703,7 +11703,7 @@
         <v>44980</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11776,7 +11776,7 @@
         <v>44788</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11849,7 +11849,7 @@
         <v>45397</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11922,7 +11922,7 @@
         <v>45445</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11995,7 +11995,7 @@
         <v>44953</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12068,7 +12068,7 @@
         <v>45089</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12141,7 +12141,7 @@
         <v>45251</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12214,7 +12214,7 @@
         <v>44690</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12287,7 +12287,7 @@
         <v>45079</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12360,7 +12360,7 @@
         <v>45211</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12433,7 +12433,7 @@
         <v>45411</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12506,7 +12506,7 @@
         <v>44487</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12579,7 +12579,7 @@
         <v>45590</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12652,7 +12652,7 @@
         <v>45191</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12725,7 +12725,7 @@
         <v>45126</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12798,7 +12798,7 @@
         <v>45099</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12871,7 +12871,7 @@
         <v>45040</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12944,7 +12944,7 @@
         <v>45606</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13017,7 +13017,7 @@
         <v>45022</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13090,7 +13090,7 @@
         <v>45022</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13163,7 +13163,7 @@
         <v>45392</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13236,7 +13236,7 @@
         <v>44652</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13309,7 +13309,7 @@
         <v>45159</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13382,7 +13382,7 @@
         <v>45219</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13455,7 +13455,7 @@
         <v>45237</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13528,7 +13528,7 @@
         <v>45187</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13601,7 +13601,7 @@
         <v>45637</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13674,7 +13674,7 @@
         <v>45049</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13747,7 +13747,7 @@
         <v>45775</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13820,7 +13820,7 @@
         <v>45230</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13893,7 +13893,7 @@
         <v>45481</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13966,7 +13966,7 @@
         <v>45566</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14039,7 +14039,7 @@
         <v>45582</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14112,7 +14112,7 @@
         <v>45609</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14185,7 +14185,7 @@
         <v>45484</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14258,7 +14258,7 @@
         <v>45688</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14331,7 +14331,7 @@
         <v>45610</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14404,7 +14404,7 @@
         <v>44572</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14477,7 +14477,7 @@
         <v>45392</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14550,7 +14550,7 @@
         <v>45019</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14623,7 +14623,7 @@
         <v>44973</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14701,7 +14701,7 @@
         <v>45474</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14774,7 +14774,7 @@
         <v>45341</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14847,7 +14847,7 @@
         <v>45400</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14920,7 +14920,7 @@
         <v>44519</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14993,7 +14993,7 @@
         <v>45615</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15066,7 +15066,7 @@
         <v>45749</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15139,7 +15139,7 @@
         <v>45559</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15212,7 +15212,7 @@
         <v>45309</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15285,7 +15285,7 @@
         <v>45211</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15358,7 +15358,7 @@
         <v>45211</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15431,7 +15431,7 @@
         <v>44683</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15504,7 +15504,7 @@
         <v>45615</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15577,7 +15577,7 @@
         <v>45665</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15650,7 +15650,7 @@
         <v>44978</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15723,7 +15723,7 @@
         <v>44978</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15796,7 +15796,7 @@
         <v>46024</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15869,7 +15869,7 @@
         <v>45700</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15942,7 +15942,7 @@
         <v>45148</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16015,7 +16015,7 @@
         <v>45164</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16088,7 +16088,7 @@
         <v>45166</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16161,7 +16161,7 @@
         <v>44896</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16234,7 +16234,7 @@
         <v>45475</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16307,7 +16307,7 @@
         <v>44739</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16380,7 +16380,7 @@
         <v>45394</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16453,7 +16453,7 @@
         <v>45606</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16526,7 +16526,7 @@
         <v>44949</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16599,7 +16599,7 @@
         <v>45741</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16672,7 +16672,7 @@
         <v>45355</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16745,7 +16745,7 @@
         <v>45188</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16823,7 +16823,7 @@
         <v>45422</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16896,7 +16896,7 @@
         <v>46036</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16969,7 +16969,7 @@
         <v>45369</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17042,7 +17042,7 @@
         <v>44982</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17115,7 +17115,7 @@
         <v>44834</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17188,7 +17188,7 @@
         <v>45681</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17261,7 +17261,7 @@
         <v>45909</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17334,7 +17334,7 @@
         <v>45908</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17407,7 +17407,7 @@
         <v>44791</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17480,7 +17480,7 @@
         <v>45455</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17553,7 +17553,7 @@
         <v>46044</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17626,7 +17626,7 @@
         <v>45915</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17699,7 +17699,7 @@
         <v>45915</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17772,7 +17772,7 @@
         <v>45915</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17845,7 +17845,7 @@
         <v>46049</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17918,7 +17918,7 @@
         <v>45665</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17991,7 +17991,7 @@
         <v>44977</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18064,7 +18064,7 @@
         <v>45537</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18137,7 +18137,7 @@
         <v>44958</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18210,7 +18210,7 @@
         <v>45800</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18283,7 +18283,7 @@
         <v>44783</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18356,7 +18356,7 @@
         <v>45804</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18429,7 +18429,7 @@
         <v>46055</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18502,7 +18502,7 @@
         <v>45349</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18575,7 +18575,7 @@
         <v>45921</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18648,7 +18648,7 @@
         <v>44487</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18726,7 +18726,7 @@
         <v>44593</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18799,7 +18799,7 @@
         <v>45021</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18872,7 +18872,7 @@
         <v>44600</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18945,7 +18945,7 @@
         <v>45415</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19018,7 +19018,7 @@
         <v>46058</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19091,7 +19091,7 @@
         <v>46062</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19164,7 +19164,7 @@
         <v>45475</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19237,7 +19237,7 @@
         <v>45323</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19310,7 +19310,7 @@
         <v>45931</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19383,7 +19383,7 @@
         <v>45740</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19456,7 +19456,7 @@
         <v>45475</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19529,7 +19529,7 @@
         <v>45735</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19602,7 +19602,7 @@
         <v>45155</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19675,7 +19675,7 @@
         <v>46069</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19753,7 +19753,7 @@
         <v>45037</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19826,7 +19826,7 @@
         <v>44690</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19899,7 +19899,7 @@
         <v>45938</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19972,7 +19972,7 @@
         <v>46071</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20050,7 +20050,7 @@
         <v>45938</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20123,7 +20123,7 @@
         <v>45938</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20196,7 +20196,7 @@
         <v>45641</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20269,7 +20269,7 @@
         <v>44593</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20342,7 +20342,7 @@
         <v>46071</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20420,7 +20420,7 @@
         <v>45938</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20493,7 +20493,7 @@
         <v>44504</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20566,7 +20566,7 @@
         <v>46072</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20639,7 +20639,7 @@
         <v>46072</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20712,7 +20712,7 @@
         <v>46071</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20790,7 +20790,7 @@
         <v>45126</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20863,7 +20863,7 @@
         <v>45126</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20936,7 +20936,7 @@
         <v>46078</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21009,7 +21009,7 @@
         <v>44799</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21082,7 +21082,7 @@
         <v>45155</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21155,7 +21155,7 @@
         <v>45225</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21228,7 +21228,7 @@
         <v>46079</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21301,7 +21301,7 @@
         <v>46079</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21374,7 +21374,7 @@
         <v>45901</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21447,7 +21447,7 @@
         <v>45953</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21520,7 +21520,7 @@
         <v>44852</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21593,7 +21593,7 @@
         <v>45190</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21666,7 +21666,7 @@
         <v>45433</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21739,7 +21739,7 @@
         <v>45067</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21812,7 +21812,7 @@
         <v>44953</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21885,7 +21885,7 @@
         <v>45107</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21958,7 +21958,7 @@
         <v>46085</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22031,7 +22031,7 @@
         <v>44729</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22104,7 +22104,7 @@
         <v>46085</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22177,7 +22177,7 @@
         <v>46085</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22250,7 +22250,7 @@
         <v>45813</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22323,7 +22323,7 @@
         <v>44984</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22396,7 +22396,7 @@
         <v>46090</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22469,7 +22469,7 @@
         <v>45960</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22542,7 +22542,7 @@
         <v>45964</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22615,7 +22615,7 @@
         <v>44507</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22688,7 +22688,7 @@
         <v>45964</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22761,7 +22761,7 @@
         <v>44473</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22834,7 +22834,7 @@
         <v>45189</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22907,7 +22907,7 @@
         <v>45048</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22980,7 +22980,7 @@
         <v>45191</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23053,7 +23053,7 @@
         <v>45967</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23126,7 +23126,7 @@
         <v>45967</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23199,7 +23199,7 @@
         <v>44619</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23272,7 +23272,7 @@
         <v>45434</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23345,7 +23345,7 @@
         <v>45036</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23418,7 +23418,7 @@
         <v>45971</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23491,7 +23491,7 @@
         <v>44907</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23564,7 +23564,7 @@
         <v>45273</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23642,7 +23642,7 @@
         <v>45211</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23715,7 +23715,7 @@
         <v>45229</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23788,7 +23788,7 @@
         <v>45132</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23861,7 +23861,7 @@
         <v>45084</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23934,7 +23934,7 @@
         <v>45979</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24007,7 +24007,7 @@
         <v>44519</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24080,7 +24080,7 @@
         <v>46107</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24153,7 +24153,7 @@
         <v>45981</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24226,7 +24226,7 @@
         <v>45102</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24299,7 +24299,7 @@
         <v>45102</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24372,7 +24372,7 @@
         <v>44839</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24445,7 +24445,7 @@
         <v>45317</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24518,7 +24518,7 @@
         <v>46120</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24591,7 +24591,7 @@
         <v>46120</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24664,7 +24664,7 @@
         <v>45989</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24737,7 +24737,7 @@
         <v>45825</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24810,7 +24810,7 @@
         <v>45826</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24883,7 +24883,7 @@
         <v>44979</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24956,7 +24956,7 @@
         <v>45716</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25029,7 +25029,7 @@
         <v>45826</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25102,7 +25102,7 @@
         <v>45091</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25175,7 +25175,7 @@
         <v>45986</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25248,7 +25248,7 @@
         <v>45994</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25321,7 +25321,7 @@
         <v>45716</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25394,7 +25394,7 @@
         <v>45826</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25467,7 +25467,7 @@
         <v>45826</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25540,7 +25540,7 @@
         <v>46127</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25613,7 +25613,7 @@
         <v>45826</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25686,7 +25686,7 @@
         <v>45826</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25759,7 +25759,7 @@
         <v>46127</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25832,7 +25832,7 @@
         <v>46127</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25905,7 +25905,7 @@
         <v>45121</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25978,7 +25978,7 @@
         <v>45191</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26051,7 +26051,7 @@
         <v>46133</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26124,7 +26124,7 @@
         <v>44979</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26197,7 +26197,7 @@
         <v>45113</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26270,7 +26270,7 @@
         <v>45113</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26343,7 +26343,7 @@
         <v>45167</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26416,7 +26416,7 @@
         <v>46134</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26489,7 +26489,7 @@
         <v>45832</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26562,7 +26562,7 @@
         <v>45069</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26635,7 +26635,7 @@
         <v>45069</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26708,7 +26708,7 @@
         <v>45401</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26781,7 +26781,7 @@
         <v>45348</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26854,7 +26854,7 @@
         <v>45835</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26927,7 +26927,7 @@
         <v>44993</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27000,7 +27000,7 @@
         <v>45408</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27073,7 +27073,7 @@
         <v>45645</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27146,7 +27146,7 @@
         <v>45376</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27219,7 +27219,7 @@
         <v>44683</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27292,7 +27292,7 @@
         <v>45629</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27365,7 +27365,7 @@
         <v>46139</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27438,7 +27438,7 @@
         <v>45392</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27511,7 +27511,7 @@
         <v>45966</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27584,7 +27584,7 @@
         <v>45905</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27657,7 +27657,7 @@
         <v>45461</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27730,7 +27730,7 @@
         <v>45349</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27803,7 +27803,7 @@
         <v>45901</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27876,7 +27876,7 @@
         <v>45805</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27949,7 +27949,7 @@
         <v>45909</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28022,7 +28022,7 @@
         <v>45845</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28095,7 +28095,7 @@
         <v>45621</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28168,7 +28168,7 @@
         <v>44524</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28241,7 +28241,7 @@
         <v>45091</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28314,7 +28314,7 @@
         <v>45551</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28392,7 +28392,7 @@
         <v>45727</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28465,7 +28465,7 @@
         <v>45401</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28538,7 +28538,7 @@
         <v>44897</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28611,7 +28611,7 @@
         <v>45632</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28684,7 +28684,7 @@
         <v>45113</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28757,7 +28757,7 @@
         <v>45849</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28830,7 +28830,7 @@
         <v>45574</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28903,7 +28903,7 @@
         <v>45335</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28976,7 +28976,7 @@
         <v>45335</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29049,7 +29049,7 @@
         <v>45775</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29122,7 +29122,7 @@
         <v>45716</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29195,7 +29195,7 @@
         <v>45851</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29268,7 +29268,7 @@
         <v>45851</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29341,7 +29341,7 @@
         <v>45200</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29414,7 +29414,7 @@
         <v>45755</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29487,7 +29487,7 @@
         <v>45772</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29560,7 +29560,7 @@
         <v>45070</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29633,7 +29633,7 @@
         <v>45818</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29706,7 +29706,7 @@
         <v>45915</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29784,7 +29784,7 @@
         <v>45222</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29857,7 +29857,7 @@
         <v>44944</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29930,7 +29930,7 @@
         <v>45857</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30003,7 +30003,7 @@
         <v>45819</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30076,7 +30076,7 @@
         <v>45524</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30149,7 +30149,7 @@
         <v>45818</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30222,7 +30222,7 @@
         <v>45370</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30295,7 +30295,7 @@
         <v>45400</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30368,7 +30368,7 @@
         <v>45021</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30441,7 +30441,7 @@
         <v>46006</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30514,7 +30514,7 @@
         <v>45972</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30587,7 +30587,7 @@
         <v>44900</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30660,7 +30660,7 @@
         <v>44922</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30733,7 +30733,7 @@
         <v>44781</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30806,7 +30806,7 @@
         <v>45466</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30879,7 +30879,7 @@
         <v>45966</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30952,7 +30952,7 @@
         <v>45863</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31025,7 +31025,7 @@
         <v>46055</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31098,7 +31098,7 @@
         <v>45716</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31171,7 +31171,7 @@
         <v>45938</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31244,7 +31244,7 @@
         <v>45327</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31317,7 +31317,7 @@
         <v>45976</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31390,7 +31390,7 @@
         <v>45750</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31463,7 +31463,7 @@
         <v>45217</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31536,7 +31536,7 @@
         <v>45790</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31609,7 +31609,7 @@
         <v>45425</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31682,7 +31682,7 @@
         <v>44951</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31755,7 +31755,7 @@
         <v>46043</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31828,7 +31828,7 @@
         <v>45976</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31901,7 +31901,7 @@
         <v>45099</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31974,7 +31974,7 @@
         <v>46142</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32047,7 +32047,7 @@
         <v>45204</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32125,7 +32125,7 @@
         <v>45561</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32203,7 +32203,7 @@
         <v>45258</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32276,7 +32276,7 @@
         <v>45349</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32349,7 +32349,7 @@
         <v>45310</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32422,7 +32422,7 @@
         <v>45740</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32495,7 +32495,7 @@
         <v>45573</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32568,7 +32568,7 @@
         <v>45789</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32641,7 +32641,7 @@
         <v>44728</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32714,7 +32714,7 @@
         <v>45258</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32787,7 +32787,7 @@
         <v>45258</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32860,7 +32860,7 @@
         <v>45600</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32933,7 +32933,7 @@
         <v>44930</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33006,7 +33006,7 @@
         <v>45400</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33079,7 +33079,7 @@
         <v>46155</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33152,7 +33152,7 @@
         <v>45707</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33225,7 +33225,7 @@
         <v>44698</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33298,7 +33298,7 @@
         <v>46069</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33376,7 +33376,7 @@
         <v>45028</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33449,7 +33449,7 @@
         <v>45392</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33522,7 +33522,7 @@
         <v>45531</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33595,7 +33595,7 @@
         <v>44900</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33668,7 +33668,7 @@
         <v>45196</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33741,7 +33741,7 @@
         <v>44586</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33814,7 +33814,7 @@
         <v>46160</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33887,7 +33887,7 @@
         <v>46160</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33960,7 +33960,7 @@
         <v>45161</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34038,7 +34038,7 @@
         <v>45902</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34111,7 +34111,7 @@
         <v>45180</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34184,7 +34184,7 @@
         <v>46162</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34257,7 +34257,7 @@
         <v>46162</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34330,7 +34330,7 @@
         <v>45716</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34403,7 +34403,7 @@
         <v>45048</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34476,7 +34476,7 @@
         <v>44897</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34549,7 +34549,7 @@
         <v>46169</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34622,7 +34622,7 @@
         <v>45614</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34695,7 +34695,7 @@
         <v>45881</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34768,7 +34768,7 @@
         <v>45230</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34841,7 +34841,7 @@
         <v>44977</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34914,7 +34914,7 @@
         <v>45923</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34987,7 +34987,7 @@
         <v>45587</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -35060,7 +35060,7 @@
         <v>45301</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -35133,7 +35133,7 @@
         <v>45887</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35206,7 +35206,7 @@
         <v>45887</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35279,7 +35279,7 @@
         <v>45622</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35352,7 +35352,7 @@
         <v>46182</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35425,7 +35425,7 @@
         <v>46182</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35498,7 +35498,7 @@
         <v>46183</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35571,7 +35571,7 @@
         <v>45093</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35644,7 +35644,7 @@
         <v>46185</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35717,7 +35717,7 @@
         <v>46189</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35790,7 +35790,7 @@
         <v>46188</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35863,7 +35863,7 @@
         <v>46188</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35936,7 +35936,7 @@
         <v>44965</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36009,7 +36009,7 @@
         <v>46185</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -36082,7 +36082,7 @@
         <v>46188</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36155,7 +36155,7 @@
         <v>44743</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36228,7 +36228,7 @@
         <v>46188</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36301,7 +36301,7 @@
         <v>46185</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36374,7 +36374,7 @@
         <v>44749</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36447,7 +36447,7 @@
         <v>45327</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36520,7 +36520,7 @@
         <v>45327</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36593,7 +36593,7 @@
         <v>46190</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36671,7 +36671,7 @@
         <v>45559</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36749,7 +36749,7 @@
         <v>45182</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36822,7 +36822,7 @@
         <v>46120</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36895,7 +36895,7 @@
         <v>45433</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36968,7 +36968,7 @@
         <v>46196</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37041,7 +37041,7 @@
         <v>45107</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -37114,7 +37114,7 @@
         <v>46196</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37192,7 +37192,7 @@
         <v>46196</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37270,7 +37270,7 @@
         <v>45007</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37343,7 +37343,7 @@
         <v>45007</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37416,7 +37416,7 @@
         <v>46196</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37494,7 +37494,7 @@
         <v>45148</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37567,7 +37567,7 @@
         <v>45084</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37640,7 +37640,7 @@
         <v>46010</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37713,7 +37713,7 @@
         <v>46198</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37786,7 +37786,7 @@
         <v>46197</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37864,7 +37864,7 @@
         <v>45537</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37937,7 +37937,7 @@
         <v>46197</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -38015,7 +38015,7 @@
         <v>46197</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -38093,7 +38093,7 @@
         <v>45281</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -38166,7 +38166,7 @@
         <v>45211</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38239,7 +38239,7 @@
         <v>45021</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38312,7 +38312,7 @@
         <v>44530</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38385,7 +38385,7 @@
         <v>45189</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38458,7 +38458,7 @@
         <v>44938</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38531,7 +38531,7 @@
         <v>46202</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38604,7 +38604,7 @@
         <v>44851</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38677,7 +38677,7 @@
         <v>44960</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38750,7 +38750,7 @@
         <v>46205</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38828,7 +38828,7 @@
         <v>44494</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38901,7 +38901,7 @@
         <v>44893</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38974,7 +38974,7 @@
         <v>46127</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -39052,7 +39052,7 @@
         <v>44518</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -39125,7 +39125,7 @@
         <v>44728</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -39198,7 +39198,7 @@
         <v>45009</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39271,7 +39271,7 @@
         <v>45009</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39344,7 +39344,7 @@
         <v>45009</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39417,7 +39417,7 @@
         <v>45009</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39490,7 +39490,7 @@
         <v>46212</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39563,7 +39563,7 @@
         <v>46211</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39636,7 +39636,7 @@
         <v>46212</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39709,7 +39709,7 @@
         <v>44911</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39782,7 +39782,7 @@
         <v>46213</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39855,7 +39855,7 @@
         <v>45159</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39928,7 +39928,7 @@
         <v>46259</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -40001,7 +40001,7 @@
         <v>45514</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -40074,7 +40074,7 @@
         <v>45514</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -40147,7 +40147,7 @@
         <v>45202</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40220,7 +40220,7 @@
         <v>44879</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40293,7 +40293,7 @@
         <v>46255</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40371,7 +40371,7 @@
         <v>45126</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40444,7 +40444,7 @@
         <v>45126</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40517,7 +40517,7 @@
         <v>45126</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40590,7 +40590,7 @@
         <v>45155</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40663,7 +40663,7 @@
         <v>44953</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40736,7 +40736,7 @@
         <v>45362</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40809,7 +40809,7 @@
         <v>46268</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40882,7 +40882,7 @@
         <v>44700</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40955,7 +40955,7 @@
         <v>46271</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -41028,7 +41028,7 @@
         <v>46273</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -41101,7 +41101,7 @@
         <v>46272</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -41174,7 +41174,7 @@
         <v>45743</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41247,7 +41247,7 @@
         <v>45296</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41320,7 +41320,7 @@
         <v>44530</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41393,7 +41393,7 @@
         <v>44777</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41466,7 +41466,7 @@
         <v>45644</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41539,7 +41539,7 @@
         <v>45181</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41612,7 +41612,7 @@
         <v>46188</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41685,7 +41685,7 @@
         <v>46275</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41758,7 +41758,7 @@
         <v>46279</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41836,7 +41836,7 @@
         <v>46279</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41914,7 +41914,7 @@
         <v>46279</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41992,7 +41992,7 @@
         <v>46279</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -42065,7 +42065,7 @@
         <v>46279</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -42143,7 +42143,7 @@
         <v>46279</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -42221,7 +42221,7 @@
         <v>46279</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42299,7 +42299,7 @@
         <v>46279</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42377,7 +42377,7 @@
         <v>45211</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42450,7 +42450,7 @@
         <v>46134</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42523,7 +42523,7 @@
         <v>46279</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42601,7 +42601,7 @@
         <v>46279</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42679,7 +42679,7 @@
         <v>46279</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42757,7 +42757,7 @@
         <v>45164</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42830,7 +42830,7 @@
         <v>45190</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42903,7 +42903,7 @@
         <v>44993</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42976,7 +42976,7 @@
         <v>45719</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -43049,7 +43049,7 @@
         <v>45719</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -43122,7 +43122,7 @@
         <v>45349</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -43195,7 +43195,7 @@
         <v>45531</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43268,7 +43268,7 @@
         <v>45126</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43341,7 +43341,7 @@
         <v>44861</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43414,7 +43414,7 @@
         <v>46282</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43487,7 +43487,7 @@
         <v>45772</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43560,7 +43560,7 @@
         <v>45205</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43633,7 +43633,7 @@
         <v>45474</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43706,7 +43706,7 @@
         <v>45084</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43779,7 +43779,7 @@
         <v>45126</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43852,7 +43852,7 @@
         <v>45574</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43925,7 +43925,7 @@
         <v>45204</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -44003,7 +44003,7 @@
         <v>45232</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -44076,7 +44076,7 @@
         <v>46244</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -44149,7 +44149,7 @@
         <v>46286</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -44222,7 +44222,7 @@
         <v>45098</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44295,7 +44295,7 @@
         <v>45727</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44368,7 +44368,7 @@
         <v>45392</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44441,7 +44441,7 @@
         <v>45727</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44514,7 +44514,7 @@
         <v>45706</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44587,7 +44587,7 @@
         <v>45740</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44660,7 +44660,7 @@
         <v>45341</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44733,7 +44733,7 @@
         <v>44995</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44806,7 +44806,7 @@
         <v>45926</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44879,7 +44879,7 @@
         <v>45003</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44952,7 +44952,7 @@
         <v>45477</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -45025,7 +45025,7 @@
         <v>44995</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -45098,7 +45098,7 @@
         <v>46288</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -45171,7 +45171,7 @@
         <v>45126</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -45244,7 +45244,7 @@
         <v>45514</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45317,7 +45317,7 @@
         <v>45146</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45390,7 +45390,7 @@
         <v>46288</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45463,7 +45463,7 @@
         <v>44959</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45536,7 +45536,7 @@
         <v>45068</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45614,7 +45614,7 @@
         <v>45707</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45687,7 +45687,7 @@
         <v>44851</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45760,7 +45760,7 @@
         <v>44608</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45833,7 +45833,7 @@
         <v>45095</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45906,7 +45906,7 @@
         <v>44580</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45979,7 +45979,7 @@
         <v>46290</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -46052,7 +46052,7 @@
         <v>46290</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -46125,7 +46125,7 @@
         <v>45373</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -46198,7 +46198,7 @@
         <v>45161</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -46276,7 +46276,7 @@
         <v>44984</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -46349,7 +46349,7 @@
         <v>45252</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -46422,7 +46422,7 @@
         <v>46290</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46495,7 +46495,7 @@
         <v>44761</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46568,7 +46568,7 @@
         <v>44802</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -46641,7 +46641,7 @@
         <v>45422</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -46714,7 +46714,7 @@
         <v>44808</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46787,7 +46787,7 @@
         <v>46245</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46860,7 +46860,7 @@
         <v>46160</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46933,7 +46933,7 @@
         <v>45189</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -47006,7 +47006,7 @@
         <v>46251</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -47079,7 +47079,7 @@
         <v>45772</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -47152,7 +47152,7 @@
         <v>45049</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -47225,7 +47225,7 @@
         <v>44531</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -47298,7 +47298,7 @@
         <v>45051</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -47371,7 +47371,7 @@
         <v>45051</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -47444,7 +47444,7 @@
         <v>45126</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -47517,7 +47517,7 @@
         <v>45126</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -47590,7 +47590,7 @@
         <v>45323</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -47663,7 +47663,7 @@
         <v>46253</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -47736,7 +47736,7 @@
         <v>44673</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47809,7 +47809,7 @@
         <v>45596</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47882,7 +47882,7 @@
         <v>46255</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47960,7 +47960,7 @@
         <v>46230</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -48033,7 +48033,7 @@
         <v>44893</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -48106,7 +48106,7 @@
         <v>45668</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -48179,7 +48179,7 @@
         <v>44759</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -48252,7 +48252,7 @@
         <v>46255</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -48330,7 +48330,7 @@
         <v>46255</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -48408,7 +48408,7 @@
         <v>46255</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -48486,7 +48486,7 @@
         <v>46255</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -48564,7 +48564,7 @@
         <v>46253</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -48637,7 +48637,7 @@
         <v>44594</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -48710,7 +48710,7 @@
         <v>46255</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -48788,7 +48788,7 @@
         <v>46255</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -48861,7 +48861,7 @@
         <v>45323</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -48934,7 +48934,7 @@
         <v>44852</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -49007,7 +49007,7 @@
         <v>45149</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -49080,7 +49080,7 @@
         <v>45111</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -49153,7 +49153,7 @@
         <v>45310</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -49226,7 +49226,7 @@
         <v>45204</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -49304,7 +49304,7 @@
         <v>45062</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -49377,7 +49377,7 @@
         <v>45562</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -49450,7 +49450,7 @@
         <v>45103</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -49523,7 +49523,7 @@
         <v>45688</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -49596,7 +49596,7 @@
         <v>44589</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -49669,7 +49669,7 @@
         <v>44726</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -49742,7 +49742,7 @@
         <v>45742</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -49815,7 +49815,7 @@
         <v>44524</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -49888,7 +49888,7 @@
         <v>44728</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -49961,7 +49961,7 @@
         <v>45182</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -50034,7 +50034,7 @@
         <v>44816</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -50107,7 +50107,7 @@
         <v>44840</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -50185,7 +50185,7 @@
         <v>45595</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -50258,7 +50258,7 @@
         <v>44897</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -50331,7 +50331,7 @@
         <v>45273</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -50409,7 +50409,7 @@
         <v>45349</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -50482,7 +50482,7 @@
         <v>44827</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -50555,7 +50555,7 @@
         <v>45092</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -50628,7 +50628,7 @@
         <v>44550</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -50701,7 +50701,7 @@
         <v>45076</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -50774,7 +50774,7 @@
         <v>45385</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -50847,7 +50847,7 @@
         <v>45515</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -50920,7 +50920,7 @@
         <v>45307</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -50993,7 +50993,7 @@
         <v>45317</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -51066,7 +51066,7 @@
         <v>45187</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -51139,7 +51139,7 @@
         <v>44748</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -51212,7 +51212,7 @@
         <v>44699</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -51285,7 +51285,7 @@
         <v>45400</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -51358,7 +51358,7 @@
         <v>45229</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -51431,7 +51431,7 @@
         <v>45188</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -51509,7 +51509,7 @@
         <v>45769</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -51582,7 +51582,7 @@
         <v>44769</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -51655,7 +51655,7 @@
         <v>44488</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -51733,7 +51733,7 @@
         <v>45769</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -51806,7 +51806,7 @@
         <v>45394</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -51879,7 +51879,7 @@
         <v>44955</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -51952,7 +51952,7 @@
         <v>45048</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -52025,7 +52025,7 @@
         <v>45351</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -52098,7 +52098,7 @@
         <v>45534</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -52171,7 +52171,7 @@
         <v>45215</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -52244,7 +52244,7 @@
         <v>45551</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -52317,7 +52317,7 @@
         <v>45523</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -52390,7 +52390,7 @@
         <v>44949</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -52463,7 +52463,7 @@
         <v>45684</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -52536,7 +52536,7 @@
         <v>45624</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -52609,7 +52609,7 @@
         <v>45484</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -52682,7 +52682,7 @@
         <v>45107</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -52755,7 +52755,7 @@
         <v>45445</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -52828,7 +52828,7 @@
         <v>45317</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -52901,7 +52901,7 @@
         <v>45548</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -52974,7 +52974,7 @@
         <v>45415</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -53047,7 +53047,7 @@
         <v>45638</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -53120,7 +53120,7 @@
         <v>45565</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -53193,7 +53193,7 @@
         <v>45386</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -53266,7 +53266,7 @@
         <v>44476</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -53339,7 +53339,7 @@
         <v>45191</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -53412,7 +53412,7 @@
         <v>44959</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -53485,7 +53485,7 @@
         <v>45194</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -53558,7 +53558,7 @@
         <v>45377</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -53631,7 +53631,7 @@
         <v>45387</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -53704,7 +53704,7 @@
         <v>44903</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -53777,7 +53777,7 @@
         <v>44900</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -53850,7 +53850,7 @@
         <v>44852</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -53923,7 +53923,7 @@
         <v>45200</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -53996,7 +53996,7 @@
         <v>45534</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -54069,7 +54069,7 @@
         <v>45191</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -54142,7 +54142,7 @@
         <v>45386</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -54215,7 +54215,7 @@
         <v>45287</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -54288,7 +54288,7 @@
         <v>45386</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -54361,7 +54361,7 @@
         <v>45386</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -54434,7 +54434,7 @@
         <v>45386</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -54507,7 +54507,7 @@
         <v>45387</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -54580,7 +54580,7 @@
         <v>44519</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -54653,7 +54653,7 @@
         <v>45534</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -54726,7 +54726,7 @@
         <v>45377</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -54799,7 +54799,7 @@
         <v>44928</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -54872,7 +54872,7 @@
         <v>45377</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -54945,7 +54945,7 @@
         <v>44519</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -55018,7 +55018,7 @@
         <v>45200</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -55091,7 +55091,7 @@
         <v>44900</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -55164,7 +55164,7 @@
         <v>45330</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -55237,7 +55237,7 @@
         <v>44959</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -55310,7 +55310,7 @@
         <v>45348</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -55383,7 +55383,7 @@
         <v>45813</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -55456,7 +55456,7 @@
         <v>45813</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -55529,7 +55529,7 @@
         <v>45849</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -55602,7 +55602,7 @@
         <v>45898</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -55675,7 +55675,7 @@
         <v>45935</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -55748,7 +55748,7 @@
         <v>45978</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -55821,7 +55821,7 @@
         <v>46034</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -55894,7 +55894,7 @@
         <v>46049</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -55967,7 +55967,7 @@
         <v>46049</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -56040,7 +56040,7 @@
         <v>46065</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -56113,7 +56113,7 @@
         <v>46092</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -56186,7 +56186,7 @@
         <v>46062</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -56259,7 +56259,7 @@
         <v>46119</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -56332,7 +56332,7 @@
         <v>46119</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -56405,7 +56405,7 @@
         <v>46127</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -56478,7 +56478,7 @@
         <v>46167</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -56551,7 +56551,7 @@
         <v>46156</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -56624,7 +56624,7 @@
         <v>46183</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -56697,7 +56697,7 @@
         <v>46283</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -56770,7 +56770,7 @@
         <v>46286</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -56843,7 +56843,7 @@
         <v>46191</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -56916,7 +56916,7 @@
         <v>46276</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>

--- a/Översikt EMMABODA.xlsx
+++ b/Översikt EMMABODA.xlsx
@@ -601,7 +601,7 @@
         <v>45534</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>45440</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -830,7 +830,7 @@
         <v>45387</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>45202</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
         <v>45030</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>44480</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1276,7 +1276,7 @@
         <v>45616</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>44706</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>44811</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>45330</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1713,7 +1713,7 @@
         <v>45359</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         <v>46136</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1931,7 +1931,7 @@
         <v>45369</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
         <v>45086</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>44937</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2257,7 +2257,7 @@
         <v>46062</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2367,7 +2367,7 @@
         <v>46069</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         <v>46214</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2579,7 +2579,7 @@
         <v>44762</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         <v>44895</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2789,7 +2789,7 @@
         <v>45166</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2894,7 +2894,7 @@
         <v>44966</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2999,7 +2999,7 @@
         <v>45797</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
         <v>44570</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3213,7 +3213,7 @@
         <v>44984</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3318,7 +3318,7 @@
         <v>45953</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3427,7 +3427,7 @@
         <v>45196</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3532,7 +3532,7 @@
         <v>46135</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3642,7 +3642,7 @@
         <v>45967</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3747,7 +3747,7 @@
         <v>45763</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3856,7 +3856,7 @@
         <v>45104</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3961,7 +3961,7 @@
         <v>45335</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4066,7 +4066,7 @@
         <v>45161</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4176,7 +4176,7 @@
         <v>45068</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4286,7 +4286,7 @@
         <v>44771</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4395,7 +4395,7 @@
         <v>46213</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4500,7 +4500,7 @@
         <v>46213</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4605,7 +4605,7 @@
         <v>46218</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4710,7 +4710,7 @@
         <v>46282</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4815,7 +4815,7 @@
         <v>46055</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4920,7 +4920,7 @@
         <v>45229</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5029,7 +5029,7 @@
         <v>45107</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5138,7 +5138,7 @@
         <v>44495</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5247,7 +5247,7 @@
         <v>46253</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5352,7 +5352,7 @@
         <v>45092</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5457,7 +5457,7 @@
         <v>44488</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5567,7 +5567,7 @@
         <v>45509</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5672,7 +5672,7 @@
         <v>45387</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5781,7 +5781,7 @@
         <v>44588</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5886,7 +5886,7 @@
         <v>45611</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5995,7 +5995,7 @@
         <v>45330</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6104,7 +6104,7 @@
         <v>44852</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6213,7 +6213,7 @@
         <v>45442</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6318,7 +6318,7 @@
         <v>45153</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6423,7 +6423,7 @@
         <v>45386</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6528,7 +6528,7 @@
         <v>45685</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6637,7 +6637,7 @@
         <v>45813</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6746,7 +6746,7 @@
         <v>46275</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6855,7 +6855,7 @@
         <v>44530</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6928,7 +6928,7 @@
         <v>44764</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7001,7 +7001,7 @@
         <v>44530</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7074,7 +7074,7 @@
         <v>44496</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         <v>44488</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7220,7 +7220,7 @@
         <v>44529</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7293,7 +7293,7 @@
         <v>44490</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7366,7 +7366,7 @@
         <v>44601</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7439,7 +7439,7 @@
         <v>44600</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7512,7 +7512,7 @@
         <v>44496</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7585,7 +7585,7 @@
         <v>44507</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7658,7 +7658,7 @@
         <v>44507</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7731,7 +7731,7 @@
         <v>44507</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7804,7 +7804,7 @@
         <v>44728</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7877,7 +7877,7 @@
         <v>44599</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7950,7 +7950,7 @@
         <v>44691</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8023,7 +8023,7 @@
         <v>44628</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8096,7 +8096,7 @@
         <v>44504</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8169,7 +8169,7 @@
         <v>44515</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8242,7 +8242,7 @@
         <v>44851</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8315,7 +8315,7 @@
         <v>44860</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8388,7 +8388,7 @@
         <v>44648</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8461,7 +8461,7 @@
         <v>44523</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8534,7 +8534,7 @@
         <v>44628</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8607,7 +8607,7 @@
         <v>44788</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8680,7 +8680,7 @@
         <v>44627</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8753,7 +8753,7 @@
         <v>44498</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8826,7 +8826,7 @@
         <v>44768</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8899,7 +8899,7 @@
         <v>44851</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8972,7 +8972,7 @@
         <v>44529</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9045,7 +9045,7 @@
         <v>44813</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9118,7 +9118,7 @@
         <v>44809</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         <v>44771</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9264,7 +9264,7 @@
         <v>44587</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9337,7 +9337,7 @@
         <v>44496</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9410,7 +9410,7 @@
         <v>44507</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9483,7 +9483,7 @@
         <v>44507</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9556,7 +9556,7 @@
         <v>44487</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9634,7 +9634,7 @@
         <v>44652</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9707,7 +9707,7 @@
         <v>44600</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9780,7 +9780,7 @@
         <v>44628</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9853,7 +9853,7 @@
         <v>44600</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9926,7 +9926,7 @@
         <v>44501</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9999,7 +9999,7 @@
         <v>44852</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10072,7 +10072,7 @@
         <v>44839</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10145,7 +10145,7 @@
         <v>44615</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10223,7 +10223,7 @@
         <v>44622</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10296,7 +10296,7 @@
         <v>44524</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10369,7 +10369,7 @@
         <v>44712</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10442,7 +10442,7 @@
         <v>44743</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10515,7 +10515,7 @@
         <v>44722</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10588,7 +10588,7 @@
         <v>44532</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10666,7 +10666,7 @@
         <v>44593</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10739,7 +10739,7 @@
         <v>44652</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10812,7 +10812,7 @@
         <v>44699</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10885,7 +10885,7 @@
         <v>44820</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10963,7 +10963,7 @@
         <v>44847</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11036,7 +11036,7 @@
         <v>44743</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11109,7 +11109,7 @@
         <v>44488</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11187,7 +11187,7 @@
         <v>44589</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11260,7 +11260,7 @@
         <v>44551</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11338,7 +11338,7 @@
         <v>44600</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11411,7 +11411,7 @@
         <v>44600</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11484,7 +11484,7 @@
         <v>44725</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11557,7 +11557,7 @@
         <v>44655</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11630,7 +11630,7 @@
         <v>44530</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11703,7 +11703,7 @@
         <v>44980</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11776,7 +11776,7 @@
         <v>44788</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11849,7 +11849,7 @@
         <v>45397</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11922,7 +11922,7 @@
         <v>45445</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11995,7 +11995,7 @@
         <v>44953</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12068,7 +12068,7 @@
         <v>45089</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12141,7 +12141,7 @@
         <v>45251</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12214,7 +12214,7 @@
         <v>44690</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12287,7 +12287,7 @@
         <v>45079</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12360,7 +12360,7 @@
         <v>45211</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12433,7 +12433,7 @@
         <v>45411</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12506,7 +12506,7 @@
         <v>44487</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12579,7 +12579,7 @@
         <v>45590</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12652,7 +12652,7 @@
         <v>45191</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12725,7 +12725,7 @@
         <v>45126</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12798,7 +12798,7 @@
         <v>45099</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12871,7 +12871,7 @@
         <v>45040</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12944,7 +12944,7 @@
         <v>45606</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13017,7 +13017,7 @@
         <v>45022</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13090,7 +13090,7 @@
         <v>45022</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13163,7 +13163,7 @@
         <v>45392</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13236,7 +13236,7 @@
         <v>44652</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13309,7 +13309,7 @@
         <v>45159</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13382,7 +13382,7 @@
         <v>45219</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13455,7 +13455,7 @@
         <v>45237</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13528,7 +13528,7 @@
         <v>45187</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13601,7 +13601,7 @@
         <v>45637</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13674,7 +13674,7 @@
         <v>45049</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13747,7 +13747,7 @@
         <v>45775</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13820,7 +13820,7 @@
         <v>45230</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13893,7 +13893,7 @@
         <v>45481</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13966,7 +13966,7 @@
         <v>45566</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14039,7 +14039,7 @@
         <v>45582</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14112,7 +14112,7 @@
         <v>45609</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14185,7 +14185,7 @@
         <v>45484</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14258,7 +14258,7 @@
         <v>45688</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14331,7 +14331,7 @@
         <v>45610</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14404,7 +14404,7 @@
         <v>44572</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14477,7 +14477,7 @@
         <v>45392</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14550,7 +14550,7 @@
         <v>45019</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14623,7 +14623,7 @@
         <v>44973</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14701,7 +14701,7 @@
         <v>45474</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14774,7 +14774,7 @@
         <v>45341</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14847,7 +14847,7 @@
         <v>45400</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14920,7 +14920,7 @@
         <v>44519</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14993,7 +14993,7 @@
         <v>45615</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15066,7 +15066,7 @@
         <v>45749</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15139,7 +15139,7 @@
         <v>45559</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15212,7 +15212,7 @@
         <v>45309</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15285,7 +15285,7 @@
         <v>45211</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15358,7 +15358,7 @@
         <v>45211</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15431,7 +15431,7 @@
         <v>44683</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15504,7 +15504,7 @@
         <v>45615</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15577,7 +15577,7 @@
         <v>45665</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15650,7 +15650,7 @@
         <v>44978</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15723,7 +15723,7 @@
         <v>44978</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15796,7 +15796,7 @@
         <v>46024</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15869,7 +15869,7 @@
         <v>45700</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15942,7 +15942,7 @@
         <v>45148</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16015,7 +16015,7 @@
         <v>45164</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16088,7 +16088,7 @@
         <v>45166</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16161,7 +16161,7 @@
         <v>44896</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16234,7 +16234,7 @@
         <v>45475</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16307,7 +16307,7 @@
         <v>44739</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16380,7 +16380,7 @@
         <v>45394</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16453,7 +16453,7 @@
         <v>45606</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16526,7 +16526,7 @@
         <v>44949</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16599,7 +16599,7 @@
         <v>45741</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16672,7 +16672,7 @@
         <v>45355</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16745,7 +16745,7 @@
         <v>45188</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16823,7 +16823,7 @@
         <v>45422</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16896,7 +16896,7 @@
         <v>46036</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16969,7 +16969,7 @@
         <v>45369</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17042,7 +17042,7 @@
         <v>44982</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17115,7 +17115,7 @@
         <v>44834</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17188,7 +17188,7 @@
         <v>45681</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17261,7 +17261,7 @@
         <v>45909</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17334,7 +17334,7 @@
         <v>45908</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17407,7 +17407,7 @@
         <v>44791</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17480,7 +17480,7 @@
         <v>45455</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17553,7 +17553,7 @@
         <v>46044</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17626,7 +17626,7 @@
         <v>45915</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17699,7 +17699,7 @@
         <v>45915</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17772,7 +17772,7 @@
         <v>45915</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17845,7 +17845,7 @@
         <v>46049</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17918,7 +17918,7 @@
         <v>45665</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17991,7 +17991,7 @@
         <v>44977</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18064,7 +18064,7 @@
         <v>45537</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18137,7 +18137,7 @@
         <v>44958</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18210,7 +18210,7 @@
         <v>45800</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18283,7 +18283,7 @@
         <v>44783</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18356,7 +18356,7 @@
         <v>45804</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18429,7 +18429,7 @@
         <v>46055</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18502,7 +18502,7 @@
         <v>45349</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18575,7 +18575,7 @@
         <v>45921</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18648,7 +18648,7 @@
         <v>44487</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18726,7 +18726,7 @@
         <v>44593</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18799,7 +18799,7 @@
         <v>45021</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18872,7 +18872,7 @@
         <v>44600</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18945,7 +18945,7 @@
         <v>45415</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19018,7 +19018,7 @@
         <v>46058</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19091,7 +19091,7 @@
         <v>46062</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19164,7 +19164,7 @@
         <v>45475</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19237,7 +19237,7 @@
         <v>45323</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19310,7 +19310,7 @@
         <v>45931</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19383,7 +19383,7 @@
         <v>45740</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19456,7 +19456,7 @@
         <v>45475</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19529,7 +19529,7 @@
         <v>45735</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19602,7 +19602,7 @@
         <v>45155</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19675,7 +19675,7 @@
         <v>46069</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19753,7 +19753,7 @@
         <v>45037</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19826,7 +19826,7 @@
         <v>44690</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19899,7 +19899,7 @@
         <v>45938</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19972,7 +19972,7 @@
         <v>46071</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20050,7 +20050,7 @@
         <v>45938</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20123,7 +20123,7 @@
         <v>45938</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20196,7 +20196,7 @@
         <v>45641</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20269,7 +20269,7 @@
         <v>44593</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20342,7 +20342,7 @@
         <v>46071</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20420,7 +20420,7 @@
         <v>45938</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20493,7 +20493,7 @@
         <v>44504</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20566,7 +20566,7 @@
         <v>46072</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20639,7 +20639,7 @@
         <v>46072</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20712,7 +20712,7 @@
         <v>46071</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20790,7 +20790,7 @@
         <v>45126</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20863,7 +20863,7 @@
         <v>45126</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20936,7 +20936,7 @@
         <v>46078</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21009,7 +21009,7 @@
         <v>44799</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21082,7 +21082,7 @@
         <v>45155</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21155,7 +21155,7 @@
         <v>45225</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21228,7 +21228,7 @@
         <v>46079</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21301,7 +21301,7 @@
         <v>46079</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21374,7 +21374,7 @@
         <v>45901</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21447,7 +21447,7 @@
         <v>45953</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21520,7 +21520,7 @@
         <v>44852</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21593,7 +21593,7 @@
         <v>45190</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21666,7 +21666,7 @@
         <v>45433</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21739,7 +21739,7 @@
         <v>45067</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21812,7 +21812,7 @@
         <v>44953</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21885,7 +21885,7 @@
         <v>45107</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21958,7 +21958,7 @@
         <v>46085</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22031,7 +22031,7 @@
         <v>44729</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22104,7 +22104,7 @@
         <v>46085</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22177,7 +22177,7 @@
         <v>46085</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22250,7 +22250,7 @@
         <v>45813</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22323,7 +22323,7 @@
         <v>44984</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22396,7 +22396,7 @@
         <v>46090</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22469,7 +22469,7 @@
         <v>45960</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22542,7 +22542,7 @@
         <v>45964</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22615,7 +22615,7 @@
         <v>44507</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22688,7 +22688,7 @@
         <v>45964</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22761,7 +22761,7 @@
         <v>44473</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22834,7 +22834,7 @@
         <v>45189</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22907,7 +22907,7 @@
         <v>45048</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22980,7 +22980,7 @@
         <v>45191</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23053,7 +23053,7 @@
         <v>45967</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23126,7 +23126,7 @@
         <v>45967</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23199,7 +23199,7 @@
         <v>44619</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23272,7 +23272,7 @@
         <v>45434</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23345,7 +23345,7 @@
         <v>45036</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23418,7 +23418,7 @@
         <v>45971</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23491,7 +23491,7 @@
         <v>44907</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23564,7 +23564,7 @@
         <v>45273</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23642,7 +23642,7 @@
         <v>45211</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23715,7 +23715,7 @@
         <v>45229</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23788,7 +23788,7 @@
         <v>45132</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23861,7 +23861,7 @@
         <v>45084</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23934,7 +23934,7 @@
         <v>45979</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24007,7 +24007,7 @@
         <v>44519</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24080,7 +24080,7 @@
         <v>46107</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24153,7 +24153,7 @@
         <v>45981</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24226,7 +24226,7 @@
         <v>45102</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24299,7 +24299,7 @@
         <v>45102</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24372,7 +24372,7 @@
         <v>44839</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24445,7 +24445,7 @@
         <v>45317</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24518,7 +24518,7 @@
         <v>46120</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24591,7 +24591,7 @@
         <v>46120</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24664,7 +24664,7 @@
         <v>45989</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24737,7 +24737,7 @@
         <v>45825</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24810,7 +24810,7 @@
         <v>45826</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24883,7 +24883,7 @@
         <v>44979</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24956,7 +24956,7 @@
         <v>45716</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25029,7 +25029,7 @@
         <v>45826</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25102,7 +25102,7 @@
         <v>45091</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25175,7 +25175,7 @@
         <v>45986</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25248,7 +25248,7 @@
         <v>45994</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25321,7 +25321,7 @@
         <v>45716</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25394,7 +25394,7 @@
         <v>45826</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25467,7 +25467,7 @@
         <v>45826</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25540,7 +25540,7 @@
         <v>46127</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25613,7 +25613,7 @@
         <v>45826</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25686,7 +25686,7 @@
         <v>45826</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25759,7 +25759,7 @@
         <v>46127</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25832,7 +25832,7 @@
         <v>46127</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25905,7 +25905,7 @@
         <v>45121</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25978,7 +25978,7 @@
         <v>45191</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26051,7 +26051,7 @@
         <v>46133</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26124,7 +26124,7 @@
         <v>44979</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26197,7 +26197,7 @@
         <v>45113</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26270,7 +26270,7 @@
         <v>45113</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26343,7 +26343,7 @@
         <v>45167</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26416,7 +26416,7 @@
         <v>46134</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26489,7 +26489,7 @@
         <v>45832</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26562,7 +26562,7 @@
         <v>45069</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26635,7 +26635,7 @@
         <v>45069</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26708,7 +26708,7 @@
         <v>45401</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26781,7 +26781,7 @@
         <v>45348</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26854,7 +26854,7 @@
         <v>45835</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26927,7 +26927,7 @@
         <v>44993</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27000,7 +27000,7 @@
         <v>45408</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27073,7 +27073,7 @@
         <v>45645</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27146,7 +27146,7 @@
         <v>45376</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27219,7 +27219,7 @@
         <v>44683</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27292,7 +27292,7 @@
         <v>45629</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27365,7 +27365,7 @@
         <v>46139</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27438,7 +27438,7 @@
         <v>45392</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27511,7 +27511,7 @@
         <v>45966</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27584,7 +27584,7 @@
         <v>45905</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27657,7 +27657,7 @@
         <v>45461</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27730,7 +27730,7 @@
         <v>45349</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27803,7 +27803,7 @@
         <v>45901</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27876,7 +27876,7 @@
         <v>45805</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27949,7 +27949,7 @@
         <v>45909</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28022,7 +28022,7 @@
         <v>45845</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28095,7 +28095,7 @@
         <v>45621</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28168,7 +28168,7 @@
         <v>44524</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28241,7 +28241,7 @@
         <v>45091</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28314,7 +28314,7 @@
         <v>45551</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28392,7 +28392,7 @@
         <v>45727</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28465,7 +28465,7 @@
         <v>45401</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28538,7 +28538,7 @@
         <v>44897</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28611,7 +28611,7 @@
         <v>45632</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28684,7 +28684,7 @@
         <v>45113</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28757,7 +28757,7 @@
         <v>45849</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28830,7 +28830,7 @@
         <v>45574</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28903,7 +28903,7 @@
         <v>45335</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28976,7 +28976,7 @@
         <v>45335</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29049,7 +29049,7 @@
         <v>45775</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29122,7 +29122,7 @@
         <v>45716</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29195,7 +29195,7 @@
         <v>45851</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29268,7 +29268,7 @@
         <v>45851</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29341,7 +29341,7 @@
         <v>45200</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29414,7 +29414,7 @@
         <v>45755</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29487,7 +29487,7 @@
         <v>45772</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29560,7 +29560,7 @@
         <v>45070</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29633,7 +29633,7 @@
         <v>45818</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29706,7 +29706,7 @@
         <v>45915</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29784,7 +29784,7 @@
         <v>45222</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29857,7 +29857,7 @@
         <v>44944</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29930,7 +29930,7 @@
         <v>45857</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30003,7 +30003,7 @@
         <v>45819</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30076,7 +30076,7 @@
         <v>45524</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30149,7 +30149,7 @@
         <v>45818</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30222,7 +30222,7 @@
         <v>45370</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30295,7 +30295,7 @@
         <v>45400</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30368,7 +30368,7 @@
         <v>45021</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30441,7 +30441,7 @@
         <v>46006</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30514,7 +30514,7 @@
         <v>45972</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30587,7 +30587,7 @@
         <v>44900</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30660,7 +30660,7 @@
         <v>44922</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30733,7 +30733,7 @@
         <v>44781</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30806,7 +30806,7 @@
         <v>45466</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30879,7 +30879,7 @@
         <v>45966</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30952,7 +30952,7 @@
         <v>45863</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31025,7 +31025,7 @@
         <v>46055</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31098,7 +31098,7 @@
         <v>45716</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31171,7 +31171,7 @@
         <v>45938</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31244,7 +31244,7 @@
         <v>45327</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31317,7 +31317,7 @@
         <v>45976</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31390,7 +31390,7 @@
         <v>45750</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31463,7 +31463,7 @@
         <v>45217</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31536,7 +31536,7 @@
         <v>45790</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31609,7 +31609,7 @@
         <v>45425</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31682,7 +31682,7 @@
         <v>44951</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31755,7 +31755,7 @@
         <v>46043</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31828,7 +31828,7 @@
         <v>45976</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31901,7 +31901,7 @@
         <v>45099</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31974,7 +31974,7 @@
         <v>46142</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32047,7 +32047,7 @@
         <v>45204</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32125,7 +32125,7 @@
         <v>45561</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32203,7 +32203,7 @@
         <v>45258</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32276,7 +32276,7 @@
         <v>45349</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32349,7 +32349,7 @@
         <v>45310</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32422,7 +32422,7 @@
         <v>45740</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32495,7 +32495,7 @@
         <v>45573</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32568,7 +32568,7 @@
         <v>45789</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32641,7 +32641,7 @@
         <v>44728</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32714,7 +32714,7 @@
         <v>45258</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32787,7 +32787,7 @@
         <v>45258</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32860,7 +32860,7 @@
         <v>45600</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32933,7 +32933,7 @@
         <v>44930</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33006,7 +33006,7 @@
         <v>45400</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33079,7 +33079,7 @@
         <v>46155</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33152,7 +33152,7 @@
         <v>45707</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33225,7 +33225,7 @@
         <v>44698</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33298,7 +33298,7 @@
         <v>46069</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33376,7 +33376,7 @@
         <v>45028</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33449,7 +33449,7 @@
         <v>45392</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33522,7 +33522,7 @@
         <v>45531</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33595,7 +33595,7 @@
         <v>44900</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33668,7 +33668,7 @@
         <v>45196</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33741,7 +33741,7 @@
         <v>44586</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33814,7 +33814,7 @@
         <v>46160</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33887,7 +33887,7 @@
         <v>46160</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33960,7 +33960,7 @@
         <v>45161</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34038,7 +34038,7 @@
         <v>45902</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34111,7 +34111,7 @@
         <v>45180</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34184,7 +34184,7 @@
         <v>46162</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34257,7 +34257,7 @@
         <v>46162</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34330,7 +34330,7 @@
         <v>45716</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34403,7 +34403,7 @@
         <v>45048</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34476,7 +34476,7 @@
         <v>44897</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34549,7 +34549,7 @@
         <v>46169</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34622,7 +34622,7 @@
         <v>45614</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34695,7 +34695,7 @@
         <v>45881</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34768,7 +34768,7 @@
         <v>45230</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34841,7 +34841,7 @@
         <v>44977</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34914,7 +34914,7 @@
         <v>45923</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34987,7 +34987,7 @@
         <v>45587</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -35060,7 +35060,7 @@
         <v>45301</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -35133,7 +35133,7 @@
         <v>45887</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35206,7 +35206,7 @@
         <v>45887</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35279,7 +35279,7 @@
         <v>45622</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35352,7 +35352,7 @@
         <v>46182</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35425,7 +35425,7 @@
         <v>46182</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35498,7 +35498,7 @@
         <v>46183</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35571,7 +35571,7 @@
         <v>45093</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35644,7 +35644,7 @@
         <v>46185</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35717,7 +35717,7 @@
         <v>46189</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35790,7 +35790,7 @@
         <v>46188</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35863,7 +35863,7 @@
         <v>46188</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35936,7 +35936,7 @@
         <v>44965</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36009,7 +36009,7 @@
         <v>46185</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -36082,7 +36082,7 @@
         <v>46188</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36155,7 +36155,7 @@
         <v>44743</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36228,7 +36228,7 @@
         <v>46188</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36301,7 +36301,7 @@
         <v>46185</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36374,7 +36374,7 @@
         <v>44749</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36447,7 +36447,7 @@
         <v>45327</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36520,7 +36520,7 @@
         <v>45327</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36593,7 +36593,7 @@
         <v>46190</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36671,7 +36671,7 @@
         <v>45559</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36749,7 +36749,7 @@
         <v>45182</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36822,7 +36822,7 @@
         <v>46120</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36895,7 +36895,7 @@
         <v>45433</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36968,7 +36968,7 @@
         <v>46196</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37041,7 +37041,7 @@
         <v>45107</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -37114,7 +37114,7 @@
         <v>46196</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37192,7 +37192,7 @@
         <v>46196</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37270,7 +37270,7 @@
         <v>45007</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37343,7 +37343,7 @@
         <v>45007</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37416,7 +37416,7 @@
         <v>46196</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37494,7 +37494,7 @@
         <v>45148</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37567,7 +37567,7 @@
         <v>45084</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37640,7 +37640,7 @@
         <v>46010</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37713,7 +37713,7 @@
         <v>46198</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37786,7 +37786,7 @@
         <v>46197</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37864,7 +37864,7 @@
         <v>45537</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37937,7 +37937,7 @@
         <v>46197</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -38015,7 +38015,7 @@
         <v>46197</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -38093,7 +38093,7 @@
         <v>45281</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -38166,7 +38166,7 @@
         <v>45211</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38239,7 +38239,7 @@
         <v>45021</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38312,7 +38312,7 @@
         <v>44530</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38385,7 +38385,7 @@
         <v>45189</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38458,7 +38458,7 @@
         <v>44938</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38531,7 +38531,7 @@
         <v>46202</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38604,7 +38604,7 @@
         <v>44851</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38677,7 +38677,7 @@
         <v>44960</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38750,7 +38750,7 @@
         <v>46205</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38828,7 +38828,7 @@
         <v>44494</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38901,7 +38901,7 @@
         <v>44893</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38974,7 +38974,7 @@
         <v>46127</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -39052,7 +39052,7 @@
         <v>44518</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -39125,7 +39125,7 @@
         <v>44728</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -39198,7 +39198,7 @@
         <v>45009</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39271,7 +39271,7 @@
         <v>45009</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39344,7 +39344,7 @@
         <v>45009</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39417,7 +39417,7 @@
         <v>45009</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39490,7 +39490,7 @@
         <v>46212</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39563,7 +39563,7 @@
         <v>46211</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39636,7 +39636,7 @@
         <v>46212</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39709,7 +39709,7 @@
         <v>44911</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39782,7 +39782,7 @@
         <v>46213</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39855,7 +39855,7 @@
         <v>45159</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39928,7 +39928,7 @@
         <v>46259</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -40001,7 +40001,7 @@
         <v>45514</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -40074,7 +40074,7 @@
         <v>45514</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -40147,7 +40147,7 @@
         <v>45202</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40220,7 +40220,7 @@
         <v>44879</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40293,7 +40293,7 @@
         <v>46255</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40371,7 +40371,7 @@
         <v>45126</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40444,7 +40444,7 @@
         <v>45126</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40517,7 +40517,7 @@
         <v>45126</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40590,7 +40590,7 @@
         <v>45155</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40663,7 +40663,7 @@
         <v>44953</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40736,7 +40736,7 @@
         <v>45362</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40809,7 +40809,7 @@
         <v>46268</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40882,7 +40882,7 @@
         <v>44700</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40955,7 +40955,7 @@
         <v>46271</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -41028,7 +41028,7 @@
         <v>46273</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -41101,7 +41101,7 @@
         <v>46272</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -41174,7 +41174,7 @@
         <v>45743</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41247,7 +41247,7 @@
         <v>45296</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41320,7 +41320,7 @@
         <v>44530</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41393,7 +41393,7 @@
         <v>44777</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41466,7 +41466,7 @@
         <v>45644</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41539,7 +41539,7 @@
         <v>45181</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41612,7 +41612,7 @@
         <v>46188</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41685,7 +41685,7 @@
         <v>46275</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41758,7 +41758,7 @@
         <v>46279</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41836,7 +41836,7 @@
         <v>46279</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41914,7 +41914,7 @@
         <v>46279</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41992,7 +41992,7 @@
         <v>46279</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -42065,7 +42065,7 @@
         <v>46279</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -42143,7 +42143,7 @@
         <v>46279</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -42221,7 +42221,7 @@
         <v>46279</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42299,7 +42299,7 @@
         <v>46279</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42377,7 +42377,7 @@
         <v>45211</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42450,7 +42450,7 @@
         <v>46134</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42523,7 +42523,7 @@
         <v>46279</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42601,7 +42601,7 @@
         <v>46279</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42679,7 +42679,7 @@
         <v>46279</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42757,7 +42757,7 @@
         <v>45164</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42830,7 +42830,7 @@
         <v>45190</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42903,7 +42903,7 @@
         <v>44993</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42976,7 +42976,7 @@
         <v>45719</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -43049,7 +43049,7 @@
         <v>45719</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -43122,7 +43122,7 @@
         <v>45349</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -43195,7 +43195,7 @@
         <v>45531</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43268,7 +43268,7 @@
         <v>45126</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43341,7 +43341,7 @@
         <v>44861</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43414,7 +43414,7 @@
         <v>46282</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43487,7 +43487,7 @@
         <v>45772</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43560,7 +43560,7 @@
         <v>45205</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43633,7 +43633,7 @@
         <v>45474</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43706,7 +43706,7 @@
         <v>45084</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43779,7 +43779,7 @@
         <v>45126</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43852,7 +43852,7 @@
         <v>45574</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43925,7 +43925,7 @@
         <v>45204</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -44003,7 +44003,7 @@
         <v>45232</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -44076,7 +44076,7 @@
         <v>46244</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -44149,7 +44149,7 @@
         <v>46286</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -44222,7 +44222,7 @@
         <v>45098</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44295,7 +44295,7 @@
         <v>45727</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44368,7 +44368,7 @@
         <v>45392</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44441,7 +44441,7 @@
         <v>45727</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44514,7 +44514,7 @@
         <v>45706</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44587,7 +44587,7 @@
         <v>45740</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44660,7 +44660,7 @@
         <v>45341</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44733,7 +44733,7 @@
         <v>44995</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44806,7 +44806,7 @@
         <v>45926</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44879,7 +44879,7 @@
         <v>45003</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44952,7 +44952,7 @@
         <v>45477</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -45025,7 +45025,7 @@
         <v>44995</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -45098,7 +45098,7 @@
         <v>46288</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -45171,7 +45171,7 @@
         <v>45126</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -45244,7 +45244,7 @@
         <v>45514</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45317,7 +45317,7 @@
         <v>45146</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45390,7 +45390,7 @@
         <v>46288</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45463,7 +45463,7 @@
         <v>44959</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45536,7 +45536,7 @@
         <v>45068</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45614,7 +45614,7 @@
         <v>45707</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45687,7 +45687,7 @@
         <v>44851</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45760,7 +45760,7 @@
         <v>44608</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45833,7 +45833,7 @@
         <v>45095</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45906,7 +45906,7 @@
         <v>44580</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45979,7 +45979,7 @@
         <v>46290</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -46052,7 +46052,7 @@
         <v>46290</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -46125,7 +46125,7 @@
         <v>45373</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -46198,7 +46198,7 @@
         <v>45161</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -46276,7 +46276,7 @@
         <v>44984</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -46349,7 +46349,7 @@
         <v>45252</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -46422,7 +46422,7 @@
         <v>46290</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46495,7 +46495,7 @@
         <v>44761</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46568,7 +46568,7 @@
         <v>44802</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -46641,7 +46641,7 @@
         <v>45422</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -46714,7 +46714,7 @@
         <v>44808</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46787,7 +46787,7 @@
         <v>46245</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46860,7 +46860,7 @@
         <v>46160</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46933,7 +46933,7 @@
         <v>45189</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -47006,7 +47006,7 @@
         <v>46251</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -47079,7 +47079,7 @@
         <v>45772</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -47152,7 +47152,7 @@
         <v>45049</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -47225,7 +47225,7 @@
         <v>44531</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -47298,7 +47298,7 @@
         <v>45051</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -47371,7 +47371,7 @@
         <v>45051</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -47444,7 +47444,7 @@
         <v>45126</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -47517,7 +47517,7 @@
         <v>45126</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -47590,7 +47590,7 @@
         <v>45323</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -47663,7 +47663,7 @@
         <v>46253</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -47736,7 +47736,7 @@
         <v>44673</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47809,7 +47809,7 @@
         <v>45596</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47882,7 +47882,7 @@
         <v>46255</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47960,7 +47960,7 @@
         <v>46230</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -48033,7 +48033,7 @@
         <v>44893</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -48106,7 +48106,7 @@
         <v>45668</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -48179,7 +48179,7 @@
         <v>44759</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -48252,7 +48252,7 @@
         <v>46255</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -48330,7 +48330,7 @@
         <v>46255</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -48408,7 +48408,7 @@
         <v>46255</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -48486,7 +48486,7 @@
         <v>46255</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -48564,7 +48564,7 @@
         <v>46253</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -48637,7 +48637,7 @@
         <v>44594</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -48710,7 +48710,7 @@
         <v>46255</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -48788,7 +48788,7 @@
         <v>46255</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -48861,7 +48861,7 @@
         <v>45323</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -48934,7 +48934,7 @@
         <v>44852</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -49007,7 +49007,7 @@
         <v>45149</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -49080,7 +49080,7 @@
         <v>45111</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -49153,7 +49153,7 @@
         <v>45310</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -49226,7 +49226,7 @@
         <v>45204</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -49304,7 +49304,7 @@
         <v>45062</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -49377,7 +49377,7 @@
         <v>45562</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -49450,7 +49450,7 @@
         <v>45103</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -49523,7 +49523,7 @@
         <v>45688</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -49596,7 +49596,7 @@
         <v>44589</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -49669,7 +49669,7 @@
         <v>44726</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -49742,7 +49742,7 @@
         <v>45742</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -49815,7 +49815,7 @@
         <v>44524</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -49888,7 +49888,7 @@
         <v>44728</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -49961,7 +49961,7 @@
         <v>45182</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -50034,7 +50034,7 @@
         <v>44816</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -50107,7 +50107,7 @@
         <v>44840</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -50185,7 +50185,7 @@
         <v>45595</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -50258,7 +50258,7 @@
         <v>44897</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -50331,7 +50331,7 @@
         <v>45273</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -50409,7 +50409,7 @@
         <v>45349</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -50482,7 +50482,7 @@
         <v>44827</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -50555,7 +50555,7 @@
         <v>45092</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -50628,7 +50628,7 @@
         <v>44550</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -50701,7 +50701,7 @@
         <v>45076</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -50774,7 +50774,7 @@
         <v>45385</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -50847,7 +50847,7 @@
         <v>45515</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -50920,7 +50920,7 @@
         <v>45307</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -50993,7 +50993,7 @@
         <v>45317</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -51066,7 +51066,7 @@
         <v>45187</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -51139,7 +51139,7 @@
         <v>44748</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -51212,7 +51212,7 @@
         <v>44699</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -51285,7 +51285,7 @@
         <v>45400</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -51358,7 +51358,7 @@
         <v>45229</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -51431,7 +51431,7 @@
         <v>45188</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -51509,7 +51509,7 @@
         <v>45769</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -51582,7 +51582,7 @@
         <v>44769</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -51655,7 +51655,7 @@
         <v>44488</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -51733,7 +51733,7 @@
         <v>45769</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -51806,7 +51806,7 @@
         <v>45394</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -51879,7 +51879,7 @@
         <v>44955</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -51952,7 +51952,7 @@
         <v>45048</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -52025,7 +52025,7 @@
         <v>45351</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -52098,7 +52098,7 @@
         <v>45534</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -52171,7 +52171,7 @@
         <v>45215</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -52244,7 +52244,7 @@
         <v>45551</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -52317,7 +52317,7 @@
         <v>45523</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -52390,7 +52390,7 @@
         <v>44949</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -52463,7 +52463,7 @@
         <v>45684</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -52536,7 +52536,7 @@
         <v>45624</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -52609,7 +52609,7 @@
         <v>45484</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -52682,7 +52682,7 @@
         <v>45107</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -52755,7 +52755,7 @@
         <v>45445</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -52828,7 +52828,7 @@
         <v>45317</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -52901,7 +52901,7 @@
         <v>45548</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -52974,7 +52974,7 @@
         <v>45415</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -53047,7 +53047,7 @@
         <v>45638</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -53120,7 +53120,7 @@
         <v>45565</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -53193,7 +53193,7 @@
         <v>45386</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -53266,7 +53266,7 @@
         <v>44476</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -53339,7 +53339,7 @@
         <v>45191</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -53412,7 +53412,7 @@
         <v>44959</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -53485,7 +53485,7 @@
         <v>45194</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -53558,7 +53558,7 @@
         <v>45377</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -53631,7 +53631,7 @@
         <v>45387</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -53704,7 +53704,7 @@
         <v>44903</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -53777,7 +53777,7 @@
         <v>44900</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -53850,7 +53850,7 @@
         <v>44852</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -53923,7 +53923,7 @@
         <v>45200</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -53996,7 +53996,7 @@
         <v>45534</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -54069,7 +54069,7 @@
         <v>45191</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -54142,7 +54142,7 @@
         <v>45386</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -54215,7 +54215,7 @@
         <v>45287</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -54288,7 +54288,7 @@
         <v>45386</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -54361,7 +54361,7 @@
         <v>45386</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -54434,7 +54434,7 @@
         <v>45386</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -54507,7 +54507,7 @@
         <v>45387</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -54580,7 +54580,7 @@
         <v>44519</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -54653,7 +54653,7 @@
         <v>45534</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -54726,7 +54726,7 @@
         <v>45377</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -54799,7 +54799,7 @@
         <v>44928</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -54872,7 +54872,7 @@
         <v>45377</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -54945,7 +54945,7 @@
         <v>44519</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -55018,7 +55018,7 @@
         <v>45200</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -55091,7 +55091,7 @@
         <v>44900</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -55164,7 +55164,7 @@
         <v>45330</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -55237,7 +55237,7 @@
         <v>44959</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -55310,7 +55310,7 @@
         <v>45348</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -55383,7 +55383,7 @@
         <v>45813</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -55456,7 +55456,7 @@
         <v>45813</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -55529,7 +55529,7 @@
         <v>45849</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -55602,7 +55602,7 @@
         <v>45898</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -55675,7 +55675,7 @@
         <v>45935</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -55748,7 +55748,7 @@
         <v>45978</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -55821,7 +55821,7 @@
         <v>46034</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -55894,7 +55894,7 @@
         <v>46049</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -55967,7 +55967,7 @@
         <v>46049</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -56040,7 +56040,7 @@
         <v>46065</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -56113,7 +56113,7 @@
         <v>46092</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -56186,7 +56186,7 @@
         <v>46062</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -56259,7 +56259,7 @@
         <v>46119</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -56332,7 +56332,7 @@
         <v>46119</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -56405,7 +56405,7 @@
         <v>46127</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -56478,7 +56478,7 @@
         <v>46167</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -56551,7 +56551,7 @@
         <v>46156</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -56624,7 +56624,7 @@
         <v>46183</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -56697,7 +56697,7 @@
         <v>46283</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -56770,7 +56770,7 @@
         <v>46286</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -56843,7 +56843,7 @@
         <v>46191</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -56916,7 +56916,7 @@
         <v>46276</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>

--- a/Översikt EMMABODA.xlsx
+++ b/Översikt EMMABODA.xlsx
@@ -601,7 +601,7 @@
         <v>45534</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>45440</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -830,7 +830,7 @@
         <v>45387</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>45202</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
         <v>45030</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>44480</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1276,7 +1276,7 @@
         <v>45616</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>44706</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>44811</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>45330</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1713,7 +1713,7 @@
         <v>45359</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         <v>46136</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1931,7 +1931,7 @@
         <v>45369</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
         <v>45086</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>44937</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2257,7 +2257,7 @@
         <v>46062</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2367,7 +2367,7 @@
         <v>46069</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         <v>46214</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2579,7 +2579,7 @@
         <v>44771</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2688,7 +2688,7 @@
         <v>45107</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2797,7 +2797,7 @@
         <v>45104</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2902,7 +2902,7 @@
         <v>44488</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3012,7 +3012,7 @@
         <v>45335</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3117,7 +3117,7 @@
         <v>45068</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3227,7 +3227,7 @@
         <v>45161</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3337,7 +3337,7 @@
         <v>44895</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3442,7 +3442,7 @@
         <v>45797</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3551,7 +3551,7 @@
         <v>45166</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
         <v>44762</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3761,7 +3761,7 @@
         <v>44570</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3866,7 +3866,7 @@
         <v>45092</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3971,7 +3971,7 @@
         <v>45953</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4080,7 +4080,7 @@
         <v>44495</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4189,7 +4189,7 @@
         <v>45196</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4294,7 +4294,7 @@
         <v>45967</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4399,7 +4399,7 @@
         <v>46135</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4509,7 +4509,7 @@
         <v>45763</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4618,7 +4618,7 @@
         <v>44984</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4723,7 +4723,7 @@
         <v>45229</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4832,7 +4832,7 @@
         <v>44966</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4937,7 +4937,7 @@
         <v>46213</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
         <v>46213</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5147,7 +5147,7 @@
         <v>46218</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5252,7 +5252,7 @@
         <v>46282</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5357,7 +5357,7 @@
         <v>46055</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
         <v>46253</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5567,7 +5567,7 @@
         <v>44588</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5672,7 +5672,7 @@
         <v>45509</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5777,7 +5777,7 @@
         <v>45387</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5886,7 +5886,7 @@
         <v>45611</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5995,7 +5995,7 @@
         <v>45330</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6104,7 +6104,7 @@
         <v>44852</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6213,7 +6213,7 @@
         <v>45442</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6318,7 +6318,7 @@
         <v>45153</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6423,7 +6423,7 @@
         <v>45386</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6528,7 +6528,7 @@
         <v>45685</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6637,7 +6637,7 @@
         <v>45813</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6746,7 +6746,7 @@
         <v>46275</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6855,7 +6855,7 @@
         <v>44530</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6928,7 +6928,7 @@
         <v>44496</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7001,7 +7001,7 @@
         <v>44764</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7074,7 +7074,7 @@
         <v>44488</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         <v>44496</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7220,7 +7220,7 @@
         <v>44530</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7293,7 +7293,7 @@
         <v>44490</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7366,7 +7366,7 @@
         <v>44529</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7439,7 +7439,7 @@
         <v>44601</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7512,7 +7512,7 @@
         <v>44600</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7585,7 +7585,7 @@
         <v>44507</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7658,7 +7658,7 @@
         <v>44507</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7731,7 +7731,7 @@
         <v>44507</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7804,7 +7804,7 @@
         <v>44728</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7877,7 +7877,7 @@
         <v>44599</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7950,7 +7950,7 @@
         <v>44691</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8023,7 +8023,7 @@
         <v>44628</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8096,7 +8096,7 @@
         <v>44504</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8169,7 +8169,7 @@
         <v>44515</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8242,7 +8242,7 @@
         <v>44851</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8315,7 +8315,7 @@
         <v>44860</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8388,7 +8388,7 @@
         <v>44523</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8461,7 +8461,7 @@
         <v>44648</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8534,7 +8534,7 @@
         <v>44628</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8607,7 +8607,7 @@
         <v>44788</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8680,7 +8680,7 @@
         <v>44627</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8753,7 +8753,7 @@
         <v>44498</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8826,7 +8826,7 @@
         <v>44768</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8899,7 +8899,7 @@
         <v>44851</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8972,7 +8972,7 @@
         <v>44529</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9045,7 +9045,7 @@
         <v>44813</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9118,7 +9118,7 @@
         <v>44809</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         <v>44771</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9264,7 +9264,7 @@
         <v>44587</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9337,7 +9337,7 @@
         <v>44496</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9410,7 +9410,7 @@
         <v>44622</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9483,7 +9483,7 @@
         <v>44488</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9561,7 +9561,7 @@
         <v>44507</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9634,7 +9634,7 @@
         <v>44507</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9707,7 +9707,7 @@
         <v>44524</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9780,7 +9780,7 @@
         <v>44487</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9858,7 +9858,7 @@
         <v>44712</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9931,7 +9931,7 @@
         <v>44589</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10004,7 +10004,7 @@
         <v>44551</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10082,7 +10082,7 @@
         <v>44593</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10155,7 +10155,7 @@
         <v>44652</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10228,7 +10228,7 @@
         <v>44600</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10301,7 +10301,7 @@
         <v>44699</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10374,7 +10374,7 @@
         <v>44652</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10447,7 +10447,7 @@
         <v>44628</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10520,7 +10520,7 @@
         <v>44600</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10593,7 +10593,7 @@
         <v>44725</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10666,7 +10666,7 @@
         <v>44820</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10744,7 +10744,7 @@
         <v>44743</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10817,7 +10817,7 @@
         <v>44600</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10890,7 +10890,7 @@
         <v>44501</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10963,7 +10963,7 @@
         <v>44600</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11036,7 +11036,7 @@
         <v>44852</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11109,7 +11109,7 @@
         <v>44839</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11182,7 +11182,7 @@
         <v>44847</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11255,7 +11255,7 @@
         <v>44743</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11328,7 +11328,7 @@
         <v>44615</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11406,7 +11406,7 @@
         <v>44655</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11479,7 +11479,7 @@
         <v>45719</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11552,7 +11552,7 @@
         <v>44722</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11625,7 +11625,7 @@
         <v>44532</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11703,7 +11703,7 @@
         <v>45189</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11776,7 +11776,7 @@
         <v>45411</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11849,7 +11849,7 @@
         <v>45099</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11922,7 +11922,7 @@
         <v>44530</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11995,7 +11995,7 @@
         <v>44788</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12068,7 +12068,7 @@
         <v>44593</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12141,7 +12141,7 @@
         <v>45422</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12214,7 +12214,7 @@
         <v>44816</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12287,7 +12287,7 @@
         <v>45048</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12360,7 +12360,7 @@
         <v>44608</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12433,7 +12433,7 @@
         <v>45113</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12506,7 +12506,7 @@
         <v>45187</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12579,7 +12579,7 @@
         <v>45219</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12652,7 +12652,7 @@
         <v>45007</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12725,7 +12725,7 @@
         <v>45229</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12798,7 +12798,7 @@
         <v>45385</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12871,7 +12871,7 @@
         <v>45335</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12944,7 +12944,7 @@
         <v>45204</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13022,7 +13022,7 @@
         <v>45349</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13095,7 +13095,7 @@
         <v>45164</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13168,7 +13168,7 @@
         <v>45190</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13241,7 +13241,7 @@
         <v>45740</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13314,7 +13314,7 @@
         <v>44759</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13387,7 +13387,7 @@
         <v>45317</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13460,7 +13460,7 @@
         <v>45211</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13533,7 +13533,7 @@
         <v>45211</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13606,7 +13606,7 @@
         <v>45211</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13679,7 +13679,7 @@
         <v>44739</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13752,7 +13752,7 @@
         <v>45126</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13825,7 +13825,7 @@
         <v>44698</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13898,7 +13898,7 @@
         <v>45317</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13971,7 +13971,7 @@
         <v>45126</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14044,7 +14044,7 @@
         <v>45376</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14117,7 +14117,7 @@
         <v>44959</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14190,7 +14190,7 @@
         <v>45373</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14263,7 +14263,7 @@
         <v>45126</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14336,7 +14336,7 @@
         <v>45211</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14409,7 +14409,7 @@
         <v>45719</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14482,7 +14482,7 @@
         <v>44977</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14555,7 +14555,7 @@
         <v>45327</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14628,7 +14628,7 @@
         <v>45348</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14701,7 +14701,7 @@
         <v>45461</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14774,7 +14774,7 @@
         <v>45069</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14847,7 +14847,7 @@
         <v>45069</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14920,7 +14920,7 @@
         <v>45397</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14993,7 +14993,7 @@
         <v>44861</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15066,7 +15066,7 @@
         <v>45126</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15139,7 +15139,7 @@
         <v>45615</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15212,7 +15212,7 @@
         <v>45204</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15290,7 +15290,7 @@
         <v>44728</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15363,7 +15363,7 @@
         <v>45335</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15436,7 +15436,7 @@
         <v>45093</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15509,7 +15509,7 @@
         <v>45369</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15582,7 +15582,7 @@
         <v>45273</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15660,7 +15660,7 @@
         <v>45204</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15738,7 +15738,7 @@
         <v>45595</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15811,7 +15811,7 @@
         <v>45615</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15884,7 +15884,7 @@
         <v>45400</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15957,7 +15957,7 @@
         <v>45433</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16030,7 +16030,7 @@
         <v>44907</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16103,7 +16103,7 @@
         <v>45474</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16176,7 +16176,7 @@
         <v>45237</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16249,7 +16249,7 @@
         <v>44531</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16322,7 +16322,7 @@
         <v>44504</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16395,7 +16395,7 @@
         <v>45103</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16468,7 +16468,7 @@
         <v>45474</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16541,7 +16541,7 @@
         <v>44852</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16614,7 +16614,7 @@
         <v>45121</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16687,7 +16687,7 @@
         <v>45341</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16760,7 +16760,7 @@
         <v>45341</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16833,7 +16833,7 @@
         <v>45887</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16906,7 +16906,7 @@
         <v>45887</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16979,7 +16979,7 @@
         <v>45161</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17057,7 +17057,7 @@
         <v>44953</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17130,7 +17130,7 @@
         <v>45323</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17203,7 +17203,7 @@
         <v>44953</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17276,7 +17276,7 @@
         <v>45665</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17349,7 +17349,7 @@
         <v>44572</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17422,7 +17422,7 @@
         <v>45126</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17495,7 +17495,7 @@
         <v>45273</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17573,7 +17573,7 @@
         <v>45202</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17646,7 +17646,7 @@
         <v>45531</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17719,7 +17719,7 @@
         <v>45749</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17792,7 +17792,7 @@
         <v>45600</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17865,7 +17865,7 @@
         <v>45281</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17938,7 +17938,7 @@
         <v>45155</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18011,7 +18011,7 @@
         <v>44593</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18084,7 +18084,7 @@
         <v>45477</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18157,7 +18157,7 @@
         <v>45769</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18230,7 +18230,7 @@
         <v>45514</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18303,7 +18303,7 @@
         <v>45126</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18376,7 +18376,7 @@
         <v>44951</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18449,7 +18449,7 @@
         <v>44897</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18522,7 +18522,7 @@
         <v>45003</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18595,7 +18595,7 @@
         <v>45716</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18668,7 +18668,7 @@
         <v>44984</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18741,7 +18741,7 @@
         <v>45019</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18814,7 +18814,7 @@
         <v>45161</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18892,7 +18892,7 @@
         <v>44980</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18965,7 +18965,7 @@
         <v>45700</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19038,7 +19038,7 @@
         <v>44519</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19111,7 +19111,7 @@
         <v>45741</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19184,7 +19184,7 @@
         <v>44530</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19257,7 +19257,7 @@
         <v>44519</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19330,7 +19330,7 @@
         <v>45561</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19408,7 +19408,7 @@
         <v>45189</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19481,7 +19481,7 @@
         <v>45189</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19554,7 +19554,7 @@
         <v>44550</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19627,7 +19627,7 @@
         <v>44840</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19705,7 +19705,7 @@
         <v>45099</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19778,7 +19778,7 @@
         <v>45070</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19851,7 +19851,7 @@
         <v>45475</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19924,7 +19924,7 @@
         <v>44979</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19997,7 +19997,7 @@
         <v>44896</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20070,7 +20070,7 @@
         <v>45681</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20143,7 +20143,7 @@
         <v>44900</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20216,7 +20216,7 @@
         <v>45537</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20289,7 +20289,7 @@
         <v>45132</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20362,7 +20362,7 @@
         <v>45562</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20435,7 +20435,7 @@
         <v>44600</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20508,7 +20508,7 @@
         <v>45908</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20581,7 +20581,7 @@
         <v>45551</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20654,7 +20654,7 @@
         <v>45909</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20727,7 +20727,7 @@
         <v>45523</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20800,7 +20800,7 @@
         <v>45475</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20873,7 +20873,7 @@
         <v>45215</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20946,7 +20946,7 @@
         <v>44949</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21019,7 +21019,7 @@
         <v>45684</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21092,7 +21092,7 @@
         <v>45624</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21165,7 +21165,7 @@
         <v>45037</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21238,7 +21238,7 @@
         <v>45534</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21311,7 +21311,7 @@
         <v>45484</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21384,7 +21384,7 @@
         <v>45351</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21457,7 +21457,7 @@
         <v>44982</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21530,7 +21530,7 @@
         <v>44893</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21603,7 +21603,7 @@
         <v>45915</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21676,7 +21676,7 @@
         <v>45587</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21749,7 +21749,7 @@
         <v>44683</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21822,7 +21822,7 @@
         <v>45107</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21895,7 +21895,7 @@
         <v>44993</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21968,7 +21968,7 @@
         <v>45317</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22041,7 +22041,7 @@
         <v>45915</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22114,7 +22114,7 @@
         <v>45433</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22187,7 +22187,7 @@
         <v>45915</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22260,7 +22260,7 @@
         <v>45415</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22333,7 +22333,7 @@
         <v>45638</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22406,7 +22406,7 @@
         <v>45610</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22479,7 +22479,7 @@
         <v>45349</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22552,7 +22552,7 @@
         <v>45582</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22625,7 +22625,7 @@
         <v>44995</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22698,7 +22698,7 @@
         <v>45565</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22771,7 +22771,7 @@
         <v>45445</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22844,7 +22844,7 @@
         <v>45146</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22917,7 +22917,7 @@
         <v>45155</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22990,7 +22990,7 @@
         <v>45548</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23063,7 +23063,7 @@
         <v>44897</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23136,7 +23136,7 @@
         <v>45609</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23209,7 +23209,7 @@
         <v>45688</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23282,7 +23282,7 @@
         <v>44949</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23355,7 +23355,7 @@
         <v>45484</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23428,7 +23428,7 @@
         <v>45921</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23501,7 +23501,7 @@
         <v>45386</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23574,7 +23574,7 @@
         <v>45775</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23647,7 +23647,7 @@
         <v>44494</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23720,7 +23720,7 @@
         <v>45349</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23793,7 +23793,7 @@
         <v>45566</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23866,7 +23866,7 @@
         <v>45007</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23939,7 +23939,7 @@
         <v>45481</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24012,7 +24012,7 @@
         <v>45400</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24085,7 +24085,7 @@
         <v>45400</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24158,7 +24158,7 @@
         <v>44580</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24231,7 +24231,7 @@
         <v>45559</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24309,7 +24309,7 @@
         <v>45022</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24382,7 +24382,7 @@
         <v>45022</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24455,7 +24455,7 @@
         <v>44839</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24528,7 +24528,7 @@
         <v>44955</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24601,7 +24601,7 @@
         <v>45743</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24674,7 +24674,7 @@
         <v>45455</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24747,7 +24747,7 @@
         <v>45126</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24820,7 +24820,7 @@
         <v>45126</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24893,7 +24893,7 @@
         <v>45191</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24966,7 +24966,7 @@
         <v>45126</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25039,7 +25039,7 @@
         <v>45098</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25112,7 +25112,7 @@
         <v>45211</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25185,7 +25185,7 @@
         <v>45205</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25258,7 +25258,7 @@
         <v>45167</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25331,7 +25331,7 @@
         <v>45040</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25404,7 +25404,7 @@
         <v>45166</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25477,7 +25477,7 @@
         <v>45931</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25550,7 +25550,7 @@
         <v>45252</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25623,7 +25623,7 @@
         <v>45644</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25696,7 +25696,7 @@
         <v>45392</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25769,7 +25769,7 @@
         <v>44995</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25842,7 +25842,7 @@
         <v>44973</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25920,7 +25920,7 @@
         <v>44594</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25993,7 +25993,7 @@
         <v>45084</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26066,7 +26066,7 @@
         <v>44524</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26139,7 +26139,7 @@
         <v>44978</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26212,7 +26212,7 @@
         <v>45800</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26285,7 +26285,7 @@
         <v>45537</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26358,7 +26358,7 @@
         <v>45707</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26431,7 +26431,7 @@
         <v>45622</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26504,7 +26504,7 @@
         <v>45159</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26577,7 +26577,7 @@
         <v>44977</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26650,7 +26650,7 @@
         <v>45573</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26723,7 +26723,7 @@
         <v>44953</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26796,7 +26796,7 @@
         <v>44690</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26869,7 +26869,7 @@
         <v>45021</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26942,7 +26942,7 @@
         <v>45225</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27015,7 +27015,7 @@
         <v>45665</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27088,7 +27088,7 @@
         <v>45327</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27161,7 +27161,7 @@
         <v>45048</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27234,7 +27234,7 @@
         <v>44783</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27307,7 +27307,7 @@
         <v>45804</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27380,7 +27380,7 @@
         <v>44958</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27453,7 +27453,7 @@
         <v>44978</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27526,7 +27526,7 @@
         <v>45938</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27599,7 +27599,7 @@
         <v>45769</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27672,7 +27672,7 @@
         <v>45182</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27745,7 +27745,7 @@
         <v>45091</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27818,7 +27818,7 @@
         <v>44652</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27891,7 +27891,7 @@
         <v>44748</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27964,7 +27964,7 @@
         <v>45230</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28037,7 +28037,7 @@
         <v>45062</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28110,7 +28110,7 @@
         <v>45938</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28183,7 +28183,7 @@
         <v>45938</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28256,7 +28256,7 @@
         <v>45191</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28329,7 +28329,7 @@
         <v>45095</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28402,7 +28402,7 @@
         <v>45232</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28475,7 +28475,7 @@
         <v>45938</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28548,7 +28548,7 @@
         <v>44777</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28621,7 +28621,7 @@
         <v>44960</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28694,7 +28694,7 @@
         <v>45362</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28767,7 +28767,7 @@
         <v>45009</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28840,7 +28840,7 @@
         <v>45009</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28913,7 +28913,7 @@
         <v>45182</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28986,7 +28986,7 @@
         <v>45422</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29059,7 +29059,7 @@
         <v>45559</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29132,7 +29132,7 @@
         <v>45084</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29205,7 +29205,7 @@
         <v>45813</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29278,7 +29278,7 @@
         <v>45355</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29351,7 +29351,7 @@
         <v>45392</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29424,7 +29424,7 @@
         <v>44699</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29497,7 +29497,7 @@
         <v>44700</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29570,7 +29570,7 @@
         <v>45230</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29643,7 +29643,7 @@
         <v>45148</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29716,7 +29716,7 @@
         <v>44965</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29789,7 +29789,7 @@
         <v>45531</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29862,7 +29862,7 @@
         <v>45126</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29935,7 +29935,7 @@
         <v>45434</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30008,7 +30008,7 @@
         <v>45629</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30081,7 +30081,7 @@
         <v>44852</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30154,7 +30154,7 @@
         <v>45258</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30227,7 +30227,7 @@
         <v>45825</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30300,7 +30300,7 @@
         <v>45826</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30373,7 +30373,7 @@
         <v>45826</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30446,7 +30446,7 @@
         <v>45826</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30519,7 +30519,7 @@
         <v>45826</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30592,7 +30592,7 @@
         <v>45826</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30665,7 +30665,7 @@
         <v>44619</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30738,7 +30738,7 @@
         <v>45574</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30811,7 +30811,7 @@
         <v>45009</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30884,7 +30884,7 @@
         <v>45009</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30957,7 +30957,7 @@
         <v>45107</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31030,7 +31030,7 @@
         <v>45826</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31103,7 +31103,7 @@
         <v>44922</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31176,7 +31176,7 @@
         <v>44743</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31249,7 +31249,7 @@
         <v>45408</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31322,7 +31322,7 @@
         <v>45394</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31395,7 +31395,7 @@
         <v>45092</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31468,7 +31468,7 @@
         <v>45832</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31541,7 +31541,7 @@
         <v>45953</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31614,7 +31614,7 @@
         <v>45901</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31687,7 +31687,7 @@
         <v>45960</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31760,7 +31760,7 @@
         <v>45229</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31833,7 +31833,7 @@
         <v>44728</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31906,7 +31906,7 @@
         <v>45515</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31979,7 +31979,7 @@
         <v>45964</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32052,7 +32052,7 @@
         <v>45188</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32130,7 +32130,7 @@
         <v>45188</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32208,7 +32208,7 @@
         <v>45400</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32281,7 +32281,7 @@
         <v>45964</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32354,7 +32354,7 @@
         <v>45107</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32427,7 +32427,7 @@
         <v>44673</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32500,7 +32500,7 @@
         <v>45079</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32573,7 +32573,7 @@
         <v>45164</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32646,7 +32646,7 @@
         <v>44749</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32719,7 +32719,7 @@
         <v>44726</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32792,7 +32792,7 @@
         <v>45967</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32865,7 +32865,7 @@
         <v>45645</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32938,7 +32938,7 @@
         <v>45967</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33011,7 +33011,7 @@
         <v>44802</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33084,7 +33084,7 @@
         <v>45614</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33157,7 +33157,7 @@
         <v>45805</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33230,7 +33230,7 @@
         <v>45113</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33303,7 +33303,7 @@
         <v>45971</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33376,7 +33376,7 @@
         <v>45596</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33449,7 +33449,7 @@
         <v>45621</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33522,7 +33522,7 @@
         <v>45258</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33595,7 +33595,7 @@
         <v>45258</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33668,7 +33668,7 @@
         <v>45102</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33741,7 +33741,7 @@
         <v>45735</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33814,7 +33814,7 @@
         <v>45845</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33887,7 +33887,7 @@
         <v>45727</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33960,7 +33960,7 @@
         <v>45102</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34033,7 +34033,7 @@
         <v>44729</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34106,7 +34106,7 @@
         <v>45475</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34179,7 +34179,7 @@
         <v>45716</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34252,7 +34252,7 @@
         <v>45772</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34325,7 +34325,7 @@
         <v>45775</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34398,7 +34398,7 @@
         <v>45849</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34471,7 +34471,7 @@
         <v>45716</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34544,7 +34544,7 @@
         <v>45851</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34617,7 +34617,7 @@
         <v>45851</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34690,7 +34690,7 @@
         <v>44781</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34763,7 +34763,7 @@
         <v>45148</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34836,7 +34836,7 @@
         <v>44984</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34909,7 +34909,7 @@
         <v>44761</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34982,7 +34982,7 @@
         <v>45113</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -35055,7 +35055,7 @@
         <v>45857</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -35128,7 +35128,7 @@
         <v>45742</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35201,7 +35201,7 @@
         <v>44799</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35274,7 +35274,7 @@
         <v>44683</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35347,7 +35347,7 @@
         <v>45750</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35420,7 +35420,7 @@
         <v>44827</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35493,7 +35493,7 @@
         <v>45301</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35566,7 +35566,7 @@
         <v>45863</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35639,7 +35639,7 @@
         <v>45790</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35712,7 +35712,7 @@
         <v>45309</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35785,7 +35785,7 @@
         <v>45126</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35858,7 +35858,7 @@
         <v>45445</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35931,7 +35931,7 @@
         <v>45307</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36004,7 +36004,7 @@
         <v>45716</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -36077,7 +36077,7 @@
         <v>45190</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36150,7 +36150,7 @@
         <v>45021</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36223,7 +36223,7 @@
         <v>45310</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36296,7 +36296,7 @@
         <v>45067</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36369,7 +36369,7 @@
         <v>44851</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36442,7 +36442,7 @@
         <v>45979</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36515,7 +36515,7 @@
         <v>45028</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36588,7 +36588,7 @@
         <v>45089</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36661,7 +36661,7 @@
         <v>45772</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36734,7 +36734,7 @@
         <v>44893</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36807,7 +36807,7 @@
         <v>45200</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36880,7 +36880,7 @@
         <v>45740</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36953,7 +36953,7 @@
         <v>45881</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37026,7 +37026,7 @@
         <v>44518</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -37099,7 +37099,7 @@
         <v>45222</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37172,7 +37172,7 @@
         <v>45159</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37245,7 +37245,7 @@
         <v>44769</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37318,7 +37318,7 @@
         <v>45211</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37391,7 +37391,7 @@
         <v>45187</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37464,7 +37464,7 @@
         <v>44879</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37537,7 +37537,7 @@
         <v>45401</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37610,7 +37610,7 @@
         <v>44851</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37683,7 +37683,7 @@
         <v>45049</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37756,7 +37756,7 @@
         <v>45196</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37829,7 +37829,7 @@
         <v>45392</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37902,7 +37902,7 @@
         <v>44897</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37975,7 +37975,7 @@
         <v>44690</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -38048,7 +38048,7 @@
         <v>45323</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -38121,7 +38121,7 @@
         <v>44524</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38194,7 +38194,7 @@
         <v>45415</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38267,7 +38267,7 @@
         <v>46107</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38340,7 +38340,7 @@
         <v>44487</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38413,7 +38413,7 @@
         <v>45323</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38486,7 +38486,7 @@
         <v>45068</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38564,7 +38564,7 @@
         <v>45755</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38637,7 +38637,7 @@
         <v>45111</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38710,7 +38710,7 @@
         <v>45772</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38783,7 +38783,7 @@
         <v>45637</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38856,7 +38856,7 @@
         <v>45049</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38929,7 +38929,7 @@
         <v>45466</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -39002,7 +39002,7 @@
         <v>45989</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -39075,7 +39075,7 @@
         <v>45327</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -39148,7 +39148,7 @@
         <v>44488</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39226,7 +39226,7 @@
         <v>45296</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39299,7 +39299,7 @@
         <v>45994</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39372,7 +39372,7 @@
         <v>45084</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39445,7 +39445,7 @@
         <v>46120</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39518,7 +39518,7 @@
         <v>45986</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39591,7 +39591,7 @@
         <v>44530</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39664,7 +39664,7 @@
         <v>44586</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39737,7 +39737,7 @@
         <v>46127</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39810,7 +39810,7 @@
         <v>46127</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39883,7 +39883,7 @@
         <v>46127</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39956,7 +39956,7 @@
         <v>44589</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -40029,7 +40029,7 @@
         <v>44507</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -40102,7 +40102,7 @@
         <v>44938</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40175,7 +40175,7 @@
         <v>46134</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40248,7 +40248,7 @@
         <v>46133</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40321,7 +40321,7 @@
         <v>44979</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40394,7 +40394,7 @@
         <v>45632</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40467,7 +40467,7 @@
         <v>45401</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40540,7 +40540,7 @@
         <v>45551</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40618,7 +40618,7 @@
         <v>45606</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40691,7 +40691,7 @@
         <v>45819</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40764,7 +40764,7 @@
         <v>45818</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40837,7 +40837,7 @@
         <v>45972</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40910,7 +40910,7 @@
         <v>45370</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40983,7 +40983,7 @@
         <v>45091</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -41056,7 +41056,7 @@
         <v>45149</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -41129,7 +41129,7 @@
         <v>45191</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41202,7 +41202,7 @@
         <v>45966</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41275,7 +41275,7 @@
         <v>45155</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41348,7 +41348,7 @@
         <v>45251</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41421,7 +41421,7 @@
         <v>44930</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41494,7 +41494,7 @@
         <v>45901</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41567,7 +41567,7 @@
         <v>45392</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41640,7 +41640,7 @@
         <v>46006</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41713,7 +41713,7 @@
         <v>45181</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41786,7 +41786,7 @@
         <v>45818</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41859,7 +41859,7 @@
         <v>44993</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41932,7 +41932,7 @@
         <v>45905</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -42005,7 +42005,7 @@
         <v>44728</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -42078,7 +42078,7 @@
         <v>46043</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -42151,7 +42151,7 @@
         <v>45425</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42224,7 +42224,7 @@
         <v>45036</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42297,7 +42297,7 @@
         <v>44834</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42370,7 +42370,7 @@
         <v>46024</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42443,7 +42443,7 @@
         <v>45051</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42516,7 +42516,7 @@
         <v>45051</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42589,7 +42589,7 @@
         <v>45590</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42662,7 +42662,7 @@
         <v>44808</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42735,7 +42735,7 @@
         <v>45524</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42808,7 +42808,7 @@
         <v>44944</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42881,7 +42881,7 @@
         <v>45048</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42954,7 +42954,7 @@
         <v>44487</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -43032,7 +43032,7 @@
         <v>45514</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -43105,7 +43105,7 @@
         <v>45514</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43178,7 +43178,7 @@
         <v>45966</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43251,7 +43251,7 @@
         <v>45076</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43324,7 +43324,7 @@
         <v>45392</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43397,7 +43397,7 @@
         <v>45217</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43470,7 +43470,7 @@
         <v>46036</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43543,7 +43543,7 @@
         <v>45976</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43616,7 +43616,7 @@
         <v>45688</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43689,7 +43689,7 @@
         <v>46139</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43762,7 +43762,7 @@
         <v>45740</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43835,7 +43835,7 @@
         <v>45180</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43908,7 +43908,7 @@
         <v>45668</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43981,7 +43981,7 @@
         <v>45349</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -44054,7 +44054,7 @@
         <v>45349</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -44127,7 +44127,7 @@
         <v>45641</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44200,7 +44200,7 @@
         <v>46044</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44273,7 +44273,7 @@
         <v>45915</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44351,7 +44351,7 @@
         <v>44791</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44424,7 +44424,7 @@
         <v>45310</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44497,7 +44497,7 @@
         <v>44911</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44570,7 +44570,7 @@
         <v>45394</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44643,7 +44643,7 @@
         <v>46055</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44716,7 +44716,7 @@
         <v>45909</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44789,7 +44789,7 @@
         <v>45574</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44862,7 +44862,7 @@
         <v>44900</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44935,7 +44935,7 @@
         <v>45938</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -45008,7 +45008,7 @@
         <v>46049</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -45081,7 +45081,7 @@
         <v>46055</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -45154,7 +45154,7 @@
         <v>46058</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45227,7 +45227,7 @@
         <v>46142</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45300,7 +45300,7 @@
         <v>45976</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45373,7 +45373,7 @@
         <v>46062</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45446,7 +45446,7 @@
         <v>46069</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45524,7 +45524,7 @@
         <v>46071</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45602,7 +45602,7 @@
         <v>46071</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45680,7 +45680,7 @@
         <v>46072</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45753,7 +45753,7 @@
         <v>46072</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45826,7 +45826,7 @@
         <v>46071</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45904,7 +45904,7 @@
         <v>46078</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -45977,7 +45977,7 @@
         <v>45789</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -46050,7 +46050,7 @@
         <v>46079</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -46123,7 +46123,7 @@
         <v>46079</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -46196,7 +46196,7 @@
         <v>46085</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -46269,7 +46269,7 @@
         <v>46085</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -46342,7 +46342,7 @@
         <v>46069</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46420,7 +46420,7 @@
         <v>46085</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46493,7 +46493,7 @@
         <v>45707</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -46566,7 +46566,7 @@
         <v>46155</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -46639,7 +46639,7 @@
         <v>46160</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46712,7 +46712,7 @@
         <v>46090</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46785,7 +46785,7 @@
         <v>46160</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46858,7 +46858,7 @@
         <v>46162</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46931,7 +46931,7 @@
         <v>45902</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -47004,7 +47004,7 @@
         <v>46162</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -47077,7 +47077,7 @@
         <v>45923</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -47150,7 +47150,7 @@
         <v>46183</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -47223,7 +47223,7 @@
         <v>46182</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -47296,7 +47296,7 @@
         <v>46182</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -47369,7 +47369,7 @@
         <v>46185</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -47442,7 +47442,7 @@
         <v>46185</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -47515,7 +47515,7 @@
         <v>46185</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -47588,7 +47588,7 @@
         <v>46188</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -47661,7 +47661,7 @@
         <v>46188</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47734,7 +47734,7 @@
         <v>46189</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47807,7 +47807,7 @@
         <v>46188</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47880,7 +47880,7 @@
         <v>46190</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -47958,7 +47958,7 @@
         <v>46120</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -48031,7 +48031,7 @@
         <v>46196</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -48109,7 +48109,7 @@
         <v>46196</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -48187,7 +48187,7 @@
         <v>46196</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -48265,7 +48265,7 @@
         <v>46197</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -48343,7 +48343,7 @@
         <v>46197</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -48421,7 +48421,7 @@
         <v>46010</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -48494,7 +48494,7 @@
         <v>46196</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -48567,7 +48567,7 @@
         <v>46197</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -48645,7 +48645,7 @@
         <v>46198</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -48718,7 +48718,7 @@
         <v>46202</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -48791,7 +48791,7 @@
         <v>46205</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -48869,7 +48869,7 @@
         <v>46127</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -48947,7 +48947,7 @@
         <v>46211</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -49020,7 +49020,7 @@
         <v>46212</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -49093,7 +49093,7 @@
         <v>46212</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -49166,7 +49166,7 @@
         <v>46213</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -49239,7 +49239,7 @@
         <v>46268</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -49312,7 +49312,7 @@
         <v>46272</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -49385,7 +49385,7 @@
         <v>46271</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -49458,7 +49458,7 @@
         <v>46188</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -49531,7 +49531,7 @@
         <v>46273</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -49604,7 +49604,7 @@
         <v>46275</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -49677,7 +49677,7 @@
         <v>46279</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -49755,7 +49755,7 @@
         <v>46279</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -49833,7 +49833,7 @@
         <v>46279</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -49911,7 +49911,7 @@
         <v>46279</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -49989,7 +49989,7 @@
         <v>46279</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -50067,7 +50067,7 @@
         <v>46279</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -50140,7 +50140,7 @@
         <v>46279</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -50218,7 +50218,7 @@
         <v>46279</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -50296,7 +50296,7 @@
         <v>46279</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -50374,7 +50374,7 @@
         <v>46279</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -50452,7 +50452,7 @@
         <v>46279</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -50530,7 +50530,7 @@
         <v>46282</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -50603,7 +50603,7 @@
         <v>45727</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -50676,7 +50676,7 @@
         <v>46286</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -50749,7 +50749,7 @@
         <v>45706</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -50822,7 +50822,7 @@
         <v>45727</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -50895,7 +50895,7 @@
         <v>45926</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -50968,7 +50968,7 @@
         <v>46288</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -51041,7 +51041,7 @@
         <v>46244</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -51114,7 +51114,7 @@
         <v>46288</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -51187,7 +51187,7 @@
         <v>46290</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -51260,7 +51260,7 @@
         <v>46290</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -51333,7 +51333,7 @@
         <v>46290</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -51406,7 +51406,7 @@
         <v>46245</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -51479,7 +51479,7 @@
         <v>46160</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -51552,7 +51552,7 @@
         <v>46253</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -51625,7 +51625,7 @@
         <v>46251</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -51698,7 +51698,7 @@
         <v>46253</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -51771,7 +51771,7 @@
         <v>46255</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -51849,7 +51849,7 @@
         <v>46255</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -51927,7 +51927,7 @@
         <v>46134</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -52000,7 +52000,7 @@
         <v>46255</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -52078,7 +52078,7 @@
         <v>46255</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -52151,7 +52151,7 @@
         <v>45606</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -52224,7 +52224,7 @@
         <v>46255</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -52302,7 +52302,7 @@
         <v>46255</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -52380,7 +52380,7 @@
         <v>46255</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -52458,7 +52458,7 @@
         <v>46230</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -52531,7 +52531,7 @@
         <v>46255</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -52609,7 +52609,7 @@
         <v>46259</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -52682,7 +52682,7 @@
         <v>46302</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -52755,7 +52755,7 @@
         <v>46120</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -52828,7 +52828,7 @@
         <v>45716</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -52901,7 +52901,7 @@
         <v>46188</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -52974,7 +52974,7 @@
         <v>44476</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -53047,7 +53047,7 @@
         <v>45191</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -53120,7 +53120,7 @@
         <v>44959</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -53193,7 +53193,7 @@
         <v>45194</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -53266,7 +53266,7 @@
         <v>45377</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -53339,7 +53339,7 @@
         <v>45387</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -53412,7 +53412,7 @@
         <v>44903</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -53485,7 +53485,7 @@
         <v>44900</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -53558,7 +53558,7 @@
         <v>44852</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -53631,7 +53631,7 @@
         <v>45200</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -53704,7 +53704,7 @@
         <v>45534</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -53777,7 +53777,7 @@
         <v>45191</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -53850,7 +53850,7 @@
         <v>45386</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -53923,7 +53923,7 @@
         <v>45287</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -53996,7 +53996,7 @@
         <v>45386</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -54069,7 +54069,7 @@
         <v>45386</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -54142,7 +54142,7 @@
         <v>45386</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -54215,7 +54215,7 @@
         <v>45387</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -54288,7 +54288,7 @@
         <v>44519</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -54361,7 +54361,7 @@
         <v>45534</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -54434,7 +54434,7 @@
         <v>45377</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -54507,7 +54507,7 @@
         <v>44928</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -54580,7 +54580,7 @@
         <v>45377</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -54653,7 +54653,7 @@
         <v>44519</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -54726,7 +54726,7 @@
         <v>45200</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -54799,7 +54799,7 @@
         <v>44900</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -54872,7 +54872,7 @@
         <v>45330</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -54945,7 +54945,7 @@
         <v>44959</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -55018,7 +55018,7 @@
         <v>45348</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -55091,7 +55091,7 @@
         <v>45813</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -55164,7 +55164,7 @@
         <v>45813</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -55237,7 +55237,7 @@
         <v>45849</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -55310,7 +55310,7 @@
         <v>45898</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -55383,7 +55383,7 @@
         <v>45935</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -55456,7 +55456,7 @@
         <v>45978</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -55529,7 +55529,7 @@
         <v>46034</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -55602,7 +55602,7 @@
         <v>46049</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -55675,7 +55675,7 @@
         <v>46049</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -55748,7 +55748,7 @@
         <v>46065</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -55821,7 +55821,7 @@
         <v>46092</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -55894,7 +55894,7 @@
         <v>46062</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -55967,7 +55967,7 @@
         <v>46119</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -56040,7 +56040,7 @@
         <v>46119</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -56113,7 +56113,7 @@
         <v>46127</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -56186,7 +56186,7 @@
         <v>46167</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -56259,7 +56259,7 @@
         <v>46156</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -56332,7 +56332,7 @@
         <v>46183</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -56405,7 +56405,7 @@
         <v>46286</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -56478,7 +56478,7 @@
         <v>46283</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -56551,7 +56551,7 @@
         <v>46191</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -56624,7 +56624,7 @@
         <v>46276</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>

--- a/Översikt EMMABODA.xlsx
+++ b/Översikt EMMABODA.xlsx
@@ -601,7 +601,7 @@
         <v>45534</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>45440</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -830,7 +830,7 @@
         <v>45387</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>45202</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
         <v>45030</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>44480</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1276,7 +1276,7 @@
         <v>45616</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>44706</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>44811</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>45330</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1713,7 +1713,7 @@
         <v>45359</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         <v>46136</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1931,7 +1931,7 @@
         <v>45369</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
         <v>45086</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>44937</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2257,7 +2257,7 @@
         <v>46062</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2367,7 +2367,7 @@
         <v>46069</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         <v>46214</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2579,7 +2579,7 @@
         <v>44771</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2688,7 +2688,7 @@
         <v>45107</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2797,7 +2797,7 @@
         <v>45104</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2902,7 +2902,7 @@
         <v>44488</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3012,7 +3012,7 @@
         <v>45335</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3117,7 +3117,7 @@
         <v>45068</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3227,7 +3227,7 @@
         <v>45161</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3337,7 +3337,7 @@
         <v>44895</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3442,7 +3442,7 @@
         <v>45797</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3551,7 +3551,7 @@
         <v>45166</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
         <v>44762</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3761,7 +3761,7 @@
         <v>44570</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3866,7 +3866,7 @@
         <v>45092</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3971,7 +3971,7 @@
         <v>45953</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4080,7 +4080,7 @@
         <v>44495</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4189,7 +4189,7 @@
         <v>45196</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4294,7 +4294,7 @@
         <v>45967</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4399,7 +4399,7 @@
         <v>46135</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4509,7 +4509,7 @@
         <v>45763</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4618,7 +4618,7 @@
         <v>44984</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4723,7 +4723,7 @@
         <v>45229</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4832,7 +4832,7 @@
         <v>44966</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4937,7 +4937,7 @@
         <v>46213</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
         <v>46213</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5147,7 +5147,7 @@
         <v>46218</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5252,7 +5252,7 @@
         <v>46282</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5357,7 +5357,7 @@
         <v>46055</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
         <v>46253</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5567,7 +5567,7 @@
         <v>44588</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5672,7 +5672,7 @@
         <v>45509</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5777,7 +5777,7 @@
         <v>45387</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5886,7 +5886,7 @@
         <v>45611</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5995,7 +5995,7 @@
         <v>45330</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6104,7 +6104,7 @@
         <v>44852</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6213,7 +6213,7 @@
         <v>45442</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6318,7 +6318,7 @@
         <v>45153</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6423,7 +6423,7 @@
         <v>45386</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6528,7 +6528,7 @@
         <v>45685</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6637,7 +6637,7 @@
         <v>45813</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6746,7 +6746,7 @@
         <v>46275</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6855,7 +6855,7 @@
         <v>44530</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6928,7 +6928,7 @@
         <v>44496</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7001,7 +7001,7 @@
         <v>44764</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7074,7 +7074,7 @@
         <v>44488</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         <v>44496</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7220,7 +7220,7 @@
         <v>44530</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7293,7 +7293,7 @@
         <v>44490</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7366,7 +7366,7 @@
         <v>44529</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7439,7 +7439,7 @@
         <v>44601</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7512,7 +7512,7 @@
         <v>44600</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7585,7 +7585,7 @@
         <v>44507</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7658,7 +7658,7 @@
         <v>44507</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7731,7 +7731,7 @@
         <v>44507</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7804,7 +7804,7 @@
         <v>44728</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7877,7 +7877,7 @@
         <v>44599</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7950,7 +7950,7 @@
         <v>44691</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8023,7 +8023,7 @@
         <v>44628</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8096,7 +8096,7 @@
         <v>44504</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8169,7 +8169,7 @@
         <v>44515</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8242,7 +8242,7 @@
         <v>44851</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8315,7 +8315,7 @@
         <v>44860</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8388,7 +8388,7 @@
         <v>44523</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8461,7 +8461,7 @@
         <v>44648</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8534,7 +8534,7 @@
         <v>44628</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8607,7 +8607,7 @@
         <v>44788</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8680,7 +8680,7 @@
         <v>44627</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8753,7 +8753,7 @@
         <v>44498</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8826,7 +8826,7 @@
         <v>44768</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8899,7 +8899,7 @@
         <v>44851</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8972,7 +8972,7 @@
         <v>44529</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9045,7 +9045,7 @@
         <v>44813</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9118,7 +9118,7 @@
         <v>44809</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         <v>44771</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9264,7 +9264,7 @@
         <v>44587</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9337,7 +9337,7 @@
         <v>44496</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9410,7 +9410,7 @@
         <v>44622</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9483,7 +9483,7 @@
         <v>44488</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9561,7 +9561,7 @@
         <v>44507</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9634,7 +9634,7 @@
         <v>44507</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9707,7 +9707,7 @@
         <v>44524</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9780,7 +9780,7 @@
         <v>44487</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9858,7 +9858,7 @@
         <v>44712</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9931,7 +9931,7 @@
         <v>44589</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10004,7 +10004,7 @@
         <v>44551</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10082,7 +10082,7 @@
         <v>44593</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10155,7 +10155,7 @@
         <v>44652</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10228,7 +10228,7 @@
         <v>44600</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10301,7 +10301,7 @@
         <v>44699</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10374,7 +10374,7 @@
         <v>44652</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10447,7 +10447,7 @@
         <v>44628</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10520,7 +10520,7 @@
         <v>44600</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10593,7 +10593,7 @@
         <v>44725</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10666,7 +10666,7 @@
         <v>44820</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10744,7 +10744,7 @@
         <v>44743</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10817,7 +10817,7 @@
         <v>44600</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10890,7 +10890,7 @@
         <v>44501</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10963,7 +10963,7 @@
         <v>44600</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11036,7 +11036,7 @@
         <v>44852</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11109,7 +11109,7 @@
         <v>44839</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11182,7 +11182,7 @@
         <v>44847</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11255,7 +11255,7 @@
         <v>44743</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11328,7 +11328,7 @@
         <v>44615</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11406,7 +11406,7 @@
         <v>44655</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11479,7 +11479,7 @@
         <v>45719</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11552,7 +11552,7 @@
         <v>44722</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11625,7 +11625,7 @@
         <v>44532</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11703,7 +11703,7 @@
         <v>45189</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11776,7 +11776,7 @@
         <v>45411</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11849,7 +11849,7 @@
         <v>45099</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11922,7 +11922,7 @@
         <v>44530</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11995,7 +11995,7 @@
         <v>44788</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12068,7 +12068,7 @@
         <v>44593</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12141,7 +12141,7 @@
         <v>45422</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12214,7 +12214,7 @@
         <v>44816</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12287,7 +12287,7 @@
         <v>45048</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12360,7 +12360,7 @@
         <v>44608</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12433,7 +12433,7 @@
         <v>45113</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12506,7 +12506,7 @@
         <v>45187</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12579,7 +12579,7 @@
         <v>45219</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12652,7 +12652,7 @@
         <v>45007</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12725,7 +12725,7 @@
         <v>45229</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12798,7 +12798,7 @@
         <v>45385</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12871,7 +12871,7 @@
         <v>45335</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12944,7 +12944,7 @@
         <v>45204</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13022,7 +13022,7 @@
         <v>45349</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13095,7 +13095,7 @@
         <v>45164</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13168,7 +13168,7 @@
         <v>45190</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13241,7 +13241,7 @@
         <v>45740</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13314,7 +13314,7 @@
         <v>44759</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13387,7 +13387,7 @@
         <v>45317</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13460,7 +13460,7 @@
         <v>45211</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13533,7 +13533,7 @@
         <v>45211</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13606,7 +13606,7 @@
         <v>45211</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13679,7 +13679,7 @@
         <v>44739</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13752,7 +13752,7 @@
         <v>45126</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13825,7 +13825,7 @@
         <v>44698</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13898,7 +13898,7 @@
         <v>45317</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13971,7 +13971,7 @@
         <v>45126</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14044,7 +14044,7 @@
         <v>45376</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14117,7 +14117,7 @@
         <v>44959</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14190,7 +14190,7 @@
         <v>45373</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14263,7 +14263,7 @@
         <v>45126</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14336,7 +14336,7 @@
         <v>45211</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14409,7 +14409,7 @@
         <v>45719</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14482,7 +14482,7 @@
         <v>44977</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14555,7 +14555,7 @@
         <v>45327</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14628,7 +14628,7 @@
         <v>45348</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14701,7 +14701,7 @@
         <v>45461</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14774,7 +14774,7 @@
         <v>45069</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14847,7 +14847,7 @@
         <v>45069</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14920,7 +14920,7 @@
         <v>45397</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14993,7 +14993,7 @@
         <v>44861</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15066,7 +15066,7 @@
         <v>45126</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15139,7 +15139,7 @@
         <v>45615</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15212,7 +15212,7 @@
         <v>45204</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15290,7 +15290,7 @@
         <v>44728</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15363,7 +15363,7 @@
         <v>45335</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15436,7 +15436,7 @@
         <v>45093</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15509,7 +15509,7 @@
         <v>45369</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15582,7 +15582,7 @@
         <v>45273</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15660,7 +15660,7 @@
         <v>45204</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15738,7 +15738,7 @@
         <v>45595</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15811,7 +15811,7 @@
         <v>45615</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15884,7 +15884,7 @@
         <v>45400</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15957,7 +15957,7 @@
         <v>45433</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16030,7 +16030,7 @@
         <v>44907</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16103,7 +16103,7 @@
         <v>45474</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16176,7 +16176,7 @@
         <v>45237</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16249,7 +16249,7 @@
         <v>44531</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16322,7 +16322,7 @@
         <v>44504</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16395,7 +16395,7 @@
         <v>45103</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16468,7 +16468,7 @@
         <v>45474</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16541,7 +16541,7 @@
         <v>44852</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16614,7 +16614,7 @@
         <v>45121</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16687,7 +16687,7 @@
         <v>45341</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16760,7 +16760,7 @@
         <v>45341</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16833,7 +16833,7 @@
         <v>45887</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16906,7 +16906,7 @@
         <v>45887</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16979,7 +16979,7 @@
         <v>45161</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17057,7 +17057,7 @@
         <v>44953</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17130,7 +17130,7 @@
         <v>45323</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17203,7 +17203,7 @@
         <v>44953</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17276,7 +17276,7 @@
         <v>45665</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17349,7 +17349,7 @@
         <v>44572</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17422,7 +17422,7 @@
         <v>45126</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17495,7 +17495,7 @@
         <v>45273</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17573,7 +17573,7 @@
         <v>45202</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17646,7 +17646,7 @@
         <v>45531</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17719,7 +17719,7 @@
         <v>45749</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17792,7 +17792,7 @@
         <v>45600</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17865,7 +17865,7 @@
         <v>45281</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17938,7 +17938,7 @@
         <v>45155</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18011,7 +18011,7 @@
         <v>44593</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18084,7 +18084,7 @@
         <v>45477</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18157,7 +18157,7 @@
         <v>45769</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18230,7 +18230,7 @@
         <v>45514</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18303,7 +18303,7 @@
         <v>45126</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18376,7 +18376,7 @@
         <v>44951</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18449,7 +18449,7 @@
         <v>44897</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18522,7 +18522,7 @@
         <v>45003</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18595,7 +18595,7 @@
         <v>45716</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18668,7 +18668,7 @@
         <v>44984</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18741,7 +18741,7 @@
         <v>45019</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18814,7 +18814,7 @@
         <v>45161</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18892,7 +18892,7 @@
         <v>44980</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18965,7 +18965,7 @@
         <v>45700</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19038,7 +19038,7 @@
         <v>44519</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19111,7 +19111,7 @@
         <v>45741</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19184,7 +19184,7 @@
         <v>44530</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19257,7 +19257,7 @@
         <v>44519</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19330,7 +19330,7 @@
         <v>45561</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19408,7 +19408,7 @@
         <v>45189</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19481,7 +19481,7 @@
         <v>45189</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19554,7 +19554,7 @@
         <v>44550</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19627,7 +19627,7 @@
         <v>44840</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19705,7 +19705,7 @@
         <v>45099</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19778,7 +19778,7 @@
         <v>45070</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19851,7 +19851,7 @@
         <v>45475</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19924,7 +19924,7 @@
         <v>44979</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19997,7 +19997,7 @@
         <v>44896</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20070,7 +20070,7 @@
         <v>45681</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20143,7 +20143,7 @@
         <v>44900</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20216,7 +20216,7 @@
         <v>45537</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20289,7 +20289,7 @@
         <v>45132</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20362,7 +20362,7 @@
         <v>45562</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20435,7 +20435,7 @@
         <v>44600</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20508,7 +20508,7 @@
         <v>45908</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20581,7 +20581,7 @@
         <v>45551</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20654,7 +20654,7 @@
         <v>45909</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20727,7 +20727,7 @@
         <v>45523</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20800,7 +20800,7 @@
         <v>45475</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20873,7 +20873,7 @@
         <v>45215</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20946,7 +20946,7 @@
         <v>44949</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21019,7 +21019,7 @@
         <v>45684</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21092,7 +21092,7 @@
         <v>45624</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21165,7 +21165,7 @@
         <v>45037</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21238,7 +21238,7 @@
         <v>45534</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21311,7 +21311,7 @@
         <v>45484</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21384,7 +21384,7 @@
         <v>45351</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21457,7 +21457,7 @@
         <v>44982</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21530,7 +21530,7 @@
         <v>44893</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21603,7 +21603,7 @@
         <v>45915</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21676,7 +21676,7 @@
         <v>45587</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21749,7 +21749,7 @@
         <v>44683</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21822,7 +21822,7 @@
         <v>45107</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21895,7 +21895,7 @@
         <v>44993</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21968,7 +21968,7 @@
         <v>45317</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22041,7 +22041,7 @@
         <v>45915</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22114,7 +22114,7 @@
         <v>45433</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22187,7 +22187,7 @@
         <v>45915</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22260,7 +22260,7 @@
         <v>45415</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22333,7 +22333,7 @@
         <v>45638</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22406,7 +22406,7 @@
         <v>45610</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22479,7 +22479,7 @@
         <v>45349</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22552,7 +22552,7 @@
         <v>45582</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22625,7 +22625,7 @@
         <v>44995</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22698,7 +22698,7 @@
         <v>45565</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22771,7 +22771,7 @@
         <v>45445</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22844,7 +22844,7 @@
         <v>45146</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22917,7 +22917,7 @@
         <v>45155</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22990,7 +22990,7 @@
         <v>45548</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23063,7 +23063,7 @@
         <v>44897</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23136,7 +23136,7 @@
         <v>45609</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23209,7 +23209,7 @@
         <v>45688</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23282,7 +23282,7 @@
         <v>44949</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23355,7 +23355,7 @@
         <v>45484</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23428,7 +23428,7 @@
         <v>45921</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23501,7 +23501,7 @@
         <v>45386</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23574,7 +23574,7 @@
         <v>45775</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23647,7 +23647,7 @@
         <v>44494</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23720,7 +23720,7 @@
         <v>45349</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23793,7 +23793,7 @@
         <v>45566</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23866,7 +23866,7 @@
         <v>45007</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23939,7 +23939,7 @@
         <v>45481</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24012,7 +24012,7 @@
         <v>45400</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24085,7 +24085,7 @@
         <v>45400</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24158,7 +24158,7 @@
         <v>44580</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24231,7 +24231,7 @@
         <v>45559</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24309,7 +24309,7 @@
         <v>45022</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24382,7 +24382,7 @@
         <v>45022</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24455,7 +24455,7 @@
         <v>44839</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24528,7 +24528,7 @@
         <v>44955</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24601,7 +24601,7 @@
         <v>45743</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24674,7 +24674,7 @@
         <v>45455</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24747,7 +24747,7 @@
         <v>45126</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24820,7 +24820,7 @@
         <v>45126</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24893,7 +24893,7 @@
         <v>45191</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24966,7 +24966,7 @@
         <v>45126</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25039,7 +25039,7 @@
         <v>45098</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25112,7 +25112,7 @@
         <v>45211</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25185,7 +25185,7 @@
         <v>45205</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25258,7 +25258,7 @@
         <v>45167</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25331,7 +25331,7 @@
         <v>45040</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25404,7 +25404,7 @@
         <v>45166</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25477,7 +25477,7 @@
         <v>45931</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25550,7 +25550,7 @@
         <v>45252</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25623,7 +25623,7 @@
         <v>45644</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25696,7 +25696,7 @@
         <v>45392</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25769,7 +25769,7 @@
         <v>44995</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25842,7 +25842,7 @@
         <v>44973</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25920,7 +25920,7 @@
         <v>44594</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25993,7 +25993,7 @@
         <v>45084</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26066,7 +26066,7 @@
         <v>44524</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26139,7 +26139,7 @@
         <v>44978</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26212,7 +26212,7 @@
         <v>45800</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26285,7 +26285,7 @@
         <v>45537</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26358,7 +26358,7 @@
         <v>45707</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26431,7 +26431,7 @@
         <v>45622</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26504,7 +26504,7 @@
         <v>45159</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26577,7 +26577,7 @@
         <v>44977</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26650,7 +26650,7 @@
         <v>45573</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26723,7 +26723,7 @@
         <v>44953</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26796,7 +26796,7 @@
         <v>44690</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26869,7 +26869,7 @@
         <v>45021</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26942,7 +26942,7 @@
         <v>45225</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27015,7 +27015,7 @@
         <v>45665</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27088,7 +27088,7 @@
         <v>45327</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27161,7 +27161,7 @@
         <v>45048</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27234,7 +27234,7 @@
         <v>44783</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27307,7 +27307,7 @@
         <v>45804</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27380,7 +27380,7 @@
         <v>44958</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27453,7 +27453,7 @@
         <v>44978</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27526,7 +27526,7 @@
         <v>45938</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27599,7 +27599,7 @@
         <v>45769</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27672,7 +27672,7 @@
         <v>45182</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27745,7 +27745,7 @@
         <v>45091</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27818,7 +27818,7 @@
         <v>44652</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27891,7 +27891,7 @@
         <v>44748</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27964,7 +27964,7 @@
         <v>45230</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28037,7 +28037,7 @@
         <v>45062</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28110,7 +28110,7 @@
         <v>45938</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28183,7 +28183,7 @@
         <v>45938</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28256,7 +28256,7 @@
         <v>45191</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28329,7 +28329,7 @@
         <v>45095</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28402,7 +28402,7 @@
         <v>45232</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28475,7 +28475,7 @@
         <v>45938</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28548,7 +28548,7 @@
         <v>44777</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28621,7 +28621,7 @@
         <v>44960</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28694,7 +28694,7 @@
         <v>45362</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28767,7 +28767,7 @@
         <v>45009</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28840,7 +28840,7 @@
         <v>45009</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28913,7 +28913,7 @@
         <v>45182</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28986,7 +28986,7 @@
         <v>45422</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29059,7 +29059,7 @@
         <v>45559</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29132,7 +29132,7 @@
         <v>45084</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29205,7 +29205,7 @@
         <v>45813</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29278,7 +29278,7 @@
         <v>45355</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29351,7 +29351,7 @@
         <v>45392</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29424,7 +29424,7 @@
         <v>44699</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29497,7 +29497,7 @@
         <v>44700</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29570,7 +29570,7 @@
         <v>45230</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29643,7 +29643,7 @@
         <v>45148</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29716,7 +29716,7 @@
         <v>44965</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29789,7 +29789,7 @@
         <v>45531</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29862,7 +29862,7 @@
         <v>45126</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29935,7 +29935,7 @@
         <v>45434</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30008,7 +30008,7 @@
         <v>45629</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30081,7 +30081,7 @@
         <v>44852</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30154,7 +30154,7 @@
         <v>45258</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30227,7 +30227,7 @@
         <v>45825</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30300,7 +30300,7 @@
         <v>45826</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30373,7 +30373,7 @@
         <v>45826</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30446,7 +30446,7 @@
         <v>45826</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30519,7 +30519,7 @@
         <v>45826</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30592,7 +30592,7 @@
         <v>45826</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30665,7 +30665,7 @@
         <v>44619</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30738,7 +30738,7 @@
         <v>45574</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30811,7 +30811,7 @@
         <v>45009</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30884,7 +30884,7 @@
         <v>45009</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30957,7 +30957,7 @@
         <v>45107</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31030,7 +31030,7 @@
         <v>45826</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31103,7 +31103,7 @@
         <v>44922</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31176,7 +31176,7 @@
         <v>44743</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31249,7 +31249,7 @@
         <v>45408</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31322,7 +31322,7 @@
         <v>45394</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31395,7 +31395,7 @@
         <v>45092</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31468,7 +31468,7 @@
         <v>45832</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31541,7 +31541,7 @@
         <v>45953</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31614,7 +31614,7 @@
         <v>45901</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31687,7 +31687,7 @@
         <v>45960</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31760,7 +31760,7 @@
         <v>45229</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31833,7 +31833,7 @@
         <v>44728</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31906,7 +31906,7 @@
         <v>45515</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31979,7 +31979,7 @@
         <v>45964</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32052,7 +32052,7 @@
         <v>45188</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32130,7 +32130,7 @@
         <v>45188</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32208,7 +32208,7 @@
         <v>45400</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32281,7 +32281,7 @@
         <v>45964</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32354,7 +32354,7 @@
         <v>45107</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32427,7 +32427,7 @@
         <v>44673</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32500,7 +32500,7 @@
         <v>45079</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32573,7 +32573,7 @@
         <v>45164</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32646,7 +32646,7 @@
         <v>44749</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32719,7 +32719,7 @@
         <v>44726</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32792,7 +32792,7 @@
         <v>45967</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32865,7 +32865,7 @@
         <v>45645</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32938,7 +32938,7 @@
         <v>45967</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33011,7 +33011,7 @@
         <v>44802</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33084,7 +33084,7 @@
         <v>45614</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33157,7 +33157,7 @@
         <v>45805</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33230,7 +33230,7 @@
         <v>45113</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33303,7 +33303,7 @@
         <v>45971</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33376,7 +33376,7 @@
         <v>45596</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33449,7 +33449,7 @@
         <v>45621</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33522,7 +33522,7 @@
         <v>45258</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33595,7 +33595,7 @@
         <v>45258</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33668,7 +33668,7 @@
         <v>45102</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33741,7 +33741,7 @@
         <v>45735</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33814,7 +33814,7 @@
         <v>45845</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33887,7 +33887,7 @@
         <v>45727</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33960,7 +33960,7 @@
         <v>45102</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34033,7 +34033,7 @@
         <v>44729</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34106,7 +34106,7 @@
         <v>45475</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34179,7 +34179,7 @@
         <v>45716</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34252,7 +34252,7 @@
         <v>45772</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34325,7 +34325,7 @@
         <v>45775</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34398,7 +34398,7 @@
         <v>45849</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34471,7 +34471,7 @@
         <v>45716</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34544,7 +34544,7 @@
         <v>45851</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34617,7 +34617,7 @@
         <v>45851</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34690,7 +34690,7 @@
         <v>44781</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34763,7 +34763,7 @@
         <v>45148</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34836,7 +34836,7 @@
         <v>44984</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34909,7 +34909,7 @@
         <v>44761</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34982,7 +34982,7 @@
         <v>45113</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -35055,7 +35055,7 @@
         <v>45857</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -35128,7 +35128,7 @@
         <v>45742</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35201,7 +35201,7 @@
         <v>44799</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35274,7 +35274,7 @@
         <v>44683</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35347,7 +35347,7 @@
         <v>45750</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35420,7 +35420,7 @@
         <v>44827</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35493,7 +35493,7 @@
         <v>45301</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35566,7 +35566,7 @@
         <v>45863</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35639,7 +35639,7 @@
         <v>45790</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35712,7 +35712,7 @@
         <v>45309</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35785,7 +35785,7 @@
         <v>45126</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35858,7 +35858,7 @@
         <v>45445</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35931,7 +35931,7 @@
         <v>45307</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36004,7 +36004,7 @@
         <v>45716</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -36077,7 +36077,7 @@
         <v>45190</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36150,7 +36150,7 @@
         <v>45021</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36223,7 +36223,7 @@
         <v>45310</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36296,7 +36296,7 @@
         <v>45067</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36369,7 +36369,7 @@
         <v>44851</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36442,7 +36442,7 @@
         <v>45979</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36515,7 +36515,7 @@
         <v>45028</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36588,7 +36588,7 @@
         <v>45089</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36661,7 +36661,7 @@
         <v>45772</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36734,7 +36734,7 @@
         <v>44893</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36807,7 +36807,7 @@
         <v>45200</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36880,7 +36880,7 @@
         <v>45740</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36953,7 +36953,7 @@
         <v>45881</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37026,7 +37026,7 @@
         <v>44518</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -37099,7 +37099,7 @@
         <v>45222</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37172,7 +37172,7 @@
         <v>45159</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37245,7 +37245,7 @@
         <v>44769</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37318,7 +37318,7 @@
         <v>45211</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37391,7 +37391,7 @@
         <v>45187</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37464,7 +37464,7 @@
         <v>44879</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37537,7 +37537,7 @@
         <v>45401</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37610,7 +37610,7 @@
         <v>44851</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37683,7 +37683,7 @@
         <v>45049</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37756,7 +37756,7 @@
         <v>45196</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37829,7 +37829,7 @@
         <v>45392</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37902,7 +37902,7 @@
         <v>44897</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37975,7 +37975,7 @@
         <v>44690</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -38048,7 +38048,7 @@
         <v>45323</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -38121,7 +38121,7 @@
         <v>44524</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38194,7 +38194,7 @@
         <v>45415</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38267,7 +38267,7 @@
         <v>46107</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38340,7 +38340,7 @@
         <v>44487</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38413,7 +38413,7 @@
         <v>45323</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38486,7 +38486,7 @@
         <v>45068</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38564,7 +38564,7 @@
         <v>45755</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38637,7 +38637,7 @@
         <v>45111</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38710,7 +38710,7 @@
         <v>45772</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38783,7 +38783,7 @@
         <v>45637</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38856,7 +38856,7 @@
         <v>45049</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38929,7 +38929,7 @@
         <v>45466</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -39002,7 +39002,7 @@
         <v>45989</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -39075,7 +39075,7 @@
         <v>45327</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -39148,7 +39148,7 @@
         <v>44488</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39226,7 +39226,7 @@
         <v>45296</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39299,7 +39299,7 @@
         <v>45994</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39372,7 +39372,7 @@
         <v>45084</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39445,7 +39445,7 @@
         <v>46120</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39518,7 +39518,7 @@
         <v>45986</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39591,7 +39591,7 @@
         <v>44530</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39664,7 +39664,7 @@
         <v>44586</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39737,7 +39737,7 @@
         <v>46127</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39810,7 +39810,7 @@
         <v>46127</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39883,7 +39883,7 @@
         <v>46127</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39956,7 +39956,7 @@
         <v>44589</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -40029,7 +40029,7 @@
         <v>44507</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -40102,7 +40102,7 @@
         <v>44938</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40175,7 +40175,7 @@
         <v>46134</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40248,7 +40248,7 @@
         <v>46133</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40321,7 +40321,7 @@
         <v>44979</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40394,7 +40394,7 @@
         <v>45632</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40467,7 +40467,7 @@
         <v>45401</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40540,7 +40540,7 @@
         <v>45551</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40618,7 +40618,7 @@
         <v>45606</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40691,7 +40691,7 @@
         <v>45819</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40764,7 +40764,7 @@
         <v>45818</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40837,7 +40837,7 @@
         <v>45972</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40910,7 +40910,7 @@
         <v>45370</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40983,7 +40983,7 @@
         <v>45091</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -41056,7 +41056,7 @@
         <v>45149</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -41129,7 +41129,7 @@
         <v>45191</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41202,7 +41202,7 @@
         <v>45966</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41275,7 +41275,7 @@
         <v>45155</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41348,7 +41348,7 @@
         <v>45251</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41421,7 +41421,7 @@
         <v>44930</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41494,7 +41494,7 @@
         <v>45901</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41567,7 +41567,7 @@
         <v>45392</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41640,7 +41640,7 @@
         <v>46006</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41713,7 +41713,7 @@
         <v>45181</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41786,7 +41786,7 @@
         <v>45818</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41859,7 +41859,7 @@
         <v>44993</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41932,7 +41932,7 @@
         <v>45905</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -42005,7 +42005,7 @@
         <v>44728</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -42078,7 +42078,7 @@
         <v>46043</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -42151,7 +42151,7 @@
         <v>45425</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42224,7 +42224,7 @@
         <v>45036</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42297,7 +42297,7 @@
         <v>44834</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42370,7 +42370,7 @@
         <v>46024</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42443,7 +42443,7 @@
         <v>45051</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42516,7 +42516,7 @@
         <v>45051</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42589,7 +42589,7 @@
         <v>45590</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42662,7 +42662,7 @@
         <v>44808</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42735,7 +42735,7 @@
         <v>45524</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42808,7 +42808,7 @@
         <v>44944</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42881,7 +42881,7 @@
         <v>45048</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42954,7 +42954,7 @@
         <v>44487</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -43032,7 +43032,7 @@
         <v>45514</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -43105,7 +43105,7 @@
         <v>45514</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43178,7 +43178,7 @@
         <v>45966</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43251,7 +43251,7 @@
         <v>45076</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43324,7 +43324,7 @@
         <v>45392</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43397,7 +43397,7 @@
         <v>45217</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43470,7 +43470,7 @@
         <v>46036</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43543,7 +43543,7 @@
         <v>45976</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43616,7 +43616,7 @@
         <v>45688</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43689,7 +43689,7 @@
         <v>46139</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43762,7 +43762,7 @@
         <v>45740</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43835,7 +43835,7 @@
         <v>45180</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43908,7 +43908,7 @@
         <v>45668</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43981,7 +43981,7 @@
         <v>45349</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -44054,7 +44054,7 @@
         <v>45349</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -44127,7 +44127,7 @@
         <v>45641</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44200,7 +44200,7 @@
         <v>46044</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44273,7 +44273,7 @@
         <v>45915</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44351,7 +44351,7 @@
         <v>44791</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44424,7 +44424,7 @@
         <v>45310</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44497,7 +44497,7 @@
         <v>44911</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44570,7 +44570,7 @@
         <v>45394</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44643,7 +44643,7 @@
         <v>46055</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44716,7 +44716,7 @@
         <v>45909</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44789,7 +44789,7 @@
         <v>45574</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44862,7 +44862,7 @@
         <v>44900</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44935,7 +44935,7 @@
         <v>45938</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -45008,7 +45008,7 @@
         <v>46049</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -45081,7 +45081,7 @@
         <v>46055</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -45154,7 +45154,7 @@
         <v>46058</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45227,7 +45227,7 @@
         <v>46142</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45300,7 +45300,7 @@
         <v>45976</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45373,7 +45373,7 @@
         <v>46062</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45446,7 +45446,7 @@
         <v>46069</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45524,7 +45524,7 @@
         <v>46071</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45602,7 +45602,7 @@
         <v>46071</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45680,7 +45680,7 @@
         <v>46072</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45753,7 +45753,7 @@
         <v>46072</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45826,7 +45826,7 @@
         <v>46071</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45904,7 +45904,7 @@
         <v>46078</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -45977,7 +45977,7 @@
         <v>45789</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -46050,7 +46050,7 @@
         <v>46079</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -46123,7 +46123,7 @@
         <v>46079</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -46196,7 +46196,7 @@
         <v>46085</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -46269,7 +46269,7 @@
         <v>46085</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -46342,7 +46342,7 @@
         <v>46069</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46420,7 +46420,7 @@
         <v>46085</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46493,7 +46493,7 @@
         <v>45707</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -46566,7 +46566,7 @@
         <v>46155</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -46639,7 +46639,7 @@
         <v>46160</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46712,7 +46712,7 @@
         <v>46090</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46785,7 +46785,7 @@
         <v>46160</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46858,7 +46858,7 @@
         <v>46162</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46931,7 +46931,7 @@
         <v>45902</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -47004,7 +47004,7 @@
         <v>46162</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -47077,7 +47077,7 @@
         <v>45923</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -47150,7 +47150,7 @@
         <v>46183</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -47223,7 +47223,7 @@
         <v>46182</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -47296,7 +47296,7 @@
         <v>46182</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -47369,7 +47369,7 @@
         <v>46185</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -47442,7 +47442,7 @@
         <v>46185</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -47515,7 +47515,7 @@
         <v>46185</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -47588,7 +47588,7 @@
         <v>46188</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -47661,7 +47661,7 @@
         <v>46188</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47734,7 +47734,7 @@
         <v>46189</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47807,7 +47807,7 @@
         <v>46188</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47880,7 +47880,7 @@
         <v>46190</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -47958,7 +47958,7 @@
         <v>46120</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -48031,7 +48031,7 @@
         <v>46196</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -48109,7 +48109,7 @@
         <v>46196</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -48187,7 +48187,7 @@
         <v>46196</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -48265,7 +48265,7 @@
         <v>46197</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -48343,7 +48343,7 @@
         <v>46197</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -48421,7 +48421,7 @@
         <v>46010</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -48494,7 +48494,7 @@
         <v>46196</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -48567,7 +48567,7 @@
         <v>46197</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -48645,7 +48645,7 @@
         <v>46198</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -48718,7 +48718,7 @@
         <v>46202</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -48791,7 +48791,7 @@
         <v>46205</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -48869,7 +48869,7 @@
         <v>46127</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -48947,7 +48947,7 @@
         <v>46211</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -49020,7 +49020,7 @@
         <v>46212</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -49093,7 +49093,7 @@
         <v>46212</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -49166,7 +49166,7 @@
         <v>46213</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -49239,7 +49239,7 @@
         <v>46268</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -49312,7 +49312,7 @@
         <v>46272</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -49385,7 +49385,7 @@
         <v>46271</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -49458,7 +49458,7 @@
         <v>46188</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -49531,7 +49531,7 @@
         <v>46273</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -49604,7 +49604,7 @@
         <v>46275</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -49677,7 +49677,7 @@
         <v>46279</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -49755,7 +49755,7 @@
         <v>46279</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -49833,7 +49833,7 @@
         <v>46279</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -49911,7 +49911,7 @@
         <v>46279</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -49989,7 +49989,7 @@
         <v>46279</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -50067,7 +50067,7 @@
         <v>46279</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -50140,7 +50140,7 @@
         <v>46279</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -50218,7 +50218,7 @@
         <v>46279</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -50296,7 +50296,7 @@
         <v>46279</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -50374,7 +50374,7 @@
         <v>46279</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -50452,7 +50452,7 @@
         <v>46279</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -50530,7 +50530,7 @@
         <v>46282</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -50603,7 +50603,7 @@
         <v>45727</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -50676,7 +50676,7 @@
         <v>46286</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -50749,7 +50749,7 @@
         <v>45706</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -50822,7 +50822,7 @@
         <v>45727</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -50895,7 +50895,7 @@
         <v>45926</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -50968,7 +50968,7 @@
         <v>46288</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -51041,7 +51041,7 @@
         <v>46244</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -51114,7 +51114,7 @@
         <v>46288</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -51187,7 +51187,7 @@
         <v>46290</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -51260,7 +51260,7 @@
         <v>46290</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -51333,7 +51333,7 @@
         <v>46290</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -51406,7 +51406,7 @@
         <v>46245</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -51479,7 +51479,7 @@
         <v>46160</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -51552,7 +51552,7 @@
         <v>46253</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -51625,7 +51625,7 @@
         <v>46251</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -51698,7 +51698,7 @@
         <v>46253</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -51771,7 +51771,7 @@
         <v>46255</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -51849,7 +51849,7 @@
         <v>46255</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -51927,7 +51927,7 @@
         <v>46134</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -52000,7 +52000,7 @@
         <v>46255</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -52078,7 +52078,7 @@
         <v>46255</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -52151,7 +52151,7 @@
         <v>45606</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -52224,7 +52224,7 @@
         <v>46255</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -52302,7 +52302,7 @@
         <v>46255</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -52380,7 +52380,7 @@
         <v>46255</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -52458,7 +52458,7 @@
         <v>46230</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -52531,7 +52531,7 @@
         <v>46255</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -52609,7 +52609,7 @@
         <v>46259</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -52682,7 +52682,7 @@
         <v>46302</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -52755,7 +52755,7 @@
         <v>46120</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -52828,7 +52828,7 @@
         <v>45716</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -52901,7 +52901,7 @@
         <v>46188</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -52974,7 +52974,7 @@
         <v>44476</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -53047,7 +53047,7 @@
         <v>45191</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -53120,7 +53120,7 @@
         <v>44959</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -53193,7 +53193,7 @@
         <v>45194</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -53266,7 +53266,7 @@
         <v>45377</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -53339,7 +53339,7 @@
         <v>45387</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -53412,7 +53412,7 @@
         <v>44903</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -53485,7 +53485,7 @@
         <v>44900</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -53558,7 +53558,7 @@
         <v>44852</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -53631,7 +53631,7 @@
         <v>45200</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -53704,7 +53704,7 @@
         <v>45534</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -53777,7 +53777,7 @@
         <v>45191</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -53850,7 +53850,7 @@
         <v>45386</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -53923,7 +53923,7 @@
         <v>45287</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -53996,7 +53996,7 @@
         <v>45386</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -54069,7 +54069,7 @@
         <v>45386</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -54142,7 +54142,7 @@
         <v>45386</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -54215,7 +54215,7 @@
         <v>45387</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -54288,7 +54288,7 @@
         <v>44519</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -54361,7 +54361,7 @@
         <v>45534</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -54434,7 +54434,7 @@
         <v>45377</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -54507,7 +54507,7 @@
         <v>44928</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -54580,7 +54580,7 @@
         <v>45377</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -54653,7 +54653,7 @@
         <v>44519</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -54726,7 +54726,7 @@
         <v>45200</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -54799,7 +54799,7 @@
         <v>44900</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -54872,7 +54872,7 @@
         <v>45330</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -54945,7 +54945,7 @@
         <v>44959</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -55018,7 +55018,7 @@
         <v>45348</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -55091,7 +55091,7 @@
         <v>45813</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -55164,7 +55164,7 @@
         <v>45813</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -55237,7 +55237,7 @@
         <v>45849</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -55310,7 +55310,7 @@
         <v>45898</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -55383,7 +55383,7 @@
         <v>45935</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -55456,7 +55456,7 @@
         <v>45978</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -55529,7 +55529,7 @@
         <v>46034</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -55602,7 +55602,7 @@
         <v>46049</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -55675,7 +55675,7 @@
         <v>46049</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -55748,7 +55748,7 @@
         <v>46065</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -55821,7 +55821,7 @@
         <v>46092</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -55894,7 +55894,7 @@
         <v>46062</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -55967,7 +55967,7 @@
         <v>46119</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -56040,7 +56040,7 @@
         <v>46119</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -56113,7 +56113,7 @@
         <v>46127</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -56186,7 +56186,7 @@
         <v>46167</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -56259,7 +56259,7 @@
         <v>46156</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -56332,7 +56332,7 @@
         <v>46183</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -56405,7 +56405,7 @@
         <v>46286</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -56478,7 +56478,7 @@
         <v>46283</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -56551,7 +56551,7 @@
         <v>46191</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -56624,7 +56624,7 @@
         <v>46276</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>

--- a/Översikt EMMABODA.xlsx
+++ b/Översikt EMMABODA.xlsx
@@ -601,7 +601,7 @@
         <v>45534</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>45440</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -830,7 +830,7 @@
         <v>45387</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>45202</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
         <v>45030</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>45616</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         <v>44706</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>44811</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         <v>45330</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1600,7 +1600,7 @@
         <v>45359</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>46136</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1818,7 +1818,7 @@
         <v>45369</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1932,7 +1932,7 @@
         <v>45086</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2038,7 +2038,7 @@
         <v>44937</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>46062</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2254,7 +2254,7 @@
         <v>46069</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2360,7 +2360,7 @@
         <v>46214</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2466,7 +2466,7 @@
         <v>44762</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2571,7 +2571,7 @@
         <v>45166</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2676,7 +2676,7 @@
         <v>44966</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2781,7 +2781,7 @@
         <v>44570</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2886,7 +2886,7 @@
         <v>44984</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2991,7 +2991,7 @@
         <v>45763</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3100,7 +3100,7 @@
         <v>45196</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3205,7 +3205,7 @@
         <v>45797</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3314,7 +3314,7 @@
         <v>45104</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3419,7 +3419,7 @@
         <v>45335</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
         <v>45953</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3633,7 +3633,7 @@
         <v>45161</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3743,7 +3743,7 @@
         <v>45068</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3853,7 +3853,7 @@
         <v>44771</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3962,7 +3962,7 @@
         <v>46135</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4072,7 +4072,7 @@
         <v>45967</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4177,7 +4177,7 @@
         <v>45229</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4286,7 +4286,7 @@
         <v>46213</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4391,7 +4391,7 @@
         <v>46213</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4496,7 +4496,7 @@
         <v>46218</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4601,7 +4601,7 @@
         <v>45107</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4710,7 +4710,7 @@
         <v>44495</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4819,7 +4819,7 @@
         <v>46282</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4924,7 +4924,7 @@
         <v>46055</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5029,7 +5029,7 @@
         <v>45092</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5134,7 +5134,7 @@
         <v>46253</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5239,7 +5239,7 @@
         <v>44488</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5349,7 +5349,7 @@
         <v>44895</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5454,7 +5454,7 @@
         <v>45509</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5559,7 +5559,7 @@
         <v>45387</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5668,7 +5668,7 @@
         <v>44588</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5773,7 +5773,7 @@
         <v>45611</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5882,7 +5882,7 @@
         <v>45330</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5991,7 +5991,7 @@
         <v>44852</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6100,7 +6100,7 @@
         <v>45442</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6205,7 +6205,7 @@
         <v>45153</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6310,7 +6310,7 @@
         <v>45386</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         <v>45685</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6524,7 +6524,7 @@
         <v>45813</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6633,7 +6633,7 @@
         <v>46275</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6742,7 +6742,7 @@
         <v>44530</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6815,7 +6815,7 @@
         <v>44488</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6888,7 +6888,7 @@
         <v>44764</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6961,7 +6961,7 @@
         <v>44530</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7034,7 +7034,7 @@
         <v>44496</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7107,7 +7107,7 @@
         <v>44529</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7180,7 +7180,7 @@
         <v>44490</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7253,7 +7253,7 @@
         <v>44601</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7326,7 +7326,7 @@
         <v>44600</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         <v>44507</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7472,7 +7472,7 @@
         <v>44507</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7545,7 +7545,7 @@
         <v>44507</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7618,7 +7618,7 @@
         <v>44728</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7691,7 +7691,7 @@
         <v>44599</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7764,7 +7764,7 @@
         <v>44496</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7837,7 +7837,7 @@
         <v>44691</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7910,7 +7910,7 @@
         <v>44628</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7983,7 +7983,7 @@
         <v>44504</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8056,7 +8056,7 @@
         <v>44515</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8129,7 +8129,7 @@
         <v>44851</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8202,7 +8202,7 @@
         <v>44860</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8275,7 +8275,7 @@
         <v>44648</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8348,7 +8348,7 @@
         <v>44523</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8421,7 +8421,7 @@
         <v>44628</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8494,7 +8494,7 @@
         <v>44788</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8567,7 +8567,7 @@
         <v>44627</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8640,7 +8640,7 @@
         <v>44498</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8713,7 +8713,7 @@
         <v>44768</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8786,7 +8786,7 @@
         <v>44851</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8859,7 +8859,7 @@
         <v>44529</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8932,7 +8932,7 @@
         <v>44813</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9005,7 +9005,7 @@
         <v>44809</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9078,7 +9078,7 @@
         <v>44771</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9151,7 +9151,7 @@
         <v>44587</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9224,7 +9224,7 @@
         <v>44496</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9297,7 +9297,7 @@
         <v>44507</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9370,7 +9370,7 @@
         <v>44507</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         <v>44487</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9521,7 +9521,7 @@
         <v>44652</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9594,7 +9594,7 @@
         <v>44600</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9667,7 +9667,7 @@
         <v>44628</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9740,7 +9740,7 @@
         <v>44600</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9813,7 +9813,7 @@
         <v>44852</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9886,7 +9886,7 @@
         <v>44501</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9959,7 +9959,7 @@
         <v>44839</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10032,7 +10032,7 @@
         <v>44615</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10110,7 +10110,7 @@
         <v>44622</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10183,7 +10183,7 @@
         <v>44524</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10256,7 +10256,7 @@
         <v>44712</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10329,7 +10329,7 @@
         <v>44743</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10402,7 +10402,7 @@
         <v>44722</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10475,7 +10475,7 @@
         <v>44532</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10553,7 +10553,7 @@
         <v>44593</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10626,7 +10626,7 @@
         <v>44699</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10699,7 +10699,7 @@
         <v>44652</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10772,7 +10772,7 @@
         <v>44820</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10850,7 +10850,7 @@
         <v>44847</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10923,7 +10923,7 @@
         <v>44743</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10996,7 +10996,7 @@
         <v>44488</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11074,7 +11074,7 @@
         <v>44589</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11147,7 +11147,7 @@
         <v>44551</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11225,7 +11225,7 @@
         <v>44600</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11298,7 +11298,7 @@
         <v>44725</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11371,7 +11371,7 @@
         <v>44600</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11444,7 +11444,7 @@
         <v>44655</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11517,7 +11517,7 @@
         <v>44530</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11590,7 +11590,7 @@
         <v>44980</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11663,7 +11663,7 @@
         <v>44788</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11736,7 +11736,7 @@
         <v>45445</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11809,7 +11809,7 @@
         <v>45397</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11882,7 +11882,7 @@
         <v>44690</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11955,7 +11955,7 @@
         <v>45079</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12028,7 +12028,7 @@
         <v>45211</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12101,7 +12101,7 @@
         <v>44953</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12174,7 +12174,7 @@
         <v>45089</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12247,7 +12247,7 @@
         <v>45251</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12320,7 +12320,7 @@
         <v>44487</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12393,7 +12393,7 @@
         <v>45590</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12466,7 +12466,7 @@
         <v>45411</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12539,7 +12539,7 @@
         <v>45099</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12612,7 +12612,7 @@
         <v>45040</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12685,7 +12685,7 @@
         <v>45191</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12758,7 +12758,7 @@
         <v>45022</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12831,7 +12831,7 @@
         <v>45022</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12904,7 +12904,7 @@
         <v>45392</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12977,7 +12977,7 @@
         <v>44652</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13050,7 +13050,7 @@
         <v>45187</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13123,7 +13123,7 @@
         <v>45126</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13196,7 +13196,7 @@
         <v>45237</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13269,7 +13269,7 @@
         <v>45159</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13342,7 +13342,7 @@
         <v>45219</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13415,7 +13415,7 @@
         <v>45637</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13488,7 +13488,7 @@
         <v>45049</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13561,7 +13561,7 @@
         <v>45230</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13634,7 +13634,7 @@
         <v>44973</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13712,7 +13712,7 @@
         <v>45474</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13785,7 +13785,7 @@
         <v>45341</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13858,7 +13858,7 @@
         <v>44519</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13931,7 +13931,7 @@
         <v>44683</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14004,7 +14004,7 @@
         <v>45559</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14077,7 +14077,7 @@
         <v>44572</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14150,7 +14150,7 @@
         <v>45309</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14223,7 +14223,7 @@
         <v>45665</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14296,7 +14296,7 @@
         <v>45392</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14369,7 +14369,7 @@
         <v>45211</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14442,7 +14442,7 @@
         <v>45211</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14515,7 +14515,7 @@
         <v>45164</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14588,7 +14588,7 @@
         <v>45148</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14661,7 +14661,7 @@
         <v>45166</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14734,7 +14734,7 @@
         <v>44896</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14807,7 +14807,7 @@
         <v>44978</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14880,7 +14880,7 @@
         <v>44978</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14953,7 +14953,7 @@
         <v>45475</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15026,7 +15026,7 @@
         <v>44739</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15099,7 +15099,7 @@
         <v>45355</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15172,7 +15172,7 @@
         <v>45188</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15250,7 +15250,7 @@
         <v>45422</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15323,7 +15323,7 @@
         <v>45394</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15396,7 +15396,7 @@
         <v>45606</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15469,7 +15469,7 @@
         <v>44949</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15542,7 +15542,7 @@
         <v>45369</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15615,7 +15615,7 @@
         <v>44982</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15688,7 +15688,7 @@
         <v>44791</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15761,7 +15761,7 @@
         <v>44834</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15834,7 +15834,7 @@
         <v>45019</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15907,7 +15907,7 @@
         <v>44783</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15980,7 +15980,7 @@
         <v>45349</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16053,7 +16053,7 @@
         <v>44487</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16131,7 +16131,7 @@
         <v>45021</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16204,7 +16204,7 @@
         <v>44600</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16277,7 +16277,7 @@
         <v>45415</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16350,7 +16350,7 @@
         <v>44593</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16423,7 +16423,7 @@
         <v>45740</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16496,7 +16496,7 @@
         <v>45475</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16569,7 +16569,7 @@
         <v>45735</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16642,7 +16642,7 @@
         <v>45037</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16715,7 +16715,7 @@
         <v>44690</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16788,7 +16788,7 @@
         <v>45155</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16861,7 +16861,7 @@
         <v>45641</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16934,7 +16934,7 @@
         <v>45475</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17007,7 +17007,7 @@
         <v>44593</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17080,7 +17080,7 @@
         <v>44799</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17153,7 +17153,7 @@
         <v>45126</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17226,7 +17226,7 @@
         <v>45155</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17299,7 +17299,7 @@
         <v>45126</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17372,7 +17372,7 @@
         <v>45225</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17445,7 +17445,7 @@
         <v>44504</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17518,7 +17518,7 @@
         <v>44852</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17591,7 +17591,7 @@
         <v>45190</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17664,7 +17664,7 @@
         <v>45433</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17737,7 +17737,7 @@
         <v>45067</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17810,7 +17810,7 @@
         <v>44953</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17883,7 +17883,7 @@
         <v>45323</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17956,7 +17956,7 @@
         <v>45107</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18029,7 +18029,7 @@
         <v>44729</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18102,7 +18102,7 @@
         <v>44984</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18175,7 +18175,7 @@
         <v>44507</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18248,7 +18248,7 @@
         <v>45189</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18321,7 +18321,7 @@
         <v>45434</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18394,7 +18394,7 @@
         <v>45048</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18467,7 +18467,7 @@
         <v>45191</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18540,7 +18540,7 @@
         <v>44619</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18613,7 +18613,7 @@
         <v>45036</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18686,7 +18686,7 @@
         <v>44907</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18759,7 +18759,7 @@
         <v>45273</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18837,7 +18837,7 @@
         <v>45229</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18910,7 +18910,7 @@
         <v>45132</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18983,7 +18983,7 @@
         <v>45084</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19056,7 +19056,7 @@
         <v>45211</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19129,7 +19129,7 @@
         <v>45102</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19202,7 +19202,7 @@
         <v>45102</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19275,7 +19275,7 @@
         <v>44839</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19348,7 +19348,7 @@
         <v>44519</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19421,7 +19421,7 @@
         <v>45749</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19494,7 +19494,7 @@
         <v>45551</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19572,7 +19572,7 @@
         <v>45401</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19645,7 +19645,7 @@
         <v>45317</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19718,7 +19718,7 @@
         <v>45632</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19791,7 +19791,7 @@
         <v>45574</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19864,7 +19864,7 @@
         <v>45818</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19937,7 +19937,7 @@
         <v>44979</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20010,7 +20010,7 @@
         <v>45915</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20088,7 +20088,7 @@
         <v>45716</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20161,7 +20161,7 @@
         <v>45615</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20234,7 +20234,7 @@
         <v>45091</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20307,7 +20307,7 @@
         <v>45887</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20380,7 +20380,7 @@
         <v>45887</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20453,7 +20453,7 @@
         <v>45819</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20526,7 +20526,7 @@
         <v>45524</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20599,7 +20599,7 @@
         <v>45818</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20672,7 +20672,7 @@
         <v>45700</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20745,7 +20745,7 @@
         <v>45121</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20818,7 +20818,7 @@
         <v>45191</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20891,7 +20891,7 @@
         <v>46006</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20964,7 +20964,7 @@
         <v>44979</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21037,7 +21037,7 @@
         <v>45113</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21110,7 +21110,7 @@
         <v>45113</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21183,7 +21183,7 @@
         <v>45972</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21256,7 +21256,7 @@
         <v>45167</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21329,7 +21329,7 @@
         <v>45615</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21402,7 +21402,7 @@
         <v>45966</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21475,7 +21475,7 @@
         <v>46055</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21548,7 +21548,7 @@
         <v>45938</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21621,7 +21621,7 @@
         <v>45069</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21694,7 +21694,7 @@
         <v>45069</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21767,7 +21767,7 @@
         <v>45976</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21840,7 +21840,7 @@
         <v>45401</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21913,7 +21913,7 @@
         <v>45348</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21986,7 +21986,7 @@
         <v>46043</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22059,7 +22059,7 @@
         <v>45976</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22132,7 +22132,7 @@
         <v>45741</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22205,7 +22205,7 @@
         <v>45408</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22278,7 +22278,7 @@
         <v>45645</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22351,7 +22351,7 @@
         <v>45376</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22424,7 +22424,7 @@
         <v>44683</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22497,7 +22497,7 @@
         <v>45629</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22570,7 +22570,7 @@
         <v>45681</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22643,7 +22643,7 @@
         <v>45909</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22716,7 +22716,7 @@
         <v>45908</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22789,7 +22789,7 @@
         <v>45461</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22862,7 +22862,7 @@
         <v>45349</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22935,7 +22935,7 @@
         <v>45915</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23008,7 +23008,7 @@
         <v>45915</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23081,7 +23081,7 @@
         <v>46142</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23154,7 +23154,7 @@
         <v>45915</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23227,7 +23227,7 @@
         <v>44524</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23300,7 +23300,7 @@
         <v>45091</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23373,7 +23373,7 @@
         <v>45921</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23446,7 +23446,7 @@
         <v>44897</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23519,7 +23519,7 @@
         <v>45113</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23592,7 +23592,7 @@
         <v>45335</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23665,7 +23665,7 @@
         <v>45335</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23738,7 +23738,7 @@
         <v>45200</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23811,7 +23811,7 @@
         <v>45755</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23884,7 +23884,7 @@
         <v>45070</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23957,7 +23957,7 @@
         <v>45931</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24030,7 +24030,7 @@
         <v>45789</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24103,7 +24103,7 @@
         <v>45222</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24176,7 +24176,7 @@
         <v>44944</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24249,7 +24249,7 @@
         <v>45938</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24322,7 +24322,7 @@
         <v>45938</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24395,7 +24395,7 @@
         <v>45370</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24468,7 +24468,7 @@
         <v>45400</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24541,7 +24541,7 @@
         <v>45938</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24614,7 +24614,7 @@
         <v>45938</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24687,7 +24687,7 @@
         <v>44900</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24760,7 +24760,7 @@
         <v>44922</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24833,7 +24833,7 @@
         <v>44781</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24906,7 +24906,7 @@
         <v>45466</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24979,7 +24979,7 @@
         <v>45901</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25052,7 +25052,7 @@
         <v>46155</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25125,7 +25125,7 @@
         <v>45953</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25198,7 +25198,7 @@
         <v>45707</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25271,7 +25271,7 @@
         <v>46069</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25349,7 +25349,7 @@
         <v>45716</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25422,7 +25422,7 @@
         <v>45327</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25495,7 +25495,7 @@
         <v>45217</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25568,7 +25568,7 @@
         <v>45960</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25641,7 +25641,7 @@
         <v>45425</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25714,7 +25714,7 @@
         <v>44951</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25787,7 +25787,7 @@
         <v>45964</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25860,7 +25860,7 @@
         <v>46160</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25933,7 +25933,7 @@
         <v>45964</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26006,7 +26006,7 @@
         <v>45967</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26079,7 +26079,7 @@
         <v>45967</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26152,7 +26152,7 @@
         <v>45099</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26225,7 +26225,7 @@
         <v>46160</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26298,7 +26298,7 @@
         <v>45204</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26376,7 +26376,7 @@
         <v>45902</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26449,7 +26449,7 @@
         <v>45561</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26527,7 +26527,7 @@
         <v>45971</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26600,7 +26600,7 @@
         <v>46162</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26673,7 +26673,7 @@
         <v>45258</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26746,7 +26746,7 @@
         <v>46162</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26819,7 +26819,7 @@
         <v>45349</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26892,7 +26892,7 @@
         <v>45310</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26965,7 +26965,7 @@
         <v>45740</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27038,7 +27038,7 @@
         <v>45979</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27111,7 +27111,7 @@
         <v>45573</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27184,7 +27184,7 @@
         <v>44728</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27257,7 +27257,7 @@
         <v>45258</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27330,7 +27330,7 @@
         <v>45258</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27403,7 +27403,7 @@
         <v>45600</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27476,7 +27476,7 @@
         <v>44930</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27549,7 +27549,7 @@
         <v>45400</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27622,7 +27622,7 @@
         <v>44698</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27695,7 +27695,7 @@
         <v>45028</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27768,7 +27768,7 @@
         <v>45392</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27841,7 +27841,7 @@
         <v>45989</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27914,7 +27914,7 @@
         <v>45531</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27987,7 +27987,7 @@
         <v>44900</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28060,7 +28060,7 @@
         <v>45196</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28133,7 +28133,7 @@
         <v>44586</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28206,7 +28206,7 @@
         <v>45161</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28284,7 +28284,7 @@
         <v>45180</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28357,7 +28357,7 @@
         <v>45986</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28430,7 +28430,7 @@
         <v>45716</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28503,7 +28503,7 @@
         <v>45994</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28576,7 +28576,7 @@
         <v>45048</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28649,7 +28649,7 @@
         <v>44897</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28722,7 +28722,7 @@
         <v>45614</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28795,7 +28795,7 @@
         <v>45230</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28868,7 +28868,7 @@
         <v>44977</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28941,7 +28941,7 @@
         <v>45587</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29014,7 +29014,7 @@
         <v>45923</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29087,7 +29087,7 @@
         <v>45301</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29160,7 +29160,7 @@
         <v>45622</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29233,7 +29233,7 @@
         <v>46024</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29306,7 +29306,7 @@
         <v>45093</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29379,7 +29379,7 @@
         <v>44965</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29452,7 +29452,7 @@
         <v>46036</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29525,7 +29525,7 @@
         <v>44743</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29598,7 +29598,7 @@
         <v>44749</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29671,7 +29671,7 @@
         <v>45327</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29744,7 +29744,7 @@
         <v>45327</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29817,7 +29817,7 @@
         <v>46044</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29890,7 +29890,7 @@
         <v>45559</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29968,7 +29968,7 @@
         <v>46049</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30041,7 +30041,7 @@
         <v>45182</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30114,7 +30114,7 @@
         <v>46182</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30187,7 +30187,7 @@
         <v>45433</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30260,7 +30260,7 @@
         <v>46182</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30333,7 +30333,7 @@
         <v>46055</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30406,7 +30406,7 @@
         <v>45107</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30479,7 +30479,7 @@
         <v>45007</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30552,7 +30552,7 @@
         <v>45007</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30625,7 +30625,7 @@
         <v>46183</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30698,7 +30698,7 @@
         <v>45148</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30771,7 +30771,7 @@
         <v>45084</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30844,7 +30844,7 @@
         <v>46058</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30917,7 +30917,7 @@
         <v>46062</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30990,7 +30990,7 @@
         <v>45537</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31063,7 +31063,7 @@
         <v>45281</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31136,7 +31136,7 @@
         <v>45211</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31209,7 +31209,7 @@
         <v>45021</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31282,7 +31282,7 @@
         <v>46069</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31360,7 +31360,7 @@
         <v>46185</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31433,7 +31433,7 @@
         <v>46189</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31506,7 +31506,7 @@
         <v>44530</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31579,7 +31579,7 @@
         <v>45189</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31652,7 +31652,7 @@
         <v>46188</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31725,7 +31725,7 @@
         <v>46071</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31803,7 +31803,7 @@
         <v>44938</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31876,7 +31876,7 @@
         <v>46185</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31949,7 +31949,7 @@
         <v>46071</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32027,7 +32027,7 @@
         <v>46188</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32100,7 +32100,7 @@
         <v>46072</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32173,7 +32173,7 @@
         <v>46072</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32246,7 +32246,7 @@
         <v>46071</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32324,7 +32324,7 @@
         <v>46078</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32397,7 +32397,7 @@
         <v>44851</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32470,7 +32470,7 @@
         <v>44960</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32543,7 +32543,7 @@
         <v>46185</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32616,7 +32616,7 @@
         <v>46079</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32689,7 +32689,7 @@
         <v>46079</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32762,7 +32762,7 @@
         <v>44494</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32835,7 +32835,7 @@
         <v>46085</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32908,7 +32908,7 @@
         <v>46085</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32981,7 +32981,7 @@
         <v>46085</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33054,7 +33054,7 @@
         <v>44893</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33127,7 +33127,7 @@
         <v>46090</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33200,7 +33200,7 @@
         <v>44518</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33273,7 +33273,7 @@
         <v>44728</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33346,7 +33346,7 @@
         <v>45009</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33419,7 +33419,7 @@
         <v>45009</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33492,7 +33492,7 @@
         <v>45009</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33565,7 +33565,7 @@
         <v>45009</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33638,7 +33638,7 @@
         <v>46190</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33716,7 +33716,7 @@
         <v>44911</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33789,7 +33789,7 @@
         <v>45159</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33862,7 +33862,7 @@
         <v>46120</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33935,7 +33935,7 @@
         <v>46196</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34008,7 +34008,7 @@
         <v>45514</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34081,7 +34081,7 @@
         <v>45514</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34154,7 +34154,7 @@
         <v>45202</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34227,7 +34227,7 @@
         <v>44879</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34300,7 +34300,7 @@
         <v>46196</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34378,7 +34378,7 @@
         <v>46196</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34456,7 +34456,7 @@
         <v>46196</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34534,7 +34534,7 @@
         <v>46107</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34607,7 +34607,7 @@
         <v>45126</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34680,7 +34680,7 @@
         <v>45126</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34753,7 +34753,7 @@
         <v>45126</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34826,7 +34826,7 @@
         <v>46010</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34899,7 +34899,7 @@
         <v>46198</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34972,7 +34972,7 @@
         <v>45155</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -35045,7 +35045,7 @@
         <v>46197</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -35123,7 +35123,7 @@
         <v>46197</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35201,7 +35201,7 @@
         <v>46197</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35279,7 +35279,7 @@
         <v>46120</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35352,7 +35352,7 @@
         <v>44953</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35425,7 +35425,7 @@
         <v>45362</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35498,7 +35498,7 @@
         <v>44700</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35571,7 +35571,7 @@
         <v>46127</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35644,7 +35644,7 @@
         <v>46127</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35717,7 +35717,7 @@
         <v>46127</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35790,7 +35790,7 @@
         <v>46202</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35863,7 +35863,7 @@
         <v>46133</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35936,7 +35936,7 @@
         <v>45743</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36009,7 +36009,7 @@
         <v>45296</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -36082,7 +36082,7 @@
         <v>44530</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36155,7 +36155,7 @@
         <v>44777</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36228,7 +36228,7 @@
         <v>46134</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36301,7 +36301,7 @@
         <v>45644</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36374,7 +36374,7 @@
         <v>45181</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36447,7 +36447,7 @@
         <v>44993</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36520,7 +36520,7 @@
         <v>45211</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36593,7 +36593,7 @@
         <v>45164</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36666,7 +36666,7 @@
         <v>46139</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36739,7 +36739,7 @@
         <v>45190</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36812,7 +36812,7 @@
         <v>44993</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36885,7 +36885,7 @@
         <v>45392</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36958,7 +36958,7 @@
         <v>45719</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37031,7 +37031,7 @@
         <v>45719</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -37104,7 +37104,7 @@
         <v>45349</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37177,7 +37177,7 @@
         <v>45966</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37250,7 +37250,7 @@
         <v>45905</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37323,7 +37323,7 @@
         <v>46205</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37401,7 +37401,7 @@
         <v>45531</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37474,7 +37474,7 @@
         <v>45901</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37547,7 +37547,7 @@
         <v>45126</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37620,7 +37620,7 @@
         <v>44861</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37693,7 +37693,7 @@
         <v>45909</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37766,7 +37766,7 @@
         <v>45772</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37839,7 +37839,7 @@
         <v>45205</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37912,7 +37912,7 @@
         <v>45474</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37985,7 +37985,7 @@
         <v>45084</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -38058,7 +38058,7 @@
         <v>46127</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -38136,7 +38136,7 @@
         <v>45126</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38209,7 +38209,7 @@
         <v>45574</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38282,7 +38282,7 @@
         <v>46212</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38355,7 +38355,7 @@
         <v>46211</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38428,7 +38428,7 @@
         <v>45204</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38506,7 +38506,7 @@
         <v>46212</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38579,7 +38579,7 @@
         <v>45232</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38652,7 +38652,7 @@
         <v>45098</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38725,7 +38725,7 @@
         <v>46213</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38798,7 +38798,7 @@
         <v>45392</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38871,7 +38871,7 @@
         <v>45740</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38944,7 +38944,7 @@
         <v>45341</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -39017,7 +39017,7 @@
         <v>44995</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -39090,7 +39090,7 @@
         <v>45003</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -39163,7 +39163,7 @@
         <v>45477</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39236,7 +39236,7 @@
         <v>44995</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39309,7 +39309,7 @@
         <v>45126</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39382,7 +39382,7 @@
         <v>45514</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39455,7 +39455,7 @@
         <v>45146</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39528,7 +39528,7 @@
         <v>46271</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39601,7 +39601,7 @@
         <v>46273</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39674,7 +39674,7 @@
         <v>46272</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39747,7 +39747,7 @@
         <v>44959</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39820,7 +39820,7 @@
         <v>45068</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39898,7 +39898,7 @@
         <v>45707</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39971,7 +39971,7 @@
         <v>44851</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -40044,7 +40044,7 @@
         <v>44608</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -40117,7 +40117,7 @@
         <v>45095</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40190,7 +40190,7 @@
         <v>44580</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40263,7 +40263,7 @@
         <v>46188</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40336,7 +40336,7 @@
         <v>46275</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40409,7 +40409,7 @@
         <v>45373</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40482,7 +40482,7 @@
         <v>45161</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40560,7 +40560,7 @@
         <v>44984</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40633,7 +40633,7 @@
         <v>45252</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40706,7 +40706,7 @@
         <v>44761</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40779,7 +40779,7 @@
         <v>44802</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40852,7 +40852,7 @@
         <v>46279</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40930,7 +40930,7 @@
         <v>46279</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -41008,7 +41008,7 @@
         <v>45422</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -41081,7 +41081,7 @@
         <v>46279</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -41159,7 +41159,7 @@
         <v>44808</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41232,7 +41232,7 @@
         <v>46279</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41305,7 +41305,7 @@
         <v>46279</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41383,7 +41383,7 @@
         <v>46279</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41461,7 +41461,7 @@
         <v>46279</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41539,7 +41539,7 @@
         <v>46279</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41617,7 +41617,7 @@
         <v>46279</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41695,7 +41695,7 @@
         <v>46279</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41773,7 +41773,7 @@
         <v>46279</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41851,7 +41851,7 @@
         <v>45189</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41924,7 +41924,7 @@
         <v>45772</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41997,7 +41997,7 @@
         <v>45049</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -42070,7 +42070,7 @@
         <v>44531</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -42143,7 +42143,7 @@
         <v>45051</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -42216,7 +42216,7 @@
         <v>45051</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42289,7 +42289,7 @@
         <v>45126</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42362,7 +42362,7 @@
         <v>45126</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42435,7 +42435,7 @@
         <v>45323</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42508,7 +42508,7 @@
         <v>44673</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42581,7 +42581,7 @@
         <v>45596</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42654,7 +42654,7 @@
         <v>46282</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42727,7 +42727,7 @@
         <v>44893</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42800,7 +42800,7 @@
         <v>45668</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42873,7 +42873,7 @@
         <v>44759</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42946,7 +42946,7 @@
         <v>44594</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -43019,7 +43019,7 @@
         <v>45323</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -43092,7 +43092,7 @@
         <v>46244</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -43165,7 +43165,7 @@
         <v>44852</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43238,7 +43238,7 @@
         <v>45149</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43311,7 +43311,7 @@
         <v>46286</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43384,7 +43384,7 @@
         <v>45111</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43457,7 +43457,7 @@
         <v>45310</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43530,7 +43530,7 @@
         <v>45727</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43603,7 +43603,7 @@
         <v>45727</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43676,7 +43676,7 @@
         <v>45706</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43749,7 +43749,7 @@
         <v>45204</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43827,7 +43827,7 @@
         <v>45062</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43900,7 +43900,7 @@
         <v>45562</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43973,7 +43973,7 @@
         <v>45926</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -44046,7 +44046,7 @@
         <v>45103</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -44119,7 +44119,7 @@
         <v>45688</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -44192,7 +44192,7 @@
         <v>44589</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44265,7 +44265,7 @@
         <v>46288</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44338,7 +44338,7 @@
         <v>44726</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44411,7 +44411,7 @@
         <v>45742</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44484,7 +44484,7 @@
         <v>44524</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44557,7 +44557,7 @@
         <v>44728</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44630,7 +44630,7 @@
         <v>45182</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44703,7 +44703,7 @@
         <v>44816</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44776,7 +44776,7 @@
         <v>46288</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44849,7 +44849,7 @@
         <v>44840</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44927,7 +44927,7 @@
         <v>45595</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -45000,7 +45000,7 @@
         <v>44897</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -45073,7 +45073,7 @@
         <v>45273</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -45151,7 +45151,7 @@
         <v>45349</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -45224,7 +45224,7 @@
         <v>44827</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45297,7 +45297,7 @@
         <v>45092</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45370,7 +45370,7 @@
         <v>46290</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45443,7 +45443,7 @@
         <v>46290</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45516,7 +45516,7 @@
         <v>46290</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45589,7 +45589,7 @@
         <v>44550</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45662,7 +45662,7 @@
         <v>45076</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45735,7 +45735,7 @@
         <v>45385</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45808,7 +45808,7 @@
         <v>45515</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45881,7 +45881,7 @@
         <v>45307</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45954,7 +45954,7 @@
         <v>45317</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -46027,7 +46027,7 @@
         <v>45187</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -46100,7 +46100,7 @@
         <v>44748</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -46173,7 +46173,7 @@
         <v>46160</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -46246,7 +46246,7 @@
         <v>46251</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -46319,7 +46319,7 @@
         <v>44699</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -46392,7 +46392,7 @@
         <v>45400</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46465,7 +46465,7 @@
         <v>45229</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46538,7 +46538,7 @@
         <v>45188</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -46616,7 +46616,7 @@
         <v>45769</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -46689,7 +46689,7 @@
         <v>44769</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46762,7 +46762,7 @@
         <v>46253</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46835,7 +46835,7 @@
         <v>46255</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46913,7 +46913,7 @@
         <v>44488</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46991,7 +46991,7 @@
         <v>45769</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -47064,7 +47064,7 @@
         <v>46255</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -47142,7 +47142,7 @@
         <v>46255</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -47220,7 +47220,7 @@
         <v>46255</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -47298,7 +47298,7 @@
         <v>46255</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -47376,7 +47376,7 @@
         <v>46253</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -47449,7 +47449,7 @@
         <v>46255</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -47527,7 +47527,7 @@
         <v>46255</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -47600,7 +47600,7 @@
         <v>45606</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -47673,7 +47673,7 @@
         <v>45394</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -47746,7 +47746,7 @@
         <v>44955</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47819,7 +47819,7 @@
         <v>45048</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47892,7 +47892,7 @@
         <v>45351</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47965,7 +47965,7 @@
         <v>45534</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -48038,7 +48038,7 @@
         <v>45215</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -48111,7 +48111,7 @@
         <v>45551</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -48184,7 +48184,7 @@
         <v>45523</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -48257,7 +48257,7 @@
         <v>44949</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -48330,7 +48330,7 @@
         <v>45684</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -48403,7 +48403,7 @@
         <v>45624</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -48476,7 +48476,7 @@
         <v>45484</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -48549,7 +48549,7 @@
         <v>46230</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -48622,7 +48622,7 @@
         <v>45107</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -48695,7 +48695,7 @@
         <v>45445</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -48768,7 +48768,7 @@
         <v>45317</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -48841,7 +48841,7 @@
         <v>45548</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -48914,7 +48914,7 @@
         <v>45415</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -48987,7 +48987,7 @@
         <v>45638</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -49060,7 +49060,7 @@
         <v>45565</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -49133,7 +49133,7 @@
         <v>45386</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -49206,7 +49206,7 @@
         <v>46255</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -49284,7 +49284,7 @@
         <v>45716</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -49357,7 +49357,7 @@
         <v>46120</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -49430,7 +49430,7 @@
         <v>45775</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -49503,7 +49503,7 @@
         <v>45481</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -49576,7 +49576,7 @@
         <v>46188</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -49649,7 +49649,7 @@
         <v>45566</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -49722,7 +49722,7 @@
         <v>45582</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -49795,7 +49795,7 @@
         <v>45609</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -49868,7 +49868,7 @@
         <v>45484</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -49941,7 +49941,7 @@
         <v>45688</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -50014,7 +50014,7 @@
         <v>45610</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -50087,7 +50087,7 @@
         <v>46302</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -50160,7 +50160,7 @@
         <v>45400</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -50233,7 +50233,7 @@
         <v>46259</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -50306,7 +50306,7 @@
         <v>45455</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -50379,7 +50379,7 @@
         <v>45665</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -50452,7 +50452,7 @@
         <v>44977</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -50525,7 +50525,7 @@
         <v>45537</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -50598,7 +50598,7 @@
         <v>46306</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -50671,7 +50671,7 @@
         <v>44958</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -50744,7 +50744,7 @@
         <v>46308</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -50817,7 +50817,7 @@
         <v>45800</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -50890,7 +50890,7 @@
         <v>45804</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -50963,7 +50963,7 @@
         <v>45813</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -51036,7 +51036,7 @@
         <v>46134</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -51109,7 +51109,7 @@
         <v>46268</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -51182,7 +51182,7 @@
         <v>45825</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -51255,7 +51255,7 @@
         <v>45826</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -51328,7 +51328,7 @@
         <v>45826</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -51401,7 +51401,7 @@
         <v>46245</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -51474,7 +51474,7 @@
         <v>45826</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -51547,7 +51547,7 @@
         <v>45826</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -51620,7 +51620,7 @@
         <v>45826</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -51693,7 +51693,7 @@
         <v>45826</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -51766,7 +51766,7 @@
         <v>45832</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -51839,7 +51839,7 @@
         <v>45805</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -51912,7 +51912,7 @@
         <v>45845</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -51985,7 +51985,7 @@
         <v>45621</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -52058,7 +52058,7 @@
         <v>45727</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -52131,7 +52131,7 @@
         <v>45849</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -52204,7 +52204,7 @@
         <v>45775</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -52277,7 +52277,7 @@
         <v>45716</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -52350,7 +52350,7 @@
         <v>45851</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -52423,7 +52423,7 @@
         <v>45851</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -52496,7 +52496,7 @@
         <v>45772</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -52569,7 +52569,7 @@
         <v>45857</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -52642,7 +52642,7 @@
         <v>45863</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -52715,7 +52715,7 @@
         <v>45750</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -52788,7 +52788,7 @@
         <v>45790</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -52861,7 +52861,7 @@
         <v>45881</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -52934,7 +52934,7 @@
         <v>44476</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -53007,7 +53007,7 @@
         <v>45191</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -53080,7 +53080,7 @@
         <v>44959</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -53153,7 +53153,7 @@
         <v>45194</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -53226,7 +53226,7 @@
         <v>45377</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -53299,7 +53299,7 @@
         <v>45387</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -53372,7 +53372,7 @@
         <v>44903</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -53445,7 +53445,7 @@
         <v>44900</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -53518,7 +53518,7 @@
         <v>44852</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -53591,7 +53591,7 @@
         <v>45200</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -53664,7 +53664,7 @@
         <v>45534</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -53737,7 +53737,7 @@
         <v>45191</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -53810,7 +53810,7 @@
         <v>45386</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -53883,7 +53883,7 @@
         <v>45287</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -53956,7 +53956,7 @@
         <v>45386</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -54029,7 +54029,7 @@
         <v>45386</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -54102,7 +54102,7 @@
         <v>45386</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -54175,7 +54175,7 @@
         <v>45387</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -54248,7 +54248,7 @@
         <v>44519</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -54321,7 +54321,7 @@
         <v>45534</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -54394,7 +54394,7 @@
         <v>45377</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -54467,7 +54467,7 @@
         <v>44928</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -54540,7 +54540,7 @@
         <v>45377</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -54613,7 +54613,7 @@
         <v>44519</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -54686,7 +54686,7 @@
         <v>45200</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -54759,7 +54759,7 @@
         <v>44900</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -54832,7 +54832,7 @@
         <v>45330</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -54905,7 +54905,7 @@
         <v>44959</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -54978,7 +54978,7 @@
         <v>45348</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -55051,7 +55051,7 @@
         <v>45813</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -55124,7 +55124,7 @@
         <v>45813</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -55197,7 +55197,7 @@
         <v>45849</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -55270,7 +55270,7 @@
         <v>45898</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -55343,7 +55343,7 @@
         <v>45935</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -55416,7 +55416,7 @@
         <v>45978</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -55489,7 +55489,7 @@
         <v>46034</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -55562,7 +55562,7 @@
         <v>46049</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -55635,7 +55635,7 @@
         <v>46049</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -55708,7 +55708,7 @@
         <v>46065</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -55781,7 +55781,7 @@
         <v>46092</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -55854,7 +55854,7 @@
         <v>46062</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -55927,7 +55927,7 @@
         <v>46119</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -56000,7 +56000,7 @@
         <v>46119</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -56073,7 +56073,7 @@
         <v>46127</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -56146,7 +56146,7 @@
         <v>46167</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -56219,7 +56219,7 @@
         <v>46156</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -56292,7 +56292,7 @@
         <v>46183</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -56365,7 +56365,7 @@
         <v>46191</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -56438,7 +56438,7 @@
         <v>46276</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -56516,7 +56516,7 @@
         <v>46283</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -56589,7 +56589,7 @@
         <v>46286</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>

--- a/Översikt EMMABODA.xlsx
+++ b/Översikt EMMABODA.xlsx
@@ -601,7 +601,7 @@
         <v>45534</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>45440</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -830,7 +830,7 @@
         <v>45387</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>45202</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
         <v>45030</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>45616</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         <v>44706</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>44811</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         <v>45330</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1600,7 +1600,7 @@
         <v>45359</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>46136</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1818,7 +1818,7 @@
         <v>45369</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1932,7 +1932,7 @@
         <v>45086</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2038,7 +2038,7 @@
         <v>44937</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>46062</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2254,7 +2254,7 @@
         <v>46069</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2360,7 +2360,7 @@
         <v>46214</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2466,7 +2466,7 @@
         <v>44762</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2571,7 +2571,7 @@
         <v>45166</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2676,7 +2676,7 @@
         <v>44966</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2781,7 +2781,7 @@
         <v>44570</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2886,7 +2886,7 @@
         <v>44984</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2991,7 +2991,7 @@
         <v>45763</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3100,7 +3100,7 @@
         <v>45196</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3205,7 +3205,7 @@
         <v>45797</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3314,7 +3314,7 @@
         <v>45104</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3419,7 +3419,7 @@
         <v>45335</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
         <v>45953</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3633,7 +3633,7 @@
         <v>45161</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3743,7 +3743,7 @@
         <v>45068</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3853,7 +3853,7 @@
         <v>44771</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3962,7 +3962,7 @@
         <v>46135</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4072,7 +4072,7 @@
         <v>45967</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4177,7 +4177,7 @@
         <v>45229</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4286,7 +4286,7 @@
         <v>46213</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4391,7 +4391,7 @@
         <v>46213</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4496,7 +4496,7 @@
         <v>46218</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4601,7 +4601,7 @@
         <v>45107</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4710,7 +4710,7 @@
         <v>44495</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4819,7 +4819,7 @@
         <v>46282</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4924,7 +4924,7 @@
         <v>46055</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5029,7 +5029,7 @@
         <v>45092</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5134,7 +5134,7 @@
         <v>46253</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5239,7 +5239,7 @@
         <v>44488</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5349,7 +5349,7 @@
         <v>44895</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5454,7 +5454,7 @@
         <v>45509</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5559,7 +5559,7 @@
         <v>45387</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5668,7 +5668,7 @@
         <v>44588</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5773,7 +5773,7 @@
         <v>45611</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5882,7 +5882,7 @@
         <v>45330</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5991,7 +5991,7 @@
         <v>44852</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6100,7 +6100,7 @@
         <v>45442</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6205,7 +6205,7 @@
         <v>45153</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6310,7 +6310,7 @@
         <v>45386</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         <v>45685</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6524,7 +6524,7 @@
         <v>45813</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6633,7 +6633,7 @@
         <v>46275</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6742,7 +6742,7 @@
         <v>44530</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6815,7 +6815,7 @@
         <v>44488</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6888,7 +6888,7 @@
         <v>44764</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6961,7 +6961,7 @@
         <v>44530</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7034,7 +7034,7 @@
         <v>44496</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7107,7 +7107,7 @@
         <v>44529</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7180,7 +7180,7 @@
         <v>44490</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7253,7 +7253,7 @@
         <v>44601</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7326,7 +7326,7 @@
         <v>44600</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         <v>44507</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7472,7 +7472,7 @@
         <v>44507</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7545,7 +7545,7 @@
         <v>44507</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7618,7 +7618,7 @@
         <v>44728</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7691,7 +7691,7 @@
         <v>44599</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7764,7 +7764,7 @@
         <v>44496</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7837,7 +7837,7 @@
         <v>44691</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7910,7 +7910,7 @@
         <v>44628</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7983,7 +7983,7 @@
         <v>44504</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8056,7 +8056,7 @@
         <v>44515</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8129,7 +8129,7 @@
         <v>44851</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8202,7 +8202,7 @@
         <v>44860</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8275,7 +8275,7 @@
         <v>44648</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8348,7 +8348,7 @@
         <v>44523</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8421,7 +8421,7 @@
         <v>44628</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8494,7 +8494,7 @@
         <v>44788</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8567,7 +8567,7 @@
         <v>44627</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8640,7 +8640,7 @@
         <v>44498</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8713,7 +8713,7 @@
         <v>44768</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8786,7 +8786,7 @@
         <v>44851</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8859,7 +8859,7 @@
         <v>44529</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8932,7 +8932,7 @@
         <v>44813</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9005,7 +9005,7 @@
         <v>44809</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9078,7 +9078,7 @@
         <v>44771</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9151,7 +9151,7 @@
         <v>44587</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9224,7 +9224,7 @@
         <v>44496</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9297,7 +9297,7 @@
         <v>44507</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9370,7 +9370,7 @@
         <v>44507</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         <v>44487</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9521,7 +9521,7 @@
         <v>44652</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9594,7 +9594,7 @@
         <v>44600</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9667,7 +9667,7 @@
         <v>44628</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9740,7 +9740,7 @@
         <v>44600</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9813,7 +9813,7 @@
         <v>44852</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9886,7 +9886,7 @@
         <v>44501</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9959,7 +9959,7 @@
         <v>44839</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10032,7 +10032,7 @@
         <v>44615</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10110,7 +10110,7 @@
         <v>44622</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10183,7 +10183,7 @@
         <v>44524</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10256,7 +10256,7 @@
         <v>44712</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10329,7 +10329,7 @@
         <v>44743</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10402,7 +10402,7 @@
         <v>44722</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10475,7 +10475,7 @@
         <v>44532</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10553,7 +10553,7 @@
         <v>44593</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10626,7 +10626,7 @@
         <v>44699</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10699,7 +10699,7 @@
         <v>44652</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10772,7 +10772,7 @@
         <v>44820</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10850,7 +10850,7 @@
         <v>44847</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10923,7 +10923,7 @@
         <v>44743</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10996,7 +10996,7 @@
         <v>44488</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11074,7 +11074,7 @@
         <v>44589</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11147,7 +11147,7 @@
         <v>44551</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11225,7 +11225,7 @@
         <v>44600</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11298,7 +11298,7 @@
         <v>44725</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11371,7 +11371,7 @@
         <v>44600</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11444,7 +11444,7 @@
         <v>44655</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11517,7 +11517,7 @@
         <v>44530</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11590,7 +11590,7 @@
         <v>44980</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11663,7 +11663,7 @@
         <v>44788</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11736,7 +11736,7 @@
         <v>45445</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11809,7 +11809,7 @@
         <v>45397</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11882,7 +11882,7 @@
         <v>44690</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11955,7 +11955,7 @@
         <v>45079</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12028,7 +12028,7 @@
         <v>45211</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12101,7 +12101,7 @@
         <v>44953</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12174,7 +12174,7 @@
         <v>45089</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12247,7 +12247,7 @@
         <v>45251</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12320,7 +12320,7 @@
         <v>44487</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12393,7 +12393,7 @@
         <v>45590</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12466,7 +12466,7 @@
         <v>45411</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12539,7 +12539,7 @@
         <v>45099</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12612,7 +12612,7 @@
         <v>45040</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12685,7 +12685,7 @@
         <v>45191</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12758,7 +12758,7 @@
         <v>45022</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12831,7 +12831,7 @@
         <v>45022</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12904,7 +12904,7 @@
         <v>45392</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12977,7 +12977,7 @@
         <v>44652</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13050,7 +13050,7 @@
         <v>45187</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13123,7 +13123,7 @@
         <v>45126</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13196,7 +13196,7 @@
         <v>45237</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13269,7 +13269,7 @@
         <v>45159</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13342,7 +13342,7 @@
         <v>45219</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13415,7 +13415,7 @@
         <v>45637</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13488,7 +13488,7 @@
         <v>45049</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13561,7 +13561,7 @@
         <v>45230</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13634,7 +13634,7 @@
         <v>44973</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13712,7 +13712,7 @@
         <v>45474</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13785,7 +13785,7 @@
         <v>45341</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13858,7 +13858,7 @@
         <v>44519</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13931,7 +13931,7 @@
         <v>44683</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14004,7 +14004,7 @@
         <v>45559</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14077,7 +14077,7 @@
         <v>44572</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14150,7 +14150,7 @@
         <v>45309</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14223,7 +14223,7 @@
         <v>45665</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14296,7 +14296,7 @@
         <v>45392</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14369,7 +14369,7 @@
         <v>45211</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14442,7 +14442,7 @@
         <v>45211</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14515,7 +14515,7 @@
         <v>45164</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14588,7 +14588,7 @@
         <v>45148</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14661,7 +14661,7 @@
         <v>45166</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14734,7 +14734,7 @@
         <v>44896</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14807,7 +14807,7 @@
         <v>44978</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14880,7 +14880,7 @@
         <v>44978</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14953,7 +14953,7 @@
         <v>45475</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15026,7 +15026,7 @@
         <v>44739</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15099,7 +15099,7 @@
         <v>45355</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15172,7 +15172,7 @@
         <v>45188</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15250,7 +15250,7 @@
         <v>45422</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15323,7 +15323,7 @@
         <v>45394</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15396,7 +15396,7 @@
         <v>45606</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15469,7 +15469,7 @@
         <v>44949</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15542,7 +15542,7 @@
         <v>45369</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15615,7 +15615,7 @@
         <v>44982</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15688,7 +15688,7 @@
         <v>44791</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15761,7 +15761,7 @@
         <v>44834</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15834,7 +15834,7 @@
         <v>45019</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15907,7 +15907,7 @@
         <v>44783</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15980,7 +15980,7 @@
         <v>45349</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16053,7 +16053,7 @@
         <v>44487</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16131,7 +16131,7 @@
         <v>45021</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16204,7 +16204,7 @@
         <v>44600</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16277,7 +16277,7 @@
         <v>45415</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16350,7 +16350,7 @@
         <v>44593</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16423,7 +16423,7 @@
         <v>45740</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16496,7 +16496,7 @@
         <v>45475</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16569,7 +16569,7 @@
         <v>45735</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16642,7 +16642,7 @@
         <v>45037</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16715,7 +16715,7 @@
         <v>44690</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16788,7 +16788,7 @@
         <v>45155</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16861,7 +16861,7 @@
         <v>45641</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16934,7 +16934,7 @@
         <v>45475</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17007,7 +17007,7 @@
         <v>44593</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17080,7 +17080,7 @@
         <v>44799</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17153,7 +17153,7 @@
         <v>45126</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17226,7 +17226,7 @@
         <v>45155</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17299,7 +17299,7 @@
         <v>45126</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17372,7 +17372,7 @@
         <v>45225</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17445,7 +17445,7 @@
         <v>44504</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17518,7 +17518,7 @@
         <v>44852</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17591,7 +17591,7 @@
         <v>45190</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17664,7 +17664,7 @@
         <v>45433</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17737,7 +17737,7 @@
         <v>45067</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17810,7 +17810,7 @@
         <v>44953</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17883,7 +17883,7 @@
         <v>45323</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17956,7 +17956,7 @@
         <v>45107</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18029,7 +18029,7 @@
         <v>44729</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18102,7 +18102,7 @@
         <v>44984</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18175,7 +18175,7 @@
         <v>44507</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18248,7 +18248,7 @@
         <v>45189</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18321,7 +18321,7 @@
         <v>45434</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18394,7 +18394,7 @@
         <v>45048</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18467,7 +18467,7 @@
         <v>45191</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18540,7 +18540,7 @@
         <v>44619</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18613,7 +18613,7 @@
         <v>45036</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18686,7 +18686,7 @@
         <v>44907</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18759,7 +18759,7 @@
         <v>45273</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18837,7 +18837,7 @@
         <v>45229</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18910,7 +18910,7 @@
         <v>45132</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18983,7 +18983,7 @@
         <v>45084</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19056,7 +19056,7 @@
         <v>45211</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19129,7 +19129,7 @@
         <v>45102</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19202,7 +19202,7 @@
         <v>45102</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19275,7 +19275,7 @@
         <v>44839</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19348,7 +19348,7 @@
         <v>44519</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19421,7 +19421,7 @@
         <v>45749</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19494,7 +19494,7 @@
         <v>45551</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19572,7 +19572,7 @@
         <v>45401</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19645,7 +19645,7 @@
         <v>45317</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19718,7 +19718,7 @@
         <v>45632</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19791,7 +19791,7 @@
         <v>45574</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19864,7 +19864,7 @@
         <v>45818</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19937,7 +19937,7 @@
         <v>44979</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20010,7 +20010,7 @@
         <v>45915</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20088,7 +20088,7 @@
         <v>45716</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20161,7 +20161,7 @@
         <v>45615</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20234,7 +20234,7 @@
         <v>45091</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20307,7 +20307,7 @@
         <v>45887</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20380,7 +20380,7 @@
         <v>45887</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20453,7 +20453,7 @@
         <v>45819</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20526,7 +20526,7 @@
         <v>45524</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20599,7 +20599,7 @@
         <v>45818</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20672,7 +20672,7 @@
         <v>45700</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20745,7 +20745,7 @@
         <v>45121</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20818,7 +20818,7 @@
         <v>45191</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20891,7 +20891,7 @@
         <v>46006</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20964,7 +20964,7 @@
         <v>44979</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21037,7 +21037,7 @@
         <v>45113</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21110,7 +21110,7 @@
         <v>45113</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21183,7 +21183,7 @@
         <v>45972</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21256,7 +21256,7 @@
         <v>45167</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21329,7 +21329,7 @@
         <v>45615</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21402,7 +21402,7 @@
         <v>45966</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21475,7 +21475,7 @@
         <v>46055</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21548,7 +21548,7 @@
         <v>45938</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21621,7 +21621,7 @@
         <v>45069</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21694,7 +21694,7 @@
         <v>45069</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21767,7 +21767,7 @@
         <v>45976</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21840,7 +21840,7 @@
         <v>45401</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21913,7 +21913,7 @@
         <v>45348</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21986,7 +21986,7 @@
         <v>46043</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22059,7 +22059,7 @@
         <v>45976</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22132,7 +22132,7 @@
         <v>45741</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22205,7 +22205,7 @@
         <v>45408</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22278,7 +22278,7 @@
         <v>45645</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22351,7 +22351,7 @@
         <v>45376</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22424,7 +22424,7 @@
         <v>44683</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22497,7 +22497,7 @@
         <v>45629</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22570,7 +22570,7 @@
         <v>45681</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22643,7 +22643,7 @@
         <v>45909</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22716,7 +22716,7 @@
         <v>45908</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22789,7 +22789,7 @@
         <v>45461</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22862,7 +22862,7 @@
         <v>45349</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22935,7 +22935,7 @@
         <v>45915</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23008,7 +23008,7 @@
         <v>45915</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23081,7 +23081,7 @@
         <v>46142</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23154,7 +23154,7 @@
         <v>45915</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23227,7 +23227,7 @@
         <v>44524</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23300,7 +23300,7 @@
         <v>45091</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23373,7 +23373,7 @@
         <v>45921</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23446,7 +23446,7 @@
         <v>44897</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23519,7 +23519,7 @@
         <v>45113</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23592,7 +23592,7 @@
         <v>45335</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23665,7 +23665,7 @@
         <v>45335</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23738,7 +23738,7 @@
         <v>45200</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23811,7 +23811,7 @@
         <v>45755</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23884,7 +23884,7 @@
         <v>45070</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23957,7 +23957,7 @@
         <v>45931</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24030,7 +24030,7 @@
         <v>45789</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24103,7 +24103,7 @@
         <v>45222</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24176,7 +24176,7 @@
         <v>44944</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24249,7 +24249,7 @@
         <v>45938</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24322,7 +24322,7 @@
         <v>45938</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24395,7 +24395,7 @@
         <v>45370</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24468,7 +24468,7 @@
         <v>45400</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24541,7 +24541,7 @@
         <v>45938</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24614,7 +24614,7 @@
         <v>45938</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24687,7 +24687,7 @@
         <v>44900</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24760,7 +24760,7 @@
         <v>44922</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24833,7 +24833,7 @@
         <v>44781</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24906,7 +24906,7 @@
         <v>45466</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24979,7 +24979,7 @@
         <v>45901</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25052,7 +25052,7 @@
         <v>46155</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25125,7 +25125,7 @@
         <v>45953</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25198,7 +25198,7 @@
         <v>45707</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25271,7 +25271,7 @@
         <v>46069</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25349,7 +25349,7 @@
         <v>45716</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25422,7 +25422,7 @@
         <v>45327</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25495,7 +25495,7 @@
         <v>45217</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25568,7 +25568,7 @@
         <v>45960</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25641,7 +25641,7 @@
         <v>45425</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25714,7 +25714,7 @@
         <v>44951</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25787,7 +25787,7 @@
         <v>45964</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25860,7 +25860,7 @@
         <v>46160</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25933,7 +25933,7 @@
         <v>45964</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26006,7 +26006,7 @@
         <v>45967</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26079,7 +26079,7 @@
         <v>45967</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26152,7 +26152,7 @@
         <v>45099</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26225,7 +26225,7 @@
         <v>46160</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26298,7 +26298,7 @@
         <v>45204</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26376,7 +26376,7 @@
         <v>45902</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26449,7 +26449,7 @@
         <v>45561</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26527,7 +26527,7 @@
         <v>45971</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26600,7 +26600,7 @@
         <v>46162</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26673,7 +26673,7 @@
         <v>45258</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26746,7 +26746,7 @@
         <v>46162</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26819,7 +26819,7 @@
         <v>45349</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26892,7 +26892,7 @@
         <v>45310</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26965,7 +26965,7 @@
         <v>45740</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27038,7 +27038,7 @@
         <v>45979</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27111,7 +27111,7 @@
         <v>45573</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27184,7 +27184,7 @@
         <v>44728</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27257,7 +27257,7 @@
         <v>45258</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27330,7 +27330,7 @@
         <v>45258</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27403,7 +27403,7 @@
         <v>45600</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27476,7 +27476,7 @@
         <v>44930</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27549,7 +27549,7 @@
         <v>45400</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27622,7 +27622,7 @@
         <v>44698</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27695,7 +27695,7 @@
         <v>45028</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27768,7 +27768,7 @@
         <v>45392</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27841,7 +27841,7 @@
         <v>45989</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27914,7 +27914,7 @@
         <v>45531</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27987,7 +27987,7 @@
         <v>44900</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28060,7 +28060,7 @@
         <v>45196</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28133,7 +28133,7 @@
         <v>44586</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28206,7 +28206,7 @@
         <v>45161</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28284,7 +28284,7 @@
         <v>45180</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28357,7 +28357,7 @@
         <v>45986</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28430,7 +28430,7 @@
         <v>45716</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28503,7 +28503,7 @@
         <v>45994</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28576,7 +28576,7 @@
         <v>45048</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28649,7 +28649,7 @@
         <v>44897</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28722,7 +28722,7 @@
         <v>45614</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28795,7 +28795,7 @@
         <v>45230</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28868,7 +28868,7 @@
         <v>44977</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28941,7 +28941,7 @@
         <v>45587</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29014,7 +29014,7 @@
         <v>45923</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29087,7 +29087,7 @@
         <v>45301</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29160,7 +29160,7 @@
         <v>45622</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29233,7 +29233,7 @@
         <v>46024</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29306,7 +29306,7 @@
         <v>45093</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29379,7 +29379,7 @@
         <v>44965</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29452,7 +29452,7 @@
         <v>46036</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29525,7 +29525,7 @@
         <v>44743</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29598,7 +29598,7 @@
         <v>44749</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29671,7 +29671,7 @@
         <v>45327</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29744,7 +29744,7 @@
         <v>45327</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29817,7 +29817,7 @@
         <v>46044</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29890,7 +29890,7 @@
         <v>45559</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29968,7 +29968,7 @@
         <v>46049</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30041,7 +30041,7 @@
         <v>45182</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30114,7 +30114,7 @@
         <v>46182</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30187,7 +30187,7 @@
         <v>45433</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30260,7 +30260,7 @@
         <v>46182</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30333,7 +30333,7 @@
         <v>46055</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30406,7 +30406,7 @@
         <v>45107</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30479,7 +30479,7 @@
         <v>45007</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30552,7 +30552,7 @@
         <v>45007</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30625,7 +30625,7 @@
         <v>46183</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30698,7 +30698,7 @@
         <v>45148</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30771,7 +30771,7 @@
         <v>45084</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30844,7 +30844,7 @@
         <v>46058</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30917,7 +30917,7 @@
         <v>46062</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30990,7 +30990,7 @@
         <v>45537</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31063,7 +31063,7 @@
         <v>45281</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31136,7 +31136,7 @@
         <v>45211</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31209,7 +31209,7 @@
         <v>45021</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31282,7 +31282,7 @@
         <v>46069</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31360,7 +31360,7 @@
         <v>46185</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31433,7 +31433,7 @@
         <v>46189</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31506,7 +31506,7 @@
         <v>44530</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31579,7 +31579,7 @@
         <v>45189</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31652,7 +31652,7 @@
         <v>46188</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31725,7 +31725,7 @@
         <v>46071</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31803,7 +31803,7 @@
         <v>44938</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31876,7 +31876,7 @@
         <v>46185</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31949,7 +31949,7 @@
         <v>46071</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32027,7 +32027,7 @@
         <v>46188</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32100,7 +32100,7 @@
         <v>46072</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32173,7 +32173,7 @@
         <v>46072</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32246,7 +32246,7 @@
         <v>46071</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32324,7 +32324,7 @@
         <v>46078</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32397,7 +32397,7 @@
         <v>44851</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32470,7 +32470,7 @@
         <v>44960</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32543,7 +32543,7 @@
         <v>46185</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32616,7 +32616,7 @@
         <v>46079</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32689,7 +32689,7 @@
         <v>46079</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32762,7 +32762,7 @@
         <v>44494</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32835,7 +32835,7 @@
         <v>46085</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32908,7 +32908,7 @@
         <v>46085</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32981,7 +32981,7 @@
         <v>46085</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33054,7 +33054,7 @@
         <v>44893</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33127,7 +33127,7 @@
         <v>46090</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33200,7 +33200,7 @@
         <v>44518</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33273,7 +33273,7 @@
         <v>44728</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33346,7 +33346,7 @@
         <v>45009</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33419,7 +33419,7 @@
         <v>45009</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33492,7 +33492,7 @@
         <v>45009</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33565,7 +33565,7 @@
         <v>45009</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33638,7 +33638,7 @@
         <v>46190</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33716,7 +33716,7 @@
         <v>44911</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33789,7 +33789,7 @@
         <v>45159</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33862,7 +33862,7 @@
         <v>46120</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33935,7 +33935,7 @@
         <v>46196</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34008,7 +34008,7 @@
         <v>45514</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34081,7 +34081,7 @@
         <v>45514</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34154,7 +34154,7 @@
         <v>45202</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34227,7 +34227,7 @@
         <v>44879</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34300,7 +34300,7 @@
         <v>46196</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34378,7 +34378,7 @@
         <v>46196</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34456,7 +34456,7 @@
         <v>46196</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34534,7 +34534,7 @@
         <v>46107</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34607,7 +34607,7 @@
         <v>45126</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34680,7 +34680,7 @@
         <v>45126</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34753,7 +34753,7 @@
         <v>45126</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34826,7 +34826,7 @@
         <v>46010</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34899,7 +34899,7 @@
         <v>46198</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34972,7 +34972,7 @@
         <v>45155</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -35045,7 +35045,7 @@
         <v>46197</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -35123,7 +35123,7 @@
         <v>46197</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35201,7 +35201,7 @@
         <v>46197</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35279,7 +35279,7 @@
         <v>46120</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35352,7 +35352,7 @@
         <v>44953</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35425,7 +35425,7 @@
         <v>45362</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35498,7 +35498,7 @@
         <v>44700</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35571,7 +35571,7 @@
         <v>46127</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35644,7 +35644,7 @@
         <v>46127</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35717,7 +35717,7 @@
         <v>46127</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35790,7 +35790,7 @@
         <v>46202</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35863,7 +35863,7 @@
         <v>46133</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35936,7 +35936,7 @@
         <v>45743</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36009,7 +36009,7 @@
         <v>45296</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -36082,7 +36082,7 @@
         <v>44530</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36155,7 +36155,7 @@
         <v>44777</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36228,7 +36228,7 @@
         <v>46134</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36301,7 +36301,7 @@
         <v>45644</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36374,7 +36374,7 @@
         <v>45181</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36447,7 +36447,7 @@
         <v>44993</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36520,7 +36520,7 @@
         <v>45211</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36593,7 +36593,7 @@
         <v>45164</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36666,7 +36666,7 @@
         <v>46139</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36739,7 +36739,7 @@
         <v>45190</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36812,7 +36812,7 @@
         <v>44993</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36885,7 +36885,7 @@
         <v>45392</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36958,7 +36958,7 @@
         <v>45719</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37031,7 +37031,7 @@
         <v>45719</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -37104,7 +37104,7 @@
         <v>45349</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37177,7 +37177,7 @@
         <v>45966</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37250,7 +37250,7 @@
         <v>45905</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37323,7 +37323,7 @@
         <v>46205</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37401,7 +37401,7 @@
         <v>45531</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37474,7 +37474,7 @@
         <v>45901</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37547,7 +37547,7 @@
         <v>45126</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37620,7 +37620,7 @@
         <v>44861</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37693,7 +37693,7 @@
         <v>45909</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37766,7 +37766,7 @@
         <v>45772</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37839,7 +37839,7 @@
         <v>45205</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37912,7 +37912,7 @@
         <v>45474</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37985,7 +37985,7 @@
         <v>45084</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -38058,7 +38058,7 @@
         <v>46127</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -38136,7 +38136,7 @@
         <v>45126</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38209,7 +38209,7 @@
         <v>45574</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38282,7 +38282,7 @@
         <v>46212</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38355,7 +38355,7 @@
         <v>46211</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38428,7 +38428,7 @@
         <v>45204</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38506,7 +38506,7 @@
         <v>46212</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38579,7 +38579,7 @@
         <v>45232</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38652,7 +38652,7 @@
         <v>45098</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38725,7 +38725,7 @@
         <v>46213</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38798,7 +38798,7 @@
         <v>45392</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38871,7 +38871,7 @@
         <v>45740</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38944,7 +38944,7 @@
         <v>45341</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -39017,7 +39017,7 @@
         <v>44995</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -39090,7 +39090,7 @@
         <v>45003</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -39163,7 +39163,7 @@
         <v>45477</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39236,7 +39236,7 @@
         <v>44995</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39309,7 +39309,7 @@
         <v>45126</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39382,7 +39382,7 @@
         <v>45514</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39455,7 +39455,7 @@
         <v>45146</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39528,7 +39528,7 @@
         <v>46271</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39601,7 +39601,7 @@
         <v>46273</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39674,7 +39674,7 @@
         <v>46272</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39747,7 +39747,7 @@
         <v>44959</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39820,7 +39820,7 @@
         <v>45068</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39898,7 +39898,7 @@
         <v>45707</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39971,7 +39971,7 @@
         <v>44851</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -40044,7 +40044,7 @@
         <v>44608</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -40117,7 +40117,7 @@
         <v>45095</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40190,7 +40190,7 @@
         <v>44580</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40263,7 +40263,7 @@
         <v>46188</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40336,7 +40336,7 @@
         <v>46275</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40409,7 +40409,7 @@
         <v>45373</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40482,7 +40482,7 @@
         <v>45161</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40560,7 +40560,7 @@
         <v>44984</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40633,7 +40633,7 @@
         <v>45252</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40706,7 +40706,7 @@
         <v>44761</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40779,7 +40779,7 @@
         <v>44802</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40852,7 +40852,7 @@
         <v>46279</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40930,7 +40930,7 @@
         <v>46279</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -41008,7 +41008,7 @@
         <v>45422</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -41081,7 +41081,7 @@
         <v>46279</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -41159,7 +41159,7 @@
         <v>44808</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41232,7 +41232,7 @@
         <v>46279</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41305,7 +41305,7 @@
         <v>46279</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41383,7 +41383,7 @@
         <v>46279</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41461,7 +41461,7 @@
         <v>46279</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41539,7 +41539,7 @@
         <v>46279</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41617,7 +41617,7 @@
         <v>46279</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41695,7 +41695,7 @@
         <v>46279</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41773,7 +41773,7 @@
         <v>46279</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41851,7 +41851,7 @@
         <v>45189</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41924,7 +41924,7 @@
         <v>45772</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41997,7 +41997,7 @@
         <v>45049</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -42070,7 +42070,7 @@
         <v>44531</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -42143,7 +42143,7 @@
         <v>45051</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -42216,7 +42216,7 @@
         <v>45051</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42289,7 +42289,7 @@
         <v>45126</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42362,7 +42362,7 @@
         <v>45126</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42435,7 +42435,7 @@
         <v>45323</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42508,7 +42508,7 @@
         <v>44673</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42581,7 +42581,7 @@
         <v>45596</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42654,7 +42654,7 @@
         <v>46282</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42727,7 +42727,7 @@
         <v>44893</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42800,7 +42800,7 @@
         <v>45668</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42873,7 +42873,7 @@
         <v>44759</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42946,7 +42946,7 @@
         <v>44594</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -43019,7 +43019,7 @@
         <v>45323</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -43092,7 +43092,7 @@
         <v>46244</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -43165,7 +43165,7 @@
         <v>44852</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43238,7 +43238,7 @@
         <v>45149</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43311,7 +43311,7 @@
         <v>46286</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43384,7 +43384,7 @@
         <v>45111</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43457,7 +43457,7 @@
         <v>45310</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43530,7 +43530,7 @@
         <v>45727</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43603,7 +43603,7 @@
         <v>45727</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43676,7 +43676,7 @@
         <v>45706</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43749,7 +43749,7 @@
         <v>45204</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43827,7 +43827,7 @@
         <v>45062</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43900,7 +43900,7 @@
         <v>45562</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43973,7 +43973,7 @@
         <v>45926</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -44046,7 +44046,7 @@
         <v>45103</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -44119,7 +44119,7 @@
         <v>45688</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -44192,7 +44192,7 @@
         <v>44589</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44265,7 +44265,7 @@
         <v>46288</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44338,7 +44338,7 @@
         <v>44726</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44411,7 +44411,7 @@
         <v>45742</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44484,7 +44484,7 @@
         <v>44524</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44557,7 +44557,7 @@
         <v>44728</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44630,7 +44630,7 @@
         <v>45182</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44703,7 +44703,7 @@
         <v>44816</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44776,7 +44776,7 @@
         <v>46288</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44849,7 +44849,7 @@
         <v>44840</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44927,7 +44927,7 @@
         <v>45595</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -45000,7 +45000,7 @@
         <v>44897</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -45073,7 +45073,7 @@
         <v>45273</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -45151,7 +45151,7 @@
         <v>45349</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -45224,7 +45224,7 @@
         <v>44827</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45297,7 +45297,7 @@
         <v>45092</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45370,7 +45370,7 @@
         <v>46290</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45443,7 +45443,7 @@
         <v>46290</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45516,7 +45516,7 @@
         <v>46290</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45589,7 +45589,7 @@
         <v>44550</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45662,7 +45662,7 @@
         <v>45076</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45735,7 +45735,7 @@
         <v>45385</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45808,7 +45808,7 @@
         <v>45515</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45881,7 +45881,7 @@
         <v>45307</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45954,7 +45954,7 @@
         <v>45317</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -46027,7 +46027,7 @@
         <v>45187</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -46100,7 +46100,7 @@
         <v>44748</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -46173,7 +46173,7 @@
         <v>46160</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -46246,7 +46246,7 @@
         <v>46251</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -46319,7 +46319,7 @@
         <v>44699</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -46392,7 +46392,7 @@
         <v>45400</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46465,7 +46465,7 @@
         <v>45229</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46538,7 +46538,7 @@
         <v>45188</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -46616,7 +46616,7 @@
         <v>45769</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -46689,7 +46689,7 @@
         <v>44769</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46762,7 +46762,7 @@
         <v>46253</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46835,7 +46835,7 @@
         <v>46255</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46913,7 +46913,7 @@
         <v>44488</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46991,7 +46991,7 @@
         <v>45769</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -47064,7 +47064,7 @@
         <v>46255</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -47142,7 +47142,7 @@
         <v>46255</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -47220,7 +47220,7 @@
         <v>46255</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -47298,7 +47298,7 @@
         <v>46255</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -47376,7 +47376,7 @@
         <v>46253</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -47449,7 +47449,7 @@
         <v>46255</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -47527,7 +47527,7 @@
         <v>46255</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -47600,7 +47600,7 @@
         <v>45606</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -47673,7 +47673,7 @@
         <v>45394</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -47746,7 +47746,7 @@
         <v>44955</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47819,7 +47819,7 @@
         <v>45048</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47892,7 +47892,7 @@
         <v>45351</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47965,7 +47965,7 @@
         <v>45534</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -48038,7 +48038,7 @@
         <v>45215</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -48111,7 +48111,7 @@
         <v>45551</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -48184,7 +48184,7 @@
         <v>45523</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -48257,7 +48257,7 @@
         <v>44949</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -48330,7 +48330,7 @@
         <v>45684</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -48403,7 +48403,7 @@
         <v>45624</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -48476,7 +48476,7 @@
         <v>45484</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -48549,7 +48549,7 @@
         <v>46230</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -48622,7 +48622,7 @@
         <v>45107</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -48695,7 +48695,7 @@
         <v>45445</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -48768,7 +48768,7 @@
         <v>45317</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -48841,7 +48841,7 @@
         <v>45548</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -48914,7 +48914,7 @@
         <v>45415</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -48987,7 +48987,7 @@
         <v>45638</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -49060,7 +49060,7 @@
         <v>45565</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -49133,7 +49133,7 @@
         <v>45386</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -49206,7 +49206,7 @@
         <v>46255</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -49284,7 +49284,7 @@
         <v>45716</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -49357,7 +49357,7 @@
         <v>46120</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -49430,7 +49430,7 @@
         <v>45775</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -49503,7 +49503,7 @@
         <v>45481</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -49576,7 +49576,7 @@
         <v>46188</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -49649,7 +49649,7 @@
         <v>45566</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -49722,7 +49722,7 @@
         <v>45582</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -49795,7 +49795,7 @@
         <v>45609</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -49868,7 +49868,7 @@
         <v>45484</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -49941,7 +49941,7 @@
         <v>45688</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -50014,7 +50014,7 @@
         <v>45610</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -50087,7 +50087,7 @@
         <v>46302</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -50160,7 +50160,7 @@
         <v>45400</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -50233,7 +50233,7 @@
         <v>46259</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -50306,7 +50306,7 @@
         <v>45455</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -50379,7 +50379,7 @@
         <v>45665</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -50452,7 +50452,7 @@
         <v>44977</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -50525,7 +50525,7 @@
         <v>45537</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -50598,7 +50598,7 @@
         <v>46306</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -50671,7 +50671,7 @@
         <v>44958</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -50744,7 +50744,7 @@
         <v>46308</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -50817,7 +50817,7 @@
         <v>45800</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -50890,7 +50890,7 @@
         <v>45804</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -50963,7 +50963,7 @@
         <v>45813</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -51036,7 +51036,7 @@
         <v>46134</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -51109,7 +51109,7 @@
         <v>46268</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -51182,7 +51182,7 @@
         <v>45825</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -51255,7 +51255,7 @@
         <v>45826</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -51328,7 +51328,7 @@
         <v>45826</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -51401,7 +51401,7 @@
         <v>46245</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -51474,7 +51474,7 @@
         <v>45826</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -51547,7 +51547,7 @@
         <v>45826</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -51620,7 +51620,7 @@
         <v>45826</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -51693,7 +51693,7 @@
         <v>45826</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -51766,7 +51766,7 @@
         <v>45832</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -51839,7 +51839,7 @@
         <v>45805</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -51912,7 +51912,7 @@
         <v>45845</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -51985,7 +51985,7 @@
         <v>45621</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -52058,7 +52058,7 @@
         <v>45727</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -52131,7 +52131,7 @@
         <v>45849</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -52204,7 +52204,7 @@
         <v>45775</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -52277,7 +52277,7 @@
         <v>45716</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -52350,7 +52350,7 @@
         <v>45851</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -52423,7 +52423,7 @@
         <v>45851</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -52496,7 +52496,7 @@
         <v>45772</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -52569,7 +52569,7 @@
         <v>45857</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -52642,7 +52642,7 @@
         <v>45863</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -52715,7 +52715,7 @@
         <v>45750</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -52788,7 +52788,7 @@
         <v>45790</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -52861,7 +52861,7 @@
         <v>45881</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -52934,7 +52934,7 @@
         <v>44476</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -53007,7 +53007,7 @@
         <v>45191</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -53080,7 +53080,7 @@
         <v>44959</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -53153,7 +53153,7 @@
         <v>45194</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -53226,7 +53226,7 @@
         <v>45377</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -53299,7 +53299,7 @@
         <v>45387</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -53372,7 +53372,7 @@
         <v>44903</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -53445,7 +53445,7 @@
         <v>44900</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -53518,7 +53518,7 @@
         <v>44852</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -53591,7 +53591,7 @@
         <v>45200</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -53664,7 +53664,7 @@
         <v>45534</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -53737,7 +53737,7 @@
         <v>45191</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -53810,7 +53810,7 @@
         <v>45386</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -53883,7 +53883,7 @@
         <v>45287</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -53956,7 +53956,7 @@
         <v>45386</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -54029,7 +54029,7 @@
         <v>45386</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -54102,7 +54102,7 @@
         <v>45386</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -54175,7 +54175,7 @@
         <v>45387</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -54248,7 +54248,7 @@
         <v>44519</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -54321,7 +54321,7 @@
         <v>45534</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -54394,7 +54394,7 @@
         <v>45377</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -54467,7 +54467,7 @@
         <v>44928</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -54540,7 +54540,7 @@
         <v>45377</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -54613,7 +54613,7 @@
         <v>44519</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -54686,7 +54686,7 @@
         <v>45200</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -54759,7 +54759,7 @@
         <v>44900</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -54832,7 +54832,7 @@
         <v>45330</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -54905,7 +54905,7 @@
         <v>44959</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -54978,7 +54978,7 @@
         <v>45348</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -55051,7 +55051,7 @@
         <v>45813</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -55124,7 +55124,7 @@
         <v>45813</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -55197,7 +55197,7 @@
         <v>45849</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -55270,7 +55270,7 @@
         <v>45898</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -55343,7 +55343,7 @@
         <v>45935</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -55416,7 +55416,7 @@
         <v>45978</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -55489,7 +55489,7 @@
         <v>46034</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -55562,7 +55562,7 @@
         <v>46049</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -55635,7 +55635,7 @@
         <v>46049</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -55708,7 +55708,7 @@
         <v>46065</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -55781,7 +55781,7 @@
         <v>46092</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -55854,7 +55854,7 @@
         <v>46062</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -55927,7 +55927,7 @@
         <v>46119</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -56000,7 +56000,7 @@
         <v>46119</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -56073,7 +56073,7 @@
         <v>46127</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -56146,7 +56146,7 @@
         <v>46167</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -56219,7 +56219,7 @@
         <v>46156</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -56292,7 +56292,7 @@
         <v>46183</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -56365,7 +56365,7 @@
         <v>46191</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -56438,7 +56438,7 @@
         <v>46276</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -56516,7 +56516,7 @@
         <v>46283</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -56589,7 +56589,7 @@
         <v>46286</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>

--- a/Översikt EMMABODA.xlsx
+++ b/Översikt EMMABODA.xlsx
@@ -601,7 +601,7 @@
         <v>45534</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>45440</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -830,7 +830,7 @@
         <v>45387</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>45202</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
         <v>45030</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>45616</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         <v>44706</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>44811</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         <v>45330</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1600,7 +1600,7 @@
         <v>45359</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>46136</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1818,7 +1818,7 @@
         <v>45369</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1932,7 +1932,7 @@
         <v>45086</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2038,7 +2038,7 @@
         <v>44937</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>46062</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2254,7 +2254,7 @@
         <v>46069</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2360,7 +2360,7 @@
         <v>46214</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2466,7 +2466,7 @@
         <v>44984</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2571,7 +2571,7 @@
         <v>45229</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2680,7 +2680,7 @@
         <v>45797</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2789,7 +2789,7 @@
         <v>44771</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2898,7 +2898,7 @@
         <v>44966</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         <v>45953</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3112,7 +3112,7 @@
         <v>45335</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3217,7 +3217,7 @@
         <v>45068</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3327,7 +3327,7 @@
         <v>46213</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3432,7 +3432,7 @@
         <v>46213</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3537,7 +3537,7 @@
         <v>46218</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3642,7 +3642,7 @@
         <v>44895</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3747,7 +3747,7 @@
         <v>46282</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3852,7 +3852,7 @@
         <v>46055</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3957,7 +3957,7 @@
         <v>46253</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4062,7 +4062,7 @@
         <v>45161</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4172,7 +4172,7 @@
         <v>45967</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         <v>46135</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4387,7 +4387,7 @@
         <v>45763</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4496,7 +4496,7 @@
         <v>45166</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4601,7 +4601,7 @@
         <v>44762</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4706,7 +4706,7 @@
         <v>45092</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4811,7 +4811,7 @@
         <v>44495</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4920,7 +4920,7 @@
         <v>45196</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         <v>45107</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5134,7 +5134,7 @@
         <v>45104</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5239,7 +5239,7 @@
         <v>44570</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5344,7 +5344,7 @@
         <v>44588</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5449,7 +5449,7 @@
         <v>45509</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5554,7 +5554,7 @@
         <v>45387</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5663,7 +5663,7 @@
         <v>45611</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5772,7 +5772,7 @@
         <v>45330</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5881,7 +5881,7 @@
         <v>44852</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5990,7 +5990,7 @@
         <v>45442</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6095,7 +6095,7 @@
         <v>45153</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6200,7 +6200,7 @@
         <v>45386</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6305,7 +6305,7 @@
         <v>45685</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6414,7 +6414,7 @@
         <v>45813</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6523,7 +6523,7 @@
         <v>46275</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6632,7 +6632,7 @@
         <v>44530</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6705,7 +6705,7 @@
         <v>44496</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6778,7 +6778,7 @@
         <v>44764</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6851,7 +6851,7 @@
         <v>44530</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6924,7 +6924,7 @@
         <v>44496</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6997,7 +6997,7 @@
         <v>44529</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7070,7 +7070,7 @@
         <v>44601</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7143,7 +7143,7 @@
         <v>44600</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7216,7 +7216,7 @@
         <v>44507</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7289,7 +7289,7 @@
         <v>44507</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7362,7 +7362,7 @@
         <v>44507</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7435,7 +7435,7 @@
         <v>44599</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7508,7 +7508,7 @@
         <v>44691</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7581,7 +7581,7 @@
         <v>44628</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7654,7 +7654,7 @@
         <v>44504</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         <v>44515</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7800,7 +7800,7 @@
         <v>44851</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7873,7 +7873,7 @@
         <v>44728</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7946,7 +7946,7 @@
         <v>44860</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8019,7 +8019,7 @@
         <v>44523</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8092,7 +8092,7 @@
         <v>44648</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8165,7 +8165,7 @@
         <v>44628</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8238,7 +8238,7 @@
         <v>44788</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8311,7 +8311,7 @@
         <v>44627</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8384,7 +8384,7 @@
         <v>44498</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8457,7 +8457,7 @@
         <v>44768</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8530,7 +8530,7 @@
         <v>44851</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8603,7 +8603,7 @@
         <v>44529</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8676,7 +8676,7 @@
         <v>44813</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8749,7 +8749,7 @@
         <v>44809</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8822,7 +8822,7 @@
         <v>44771</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8895,7 +8895,7 @@
         <v>44587</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8968,7 +8968,7 @@
         <v>44496</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9041,7 +9041,7 @@
         <v>44507</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9114,7 +9114,7 @@
         <v>44507</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9187,7 +9187,7 @@
         <v>44652</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9260,7 +9260,7 @@
         <v>44628</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9333,7 +9333,7 @@
         <v>44600</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9406,7 +9406,7 @@
         <v>44501</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9479,7 +9479,7 @@
         <v>44600</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9552,7 +9552,7 @@
         <v>44852</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9625,7 +9625,7 @@
         <v>44839</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9698,7 +9698,7 @@
         <v>44615</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9776,7 +9776,7 @@
         <v>44622</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9849,7 +9849,7 @@
         <v>44524</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9922,7 +9922,7 @@
         <v>44712</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9995,7 +9995,7 @@
         <v>44743</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10068,7 +10068,7 @@
         <v>44532</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10146,7 +10146,7 @@
         <v>44722</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10219,7 +10219,7 @@
         <v>44593</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10292,7 +10292,7 @@
         <v>44652</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10365,7 +10365,7 @@
         <v>44699</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10438,7 +10438,7 @@
         <v>44820</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10516,7 +10516,7 @@
         <v>44847</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10589,7 +10589,7 @@
         <v>44743</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10662,7 +10662,7 @@
         <v>44589</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10735,7 +10735,7 @@
         <v>44600</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10808,7 +10808,7 @@
         <v>44725</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10881,7 +10881,7 @@
         <v>44551</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10959,7 +10959,7 @@
         <v>44600</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11032,7 +11032,7 @@
         <v>44655</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11105,7 +11105,7 @@
         <v>44979</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11178,7 +11178,7 @@
         <v>45887</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11251,7 +11251,7 @@
         <v>45887</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11324,7 +11324,7 @@
         <v>45749</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11397,7 +11397,7 @@
         <v>44530</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11470,7 +11470,7 @@
         <v>44788</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11543,7 +11543,7 @@
         <v>45606</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11616,7 +11616,7 @@
         <v>45048</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11689,7 +11689,7 @@
         <v>45187</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11762,7 +11762,7 @@
         <v>45219</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11835,7 +11835,7 @@
         <v>45335</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11908,7 +11908,7 @@
         <v>45204</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11986,7 +11986,7 @@
         <v>45615</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12059,7 +12059,7 @@
         <v>45190</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12132,7 +12132,7 @@
         <v>45370</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12205,7 +12205,7 @@
         <v>45091</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12278,7 +12278,7 @@
         <v>45149</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12351,7 +12351,7 @@
         <v>45191</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12424,7 +12424,7 @@
         <v>45700</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12497,7 +12497,7 @@
         <v>45155</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12570,7 +12570,7 @@
         <v>44739</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12643,7 +12643,7 @@
         <v>45251</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12716,7 +12716,7 @@
         <v>44930</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12789,7 +12789,7 @@
         <v>45181</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12862,7 +12862,7 @@
         <v>45211</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12935,7 +12935,7 @@
         <v>45719</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13008,7 +13008,7 @@
         <v>45348</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13081,7 +13081,7 @@
         <v>45069</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13154,7 +13154,7 @@
         <v>45069</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13227,7 +13227,7 @@
         <v>45397</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13300,7 +13300,7 @@
         <v>45741</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13373,7 +13373,7 @@
         <v>44728</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13446,7 +13446,7 @@
         <v>45425</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13519,7 +13519,7 @@
         <v>45036</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13592,7 +13592,7 @@
         <v>45719</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13665,7 +13665,7 @@
         <v>44834</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13738,7 +13738,7 @@
         <v>45681</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13811,7 +13811,7 @@
         <v>45411</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13884,7 +13884,7 @@
         <v>45051</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13957,7 +13957,7 @@
         <v>45051</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14030,7 +14030,7 @@
         <v>46160</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14103,7 +14103,7 @@
         <v>45908</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14176,7 +14176,7 @@
         <v>45590</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14249,7 +14249,7 @@
         <v>44808</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14322,7 +14322,7 @@
         <v>45909</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14395,7 +14395,7 @@
         <v>46162</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14468,7 +14468,7 @@
         <v>45902</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14541,7 +14541,7 @@
         <v>46162</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14614,7 +14614,7 @@
         <v>44944</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14687,7 +14687,7 @@
         <v>45048</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14760,7 +14760,7 @@
         <v>45514</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14833,7 +14833,7 @@
         <v>45514</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14906,7 +14906,7 @@
         <v>45915</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14979,7 +14979,7 @@
         <v>45915</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15052,7 +15052,7 @@
         <v>45915</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15125,7 +15125,7 @@
         <v>45076</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15198,7 +15198,7 @@
         <v>45392</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15271,7 +15271,7 @@
         <v>45217</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15344,7 +15344,7 @@
         <v>45688</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15417,7 +15417,7 @@
         <v>45921</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15490,7 +15490,7 @@
         <v>45740</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15563,7 +15563,7 @@
         <v>45180</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15636,7 +15636,7 @@
         <v>45668</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15709,7 +15709,7 @@
         <v>45349</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15782,7 +15782,7 @@
         <v>45349</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15855,7 +15855,7 @@
         <v>45641</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15928,7 +15928,7 @@
         <v>45931</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16001,7 +16001,7 @@
         <v>45923</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16074,7 +16074,7 @@
         <v>44791</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16147,7 +16147,7 @@
         <v>45310</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16220,7 +16220,7 @@
         <v>44911</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16293,7 +16293,7 @@
         <v>45394</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16366,7 +16366,7 @@
         <v>45422</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16439,7 +16439,7 @@
         <v>45938</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16512,7 +16512,7 @@
         <v>44900</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16585,7 +16585,7 @@
         <v>45938</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16658,7 +16658,7 @@
         <v>45938</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16731,7 +16731,7 @@
         <v>45938</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16804,7 +16804,7 @@
         <v>45189</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16877,7 +16877,7 @@
         <v>45229</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16950,7 +16950,7 @@
         <v>45385</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17023,7 +17023,7 @@
         <v>45376</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17096,7 +17096,7 @@
         <v>45126</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17169,7 +17169,7 @@
         <v>45113</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17242,7 +17242,7 @@
         <v>45007</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17315,7 +17315,7 @@
         <v>45461</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17388,7 +17388,7 @@
         <v>45953</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17461,7 +17461,7 @@
         <v>45164</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17534,7 +17534,7 @@
         <v>46183</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17607,7 +17607,7 @@
         <v>45901</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17680,7 +17680,7 @@
         <v>46182</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17753,7 +17753,7 @@
         <v>46182</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17826,7 +17826,7 @@
         <v>46185</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17899,7 +17899,7 @@
         <v>46185</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17972,7 +17972,7 @@
         <v>45211</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18045,7 +18045,7 @@
         <v>46185</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18118,7 +18118,7 @@
         <v>45960</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18191,7 +18191,7 @@
         <v>45126</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18264,7 +18264,7 @@
         <v>44698</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18337,7 +18337,7 @@
         <v>45317</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18410,7 +18410,7 @@
         <v>46188</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18483,7 +18483,7 @@
         <v>45964</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18556,7 +18556,7 @@
         <v>45964</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18629,7 +18629,7 @@
         <v>45373</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18702,7 +18702,7 @@
         <v>46189</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18775,7 +18775,7 @@
         <v>44861</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18848,7 +18848,7 @@
         <v>46188</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18921,7 +18921,7 @@
         <v>46190</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18999,7 +18999,7 @@
         <v>45967</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19072,7 +19072,7 @@
         <v>45967</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19145,7 +19145,7 @@
         <v>45204</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19223,7 +19223,7 @@
         <v>45971</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19296,7 +19296,7 @@
         <v>45335</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19369,7 +19369,7 @@
         <v>45369</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19442,7 +19442,7 @@
         <v>46120</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19515,7 +19515,7 @@
         <v>46196</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19593,7 +19593,7 @@
         <v>46196</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19671,7 +19671,7 @@
         <v>46196</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19749,7 +19749,7 @@
         <v>45273</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19827,7 +19827,7 @@
         <v>46197</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19905,7 +19905,7 @@
         <v>46197</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19983,7 +19983,7 @@
         <v>45204</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20061,7 +20061,7 @@
         <v>45595</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20134,7 +20134,7 @@
         <v>46010</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20207,7 +20207,7 @@
         <v>45433</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20280,7 +20280,7 @@
         <v>46196</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20353,7 +20353,7 @@
         <v>46197</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20431,7 +20431,7 @@
         <v>46198</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20504,7 +20504,7 @@
         <v>45237</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20577,7 +20577,7 @@
         <v>44531</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20650,7 +20650,7 @@
         <v>44504</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20723,7 +20723,7 @@
         <v>45103</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20796,7 +20796,7 @@
         <v>45474</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20869,7 +20869,7 @@
         <v>45341</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20942,7 +20942,7 @@
         <v>46202</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21015,7 +21015,7 @@
         <v>45979</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21088,7 +21088,7 @@
         <v>45665</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21161,7 +21161,7 @@
         <v>45126</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21234,7 +21234,7 @@
         <v>45202</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21307,7 +21307,7 @@
         <v>45281</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21380,7 +21380,7 @@
         <v>45155</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21453,7 +21453,7 @@
         <v>46205</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21531,7 +21531,7 @@
         <v>44897</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21604,7 +21604,7 @@
         <v>45716</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21677,7 +21677,7 @@
         <v>46127</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21755,7 +21755,7 @@
         <v>44519</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21828,7 +21828,7 @@
         <v>45561</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21906,7 +21906,7 @@
         <v>46211</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21979,7 +21979,7 @@
         <v>45989</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22052,7 +22052,7 @@
         <v>45400</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22125,7 +22125,7 @@
         <v>45994</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22198,7 +22198,7 @@
         <v>44907</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22271,7 +22271,7 @@
         <v>45474</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22344,7 +22344,7 @@
         <v>46212</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22417,7 +22417,7 @@
         <v>46212</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22490,7 +22490,7 @@
         <v>46213</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22563,7 +22563,7 @@
         <v>45986</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22636,7 +22636,7 @@
         <v>44979</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22709,7 +22709,7 @@
         <v>45551</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22782,7 +22782,7 @@
         <v>45523</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22855,7 +22855,7 @@
         <v>45215</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22928,7 +22928,7 @@
         <v>44949</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23001,7 +23001,7 @@
         <v>45684</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23074,7 +23074,7 @@
         <v>45624</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23147,7 +23147,7 @@
         <v>45534</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23220,7 +23220,7 @@
         <v>45484</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23293,7 +23293,7 @@
         <v>45351</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23366,7 +23366,7 @@
         <v>46188</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23439,7 +23439,7 @@
         <v>45107</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23512,7 +23512,7 @@
         <v>45317</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23585,7 +23585,7 @@
         <v>45415</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23658,7 +23658,7 @@
         <v>45638</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23731,7 +23731,7 @@
         <v>46279</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23809,7 +23809,7 @@
         <v>45610</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23882,7 +23882,7 @@
         <v>45582</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23955,7 +23955,7 @@
         <v>45565</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24028,7 +24028,7 @@
         <v>45445</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24101,7 +24101,7 @@
         <v>46279</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24179,7 +24179,7 @@
         <v>46279</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24257,7 +24257,7 @@
         <v>46279</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24335,7 +24335,7 @@
         <v>46279</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24413,7 +24413,7 @@
         <v>46279</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24486,7 +24486,7 @@
         <v>45548</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24559,7 +24559,7 @@
         <v>45609</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24632,7 +24632,7 @@
         <v>45688</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24705,7 +24705,7 @@
         <v>46279</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24783,7 +24783,7 @@
         <v>46279</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24861,7 +24861,7 @@
         <v>46279</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24939,7 +24939,7 @@
         <v>46279</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25017,7 +25017,7 @@
         <v>46279</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25095,7 +25095,7 @@
         <v>45484</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25168,7 +25168,7 @@
         <v>46282</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25241,7 +25241,7 @@
         <v>45386</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25314,7 +25314,7 @@
         <v>45775</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25387,7 +25387,7 @@
         <v>45566</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25460,7 +25460,7 @@
         <v>45481</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25533,7 +25533,7 @@
         <v>45400</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25606,7 +25606,7 @@
         <v>46024</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25679,7 +25679,7 @@
         <v>45727</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25752,7 +25752,7 @@
         <v>45455</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25825,7 +25825,7 @@
         <v>46286</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25898,7 +25898,7 @@
         <v>45706</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25971,7 +25971,7 @@
         <v>46036</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26044,7 +26044,7 @@
         <v>45727</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26117,7 +26117,7 @@
         <v>45926</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26190,7 +26190,7 @@
         <v>46288</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26263,7 +26263,7 @@
         <v>46244</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26336,7 +26336,7 @@
         <v>46288</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26409,7 +26409,7 @@
         <v>46044</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26482,7 +26482,7 @@
         <v>45161</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26560,7 +26560,7 @@
         <v>45800</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26633,7 +26633,7 @@
         <v>45537</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26706,7 +26706,7 @@
         <v>44977</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26779,7 +26779,7 @@
         <v>45665</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26852,7 +26852,7 @@
         <v>46049</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26925,7 +26925,7 @@
         <v>45804</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26998,7 +26998,7 @@
         <v>44958</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27071,7 +27071,7 @@
         <v>46290</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27144,7 +27144,7 @@
         <v>46055</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27217,7 +27217,7 @@
         <v>45273</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27295,7 +27295,7 @@
         <v>46290</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27368,7 +27368,7 @@
         <v>46290</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27441,7 +27441,7 @@
         <v>46058</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27514,7 +27514,7 @@
         <v>46062</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27587,7 +27587,7 @@
         <v>45813</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27660,7 +27660,7 @@
         <v>46160</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27733,7 +27733,7 @@
         <v>46069</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27811,7 +27811,7 @@
         <v>46071</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27889,7 +27889,7 @@
         <v>46071</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27967,7 +27967,7 @@
         <v>46072</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28040,7 +28040,7 @@
         <v>46072</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28113,7 +28113,7 @@
         <v>46253</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28186,7 +28186,7 @@
         <v>46071</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28264,7 +28264,7 @@
         <v>46251</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28337,7 +28337,7 @@
         <v>45825</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28410,7 +28410,7 @@
         <v>45826</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28483,7 +28483,7 @@
         <v>45826</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28556,7 +28556,7 @@
         <v>45826</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28629,7 +28629,7 @@
         <v>45826</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28702,7 +28702,7 @@
         <v>46078</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28775,7 +28775,7 @@
         <v>45826</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28848,7 +28848,7 @@
         <v>46253</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28921,7 +28921,7 @@
         <v>45826</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28994,7 +28994,7 @@
         <v>46079</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29067,7 +29067,7 @@
         <v>46079</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29140,7 +29140,7 @@
         <v>45477</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29213,7 +29213,7 @@
         <v>45832</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29286,7 +29286,7 @@
         <v>46085</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29359,7 +29359,7 @@
         <v>46085</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29432,7 +29432,7 @@
         <v>46085</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29505,7 +29505,7 @@
         <v>45514</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29578,7 +29578,7 @@
         <v>46255</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29656,7 +29656,7 @@
         <v>46255</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29734,7 +29734,7 @@
         <v>46090</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29807,7 +29807,7 @@
         <v>46255</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29885,7 +29885,7 @@
         <v>46255</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29958,7 +29958,7 @@
         <v>45606</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30031,7 +30031,7 @@
         <v>44951</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30104,7 +30104,7 @@
         <v>45805</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30177,7 +30177,7 @@
         <v>45621</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30250,7 +30250,7 @@
         <v>45161</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30328,7 +30328,7 @@
         <v>45845</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30401,7 +30401,7 @@
         <v>46255</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30479,7 +30479,7 @@
         <v>46255</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30557,7 +30557,7 @@
         <v>46255</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30635,7 +30635,7 @@
         <v>45727</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30708,7 +30708,7 @@
         <v>46230</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30781,7 +30781,7 @@
         <v>44519</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30854,7 +30854,7 @@
         <v>46255</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30932,7 +30932,7 @@
         <v>45772</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31005,7 +31005,7 @@
         <v>45775</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31078,7 +31078,7 @@
         <v>45849</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31151,7 +31151,7 @@
         <v>45716</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31224,7 +31224,7 @@
         <v>44530</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31297,7 +31297,7 @@
         <v>45851</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31370,7 +31370,7 @@
         <v>45851</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31443,7 +31443,7 @@
         <v>46107</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31516,7 +31516,7 @@
         <v>46259</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31589,7 +31589,7 @@
         <v>46302</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31662,7 +31662,7 @@
         <v>45857</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31735,7 +31735,7 @@
         <v>45750</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31808,7 +31808,7 @@
         <v>45863</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31881,7 +31881,7 @@
         <v>45790</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31954,7 +31954,7 @@
         <v>45189</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32027,7 +32027,7 @@
         <v>45189</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32100,7 +32100,7 @@
         <v>46120</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32173,7 +32173,7 @@
         <v>46120</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32246,7 +32246,7 @@
         <v>45716</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32319,7 +32319,7 @@
         <v>46188</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32392,7 +32392,7 @@
         <v>44550</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32465,7 +32465,7 @@
         <v>45099</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32538,7 +32538,7 @@
         <v>45070</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32611,7 +32611,7 @@
         <v>46127</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32684,7 +32684,7 @@
         <v>46127</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32757,7 +32757,7 @@
         <v>46127</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32830,7 +32830,7 @@
         <v>46306</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32903,7 +32903,7 @@
         <v>45881</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32976,7 +32976,7 @@
         <v>44896</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33049,7 +33049,7 @@
         <v>44900</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33122,7 +33122,7 @@
         <v>45537</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33195,7 +33195,7 @@
         <v>45562</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33268,7 +33268,7 @@
         <v>45615</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33341,7 +33341,7 @@
         <v>46308</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33414,7 +33414,7 @@
         <v>46134</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33487,7 +33487,7 @@
         <v>46133</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33560,7 +33560,7 @@
         <v>45475</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33633,7 +33633,7 @@
         <v>45632</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33706,7 +33706,7 @@
         <v>45401</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33779,7 +33779,7 @@
         <v>45551</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33857,7 +33857,7 @@
         <v>44893</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33930,7 +33930,7 @@
         <v>45819</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34003,7 +34003,7 @@
         <v>45818</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34076,7 +34076,7 @@
         <v>45587</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34149,7 +34149,7 @@
         <v>44683</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34222,7 +34222,7 @@
         <v>45972</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34295,7 +34295,7 @@
         <v>45966</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34368,7 +34368,7 @@
         <v>45901</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34441,7 +34441,7 @@
         <v>45392</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34514,7 +34514,7 @@
         <v>46006</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34587,7 +34587,7 @@
         <v>45818</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34660,7 +34660,7 @@
         <v>44993</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34733,7 +34733,7 @@
         <v>45349</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34806,7 +34806,7 @@
         <v>44995</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34879,7 +34879,7 @@
         <v>45155</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34952,7 +34952,7 @@
         <v>45905</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35025,7 +35025,7 @@
         <v>44897</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -35098,7 +35098,7 @@
         <v>46245</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -35171,7 +35171,7 @@
         <v>46043</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35244,7 +35244,7 @@
         <v>44949</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35317,7 +35317,7 @@
         <v>45524</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35390,7 +35390,7 @@
         <v>45349</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35463,7 +35463,7 @@
         <v>46271</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35536,7 +35536,7 @@
         <v>45007</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35609,7 +35609,7 @@
         <v>46268</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35682,7 +35682,7 @@
         <v>45400</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35755,7 +35755,7 @@
         <v>44580</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35828,7 +35828,7 @@
         <v>45966</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35901,7 +35901,7 @@
         <v>45022</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35974,7 +35974,7 @@
         <v>45022</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36047,7 +36047,7 @@
         <v>44839</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -36120,7 +36120,7 @@
         <v>44955</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36193,7 +36193,7 @@
         <v>46134</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36266,7 +36266,7 @@
         <v>45976</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36339,7 +36339,7 @@
         <v>46139</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36412,7 +36412,7 @@
         <v>46314</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36485,7 +36485,7 @@
         <v>46314</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36558,7 +36558,7 @@
         <v>45098</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36631,7 +36631,7 @@
         <v>46273</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36704,7 +36704,7 @@
         <v>45211</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36777,7 +36777,7 @@
         <v>45915</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36855,7 +36855,7 @@
         <v>46315</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36933,7 +36933,7 @@
         <v>46272</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37006,7 +37006,7 @@
         <v>45040</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37079,7 +37079,7 @@
         <v>46314</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -37152,7 +37152,7 @@
         <v>46055</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37225,7 +37225,7 @@
         <v>45909</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37298,7 +37298,7 @@
         <v>45574</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37371,7 +37371,7 @@
         <v>45166</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37444,7 +37444,7 @@
         <v>45252</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37517,7 +37517,7 @@
         <v>45392</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37590,7 +37590,7 @@
         <v>44995</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37663,7 +37663,7 @@
         <v>45938</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37736,7 +37736,7 @@
         <v>44973</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37814,7 +37814,7 @@
         <v>44594</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37887,7 +37887,7 @@
         <v>46317</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37965,7 +37965,7 @@
         <v>44524</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -38038,7 +38038,7 @@
         <v>44978</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -38111,7 +38111,7 @@
         <v>45707</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -38184,7 +38184,7 @@
         <v>46142</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38257,7 +38257,7 @@
         <v>44953</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38330,7 +38330,7 @@
         <v>44690</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38403,7 +38403,7 @@
         <v>45976</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38476,7 +38476,7 @@
         <v>45021</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38549,7 +38549,7 @@
         <v>46318</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38627,7 +38627,7 @@
         <v>46275</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38700,7 +38700,7 @@
         <v>46318</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38773,7 +38773,7 @@
         <v>45048</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38846,7 +38846,7 @@
         <v>44978</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38919,7 +38919,7 @@
         <v>45769</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38992,7 +38992,7 @@
         <v>45182</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -39065,7 +39065,7 @@
         <v>44748</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -39138,7 +39138,7 @@
         <v>45062</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -39211,7 +39211,7 @@
         <v>45191</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39284,7 +39284,7 @@
         <v>45095</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39357,7 +39357,7 @@
         <v>44777</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39430,7 +39430,7 @@
         <v>45789</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39503,7 +39503,7 @@
         <v>44960</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39576,7 +39576,7 @@
         <v>45362</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39649,7 +39649,7 @@
         <v>45009</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39722,7 +39722,7 @@
         <v>45009</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39795,7 +39795,7 @@
         <v>45422</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39868,7 +39868,7 @@
         <v>46069</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39946,7 +39946,7 @@
         <v>45559</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -40019,7 +40019,7 @@
         <v>45707</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -40092,7 +40092,7 @@
         <v>45084</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -40165,7 +40165,7 @@
         <v>46155</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40238,7 +40238,7 @@
         <v>45355</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40311,7 +40311,7 @@
         <v>44700</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40384,7 +40384,7 @@
         <v>45230</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40457,7 +40457,7 @@
         <v>46160</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40530,7 +40530,7 @@
         <v>44965</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40603,7 +40603,7 @@
         <v>45629</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40676,7 +40676,7 @@
         <v>44852</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40749,7 +40749,7 @@
         <v>45258</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40822,7 +40822,7 @@
         <v>45574</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40895,7 +40895,7 @@
         <v>45009</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40968,7 +40968,7 @@
         <v>45009</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -41041,7 +41041,7 @@
         <v>45107</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -41114,7 +41114,7 @@
         <v>44922</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -41187,7 +41187,7 @@
         <v>44743</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41260,7 +41260,7 @@
         <v>45092</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41333,7 +41333,7 @@
         <v>45229</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41406,7 +41406,7 @@
         <v>45515</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41479,7 +41479,7 @@
         <v>45079</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41552,7 +41552,7 @@
         <v>45645</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41625,7 +41625,7 @@
         <v>45614</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41698,7 +41698,7 @@
         <v>45113</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41771,7 +41771,7 @@
         <v>45596</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41844,7 +41844,7 @@
         <v>45102</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41917,7 +41917,7 @@
         <v>45102</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41990,7 +41990,7 @@
         <v>44729</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -42063,7 +42063,7 @@
         <v>44781</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -42136,7 +42136,7 @@
         <v>45148</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -42209,7 +42209,7 @@
         <v>44984</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42282,7 +42282,7 @@
         <v>44761</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42355,7 +42355,7 @@
         <v>45113</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42428,7 +42428,7 @@
         <v>45742</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42501,7 +42501,7 @@
         <v>44683</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42574,7 +42574,7 @@
         <v>45445</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42647,7 +42647,7 @@
         <v>45021</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42720,7 +42720,7 @@
         <v>45067</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42793,7 +42793,7 @@
         <v>45028</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42866,7 +42866,7 @@
         <v>45772</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42939,7 +42939,7 @@
         <v>45200</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -43012,7 +43012,7 @@
         <v>45740</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -43085,7 +43085,7 @@
         <v>44518</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -43158,7 +43158,7 @@
         <v>45222</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43231,7 +43231,7 @@
         <v>45211</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43304,7 +43304,7 @@
         <v>44879</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43377,7 +43377,7 @@
         <v>45049</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43450,7 +43450,7 @@
         <v>44690</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43523,7 +43523,7 @@
         <v>44524</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43596,7 +43596,7 @@
         <v>45415</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43669,7 +43669,7 @@
         <v>45068</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43747,7 +43747,7 @@
         <v>45755</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43820,7 +43820,7 @@
         <v>45111</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43893,7 +43893,7 @@
         <v>45772</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43966,7 +43966,7 @@
         <v>45049</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -44039,7 +44039,7 @@
         <v>45084</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -44112,7 +44112,7 @@
         <v>45099</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -44185,7 +44185,7 @@
         <v>44593</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44258,7 +44258,7 @@
         <v>44816</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44331,7 +44331,7 @@
         <v>44608</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44404,7 +44404,7 @@
         <v>45349</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44477,7 +44477,7 @@
         <v>45740</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44550,7 +44550,7 @@
         <v>44759</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44623,7 +44623,7 @@
         <v>45317</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44696,7 +44696,7 @@
         <v>45211</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44769,7 +44769,7 @@
         <v>45211</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44842,7 +44842,7 @@
         <v>45126</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44915,7 +44915,7 @@
         <v>44959</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44988,7 +44988,7 @@
         <v>44977</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -45061,7 +45061,7 @@
         <v>45327</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -45134,7 +45134,7 @@
         <v>45126</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -45207,7 +45207,7 @@
         <v>44728</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45280,7 +45280,7 @@
         <v>45093</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45353,7 +45353,7 @@
         <v>44852</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45426,7 +45426,7 @@
         <v>45121</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45499,7 +45499,7 @@
         <v>45341</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45572,7 +45572,7 @@
         <v>44953</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45645,7 +45645,7 @@
         <v>45323</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45718,7 +45718,7 @@
         <v>44953</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45791,7 +45791,7 @@
         <v>44572</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45864,7 +45864,7 @@
         <v>45531</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45937,7 +45937,7 @@
         <v>45600</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -46010,7 +46010,7 @@
         <v>44593</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -46083,7 +46083,7 @@
         <v>45769</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -46156,7 +46156,7 @@
         <v>45126</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -46229,7 +46229,7 @@
         <v>45003</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -46302,7 +46302,7 @@
         <v>44984</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -46375,7 +46375,7 @@
         <v>45019</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46448,7 +46448,7 @@
         <v>44980</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46521,7 +46521,7 @@
         <v>44840</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -46599,7 +46599,7 @@
         <v>45475</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -46672,7 +46672,7 @@
         <v>45132</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46745,7 +46745,7 @@
         <v>44600</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46818,7 +46818,7 @@
         <v>45037</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46891,7 +46891,7 @@
         <v>44982</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46964,7 +46964,7 @@
         <v>44993</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -47037,7 +47037,7 @@
         <v>45433</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -47110,7 +47110,7 @@
         <v>45146</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -47183,7 +47183,7 @@
         <v>44494</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -47256,7 +47256,7 @@
         <v>45559</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -47334,7 +47334,7 @@
         <v>45743</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -47407,7 +47407,7 @@
         <v>45126</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -47480,7 +47480,7 @@
         <v>45126</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -47553,7 +47553,7 @@
         <v>45191</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -47626,7 +47626,7 @@
         <v>45126</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -47699,7 +47699,7 @@
         <v>45205</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47772,7 +47772,7 @@
         <v>45167</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47845,7 +47845,7 @@
         <v>45644</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47918,7 +47918,7 @@
         <v>45084</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -47991,7 +47991,7 @@
         <v>45622</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -48064,7 +48064,7 @@
         <v>45159</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -48137,7 +48137,7 @@
         <v>45573</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -48210,7 +48210,7 @@
         <v>45225</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -48283,7 +48283,7 @@
         <v>45327</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -48356,7 +48356,7 @@
         <v>44783</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -48429,7 +48429,7 @@
         <v>45091</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -48502,7 +48502,7 @@
         <v>44652</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -48575,7 +48575,7 @@
         <v>45230</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -48648,7 +48648,7 @@
         <v>45232</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -48721,7 +48721,7 @@
         <v>45182</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -48794,7 +48794,7 @@
         <v>45392</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -48867,7 +48867,7 @@
         <v>44699</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -48940,7 +48940,7 @@
         <v>45148</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -49013,7 +49013,7 @@
         <v>45531</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -49086,7 +49086,7 @@
         <v>45126</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -49159,7 +49159,7 @@
         <v>45434</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -49232,7 +49232,7 @@
         <v>44619</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -49305,7 +49305,7 @@
         <v>45408</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -49378,7 +49378,7 @@
         <v>45394</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -49451,7 +49451,7 @@
         <v>44728</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -49524,7 +49524,7 @@
         <v>45188</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -49602,7 +49602,7 @@
         <v>45188</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -49680,7 +49680,7 @@
         <v>45400</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -49753,7 +49753,7 @@
         <v>45107</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -49826,7 +49826,7 @@
         <v>44673</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -49899,7 +49899,7 @@
         <v>45164</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -49972,7 +49972,7 @@
         <v>44749</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -50045,7 +50045,7 @@
         <v>44726</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -50118,7 +50118,7 @@
         <v>44802</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -50191,7 +50191,7 @@
         <v>45258</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -50264,7 +50264,7 @@
         <v>45258</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -50337,7 +50337,7 @@
         <v>45735</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -50410,7 +50410,7 @@
         <v>45475</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -50483,7 +50483,7 @@
         <v>45716</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -50556,7 +50556,7 @@
         <v>44799</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -50629,7 +50629,7 @@
         <v>44827</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -50702,7 +50702,7 @@
         <v>45301</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -50775,7 +50775,7 @@
         <v>45309</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -50848,7 +50848,7 @@
         <v>45126</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -50921,7 +50921,7 @@
         <v>45307</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -50994,7 +50994,7 @@
         <v>45716</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -51067,7 +51067,7 @@
         <v>45190</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -51140,7 +51140,7 @@
         <v>45310</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -51213,7 +51213,7 @@
         <v>44851</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -51286,7 +51286,7 @@
         <v>45089</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -51359,7 +51359,7 @@
         <v>44893</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -51432,7 +51432,7 @@
         <v>45159</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -51505,7 +51505,7 @@
         <v>44769</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -51578,7 +51578,7 @@
         <v>45187</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -51651,7 +51651,7 @@
         <v>45401</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -51724,7 +51724,7 @@
         <v>44851</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -51797,7 +51797,7 @@
         <v>45196</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -51870,7 +51870,7 @@
         <v>45392</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -51943,7 +51943,7 @@
         <v>44897</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -52016,7 +52016,7 @@
         <v>45323</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -52089,7 +52089,7 @@
         <v>45323</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -52162,7 +52162,7 @@
         <v>45637</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -52235,7 +52235,7 @@
         <v>45466</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -52308,7 +52308,7 @@
         <v>45327</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -52381,7 +52381,7 @@
         <v>45296</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -52454,7 +52454,7 @@
         <v>44530</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -52527,7 +52527,7 @@
         <v>44586</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -52600,7 +52600,7 @@
         <v>44589</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -52673,7 +52673,7 @@
         <v>44507</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -52746,7 +52746,7 @@
         <v>44938</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -52819,7 +52819,7 @@
         <v>44476</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -52892,7 +52892,7 @@
         <v>45191</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -52965,7 +52965,7 @@
         <v>44959</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -53038,7 +53038,7 @@
         <v>45194</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -53111,7 +53111,7 @@
         <v>45377</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -53184,7 +53184,7 @@
         <v>45387</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -53257,7 +53257,7 @@
         <v>44903</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -53330,7 +53330,7 @@
         <v>44900</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -53403,7 +53403,7 @@
         <v>44852</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -53476,7 +53476,7 @@
         <v>45200</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -53549,7 +53549,7 @@
         <v>45534</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -53622,7 +53622,7 @@
         <v>45191</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -53695,7 +53695,7 @@
         <v>45386</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -53768,7 +53768,7 @@
         <v>45287</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -53841,7 +53841,7 @@
         <v>45386</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -53914,7 +53914,7 @@
         <v>45386</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -53987,7 +53987,7 @@
         <v>45386</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -54060,7 +54060,7 @@
         <v>45387</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -54133,7 +54133,7 @@
         <v>44519</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -54206,7 +54206,7 @@
         <v>45534</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -54279,7 +54279,7 @@
         <v>45377</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -54352,7 +54352,7 @@
         <v>44928</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -54425,7 +54425,7 @@
         <v>45377</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -54498,7 +54498,7 @@
         <v>44519</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -54571,7 +54571,7 @@
         <v>45200</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -54644,7 +54644,7 @@
         <v>44900</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -54717,7 +54717,7 @@
         <v>45330</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -54790,7 +54790,7 @@
         <v>44959</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -54863,7 +54863,7 @@
         <v>45348</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -54936,7 +54936,7 @@
         <v>45813</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -55009,7 +55009,7 @@
         <v>45813</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -55082,7 +55082,7 @@
         <v>45849</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -55155,7 +55155,7 @@
         <v>45898</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -55228,7 +55228,7 @@
         <v>45935</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -55301,7 +55301,7 @@
         <v>45978</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -55374,7 +55374,7 @@
         <v>46034</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -55447,7 +55447,7 @@
         <v>46049</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -55520,7 +55520,7 @@
         <v>46049</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -55593,7 +55593,7 @@
         <v>46065</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -55666,7 +55666,7 @@
         <v>46092</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -55739,7 +55739,7 @@
         <v>46062</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -55812,7 +55812,7 @@
         <v>46119</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -55885,7 +55885,7 @@
         <v>46119</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -55958,7 +55958,7 @@
         <v>46127</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -56031,7 +56031,7 @@
         <v>46167</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -56104,7 +56104,7 @@
         <v>46156</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -56177,7 +56177,7 @@
         <v>46183</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -56250,7 +56250,7 @@
         <v>46191</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -56323,7 +56323,7 @@
         <v>46276</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -56401,7 +56401,7 @@
         <v>46283</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -56474,7 +56474,7 @@
         <v>46286</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -56547,7 +56547,7 @@
         <v>46314</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -56620,7 +56620,7 @@
         <v>46314</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -56693,7 +56693,7 @@
         <v>46314</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -56766,7 +56766,7 @@
         <v>46314</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>

--- a/Översikt EMMABODA.xlsx
+++ b/Översikt EMMABODA.xlsx
@@ -601,7 +601,7 @@
         <v>45534</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>45440</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -830,7 +830,7 @@
         <v>45387</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>45202</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
         <v>45030</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>45616</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         <v>44706</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>44811</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         <v>45330</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1600,7 +1600,7 @@
         <v>45359</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>46136</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1818,7 +1818,7 @@
         <v>45369</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1932,7 +1932,7 @@
         <v>45086</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2038,7 +2038,7 @@
         <v>44937</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>46062</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2254,7 +2254,7 @@
         <v>46069</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2360,7 +2360,7 @@
         <v>46214</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2466,7 +2466,7 @@
         <v>44984</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2571,7 +2571,7 @@
         <v>45229</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2680,7 +2680,7 @@
         <v>45797</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2789,7 +2789,7 @@
         <v>44771</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2898,7 +2898,7 @@
         <v>44966</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         <v>45953</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3112,7 +3112,7 @@
         <v>45335</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3217,7 +3217,7 @@
         <v>45068</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3327,7 +3327,7 @@
         <v>46213</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3432,7 +3432,7 @@
         <v>46213</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3537,7 +3537,7 @@
         <v>46218</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3642,7 +3642,7 @@
         <v>44895</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3747,7 +3747,7 @@
         <v>46282</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3852,7 +3852,7 @@
         <v>46055</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3957,7 +3957,7 @@
         <v>46253</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4062,7 +4062,7 @@
         <v>45161</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4172,7 +4172,7 @@
         <v>45967</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         <v>46135</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4387,7 +4387,7 @@
         <v>45763</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4496,7 +4496,7 @@
         <v>45166</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4601,7 +4601,7 @@
         <v>44762</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4706,7 +4706,7 @@
         <v>45092</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4811,7 +4811,7 @@
         <v>44495</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4920,7 +4920,7 @@
         <v>45196</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         <v>45107</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5134,7 +5134,7 @@
         <v>45104</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5239,7 +5239,7 @@
         <v>44570</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5344,7 +5344,7 @@
         <v>44588</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5449,7 +5449,7 @@
         <v>45509</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5554,7 +5554,7 @@
         <v>45387</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5663,7 +5663,7 @@
         <v>45611</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5772,7 +5772,7 @@
         <v>45330</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5881,7 +5881,7 @@
         <v>44852</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5990,7 +5990,7 @@
         <v>45442</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6095,7 +6095,7 @@
         <v>45153</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6200,7 +6200,7 @@
         <v>45386</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6305,7 +6305,7 @@
         <v>45685</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6414,7 +6414,7 @@
         <v>45813</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6523,7 +6523,7 @@
         <v>46275</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6632,7 +6632,7 @@
         <v>44530</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6705,7 +6705,7 @@
         <v>44496</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6778,7 +6778,7 @@
         <v>44764</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6851,7 +6851,7 @@
         <v>44530</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6924,7 +6924,7 @@
         <v>44496</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6997,7 +6997,7 @@
         <v>44529</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7070,7 +7070,7 @@
         <v>44601</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7143,7 +7143,7 @@
         <v>44600</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7216,7 +7216,7 @@
         <v>44507</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7289,7 +7289,7 @@
         <v>44507</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7362,7 +7362,7 @@
         <v>44507</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7435,7 +7435,7 @@
         <v>44599</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7508,7 +7508,7 @@
         <v>44691</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7581,7 +7581,7 @@
         <v>44628</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7654,7 +7654,7 @@
         <v>44504</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         <v>44515</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7800,7 +7800,7 @@
         <v>44851</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7873,7 +7873,7 @@
         <v>44728</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7946,7 +7946,7 @@
         <v>44860</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8019,7 +8019,7 @@
         <v>44523</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8092,7 +8092,7 @@
         <v>44648</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8165,7 +8165,7 @@
         <v>44628</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8238,7 +8238,7 @@
         <v>44788</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8311,7 +8311,7 @@
         <v>44627</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8384,7 +8384,7 @@
         <v>44498</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8457,7 +8457,7 @@
         <v>44768</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8530,7 +8530,7 @@
         <v>44851</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8603,7 +8603,7 @@
         <v>44529</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8676,7 +8676,7 @@
         <v>44813</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8749,7 +8749,7 @@
         <v>44809</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8822,7 +8822,7 @@
         <v>44771</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8895,7 +8895,7 @@
         <v>44587</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8968,7 +8968,7 @@
         <v>44496</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9041,7 +9041,7 @@
         <v>44507</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9114,7 +9114,7 @@
         <v>44507</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9187,7 +9187,7 @@
         <v>44652</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9260,7 +9260,7 @@
         <v>44628</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9333,7 +9333,7 @@
         <v>44600</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9406,7 +9406,7 @@
         <v>44501</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9479,7 +9479,7 @@
         <v>44600</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9552,7 +9552,7 @@
         <v>44852</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9625,7 +9625,7 @@
         <v>44839</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9698,7 +9698,7 @@
         <v>44615</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9776,7 +9776,7 @@
         <v>44622</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9849,7 +9849,7 @@
         <v>44524</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9922,7 +9922,7 @@
         <v>44712</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9995,7 +9995,7 @@
         <v>44743</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10068,7 +10068,7 @@
         <v>44532</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10146,7 +10146,7 @@
         <v>44722</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10219,7 +10219,7 @@
         <v>44593</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10292,7 +10292,7 @@
         <v>44652</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10365,7 +10365,7 @@
         <v>44699</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10438,7 +10438,7 @@
         <v>44820</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10516,7 +10516,7 @@
         <v>44847</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10589,7 +10589,7 @@
         <v>44743</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10662,7 +10662,7 @@
         <v>44589</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10735,7 +10735,7 @@
         <v>44600</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10808,7 +10808,7 @@
         <v>44725</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10881,7 +10881,7 @@
         <v>44551</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10959,7 +10959,7 @@
         <v>44600</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11032,7 +11032,7 @@
         <v>44655</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11105,7 +11105,7 @@
         <v>44979</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11178,7 +11178,7 @@
         <v>45887</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11251,7 +11251,7 @@
         <v>45887</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11324,7 +11324,7 @@
         <v>45749</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11397,7 +11397,7 @@
         <v>44530</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11470,7 +11470,7 @@
         <v>44788</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11543,7 +11543,7 @@
         <v>45606</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11616,7 +11616,7 @@
         <v>45048</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11689,7 +11689,7 @@
         <v>45187</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11762,7 +11762,7 @@
         <v>45219</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11835,7 +11835,7 @@
         <v>45335</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11908,7 +11908,7 @@
         <v>45204</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11986,7 +11986,7 @@
         <v>45615</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12059,7 +12059,7 @@
         <v>45190</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12132,7 +12132,7 @@
         <v>45370</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12205,7 +12205,7 @@
         <v>45091</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12278,7 +12278,7 @@
         <v>45149</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12351,7 +12351,7 @@
         <v>45191</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12424,7 +12424,7 @@
         <v>45700</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12497,7 +12497,7 @@
         <v>45155</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12570,7 +12570,7 @@
         <v>44739</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12643,7 +12643,7 @@
         <v>45251</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12716,7 +12716,7 @@
         <v>44930</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12789,7 +12789,7 @@
         <v>45181</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12862,7 +12862,7 @@
         <v>45211</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12935,7 +12935,7 @@
         <v>45719</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13008,7 +13008,7 @@
         <v>45348</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13081,7 +13081,7 @@
         <v>45069</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13154,7 +13154,7 @@
         <v>45069</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13227,7 +13227,7 @@
         <v>45397</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13300,7 +13300,7 @@
         <v>45741</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13373,7 +13373,7 @@
         <v>44728</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13446,7 +13446,7 @@
         <v>45425</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13519,7 +13519,7 @@
         <v>45036</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13592,7 +13592,7 @@
         <v>45719</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13665,7 +13665,7 @@
         <v>44834</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13738,7 +13738,7 @@
         <v>45681</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13811,7 +13811,7 @@
         <v>45411</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13884,7 +13884,7 @@
         <v>45051</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13957,7 +13957,7 @@
         <v>45051</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14030,7 +14030,7 @@
         <v>46160</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14103,7 +14103,7 @@
         <v>45908</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14176,7 +14176,7 @@
         <v>45590</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14249,7 +14249,7 @@
         <v>44808</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14322,7 +14322,7 @@
         <v>45909</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14395,7 +14395,7 @@
         <v>46162</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14468,7 +14468,7 @@
         <v>45902</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14541,7 +14541,7 @@
         <v>46162</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14614,7 +14614,7 @@
         <v>44944</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14687,7 +14687,7 @@
         <v>45048</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14760,7 +14760,7 @@
         <v>45514</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14833,7 +14833,7 @@
         <v>45514</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14906,7 +14906,7 @@
         <v>45915</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14979,7 +14979,7 @@
         <v>45915</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15052,7 +15052,7 @@
         <v>45915</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15125,7 +15125,7 @@
         <v>45076</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15198,7 +15198,7 @@
         <v>45392</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15271,7 +15271,7 @@
         <v>45217</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15344,7 +15344,7 @@
         <v>45688</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15417,7 +15417,7 @@
         <v>45921</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15490,7 +15490,7 @@
         <v>45740</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15563,7 +15563,7 @@
         <v>45180</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15636,7 +15636,7 @@
         <v>45668</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15709,7 +15709,7 @@
         <v>45349</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15782,7 +15782,7 @@
         <v>45349</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15855,7 +15855,7 @@
         <v>45641</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15928,7 +15928,7 @@
         <v>45931</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16001,7 +16001,7 @@
         <v>45923</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16074,7 +16074,7 @@
         <v>44791</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16147,7 +16147,7 @@
         <v>45310</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16220,7 +16220,7 @@
         <v>44911</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16293,7 +16293,7 @@
         <v>45394</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16366,7 +16366,7 @@
         <v>45422</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16439,7 +16439,7 @@
         <v>45938</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16512,7 +16512,7 @@
         <v>44900</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16585,7 +16585,7 @@
         <v>45938</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16658,7 +16658,7 @@
         <v>45938</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16731,7 +16731,7 @@
         <v>45938</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16804,7 +16804,7 @@
         <v>45189</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16877,7 +16877,7 @@
         <v>45229</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16950,7 +16950,7 @@
         <v>45385</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17023,7 +17023,7 @@
         <v>45376</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17096,7 +17096,7 @@
         <v>45126</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17169,7 +17169,7 @@
         <v>45113</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17242,7 +17242,7 @@
         <v>45007</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17315,7 +17315,7 @@
         <v>45461</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17388,7 +17388,7 @@
         <v>45953</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17461,7 +17461,7 @@
         <v>45164</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17534,7 +17534,7 @@
         <v>46183</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17607,7 +17607,7 @@
         <v>45901</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17680,7 +17680,7 @@
         <v>46182</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17753,7 +17753,7 @@
         <v>46182</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17826,7 +17826,7 @@
         <v>46185</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17899,7 +17899,7 @@
         <v>46185</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17972,7 +17972,7 @@
         <v>45211</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18045,7 +18045,7 @@
         <v>46185</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18118,7 +18118,7 @@
         <v>45960</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18191,7 +18191,7 @@
         <v>45126</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18264,7 +18264,7 @@
         <v>44698</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18337,7 +18337,7 @@
         <v>45317</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18410,7 +18410,7 @@
         <v>46188</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18483,7 +18483,7 @@
         <v>45964</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18556,7 +18556,7 @@
         <v>45964</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18629,7 +18629,7 @@
         <v>45373</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18702,7 +18702,7 @@
         <v>46189</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18775,7 +18775,7 @@
         <v>44861</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18848,7 +18848,7 @@
         <v>46188</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18921,7 +18921,7 @@
         <v>46190</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18999,7 +18999,7 @@
         <v>45967</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19072,7 +19072,7 @@
         <v>45967</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19145,7 +19145,7 @@
         <v>45204</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19223,7 +19223,7 @@
         <v>45971</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19296,7 +19296,7 @@
         <v>45335</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19369,7 +19369,7 @@
         <v>45369</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19442,7 +19442,7 @@
         <v>46120</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19515,7 +19515,7 @@
         <v>46196</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19593,7 +19593,7 @@
         <v>46196</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19671,7 +19671,7 @@
         <v>46196</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19749,7 +19749,7 @@
         <v>45273</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19827,7 +19827,7 @@
         <v>46197</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19905,7 +19905,7 @@
         <v>46197</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19983,7 +19983,7 @@
         <v>45204</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20061,7 +20061,7 @@
         <v>45595</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20134,7 +20134,7 @@
         <v>46010</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20207,7 +20207,7 @@
         <v>45433</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20280,7 +20280,7 @@
         <v>46196</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20353,7 +20353,7 @@
         <v>46197</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20431,7 +20431,7 @@
         <v>46198</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20504,7 +20504,7 @@
         <v>45237</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20577,7 +20577,7 @@
         <v>44531</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20650,7 +20650,7 @@
         <v>44504</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20723,7 +20723,7 @@
         <v>45103</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20796,7 +20796,7 @@
         <v>45474</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20869,7 +20869,7 @@
         <v>45341</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20942,7 +20942,7 @@
         <v>46202</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21015,7 +21015,7 @@
         <v>45979</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21088,7 +21088,7 @@
         <v>45665</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21161,7 +21161,7 @@
         <v>45126</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21234,7 +21234,7 @@
         <v>45202</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21307,7 +21307,7 @@
         <v>45281</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21380,7 +21380,7 @@
         <v>45155</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21453,7 +21453,7 @@
         <v>46205</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21531,7 +21531,7 @@
         <v>44897</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21604,7 +21604,7 @@
         <v>45716</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21677,7 +21677,7 @@
         <v>46127</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21755,7 +21755,7 @@
         <v>44519</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21828,7 +21828,7 @@
         <v>45561</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21906,7 +21906,7 @@
         <v>46211</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21979,7 +21979,7 @@
         <v>45989</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22052,7 +22052,7 @@
         <v>45400</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22125,7 +22125,7 @@
         <v>45994</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22198,7 +22198,7 @@
         <v>44907</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22271,7 +22271,7 @@
         <v>45474</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22344,7 +22344,7 @@
         <v>46212</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22417,7 +22417,7 @@
         <v>46212</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22490,7 +22490,7 @@
         <v>46213</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22563,7 +22563,7 @@
         <v>45986</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22636,7 +22636,7 @@
         <v>44979</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22709,7 +22709,7 @@
         <v>45551</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22782,7 +22782,7 @@
         <v>45523</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22855,7 +22855,7 @@
         <v>45215</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22928,7 +22928,7 @@
         <v>44949</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23001,7 +23001,7 @@
         <v>45684</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23074,7 +23074,7 @@
         <v>45624</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23147,7 +23147,7 @@
         <v>45534</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23220,7 +23220,7 @@
         <v>45484</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23293,7 +23293,7 @@
         <v>45351</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23366,7 +23366,7 @@
         <v>46188</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23439,7 +23439,7 @@
         <v>45107</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23512,7 +23512,7 @@
         <v>45317</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23585,7 +23585,7 @@
         <v>45415</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23658,7 +23658,7 @@
         <v>45638</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23731,7 +23731,7 @@
         <v>46279</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23809,7 +23809,7 @@
         <v>45610</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23882,7 +23882,7 @@
         <v>45582</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23955,7 +23955,7 @@
         <v>45565</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24028,7 +24028,7 @@
         <v>45445</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24101,7 +24101,7 @@
         <v>46279</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24179,7 +24179,7 @@
         <v>46279</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24257,7 +24257,7 @@
         <v>46279</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24335,7 +24335,7 @@
         <v>46279</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24413,7 +24413,7 @@
         <v>46279</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24486,7 +24486,7 @@
         <v>45548</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24559,7 +24559,7 @@
         <v>45609</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24632,7 +24632,7 @@
         <v>45688</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24705,7 +24705,7 @@
         <v>46279</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24783,7 +24783,7 @@
         <v>46279</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24861,7 +24861,7 @@
         <v>46279</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24939,7 +24939,7 @@
         <v>46279</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25017,7 +25017,7 @@
         <v>46279</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25095,7 +25095,7 @@
         <v>45484</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25168,7 +25168,7 @@
         <v>46282</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25241,7 +25241,7 @@
         <v>45386</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25314,7 +25314,7 @@
         <v>45775</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25387,7 +25387,7 @@
         <v>45566</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25460,7 +25460,7 @@
         <v>45481</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25533,7 +25533,7 @@
         <v>45400</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25606,7 +25606,7 @@
         <v>46024</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25679,7 +25679,7 @@
         <v>45727</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25752,7 +25752,7 @@
         <v>45455</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25825,7 +25825,7 @@
         <v>46286</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25898,7 +25898,7 @@
         <v>45706</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25971,7 +25971,7 @@
         <v>46036</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26044,7 +26044,7 @@
         <v>45727</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26117,7 +26117,7 @@
         <v>45926</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26190,7 +26190,7 @@
         <v>46288</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26263,7 +26263,7 @@
         <v>46244</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26336,7 +26336,7 @@
         <v>46288</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26409,7 +26409,7 @@
         <v>46044</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26482,7 +26482,7 @@
         <v>45161</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26560,7 +26560,7 @@
         <v>45800</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26633,7 +26633,7 @@
         <v>45537</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26706,7 +26706,7 @@
         <v>44977</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26779,7 +26779,7 @@
         <v>45665</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26852,7 +26852,7 @@
         <v>46049</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26925,7 +26925,7 @@
         <v>45804</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26998,7 +26998,7 @@
         <v>44958</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27071,7 +27071,7 @@
         <v>46290</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27144,7 +27144,7 @@
         <v>46055</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27217,7 +27217,7 @@
         <v>45273</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27295,7 +27295,7 @@
         <v>46290</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27368,7 +27368,7 @@
         <v>46290</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27441,7 +27441,7 @@
         <v>46058</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27514,7 +27514,7 @@
         <v>46062</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27587,7 +27587,7 @@
         <v>45813</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27660,7 +27660,7 @@
         <v>46160</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27733,7 +27733,7 @@
         <v>46069</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27811,7 +27811,7 @@
         <v>46071</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27889,7 +27889,7 @@
         <v>46071</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27967,7 +27967,7 @@
         <v>46072</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28040,7 +28040,7 @@
         <v>46072</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28113,7 +28113,7 @@
         <v>46253</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28186,7 +28186,7 @@
         <v>46071</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28264,7 +28264,7 @@
         <v>46251</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28337,7 +28337,7 @@
         <v>45825</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28410,7 +28410,7 @@
         <v>45826</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28483,7 +28483,7 @@
         <v>45826</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28556,7 +28556,7 @@
         <v>45826</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28629,7 +28629,7 @@
         <v>45826</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28702,7 +28702,7 @@
         <v>46078</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28775,7 +28775,7 @@
         <v>45826</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28848,7 +28848,7 @@
         <v>46253</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28921,7 +28921,7 @@
         <v>45826</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28994,7 +28994,7 @@
         <v>46079</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29067,7 +29067,7 @@
         <v>46079</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29140,7 +29140,7 @@
         <v>45477</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29213,7 +29213,7 @@
         <v>45832</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29286,7 +29286,7 @@
         <v>46085</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29359,7 +29359,7 @@
         <v>46085</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29432,7 +29432,7 @@
         <v>46085</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29505,7 +29505,7 @@
         <v>45514</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29578,7 +29578,7 @@
         <v>46255</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29656,7 +29656,7 @@
         <v>46255</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29734,7 +29734,7 @@
         <v>46090</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29807,7 +29807,7 @@
         <v>46255</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29885,7 +29885,7 @@
         <v>46255</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29958,7 +29958,7 @@
         <v>45606</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30031,7 +30031,7 @@
         <v>44951</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30104,7 +30104,7 @@
         <v>45805</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30177,7 +30177,7 @@
         <v>45621</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30250,7 +30250,7 @@
         <v>45161</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30328,7 +30328,7 @@
         <v>45845</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30401,7 +30401,7 @@
         <v>46255</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30479,7 +30479,7 @@
         <v>46255</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30557,7 +30557,7 @@
         <v>46255</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30635,7 +30635,7 @@
         <v>45727</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30708,7 +30708,7 @@
         <v>46230</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30781,7 +30781,7 @@
         <v>44519</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30854,7 +30854,7 @@
         <v>46255</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30932,7 +30932,7 @@
         <v>45772</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31005,7 +31005,7 @@
         <v>45775</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31078,7 +31078,7 @@
         <v>45849</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31151,7 +31151,7 @@
         <v>45716</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31224,7 +31224,7 @@
         <v>44530</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31297,7 +31297,7 @@
         <v>45851</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31370,7 +31370,7 @@
         <v>45851</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31443,7 +31443,7 @@
         <v>46107</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31516,7 +31516,7 @@
         <v>46259</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31589,7 +31589,7 @@
         <v>46302</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31662,7 +31662,7 @@
         <v>45857</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31735,7 +31735,7 @@
         <v>45750</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31808,7 +31808,7 @@
         <v>45863</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31881,7 +31881,7 @@
         <v>45790</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31954,7 +31954,7 @@
         <v>45189</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32027,7 +32027,7 @@
         <v>45189</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32100,7 +32100,7 @@
         <v>46120</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32173,7 +32173,7 @@
         <v>46120</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32246,7 +32246,7 @@
         <v>45716</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32319,7 +32319,7 @@
         <v>46188</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32392,7 +32392,7 @@
         <v>44550</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32465,7 +32465,7 @@
         <v>45099</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32538,7 +32538,7 @@
         <v>45070</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32611,7 +32611,7 @@
         <v>46127</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32684,7 +32684,7 @@
         <v>46127</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32757,7 +32757,7 @@
         <v>46127</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32830,7 +32830,7 @@
         <v>46306</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32903,7 +32903,7 @@
         <v>45881</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32976,7 +32976,7 @@
         <v>44896</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33049,7 +33049,7 @@
         <v>44900</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33122,7 +33122,7 @@
         <v>45537</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33195,7 +33195,7 @@
         <v>45562</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33268,7 +33268,7 @@
         <v>45615</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33341,7 +33341,7 @@
         <v>46308</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33414,7 +33414,7 @@
         <v>46134</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33487,7 +33487,7 @@
         <v>46133</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33560,7 +33560,7 @@
         <v>45475</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33633,7 +33633,7 @@
         <v>45632</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33706,7 +33706,7 @@
         <v>45401</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33779,7 +33779,7 @@
         <v>45551</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33857,7 +33857,7 @@
         <v>44893</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33930,7 +33930,7 @@
         <v>45819</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34003,7 +34003,7 @@
         <v>45818</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34076,7 +34076,7 @@
         <v>45587</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34149,7 +34149,7 @@
         <v>44683</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34222,7 +34222,7 @@
         <v>45972</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34295,7 +34295,7 @@
         <v>45966</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34368,7 +34368,7 @@
         <v>45901</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34441,7 +34441,7 @@
         <v>45392</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34514,7 +34514,7 @@
         <v>46006</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34587,7 +34587,7 @@
         <v>45818</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34660,7 +34660,7 @@
         <v>44993</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34733,7 +34733,7 @@
         <v>45349</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34806,7 +34806,7 @@
         <v>44995</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34879,7 +34879,7 @@
         <v>45155</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34952,7 +34952,7 @@
         <v>45905</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35025,7 +35025,7 @@
         <v>44897</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -35098,7 +35098,7 @@
         <v>46245</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -35171,7 +35171,7 @@
         <v>46043</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35244,7 +35244,7 @@
         <v>44949</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35317,7 +35317,7 @@
         <v>45524</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35390,7 +35390,7 @@
         <v>45349</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35463,7 +35463,7 @@
         <v>46271</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35536,7 +35536,7 @@
         <v>45007</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35609,7 +35609,7 @@
         <v>46268</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35682,7 +35682,7 @@
         <v>45400</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35755,7 +35755,7 @@
         <v>44580</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35828,7 +35828,7 @@
         <v>45966</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35901,7 +35901,7 @@
         <v>45022</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35974,7 +35974,7 @@
         <v>45022</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36047,7 +36047,7 @@
         <v>44839</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -36120,7 +36120,7 @@
         <v>44955</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36193,7 +36193,7 @@
         <v>46134</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36266,7 +36266,7 @@
         <v>45976</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36339,7 +36339,7 @@
         <v>46139</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36412,7 +36412,7 @@
         <v>46314</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36485,7 +36485,7 @@
         <v>46314</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36558,7 +36558,7 @@
         <v>45098</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36631,7 +36631,7 @@
         <v>46273</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36704,7 +36704,7 @@
         <v>45211</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36777,7 +36777,7 @@
         <v>45915</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36855,7 +36855,7 @@
         <v>46315</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36933,7 +36933,7 @@
         <v>46272</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37006,7 +37006,7 @@
         <v>45040</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37079,7 +37079,7 @@
         <v>46314</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -37152,7 +37152,7 @@
         <v>46055</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37225,7 +37225,7 @@
         <v>45909</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37298,7 +37298,7 @@
         <v>45574</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37371,7 +37371,7 @@
         <v>45166</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37444,7 +37444,7 @@
         <v>45252</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37517,7 +37517,7 @@
         <v>45392</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37590,7 +37590,7 @@
         <v>44995</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37663,7 +37663,7 @@
         <v>45938</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37736,7 +37736,7 @@
         <v>44973</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37814,7 +37814,7 @@
         <v>44594</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37887,7 +37887,7 @@
         <v>46317</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37965,7 +37965,7 @@
         <v>44524</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -38038,7 +38038,7 @@
         <v>44978</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -38111,7 +38111,7 @@
         <v>45707</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -38184,7 +38184,7 @@
         <v>46142</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38257,7 +38257,7 @@
         <v>44953</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38330,7 +38330,7 @@
         <v>44690</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38403,7 +38403,7 @@
         <v>45976</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38476,7 +38476,7 @@
         <v>45021</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38549,7 +38549,7 @@
         <v>46318</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38627,7 +38627,7 @@
         <v>46275</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38700,7 +38700,7 @@
         <v>46318</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38773,7 +38773,7 @@
         <v>45048</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38846,7 +38846,7 @@
         <v>44978</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38919,7 +38919,7 @@
         <v>45769</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38992,7 +38992,7 @@
         <v>45182</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -39065,7 +39065,7 @@
         <v>44748</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -39138,7 +39138,7 @@
         <v>45062</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -39211,7 +39211,7 @@
         <v>45191</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39284,7 +39284,7 @@
         <v>45095</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39357,7 +39357,7 @@
         <v>44777</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39430,7 +39430,7 @@
         <v>45789</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39503,7 +39503,7 @@
         <v>44960</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39576,7 +39576,7 @@
         <v>45362</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39649,7 +39649,7 @@
         <v>45009</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39722,7 +39722,7 @@
         <v>45009</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39795,7 +39795,7 @@
         <v>45422</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39868,7 +39868,7 @@
         <v>46069</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39946,7 +39946,7 @@
         <v>45559</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -40019,7 +40019,7 @@
         <v>45707</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -40092,7 +40092,7 @@
         <v>45084</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -40165,7 +40165,7 @@
         <v>46155</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40238,7 +40238,7 @@
         <v>45355</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40311,7 +40311,7 @@
         <v>44700</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40384,7 +40384,7 @@
         <v>45230</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40457,7 +40457,7 @@
         <v>46160</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40530,7 +40530,7 @@
         <v>44965</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40603,7 +40603,7 @@
         <v>45629</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40676,7 +40676,7 @@
         <v>44852</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40749,7 +40749,7 @@
         <v>45258</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40822,7 +40822,7 @@
         <v>45574</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40895,7 +40895,7 @@
         <v>45009</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40968,7 +40968,7 @@
         <v>45009</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -41041,7 +41041,7 @@
         <v>45107</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -41114,7 +41114,7 @@
         <v>44922</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -41187,7 +41187,7 @@
         <v>44743</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41260,7 +41260,7 @@
         <v>45092</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41333,7 +41333,7 @@
         <v>45229</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41406,7 +41406,7 @@
         <v>45515</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41479,7 +41479,7 @@
         <v>45079</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41552,7 +41552,7 @@
         <v>45645</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41625,7 +41625,7 @@
         <v>45614</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41698,7 +41698,7 @@
         <v>45113</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41771,7 +41771,7 @@
         <v>45596</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41844,7 +41844,7 @@
         <v>45102</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41917,7 +41917,7 @@
         <v>45102</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41990,7 +41990,7 @@
         <v>44729</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -42063,7 +42063,7 @@
         <v>44781</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -42136,7 +42136,7 @@
         <v>45148</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -42209,7 +42209,7 @@
         <v>44984</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42282,7 +42282,7 @@
         <v>44761</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42355,7 +42355,7 @@
         <v>45113</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42428,7 +42428,7 @@
         <v>45742</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42501,7 +42501,7 @@
         <v>44683</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42574,7 +42574,7 @@
         <v>45445</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42647,7 +42647,7 @@
         <v>45021</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42720,7 +42720,7 @@
         <v>45067</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42793,7 +42793,7 @@
         <v>45028</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42866,7 +42866,7 @@
         <v>45772</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42939,7 +42939,7 @@
         <v>45200</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -43012,7 +43012,7 @@
         <v>45740</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -43085,7 +43085,7 @@
         <v>44518</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -43158,7 +43158,7 @@
         <v>45222</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43231,7 +43231,7 @@
         <v>45211</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43304,7 +43304,7 @@
         <v>44879</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43377,7 +43377,7 @@
         <v>45049</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43450,7 +43450,7 @@
         <v>44690</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43523,7 +43523,7 @@
         <v>44524</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43596,7 +43596,7 @@
         <v>45415</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43669,7 +43669,7 @@
         <v>45068</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43747,7 +43747,7 @@
         <v>45755</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43820,7 +43820,7 @@
         <v>45111</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43893,7 +43893,7 @@
         <v>45772</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43966,7 +43966,7 @@
         <v>45049</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -44039,7 +44039,7 @@
         <v>45084</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -44112,7 +44112,7 @@
         <v>45099</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -44185,7 +44185,7 @@
         <v>44593</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44258,7 +44258,7 @@
         <v>44816</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44331,7 +44331,7 @@
         <v>44608</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44404,7 +44404,7 @@
         <v>45349</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44477,7 +44477,7 @@
         <v>45740</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44550,7 +44550,7 @@
         <v>44759</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44623,7 +44623,7 @@
         <v>45317</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44696,7 +44696,7 @@
         <v>45211</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44769,7 +44769,7 @@
         <v>45211</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44842,7 +44842,7 @@
         <v>45126</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44915,7 +44915,7 @@
         <v>44959</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44988,7 +44988,7 @@
         <v>44977</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -45061,7 +45061,7 @@
         <v>45327</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -45134,7 +45134,7 @@
         <v>45126</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -45207,7 +45207,7 @@
         <v>44728</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45280,7 +45280,7 @@
         <v>45093</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45353,7 +45353,7 @@
         <v>44852</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45426,7 +45426,7 @@
         <v>45121</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45499,7 +45499,7 @@
         <v>45341</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45572,7 +45572,7 @@
         <v>44953</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45645,7 +45645,7 @@
         <v>45323</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45718,7 +45718,7 @@
         <v>44953</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45791,7 +45791,7 @@
         <v>44572</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45864,7 +45864,7 @@
         <v>45531</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45937,7 +45937,7 @@
         <v>45600</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -46010,7 +46010,7 @@
         <v>44593</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -46083,7 +46083,7 @@
         <v>45769</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -46156,7 +46156,7 @@
         <v>45126</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -46229,7 +46229,7 @@
         <v>45003</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -46302,7 +46302,7 @@
         <v>44984</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -46375,7 +46375,7 @@
         <v>45019</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46448,7 +46448,7 @@
         <v>44980</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46521,7 +46521,7 @@
         <v>44840</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -46599,7 +46599,7 @@
         <v>45475</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -46672,7 +46672,7 @@
         <v>45132</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46745,7 +46745,7 @@
         <v>44600</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46818,7 +46818,7 @@
         <v>45037</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46891,7 +46891,7 @@
         <v>44982</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46964,7 +46964,7 @@
         <v>44993</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -47037,7 +47037,7 @@
         <v>45433</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -47110,7 +47110,7 @@
         <v>45146</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -47183,7 +47183,7 @@
         <v>44494</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -47256,7 +47256,7 @@
         <v>45559</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -47334,7 +47334,7 @@
         <v>45743</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -47407,7 +47407,7 @@
         <v>45126</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -47480,7 +47480,7 @@
         <v>45126</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -47553,7 +47553,7 @@
         <v>45191</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -47626,7 +47626,7 @@
         <v>45126</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -47699,7 +47699,7 @@
         <v>45205</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47772,7 +47772,7 @@
         <v>45167</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47845,7 +47845,7 @@
         <v>45644</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47918,7 +47918,7 @@
         <v>45084</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -47991,7 +47991,7 @@
         <v>45622</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -48064,7 +48064,7 @@
         <v>45159</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -48137,7 +48137,7 @@
         <v>45573</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -48210,7 +48210,7 @@
         <v>45225</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -48283,7 +48283,7 @@
         <v>45327</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -48356,7 +48356,7 @@
         <v>44783</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -48429,7 +48429,7 @@
         <v>45091</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -48502,7 +48502,7 @@
         <v>44652</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -48575,7 +48575,7 @@
         <v>45230</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -48648,7 +48648,7 @@
         <v>45232</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -48721,7 +48721,7 @@
         <v>45182</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -48794,7 +48794,7 @@
         <v>45392</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -48867,7 +48867,7 @@
         <v>44699</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -48940,7 +48940,7 @@
         <v>45148</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -49013,7 +49013,7 @@
         <v>45531</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -49086,7 +49086,7 @@
         <v>45126</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -49159,7 +49159,7 @@
         <v>45434</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -49232,7 +49232,7 @@
         <v>44619</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -49305,7 +49305,7 @@
         <v>45408</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -49378,7 +49378,7 @@
         <v>45394</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -49451,7 +49451,7 @@
         <v>44728</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -49524,7 +49524,7 @@
         <v>45188</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -49602,7 +49602,7 @@
         <v>45188</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -49680,7 +49680,7 @@
         <v>45400</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -49753,7 +49753,7 @@
         <v>45107</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -49826,7 +49826,7 @@
         <v>44673</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -49899,7 +49899,7 @@
         <v>45164</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -49972,7 +49972,7 @@
         <v>44749</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -50045,7 +50045,7 @@
         <v>44726</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -50118,7 +50118,7 @@
         <v>44802</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -50191,7 +50191,7 @@
         <v>45258</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -50264,7 +50264,7 @@
         <v>45258</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -50337,7 +50337,7 @@
         <v>45735</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -50410,7 +50410,7 @@
         <v>45475</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -50483,7 +50483,7 @@
         <v>45716</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -50556,7 +50556,7 @@
         <v>44799</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -50629,7 +50629,7 @@
         <v>44827</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -50702,7 +50702,7 @@
         <v>45301</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -50775,7 +50775,7 @@
         <v>45309</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -50848,7 +50848,7 @@
         <v>45126</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -50921,7 +50921,7 @@
         <v>45307</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -50994,7 +50994,7 @@
         <v>45716</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -51067,7 +51067,7 @@
         <v>45190</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -51140,7 +51140,7 @@
         <v>45310</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -51213,7 +51213,7 @@
         <v>44851</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -51286,7 +51286,7 @@
         <v>45089</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -51359,7 +51359,7 @@
         <v>44893</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -51432,7 +51432,7 @@
         <v>45159</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -51505,7 +51505,7 @@
         <v>44769</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -51578,7 +51578,7 @@
         <v>45187</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -51651,7 +51651,7 @@
         <v>45401</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -51724,7 +51724,7 @@
         <v>44851</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -51797,7 +51797,7 @@
         <v>45196</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -51870,7 +51870,7 @@
         <v>45392</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -51943,7 +51943,7 @@
         <v>44897</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -52016,7 +52016,7 @@
         <v>45323</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -52089,7 +52089,7 @@
         <v>45323</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -52162,7 +52162,7 @@
         <v>45637</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -52235,7 +52235,7 @@
         <v>45466</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -52308,7 +52308,7 @@
         <v>45327</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -52381,7 +52381,7 @@
         <v>45296</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -52454,7 +52454,7 @@
         <v>44530</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -52527,7 +52527,7 @@
         <v>44586</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -52600,7 +52600,7 @@
         <v>44589</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -52673,7 +52673,7 @@
         <v>44507</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -52746,7 +52746,7 @@
         <v>44938</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -52819,7 +52819,7 @@
         <v>44476</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -52892,7 +52892,7 @@
         <v>45191</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -52965,7 +52965,7 @@
         <v>44959</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -53038,7 +53038,7 @@
         <v>45194</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -53111,7 +53111,7 @@
         <v>45377</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -53184,7 +53184,7 @@
         <v>45387</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -53257,7 +53257,7 @@
         <v>44903</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -53330,7 +53330,7 @@
         <v>44900</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -53403,7 +53403,7 @@
         <v>44852</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -53476,7 +53476,7 @@
         <v>45200</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -53549,7 +53549,7 @@
         <v>45534</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -53622,7 +53622,7 @@
         <v>45191</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -53695,7 +53695,7 @@
         <v>45386</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -53768,7 +53768,7 @@
         <v>45287</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -53841,7 +53841,7 @@
         <v>45386</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -53914,7 +53914,7 @@
         <v>45386</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -53987,7 +53987,7 @@
         <v>45386</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -54060,7 +54060,7 @@
         <v>45387</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -54133,7 +54133,7 @@
         <v>44519</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -54206,7 +54206,7 @@
         <v>45534</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -54279,7 +54279,7 @@
         <v>45377</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -54352,7 +54352,7 @@
         <v>44928</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -54425,7 +54425,7 @@
         <v>45377</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -54498,7 +54498,7 @@
         <v>44519</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -54571,7 +54571,7 @@
         <v>45200</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -54644,7 +54644,7 @@
         <v>44900</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -54717,7 +54717,7 @@
         <v>45330</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -54790,7 +54790,7 @@
         <v>44959</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -54863,7 +54863,7 @@
         <v>45348</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -54936,7 +54936,7 @@
         <v>45813</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -55009,7 +55009,7 @@
         <v>45813</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -55082,7 +55082,7 @@
         <v>45849</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -55155,7 +55155,7 @@
         <v>45898</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -55228,7 +55228,7 @@
         <v>45935</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -55301,7 +55301,7 @@
         <v>45978</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -55374,7 +55374,7 @@
         <v>46034</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -55447,7 +55447,7 @@
         <v>46049</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -55520,7 +55520,7 @@
         <v>46049</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -55593,7 +55593,7 @@
         <v>46065</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -55666,7 +55666,7 @@
         <v>46092</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -55739,7 +55739,7 @@
         <v>46062</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -55812,7 +55812,7 @@
         <v>46119</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -55885,7 +55885,7 @@
         <v>46119</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -55958,7 +55958,7 @@
         <v>46127</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -56031,7 +56031,7 @@
         <v>46167</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -56104,7 +56104,7 @@
         <v>46156</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -56177,7 +56177,7 @@
         <v>46183</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -56250,7 +56250,7 @@
         <v>46191</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -56323,7 +56323,7 @@
         <v>46276</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -56401,7 +56401,7 @@
         <v>46283</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -56474,7 +56474,7 @@
         <v>46286</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -56547,7 +56547,7 @@
         <v>46314</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -56620,7 +56620,7 @@
         <v>46314</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -56693,7 +56693,7 @@
         <v>46314</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -56766,7 +56766,7 @@
         <v>46314</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
